--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -3,6 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+  <bookViews>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="5"/>
+  </bookViews>
   <sheets>
     <sheet sheetId="1" name="Districts" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="Units" state="visible" r:id="rId5"/>
@@ -302,7 +305,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -313,6 +316,12 @@
     <font>
       <b/>
     </font>
+    <font>
+      <color theme="1"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -322,7 +331,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -330,14 +339,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -355,7 +371,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -401,13 +417,13 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Thai" typeface="Angsana New"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
@@ -430,19 +446,18 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Thai" typeface="Cordia New"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
@@ -465,7 +480,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -500,16 +514,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -631,9 +649,226 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
   <a:objectDefaults>
     <a:spDef>
-      <a:spPr/>
+      <a:spPr bwMode="auto"/>
       <a:bodyPr/>
       <a:lstStyle/>
       <a:style>
@@ -652,7 +887,7 @@
       </a:style>
     </a:spDef>
     <a:lnDef>
-      <a:spPr/>
+      <a:spPr bwMode="auto"/>
       <a:bodyPr/>
       <a:lstStyle/>
       <a:style>
@@ -671,14 +906,13 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:X6"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="3" width="10" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
@@ -1147,14 +1381,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" usePrinterDefaults="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="21" customWidth="1"/>
@@ -1244,14 +1478,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" usePrinterDefaults="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="11" customWidth="1"/>
@@ -1321,14 +1555,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" usePrinterDefaults="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -1380,14 +1614,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" usePrinterDefaults="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="3" width="10" customWidth="1"/>
   </cols>
@@ -1482,14 +1716,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" usePrinterDefaults="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
   </cols>
@@ -1504,38 +1738,101 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
         <v>3</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4">
         <v>5</v>
       </c>
     </row>
+    <row r="5" ht="14.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <f>B4*2</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" ht="14.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <f>B5*2</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <f>B6*2</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" ht="14.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <f>B7*2</f>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" ht="14.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <f>B8*2</f>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <f>B9*2</f>
+        <v>320</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <f>B10*2</f>
+        <v>640</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" usePrinterDefaults="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
   </cols>
@@ -1702,6 +1999,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" usePrinterDefaults="1" copies="1"/>
 </worksheet>
 </file>
--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -1,26 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <workbookPr/>
   <bookViews>
     <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="5"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Districts" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Units" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Spells" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="Harvest" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="Currencies" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="FogRings" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="Settings" state="visible" r:id="rId10"/>
+    <sheet name="Districts" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Units" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Spells" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Harvest" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Currencies" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="FogRings" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Settings" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="93">
   <si>
     <t>id</t>
   </si>
@@ -304,23 +306,16 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2">
     <font>
+      <sz val="11.000000"/>
       <color theme="1"/>
-      <family val="2"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -331,14 +326,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="1">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -348,12 +336,12 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -910,32 +898,31 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X6"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="21" customWidth="1"/>
-    <col min="6" max="6" width="23" customWidth="1"/>
-    <col min="7" max="7" width="30" customWidth="1"/>
-    <col min="8" max="8" width="28" customWidth="1"/>
-    <col min="9" max="9" width="35" customWidth="1"/>
-    <col min="10" max="10" width="19" customWidth="1"/>
-    <col min="11" max="12" width="17" customWidth="1"/>
-    <col min="13" max="13" width="23" customWidth="1"/>
-    <col min="14" max="14" width="31" customWidth="1"/>
-    <col min="15" max="15" width="28" customWidth="1"/>
-    <col min="16" max="16" width="24" customWidth="1"/>
-    <col min="17" max="18" width="32" customWidth="1"/>
-    <col min="19" max="19" width="21" customWidth="1"/>
-    <col min="20" max="21" width="19" customWidth="1"/>
-    <col min="22" max="22" width="27" customWidth="1"/>
-    <col min="23" max="23" width="26" customWidth="1"/>
-    <col min="24" max="24" width="31" customWidth="1"/>
+    <col customWidth="1" min="1" max="3" width="10"/>
+    <col customWidth="1" min="4" max="4" width="11"/>
+    <col customWidth="1" min="5" max="5" width="21"/>
+    <col customWidth="1" min="6" max="6" width="23"/>
+    <col customWidth="1" min="7" max="7" width="30"/>
+    <col customWidth="1" min="8" max="8" width="28"/>
+    <col customWidth="1" min="9" max="9" width="35"/>
+    <col customWidth="1" min="10" max="10" width="19"/>
+    <col customWidth="1" min="11" max="12" width="17"/>
+    <col customWidth="1" min="13" max="13" width="23"/>
+    <col customWidth="1" min="14" max="14" width="31"/>
+    <col customWidth="1" min="15" max="15" width="28"/>
+    <col customWidth="1" min="16" max="16" width="24"/>
+    <col customWidth="1" min="17" max="18" width="32"/>
+    <col customWidth="1" min="19" max="19" width="21"/>
+    <col customWidth="1" min="20" max="21" width="19"/>
+    <col customWidth="1" min="22" max="22" width="27"/>
+    <col customWidth="1" min="23" max="23" width="26"/>
+    <col customWidth="1" min="24" max="24" width="31"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1009,7 +996,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -1053,7 +1040,7 @@
         <v>1.2</v>
       </c>
       <c r="O2">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -1062,7 +1049,7 @@
         <v>1.2</v>
       </c>
       <c r="R2">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="S2">
         <v>200</v>
@@ -1083,7 +1070,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>26</v>
       </c>
@@ -1136,7 +1123,7 @@
         <v>1.2</v>
       </c>
       <c r="R3">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="S3" t="s">
         <v>25</v>
@@ -1157,7 +1144,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -1210,7 +1197,7 @@
         <v>1.2</v>
       </c>
       <c r="R4">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="S4">
         <v>300</v>
@@ -1231,7 +1218,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>33</v>
       </c>
@@ -1284,7 +1271,7 @@
         <v>1.2</v>
       </c>
       <c r="R5">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="S5" t="s">
         <v>25</v>
@@ -1305,7 +1292,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>35</v>
       </c>
@@ -1358,7 +1345,7 @@
         <v>1.2</v>
       </c>
       <c r="R6">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="S6">
         <v>300</v>
@@ -1380,23 +1367,24 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" usePrinterDefaults="1" copies="1"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="1" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="21" customWidth="1"/>
-    <col min="4" max="5" width="19" customWidth="1"/>
-    <col min="6" max="6" width="24" customWidth="1"/>
+    <col customWidth="1" min="1" max="2" width="10"/>
+    <col customWidth="1" min="3" max="3" width="21"/>
+    <col customWidth="1" min="4" max="5" width="19"/>
+    <col customWidth="1" min="6" max="6" width="24"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1416,7 +1404,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>43</v>
       </c>
@@ -1436,7 +1424,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>44</v>
       </c>
@@ -1456,7 +1444,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>45</v>
       </c>
@@ -1477,23 +1465,24 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" usePrinterDefaults="1" copies="1"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="1" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
+    <col customWidth="1" min="1" max="2" width="10"/>
+    <col customWidth="1" min="3" max="3" width="11"/>
+    <col customWidth="1" min="4" max="5" width="18"/>
+    <col customWidth="1" min="6" max="6" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>46</v>
       </c>
@@ -1513,7 +1502,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>52</v>
       </c>
@@ -1533,7 +1522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>53</v>
       </c>
@@ -1554,23 +1543,24 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" usePrinterDefaults="1" copies="1"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="1" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="10"/>
+    <col customWidth="1" min="2" max="2" width="15"/>
+    <col customWidth="1" min="3" max="3" width="17"/>
+    <col customWidth="1" min="4" max="4" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>54</v>
       </c>
@@ -1584,7 +1574,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>58</v>
       </c>
@@ -1598,7 +1588,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>59</v>
       </c>
@@ -1613,20 +1603,21 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" usePrinterDefaults="1" copies="1"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="1" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="3" width="10" customWidth="1"/>
+    <col customWidth="1" min="1" max="3" width="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1637,7 +1628,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>62</v>
       </c>
@@ -1648,7 +1639,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>63</v>
       </c>
@@ -1659,7 +1650,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>64</v>
       </c>
@@ -1670,7 +1661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>65</v>
       </c>
@@ -1681,7 +1672,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>66</v>
       </c>
@@ -1692,7 +1683,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>67</v>
       </c>
@@ -1703,7 +1694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>68</v>
       </c>
@@ -1715,20 +1706,21 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" usePrinterDefaults="1" copies="1"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="1" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="2" width="10" customWidth="1"/>
+    <col customWidth="1" min="1" max="2" width="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>69</v>
       </c>
@@ -1736,7 +1728,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1744,7 +1736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1752,7 +1744,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1760,7 +1752,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" ht="14.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" ht="14.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1769,7 +1761,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" ht="14.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" ht="14.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1778,7 +1770,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" ht="14.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" ht="14.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1787,7 +1779,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8" ht="14.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" ht="14.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1796,7 +1788,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9" ht="14.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" ht="14.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1805,7 +1797,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="10" ht="14.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" ht="14.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1814,7 +1806,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="11" ht="14.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" ht="14.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1824,20 +1816,22 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" usePrinterDefaults="1" copies="1"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="1" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="2" width="10" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="46.28125"/>
+    <col customWidth="1" min="2" max="2" width="18.7109375"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>71</v>
       </c>
@@ -1845,7 +1839,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>73</v>
       </c>
@@ -1853,7 +1847,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>74</v>
       </c>
@@ -1861,7 +1855,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>75</v>
       </c>
@@ -1869,7 +1863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>76</v>
       </c>
@@ -1877,7 +1871,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>77</v>
       </c>
@@ -1885,7 +1879,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>78</v>
       </c>
@@ -1893,7 +1887,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>79</v>
       </c>
@@ -1901,7 +1895,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>80</v>
       </c>
@@ -1909,7 +1903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
         <v>81</v>
       </c>
@@ -1917,7 +1911,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" t="s">
         <v>82</v>
       </c>
@@ -1925,7 +1919,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" t="s">
         <v>83</v>
       </c>
@@ -1933,7 +1927,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" t="s">
         <v>84</v>
       </c>
@@ -1941,7 +1935,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14">
       <c r="A14" t="s">
         <v>85</v>
       </c>
@@ -1949,7 +1943,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="A15" t="s">
         <v>86</v>
       </c>
@@ -1957,7 +1951,7 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="A16" t="s">
         <v>87</v>
       </c>
@@ -1965,7 +1959,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="A17" t="s">
         <v>88</v>
       </c>
@@ -1973,7 +1967,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18">
       <c r="A18" t="s">
         <v>90</v>
       </c>
@@ -1981,7 +1975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19">
       <c r="A19" t="s">
         <v>91</v>
       </c>
@@ -1989,7 +1983,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20">
       <c r="A20" t="s">
         <v>92</v>
       </c>
@@ -1998,7 +1992,9 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" usePrinterDefaults="1" copies="1"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="1" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -1,28 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr/>
-  <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="5"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Districts" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Units" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Spells" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Harvest" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Currencies" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="FogRings" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Settings" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet sheetId="1" name="Districts" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Units" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Spells" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Harvest" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="Currencies" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="FogRings" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="Research" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="Settings" state="visible" r:id="rId11"/>
   </sheets>
-  <calcPr/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="97">
   <si>
     <t>id</t>
   </si>
@@ -235,6 +231,18 @@
   </si>
   <si>
     <t>cost</t>
+  </si>
+  <si>
+    <t>cost_silver</t>
+  </si>
+  <si>
+    <t>cost_wood</t>
+  </si>
+  <si>
+    <t>cost_food</t>
+  </si>
+  <si>
+    <t>Agriculture</t>
   </si>
   <si>
     <t>key</t>
@@ -306,13 +314,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="11.000000"/>
       <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -328,20 +337,20 @@
   </fills>
   <borders count="1">
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -359,7 +368,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -405,13 +414,13 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Angsana New"/>
+        <a:font script="Thai" typeface="Tahoma"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
@@ -434,18 +443,19 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Cordia New"/>
+        <a:font script="Thai" typeface="Tahoma"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
@@ -468,6 +478,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -502,20 +513,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -637,226 +644,9 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
-</file>
-
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle"/>
-        </a:gradFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle"/>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
   <a:objectDefaults>
     <a:spDef>
-      <a:spPr bwMode="auto"/>
+      <a:spPr/>
       <a:bodyPr/>
       <a:lstStyle/>
       <a:style>
@@ -875,7 +665,7 @@
       </a:style>
     </a:spDef>
     <a:lnDef>
-      <a:spPr bwMode="auto"/>
+      <a:spPr/>
       <a:bodyPr/>
       <a:lstStyle/>
       <a:style>
@@ -894,35 +684,37 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:X6"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col customWidth="1" min="1" max="3" width="10"/>
-    <col customWidth="1" min="4" max="4" width="11"/>
-    <col customWidth="1" min="5" max="5" width="21"/>
-    <col customWidth="1" min="6" max="6" width="23"/>
-    <col customWidth="1" min="7" max="7" width="30"/>
-    <col customWidth="1" min="8" max="8" width="28"/>
-    <col customWidth="1" min="9" max="9" width="35"/>
-    <col customWidth="1" min="10" max="10" width="19"/>
-    <col customWidth="1" min="11" max="12" width="17"/>
-    <col customWidth="1" min="13" max="13" width="23"/>
-    <col customWidth="1" min="14" max="14" width="31"/>
-    <col customWidth="1" min="15" max="15" width="28"/>
-    <col customWidth="1" min="16" max="16" width="24"/>
-    <col customWidth="1" min="17" max="18" width="32"/>
-    <col customWidth="1" min="19" max="19" width="21"/>
-    <col customWidth="1" min="20" max="21" width="19"/>
-    <col customWidth="1" min="22" max="22" width="27"/>
-    <col customWidth="1" min="23" max="23" width="26"/>
-    <col customWidth="1" min="24" max="24" width="31"/>
+    <col min="1" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="21" customWidth="1"/>
+    <col min="6" max="6" width="23" customWidth="1"/>
+    <col min="7" max="7" width="30" customWidth="1"/>
+    <col min="8" max="8" width="28" customWidth="1"/>
+    <col min="9" max="9" width="35" customWidth="1"/>
+    <col min="10" max="10" width="19" customWidth="1"/>
+    <col min="11" max="12" width="17" customWidth="1"/>
+    <col min="13" max="13" width="23" customWidth="1"/>
+    <col min="14" max="14" width="31" customWidth="1"/>
+    <col min="15" max="15" width="28" customWidth="1"/>
+    <col min="16" max="16" width="24" customWidth="1"/>
+    <col min="17" max="18" width="32" customWidth="1"/>
+    <col min="19" max="19" width="21" customWidth="1"/>
+    <col min="20" max="21" width="19" customWidth="1"/>
+    <col min="22" max="22" width="27" customWidth="1"/>
+    <col min="23" max="23" width="26" customWidth="1"/>
+    <col min="24" max="24" width="31" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -996,7 +788,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -1040,7 +832,7 @@
         <v>1.2</v>
       </c>
       <c r="O2">
-        <v>1.1499999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -1049,7 +841,7 @@
         <v>1.2</v>
       </c>
       <c r="R2">
-        <v>1.1499999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="S2">
         <v>200</v>
@@ -1070,7 +862,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>26</v>
       </c>
@@ -1123,7 +915,7 @@
         <v>1.2</v>
       </c>
       <c r="R3">
-        <v>1.1499999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="S3" t="s">
         <v>25</v>
@@ -1144,7 +936,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -1197,7 +989,7 @@
         <v>1.2</v>
       </c>
       <c r="R4">
-        <v>1.1499999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="S4">
         <v>300</v>
@@ -1218,7 +1010,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>33</v>
       </c>
@@ -1271,7 +1063,7 @@
         <v>1.2</v>
       </c>
       <c r="R5">
-        <v>1.1499999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="S5" t="s">
         <v>25</v>
@@ -1292,7 +1084,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>35</v>
       </c>
@@ -1345,7 +1137,7 @@
         <v>1.2</v>
       </c>
       <c r="R6">
-        <v>1.1499999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="S6">
         <v>300</v>
@@ -1367,24 +1159,23 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="1" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col customWidth="1" min="1" max="2" width="10"/>
-    <col customWidth="1" min="3" max="3" width="21"/>
-    <col customWidth="1" min="4" max="5" width="19"/>
-    <col customWidth="1" min="6" max="6" width="24"/>
+    <col min="1" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="21" customWidth="1"/>
+    <col min="4" max="5" width="19" customWidth="1"/>
+    <col min="6" max="6" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1404,7 +1195,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>43</v>
       </c>
@@ -1424,7 +1215,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>44</v>
       </c>
@@ -1444,7 +1235,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>45</v>
       </c>
@@ -1465,24 +1256,23 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="1" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col customWidth="1" min="1" max="2" width="10"/>
-    <col customWidth="1" min="3" max="3" width="11"/>
-    <col customWidth="1" min="4" max="5" width="18"/>
-    <col customWidth="1" min="6" max="6" width="14"/>
+    <col min="1" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="11" customWidth="1"/>
+    <col min="4" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>46</v>
       </c>
@@ -1502,7 +1292,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>52</v>
       </c>
@@ -1522,7 +1312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>53</v>
       </c>
@@ -1543,24 +1333,23 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="1" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="10"/>
-    <col customWidth="1" min="2" max="2" width="15"/>
-    <col customWidth="1" min="3" max="3" width="17"/>
-    <col customWidth="1" min="4" max="4" width="18"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>54</v>
       </c>
@@ -1574,7 +1363,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>58</v>
       </c>
@@ -1588,7 +1377,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>59</v>
       </c>
@@ -1603,21 +1392,20 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="1" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col customWidth="1" min="1" max="3" width="10"/>
+    <col min="1" max="3" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1628,7 +1416,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>62</v>
       </c>
@@ -1639,7 +1427,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>63</v>
       </c>
@@ -1650,7 +1438,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>64</v>
       </c>
@@ -1661,7 +1449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>65</v>
       </c>
@@ -1672,7 +1460,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>66</v>
       </c>
@@ -1683,7 +1471,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>67</v>
       </c>
@@ -1694,7 +1482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>68</v>
       </c>
@@ -1706,21 +1494,20 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="1" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col customWidth="1" min="1" max="2" width="10"/>
+    <col min="1" max="2" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>69</v>
       </c>
@@ -1728,7 +1515,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1736,7 +1523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1744,7 +1531,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1752,249 +1539,289 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" ht="14.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
-        <f>B4*2</f>
         <v>10</v>
       </c>
     </row>
-    <row r="6" ht="14.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
-        <f>B5*2</f>
         <v>20</v>
       </c>
     </row>
-    <row r="7" ht="14.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7">
-        <f>B6*2</f>
         <v>40</v>
       </c>
     </row>
-    <row r="8" ht="14.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8">
-        <f>B7*2</f>
         <v>80</v>
       </c>
     </row>
-    <row r="9" ht="14.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9">
-        <f>B8*2</f>
         <v>160</v>
       </c>
     </row>
-    <row r="10" ht="14.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10">
-        <f>B9*2</f>
         <v>320</v>
       </c>
     </row>
-    <row r="11" ht="14.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11">
-        <f>B10*2</f>
         <v>640</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="1" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="46.28125"/>
-    <col customWidth="1" min="2" max="2" width="18.7109375"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>71</v>
       </c>
+      <c r="C1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2">
+        <v>100</v>
+      </c>
+      <c r="C2">
+        <v>25</v>
+      </c>
+      <c r="D2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B20"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="2" width="10" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>75</v>
+      </c>
       <c r="B1" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B3">
         <v>8</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B5">
         <v>10</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B7">
         <v>5</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B8">
         <v>8</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B10">
         <v>1.25</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B11">
         <v>2</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B12">
         <v>50</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B13">
         <v>5</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B14">
         <v>5</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B15">
         <v>1.45</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B18">
         <v>1</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B19">
         <v>4</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B20">
         <v>300</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="1" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="99">
   <si>
     <t>id</t>
   </si>
@@ -33,6 +33,12 @@
   </si>
   <si>
     <t>population_capacity</t>
+  </si>
+  <si>
+    <t>fog_reveal_radius</t>
+  </si>
+  <si>
+    <t>fog_discover_radius</t>
   </si>
   <si>
     <t>max_workers_per_level</t>
@@ -690,31 +696,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X6"/>
+  <dimension ref="A1:Z6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="10" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
     <col min="5" max="5" width="21" customWidth="1"/>
-    <col min="6" max="6" width="23" customWidth="1"/>
-    <col min="7" max="7" width="30" customWidth="1"/>
-    <col min="8" max="8" width="28" customWidth="1"/>
-    <col min="9" max="9" width="35" customWidth="1"/>
-    <col min="10" max="10" width="19" customWidth="1"/>
-    <col min="11" max="12" width="17" customWidth="1"/>
-    <col min="13" max="13" width="23" customWidth="1"/>
-    <col min="14" max="14" width="31" customWidth="1"/>
-    <col min="15" max="15" width="28" customWidth="1"/>
-    <col min="16" max="16" width="24" customWidth="1"/>
-    <col min="17" max="18" width="32" customWidth="1"/>
-    <col min="19" max="19" width="21" customWidth="1"/>
-    <col min="20" max="21" width="19" customWidth="1"/>
-    <col min="22" max="22" width="27" customWidth="1"/>
-    <col min="23" max="23" width="26" customWidth="1"/>
-    <col min="24" max="24" width="31" customWidth="1"/>
+    <col min="6" max="6" width="19" customWidth="1"/>
+    <col min="7" max="7" width="21" customWidth="1"/>
+    <col min="8" max="8" width="23" customWidth="1"/>
+    <col min="9" max="9" width="30" customWidth="1"/>
+    <col min="10" max="10" width="28" customWidth="1"/>
+    <col min="11" max="11" width="35" customWidth="1"/>
+    <col min="12" max="12" width="19" customWidth="1"/>
+    <col min="13" max="14" width="17" customWidth="1"/>
+    <col min="15" max="15" width="23" customWidth="1"/>
+    <col min="16" max="16" width="31" customWidth="1"/>
+    <col min="17" max="17" width="28" customWidth="1"/>
+    <col min="18" max="18" width="24" customWidth="1"/>
+    <col min="19" max="20" width="32" customWidth="1"/>
+    <col min="21" max="21" width="21" customWidth="1"/>
+    <col min="22" max="23" width="19" customWidth="1"/>
+    <col min="24" max="24" width="27" customWidth="1"/>
+    <col min="25" max="25" width="26" customWidth="1"/>
+    <col min="26" max="26" width="31" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -787,10 +795,16 @@
       <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -804,67 +818,73 @@
       <c r="E2">
         <v>3</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>5</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2">
+        <v>2</v>
+      </c>
+      <c r="P2">
+        <v>1.2</v>
+      </c>
+      <c r="Q2">
+        <v>1.15</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>1.2</v>
+      </c>
+      <c r="T2">
+        <v>1.15</v>
+      </c>
+      <c r="U2">
+        <v>200</v>
+      </c>
+      <c r="V2">
         <v>25</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="J2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-      <c r="N2">
-        <v>1.2</v>
-      </c>
-      <c r="O2">
-        <v>1.15</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>1.2</v>
-      </c>
-      <c r="R2">
-        <v>1.15</v>
-      </c>
-      <c r="S2">
-        <v>200</v>
-      </c>
-      <c r="T2">
-        <v>25</v>
-      </c>
-      <c r="U2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V2">
-        <v>1.5</v>
-      </c>
-      <c r="W2">
-        <v>0</v>
+      <c r="W2" t="s">
+        <v>27</v>
       </c>
       <c r="X2">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -878,67 +898,73 @@
       <c r="E3">
         <v>2</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>27</v>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3">
+        <v>29</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3">
         <v>75</v>
       </c>
-      <c r="K3">
+      <c r="M3">
         <v>20</v>
       </c>
-      <c r="L3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M3">
+      <c r="N3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O3">
         <v>0.75</v>
       </c>
-      <c r="N3">
+      <c r="P3">
         <v>1.25</v>
       </c>
-      <c r="O3">
-        <v>1</v>
-      </c>
-      <c r="P3">
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3">
         <v>20</v>
       </c>
-      <c r="Q3">
+      <c r="S3">
         <v>1.2</v>
       </c>
-      <c r="R3">
+      <c r="T3">
         <v>1.15</v>
       </c>
-      <c r="S3" t="s">
-        <v>25</v>
-      </c>
-      <c r="T3" t="s">
-        <v>25</v>
-      </c>
       <c r="U3" t="s">
-        <v>25</v>
-      </c>
-      <c r="V3">
-        <v>1.5</v>
-      </c>
-      <c r="W3">
-        <v>0</v>
+        <v>27</v>
+      </c>
+      <c r="V3" t="s">
+        <v>27</v>
+      </c>
+      <c r="W3" t="s">
+        <v>27</v>
       </c>
       <c r="X3">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -952,11 +978,11 @@
       <c r="E4">
         <v>0</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>30</v>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>31</v>
@@ -964,55 +990,61 @@
       <c r="I4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4">
         <v>50</v>
       </c>
-      <c r="K4">
+      <c r="M4">
         <v>10</v>
       </c>
-      <c r="L4" t="s">
-        <v>25</v>
-      </c>
-      <c r="M4">
+      <c r="N4" t="s">
+        <v>27</v>
+      </c>
+      <c r="O4">
         <v>2</v>
       </c>
-      <c r="N4">
+      <c r="P4">
         <v>1.5</v>
       </c>
-      <c r="O4">
-        <v>1</v>
-      </c>
-      <c r="P4">
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4">
         <v>20</v>
       </c>
-      <c r="Q4">
+      <c r="S4">
         <v>1.2</v>
       </c>
-      <c r="R4">
+      <c r="T4">
         <v>1.15</v>
       </c>
-      <c r="S4">
+      <c r="U4">
         <v>300</v>
       </c>
-      <c r="T4">
+      <c r="V4">
         <v>50</v>
       </c>
-      <c r="U4" t="s">
-        <v>25</v>
-      </c>
-      <c r="V4">
-        <v>1.5</v>
-      </c>
-      <c r="W4">
-        <v>30</v>
+      <c r="W4" t="s">
+        <v>27</v>
       </c>
       <c r="X4">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y4">
+        <v>30</v>
+      </c>
+      <c r="Z4">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -1026,67 +1058,73 @@
       <c r="E5">
         <v>0</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>34</v>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="J5" t="s">
-        <v>25</v>
-      </c>
-      <c r="K5">
+        <v>36</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M5">
         <v>20</v>
       </c>
-      <c r="L5" t="s">
-        <v>25</v>
-      </c>
-      <c r="M5">
+      <c r="N5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O5">
         <v>2</v>
       </c>
-      <c r="N5">
+      <c r="P5">
         <v>1.2</v>
       </c>
-      <c r="O5">
-        <v>1</v>
-      </c>
-      <c r="P5">
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
         <v>10</v>
       </c>
-      <c r="Q5">
+      <c r="S5">
         <v>1.2</v>
       </c>
-      <c r="R5">
+      <c r="T5">
         <v>1.15</v>
       </c>
-      <c r="S5" t="s">
-        <v>25</v>
-      </c>
-      <c r="T5" t="s">
-        <v>25</v>
-      </c>
       <c r="U5" t="s">
-        <v>25</v>
-      </c>
-      <c r="V5">
-        <v>1.5</v>
-      </c>
-      <c r="W5">
-        <v>0</v>
+        <v>27</v>
+      </c>
+      <c r="V5" t="s">
+        <v>27</v>
+      </c>
+      <c r="W5" t="s">
+        <v>27</v>
       </c>
       <c r="X5">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -1100,61 +1138,67 @@
       <c r="E6">
         <v>0</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>31</v>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6">
+        <v>50</v>
+      </c>
+      <c r="M6" t="s">
+        <v>27</v>
+      </c>
+      <c r="N6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O6">
+        <v>4</v>
+      </c>
+      <c r="P6">
+        <v>1.45</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>20</v>
+      </c>
+      <c r="S6">
+        <v>1.2</v>
+      </c>
+      <c r="T6">
+        <v>1.15</v>
+      </c>
+      <c r="U6">
+        <v>300</v>
+      </c>
+      <c r="V6" t="s">
+        <v>27</v>
+      </c>
+      <c r="W6" t="s">
+        <v>27</v>
+      </c>
+      <c r="X6">
+        <v>1.5</v>
+      </c>
+      <c r="Y6">
         <v>30</v>
       </c>
-      <c r="J6">
-        <v>50</v>
-      </c>
-      <c r="K6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L6" t="s">
-        <v>25</v>
-      </c>
-      <c r="M6">
-        <v>4</v>
-      </c>
-      <c r="N6">
-        <v>1.45</v>
-      </c>
-      <c r="O6">
-        <v>1</v>
-      </c>
-      <c r="P6">
-        <v>20</v>
-      </c>
-      <c r="Q6">
-        <v>1.2</v>
-      </c>
-      <c r="R6">
-        <v>1.15</v>
-      </c>
-      <c r="S6">
-        <v>300</v>
-      </c>
-      <c r="T6" t="s">
-        <v>25</v>
-      </c>
-      <c r="U6" t="s">
-        <v>25</v>
-      </c>
-      <c r="V6">
-        <v>1.5</v>
-      </c>
-      <c r="W6">
-        <v>30</v>
-      </c>
-      <c r="X6">
+      <c r="Z6">
         <v>1.5</v>
       </c>
     </row>
@@ -1180,24 +1224,24 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -1209,7 +1253,7 @@
         <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F2">
         <v>25</v>
@@ -1217,7 +1261,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B3">
         <v>3</v>
@@ -1226,7 +1270,7 @@
         <v>50</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E3">
         <v>20</v>
@@ -1237,7 +1281,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B4">
         <v>5</v>
@@ -1246,7 +1290,7 @@
         <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E4">
         <v>40</v>
@@ -1274,27 +1318,27 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -1314,7 +1358,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -1351,21 +1395,21 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -1379,7 +1423,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -1410,18 +1454,18 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C2">
         <v>5</v>
@@ -1429,10 +1473,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C3">
         <v>50</v>
@@ -1440,10 +1484,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1451,10 +1495,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C5">
         <v>100</v>
@@ -1462,7 +1506,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B6">
         <v>100</v>
@@ -1473,10 +1517,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1484,10 +1528,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C8">
         <v>10</v>
@@ -1509,10 +1553,10 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1617,21 +1661,21 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B2">
         <v>100</v>
@@ -1640,7 +1684,7 @@
         <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E2">
         <v>45</v>
@@ -1662,15 +1706,15 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -1678,7 +1722,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B3">
         <v>8</v>
@@ -1686,7 +1730,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -1694,7 +1738,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B5">
         <v>10</v>
@@ -1702,7 +1746,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -1710,7 +1754,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B7">
         <v>5</v>
@@ -1718,7 +1762,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B8">
         <v>8</v>
@@ -1726,7 +1770,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -1734,7 +1778,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B10">
         <v>1.25</v>
@@ -1742,7 +1786,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B11">
         <v>2</v>
@@ -1750,7 +1794,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B12">
         <v>50</v>
@@ -1758,7 +1802,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B13">
         <v>5</v>
@@ -1766,7 +1810,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B14">
         <v>5</v>
@@ -1774,7 +1818,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B15">
         <v>1.45</v>
@@ -1782,7 +1826,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B16">
         <v>1</v>
@@ -1790,15 +1834,15 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -1806,7 +1850,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B19">
         <v>4</v>
@@ -1814,7 +1858,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B20">
         <v>300</v>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="98">
   <si>
     <t>id</t>
   </si>
@@ -66,9 +66,6 @@
   </si>
   <si>
     <t>build_cost_exponential_growth</t>
-  </si>
-  <si>
-    <t>build_cost_distance_growth</t>
   </si>
   <si>
     <t>build_duration_seconds</t>
@@ -696,7 +693,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z6"/>
+  <dimension ref="A1:Y6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="10" customWidth="1"/>
@@ -712,17 +709,16 @@
     <col min="13" max="14" width="17" customWidth="1"/>
     <col min="15" max="15" width="23" customWidth="1"/>
     <col min="16" max="16" width="31" customWidth="1"/>
-    <col min="17" max="17" width="28" customWidth="1"/>
-    <col min="18" max="18" width="24" customWidth="1"/>
-    <col min="19" max="20" width="32" customWidth="1"/>
-    <col min="21" max="21" width="21" customWidth="1"/>
-    <col min="22" max="23" width="19" customWidth="1"/>
-    <col min="24" max="24" width="27" customWidth="1"/>
-    <col min="25" max="25" width="26" customWidth="1"/>
-    <col min="26" max="26" width="31" customWidth="1"/>
+    <col min="17" max="17" width="24" customWidth="1"/>
+    <col min="18" max="19" width="32" customWidth="1"/>
+    <col min="20" max="20" width="21" customWidth="1"/>
+    <col min="21" max="22" width="19" customWidth="1"/>
+    <col min="23" max="23" width="27" customWidth="1"/>
+    <col min="24" max="24" width="26" customWidth="1"/>
+    <col min="25" max="25" width="31" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -798,13 +794,10 @@
       <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>26</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -825,25 +818,25 @@
         <v>5</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O2">
         <v>2</v>
@@ -852,39 +845,36 @@
         <v>1.2</v>
       </c>
       <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>1.2</v>
+      </c>
+      <c r="S2">
         <v>1.15</v>
       </c>
-      <c r="R2">
+      <c r="T2">
+        <v>200</v>
+      </c>
+      <c r="U2">
+        <v>25</v>
+      </c>
+      <c r="V2" t="s">
+        <v>26</v>
+      </c>
+      <c r="W2">
+        <v>1.5</v>
+      </c>
+      <c r="X2">
         <v>0</v>
       </c>
-      <c r="S2">
-        <v>1.2</v>
-      </c>
-      <c r="T2">
-        <v>1.15</v>
-      </c>
-      <c r="U2">
-        <v>200</v>
-      </c>
-      <c r="V2">
-        <v>25</v>
-      </c>
-      <c r="W2" t="s">
+      <c r="Y2">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>27</v>
-      </c>
-      <c r="X2">
-        <v>1.5</v>
-      </c>
-      <c r="Y2">
-        <v>0</v>
-      </c>
-      <c r="Z2">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>28</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -905,16 +895,16 @@
         <v>2</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L3">
         <v>75</v>
@@ -923,7 +913,7 @@
         <v>20</v>
       </c>
       <c r="N3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O3">
         <v>0.75</v>
@@ -932,39 +922,36 @@
         <v>1.25</v>
       </c>
       <c r="Q3">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="R3">
-        <v>20</v>
+        <v>1.2</v>
       </c>
       <c r="S3">
-        <v>1.2</v>
-      </c>
-      <c r="T3">
         <v>1.15</v>
       </c>
+      <c r="T3" t="s">
+        <v>26</v>
+      </c>
       <c r="U3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V3" t="s">
-        <v>27</v>
-      </c>
-      <c r="W3" t="s">
-        <v>27</v>
+        <v>26</v>
+      </c>
+      <c r="W3">
+        <v>1.5</v>
       </c>
       <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
         <v>1.5</v>
       </c>
-      <c r="Y3">
-        <v>0</v>
-      </c>
-      <c r="Z3">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -985,16 +972,16 @@
         <v>2</v>
       </c>
       <c r="H4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="L4">
         <v>50</v>
@@ -1003,7 +990,7 @@
         <v>10</v>
       </c>
       <c r="N4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O4">
         <v>2</v>
@@ -1012,39 +999,36 @@
         <v>1.5</v>
       </c>
       <c r="Q4">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="R4">
-        <v>20</v>
+        <v>1.2</v>
       </c>
       <c r="S4">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="T4">
-        <v>1.15</v>
+        <v>300</v>
       </c>
       <c r="U4">
-        <v>300</v>
-      </c>
-      <c r="V4">
         <v>50</v>
       </c>
-      <c r="W4" t="s">
-        <v>27</v>
+      <c r="V4" t="s">
+        <v>26</v>
+      </c>
+      <c r="W4">
+        <v>1.5</v>
       </c>
       <c r="X4">
+        <v>30</v>
+      </c>
+      <c r="Y4">
         <v>1.5</v>
       </c>
-      <c r="Y4">
-        <v>30</v>
-      </c>
-      <c r="Z4">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -1065,25 +1049,25 @@
         <v>2</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M5">
         <v>20</v>
       </c>
       <c r="N5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O5">
         <v>2</v>
@@ -1092,39 +1076,36 @@
         <v>1.2</v>
       </c>
       <c r="Q5">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="R5">
-        <v>10</v>
+        <v>1.2</v>
       </c>
       <c r="S5">
-        <v>1.2</v>
-      </c>
-      <c r="T5">
         <v>1.15</v>
       </c>
+      <c r="T5" t="s">
+        <v>26</v>
+      </c>
       <c r="U5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V5" t="s">
-        <v>27</v>
-      </c>
-      <c r="W5" t="s">
-        <v>27</v>
+        <v>26</v>
+      </c>
+      <c r="W5">
+        <v>1.5</v>
       </c>
       <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
         <v>1.5</v>
       </c>
-      <c r="Y5">
-        <v>0</v>
-      </c>
-      <c r="Z5">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -1145,25 +1126,25 @@
         <v>2</v>
       </c>
       <c r="H6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J6" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="K6" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L6">
         <v>50</v>
       </c>
       <c r="M6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O6">
         <v>4</v>
@@ -1172,33 +1153,30 @@
         <v>1.45</v>
       </c>
       <c r="Q6">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="R6">
-        <v>20</v>
+        <v>1.2</v>
       </c>
       <c r="S6">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="T6">
-        <v>1.15</v>
-      </c>
-      <c r="U6">
         <v>300</v>
       </c>
+      <c r="U6" t="s">
+        <v>26</v>
+      </c>
       <c r="V6" t="s">
-        <v>27</v>
-      </c>
-      <c r="W6" t="s">
-        <v>27</v>
+        <v>26</v>
+      </c>
+      <c r="W6">
+        <v>1.5</v>
       </c>
       <c r="X6">
-        <v>1.5</v>
+        <v>30</v>
       </c>
       <c r="Y6">
-        <v>30</v>
-      </c>
-      <c r="Z6">
         <v>1.5</v>
       </c>
     </row>
@@ -1224,24 +1202,24 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -1253,7 +1231,7 @@
         <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F2">
         <v>25</v>
@@ -1261,7 +1239,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B3">
         <v>3</v>
@@ -1270,7 +1248,7 @@
         <v>50</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E3">
         <v>20</v>
@@ -1281,7 +1259,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B4">
         <v>5</v>
@@ -1290,7 +1268,7 @@
         <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E4">
         <v>40</v>
@@ -1318,27 +1296,27 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -1358,7 +1336,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -1395,21 +1373,21 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -1423,7 +1401,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -1454,18 +1432,18 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C2">
         <v>5</v>
@@ -1473,10 +1451,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C3">
         <v>50</v>
@@ -1484,10 +1462,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1495,10 +1473,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C5">
         <v>100</v>
@@ -1506,7 +1484,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B6">
         <v>100</v>
@@ -1517,10 +1495,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1528,10 +1506,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C8">
         <v>10</v>
@@ -1553,10 +1531,10 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1661,21 +1639,21 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B2">
         <v>100</v>
@@ -1684,7 +1662,7 @@
         <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E2">
         <v>45</v>
@@ -1706,15 +1684,15 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -1722,7 +1700,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B3">
         <v>8</v>
@@ -1730,7 +1708,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -1738,7 +1716,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B5">
         <v>10</v>
@@ -1746,7 +1724,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -1754,7 +1732,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B7">
         <v>5</v>
@@ -1762,7 +1740,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B8">
         <v>8</v>
@@ -1770,7 +1748,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -1778,7 +1756,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B10">
         <v>1.25</v>
@@ -1786,7 +1764,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B11">
         <v>2</v>
@@ -1794,7 +1772,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B12">
         <v>50</v>
@@ -1802,7 +1780,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B13">
         <v>5</v>
@@ -1810,7 +1788,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B14">
         <v>5</v>
@@ -1818,7 +1796,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B15">
         <v>1.45</v>
@@ -1826,7 +1804,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B16">
         <v>1</v>
@@ -1834,15 +1812,15 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>93</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -1850,7 +1828,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B19">
         <v>4</v>
@@ -1858,7 +1836,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B20">
         <v>300</v>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -6,19 +6,18 @@
   <sheets>
     <sheet sheetId="1" name="Districts" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="Units" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Spells" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="Harvest" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="Currencies" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="FogRings" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="Research" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="Settings" state="visible" r:id="rId11"/>
+    <sheet sheetId="3" name="Harvest" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Currencies" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="FogRings" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Research" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="Settings" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="89">
   <si>
     <t>id</t>
   </si>
@@ -161,90 +160,66 @@
     <t>Cavalry</t>
   </si>
   <si>
-    <t>spell</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>mana_cost</t>
+    <t>source</t>
+  </si>
+  <si>
+    <t>yield_per_tap</t>
+  </si>
+  <si>
+    <t>taps_to_exhaust</t>
+  </si>
+  <si>
+    <t>recovery_seconds</t>
+  </si>
+  <si>
+    <t>Forest</t>
+  </si>
+  <si>
+    <t>Crops</t>
+  </si>
+  <si>
+    <t>cap</t>
+  </si>
+  <si>
+    <t>start</t>
+  </si>
+  <si>
+    <t>Food</t>
+  </si>
+  <si>
+    <t>Silver</t>
+  </si>
+  <si>
+    <t>Wood</t>
+  </si>
+  <si>
+    <t>Gold</t>
+  </si>
+  <si>
+    <t>Knowledge</t>
+  </si>
+  <si>
+    <t>Gems</t>
+  </si>
+  <si>
+    <t>distance</t>
+  </si>
+  <si>
+    <t>cost</t>
+  </si>
+  <si>
+    <t>cost_silver</t>
+  </si>
+  <si>
+    <t>cost_wood</t>
+  </si>
+  <si>
+    <t>cost_food</t>
   </si>
   <si>
     <t>duration_seconds</t>
   </si>
   <si>
-    <t>effect_magnitude</t>
-  </si>
-  <si>
-    <t>upgrade_cost</t>
-  </si>
-  <si>
-    <t>Rain</t>
-  </si>
-  <si>
-    <t>Tap</t>
-  </si>
-  <si>
-    <t>source</t>
-  </si>
-  <si>
-    <t>yield_per_tap</t>
-  </si>
-  <si>
-    <t>taps_to_exhaust</t>
-  </si>
-  <si>
-    <t>recovery_seconds</t>
-  </si>
-  <si>
-    <t>Forest</t>
-  </si>
-  <si>
-    <t>Crops</t>
-  </si>
-  <si>
-    <t>cap</t>
-  </si>
-  <si>
-    <t>start</t>
-  </si>
-  <si>
-    <t>Food</t>
-  </si>
-  <si>
-    <t>Silver</t>
-  </si>
-  <si>
-    <t>Wood</t>
-  </si>
-  <si>
-    <t>Gold</t>
-  </si>
-  <si>
-    <t>Mana</t>
-  </si>
-  <si>
-    <t>Knowledge</t>
-  </si>
-  <si>
-    <t>Gems</t>
-  </si>
-  <si>
-    <t>distance</t>
-  </si>
-  <si>
-    <t>cost</t>
-  </si>
-  <si>
-    <t>cost_silver</t>
-  </si>
-  <si>
-    <t>cost_wood</t>
-  </si>
-  <si>
-    <t>cost_food</t>
-  </si>
-  <si>
     <t>Agriculture</t>
   </si>
   <si>
@@ -309,9 +284,6 @@
   </si>
   <si>
     <t>kingdom.max_builders</t>
-  </si>
-  <si>
-    <t>kingdom.mana_per_hour</t>
   </si>
 </sst>
 </file>
@@ -1285,83 +1257,6 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>10</v>
-      </c>
-      <c r="D2">
-        <v>30</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>5</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -1373,21 +1268,21 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -1401,7 +1296,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -1419,9 +1314,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="10" customWidth="1"/>
@@ -1432,15 +1327,15 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="B2" t="s">
         <v>26</v>
@@ -1451,7 +1346,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
@@ -1462,7 +1357,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
@@ -1473,7 +1368,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
@@ -1484,34 +1379,23 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>67</v>
-      </c>
-      <c r="B6">
-        <v>100</v>
+        <v>59</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
       </c>
       <c r="C6">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>69</v>
-      </c>
-      <c r="B8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8">
         <v>10</v>
       </c>
     </row>
@@ -1521,7 +1405,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -1531,10 +1415,10 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1623,7 +1507,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -1639,21 +1523,21 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B2">
         <v>100</v>
@@ -1674,9 +1558,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
@@ -1684,15 +1568,15 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -1700,7 +1584,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="B3">
         <v>8</v>
@@ -1708,7 +1592,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -1716,7 +1600,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="B5">
         <v>10</v>
@@ -1724,7 +1608,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -1732,7 +1616,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="B7">
         <v>5</v>
@@ -1740,7 +1624,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B8">
         <v>8</v>
@@ -1748,7 +1632,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -1756,7 +1640,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="B10">
         <v>1.25</v>
@@ -1764,7 +1648,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B11">
         <v>2</v>
@@ -1772,7 +1656,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B12">
         <v>50</v>
@@ -1780,7 +1664,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B13">
         <v>5</v>
@@ -1788,7 +1672,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B14">
         <v>5</v>
@@ -1796,7 +1680,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B15">
         <v>1.45</v>
@@ -1804,7 +1688,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B16">
         <v>1</v>
@@ -1812,15 +1696,15 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -1828,18 +1712,10 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="B19">
         <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>97</v>
-      </c>
-      <c r="B20">
-        <v>300</v>
       </c>
     </row>
   </sheetData>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -166,6 +166,9 @@
     <t>yield_per_tap</t>
   </si>
   <si>
+    <t>yield_per_worker</t>
+  </si>
+  <si>
     <t>taps_to_exhaust</t>
   </si>
   <si>
@@ -233,9 +236,6 @@
   </si>
   <si>
     <t>worker.work_seconds</t>
-  </si>
-  <si>
-    <t>worker.carry</t>
   </si>
   <si>
     <t>townhall_cycle.cycle_seconds</t>
@@ -1257,16 +1257,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>47</v>
       </c>
@@ -1279,32 +1280,41 @@
       <c r="D1" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
         <v>10</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
         <v>10</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>60</v>
       </c>
     </row>
@@ -1327,15 +1337,15 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B2" t="s">
         <v>26</v>
@@ -1346,7 +1356,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
@@ -1357,7 +1367,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
@@ -1368,7 +1378,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
@@ -1379,7 +1389,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
@@ -1390,7 +1400,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
@@ -1415,10 +1425,10 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1523,21 +1533,21 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B2">
         <v>100</v>
@@ -1560,7 +1570,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
@@ -1568,15 +1578,15 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -1584,7 +1594,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B3">
         <v>8</v>
@@ -1592,79 +1602,79 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B5">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B8">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B10">
-        <v>1.25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B12">
-        <v>50</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B13">
         <v>5</v>
@@ -1672,49 +1682,41 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B14">
-        <v>5</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B15">
-        <v>1.45</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>84</v>
-      </c>
-      <c r="B16">
-        <v>1</v>
+        <v>85</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>85</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>88</v>
-      </c>
-      <c r="B19">
         <v>4</v>
       </c>
     </row>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="90">
   <si>
     <t>id</t>
   </si>
@@ -236,6 +236,9 @@
   </si>
   <si>
     <t>worker.work_seconds</t>
+  </si>
+  <si>
+    <t>tap.collect_cooldown_seconds</t>
   </si>
   <si>
     <t>townhall_cycle.cycle_seconds</t>
@@ -1570,7 +1573,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
@@ -1605,7 +1608,7 @@
         <v>73</v>
       </c>
       <c r="B4">
-        <v>10</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -1613,7 +1616,7 @@
         <v>74</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1621,7 +1624,7 @@
         <v>75</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -1629,7 +1632,7 @@
         <v>76</v>
       </c>
       <c r="B7">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1637,7 +1640,7 @@
         <v>77</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1645,7 +1648,7 @@
         <v>78</v>
       </c>
       <c r="B9">
-        <v>1.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1653,7 +1656,7 @@
         <v>79</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -1661,7 +1664,7 @@
         <v>80</v>
       </c>
       <c r="B11">
-        <v>50</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -1669,7 +1672,7 @@
         <v>81</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -1685,7 +1688,7 @@
         <v>83</v>
       </c>
       <c r="B14">
-        <v>1.45</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -1693,23 +1696,23 @@
         <v>84</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>85</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>86</v>
+      <c r="B16">
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="B17">
-        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -1717,6 +1720,14 @@
         <v>88</v>
       </c>
       <c r="B18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19">
         <v>4</v>
       </c>
     </row>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="94">
   <si>
     <t>id</t>
   </si>
@@ -181,10 +181,22 @@
     <t>Crops</t>
   </si>
   <si>
+    <t>Berries</t>
+  </si>
+  <si>
+    <t>Meat</t>
+  </si>
+  <si>
     <t>cap</t>
   </si>
   <si>
     <t>start</t>
+  </si>
+  <si>
+    <t>counts_as</t>
+  </si>
+  <si>
+    <t>unit_value</t>
   </si>
   <si>
     <t>Food</t>
@@ -1260,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1321,6 +1333,40 @@
         <v>60</v>
       </c>
     </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>10</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>10</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1329,26 +1375,34 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B2" t="s">
         <v>26</v>
@@ -1356,10 +1410,16 @@
       <c r="C2">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
@@ -1367,10 +1427,16 @@
       <c r="C3">
         <v>50</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
@@ -1378,21 +1444,33 @@
       <c r="C4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
       </c>
       <c r="C5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="D5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
@@ -1400,16 +1478,62 @@
       <c r="C6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7">
+        <v>100</v>
+      </c>
+      <c r="D7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9">
         <v>10</v>
+      </c>
+      <c r="D9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1428,10 +1552,10 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1536,21 +1660,21 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B2">
         <v>100</v>
@@ -1581,15 +1705,15 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -1597,7 +1721,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B3">
         <v>8</v>
@@ -1605,7 +1729,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B4">
         <v>0.5</v>
@@ -1613,7 +1737,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B5">
         <v>10</v>
@@ -1621,7 +1745,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -1629,7 +1753,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B7">
         <v>5</v>
@@ -1637,7 +1761,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B8">
         <v>8</v>
@@ -1645,7 +1769,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -1653,7 +1777,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B10">
         <v>1.25</v>
@@ -1661,7 +1785,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B11">
         <v>2</v>
@@ -1669,7 +1793,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B12">
         <v>50</v>
@@ -1677,7 +1801,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B13">
         <v>5</v>
@@ -1685,7 +1809,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B14">
         <v>5</v>
@@ -1693,7 +1817,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B15">
         <v>1.45</v>
@@ -1701,7 +1825,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B16">
         <v>1</v>
@@ -1709,15 +1833,15 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -1725,7 +1849,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B19">
         <v>4</v>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="95">
   <si>
     <t>id</t>
   </si>
@@ -191,6 +191,9 @@
   </si>
   <si>
     <t>start</t>
+  </si>
+  <si>
+    <t>primary</t>
   </si>
   <si>
     <t>counts_as</t>
@@ -1375,15 +1378,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="1" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1399,10 +1402,13 @@
       <c r="E1" s="1" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B2" t="s">
         <v>26</v>
@@ -1410,16 +1416,19 @@
       <c r="C2">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
-        <v>26</v>
+      <c r="D2">
+        <v>1</v>
       </c>
       <c r="E2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
@@ -1427,16 +1436,19 @@
       <c r="C3">
         <v>50</v>
       </c>
-      <c r="D3" t="s">
-        <v>26</v>
+      <c r="D3">
+        <v>1</v>
       </c>
       <c r="E3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
@@ -1444,14 +1456,17 @@
       <c r="C4">
         <v>0</v>
       </c>
-      <c r="D4" t="s">
-        <v>26</v>
+      <c r="D4">
+        <v>1</v>
       </c>
       <c r="E4" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>54</v>
       </c>
@@ -1462,13 +1477,16 @@
         <v>0</v>
       </c>
       <c r="D5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="E5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>55</v>
       </c>
@@ -1479,15 +1497,18 @@
         <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>60</v>
-      </c>
-      <c r="E6">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
+        <v>61</v>
+      </c>
+      <c r="F6">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
@@ -1501,10 +1522,13 @@
       <c r="E7" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
@@ -1518,10 +1542,13 @@
       <c r="E8" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B9" t="s">
         <v>26</v>
@@ -1529,10 +1556,13 @@
       <c r="C9">
         <v>10</v>
       </c>
-      <c r="D9" t="s">
-        <v>26</v>
+      <c r="D9">
+        <v>1</v>
       </c>
       <c r="E9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1552,10 +1582,10 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1660,21 +1690,21 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B2">
         <v>100</v>
@@ -1705,15 +1735,15 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -1721,7 +1751,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B3">
         <v>8</v>
@@ -1729,7 +1759,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B4">
         <v>0.5</v>
@@ -1737,7 +1767,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B5">
         <v>10</v>
@@ -1745,7 +1775,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -1753,7 +1783,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B7">
         <v>5</v>
@@ -1761,7 +1791,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B8">
         <v>8</v>
@@ -1769,7 +1799,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -1777,7 +1807,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B10">
         <v>1.25</v>
@@ -1785,7 +1815,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B11">
         <v>2</v>
@@ -1793,7 +1823,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B12">
         <v>50</v>
@@ -1801,7 +1831,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B13">
         <v>5</v>
@@ -1809,7 +1839,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B14">
         <v>5</v>
@@ -1817,7 +1847,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B15">
         <v>1.45</v>
@@ -1825,7 +1855,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B16">
         <v>1</v>
@@ -1833,15 +1863,15 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -1849,7 +1879,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B19">
         <v>4</v>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -1,23 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <workbookPr/>
+  <bookViews>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Districts" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Units" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Harvest" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="Currencies" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="FogRings" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="Research" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="Settings" state="visible" r:id="rId10"/>
+    <sheet name="Districts" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Units" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Harvest" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Currencies" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="FogRings" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Research" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Settings" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
   <si>
     <t>id</t>
   </si>
@@ -307,14 +312,13 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2">
     <font>
+      <sz val="11.000000"/>
       <color theme="1"/>
-      <family val="2"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
@@ -330,20 +334,20 @@
   </fills>
   <borders count="1">
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -361,7 +365,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -407,13 +411,13 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Thai" typeface="Angsana New"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
@@ -436,19 +440,18 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Thai" typeface="Cordia New"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
@@ -471,7 +474,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -506,16 +508,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -637,9 +643,226 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
   <a:objectDefaults>
     <a:spDef>
-      <a:spPr/>
+      <a:spPr bwMode="auto"/>
       <a:bodyPr/>
       <a:lstStyle/>
       <a:style>
@@ -658,7 +881,7 @@
       </a:style>
     </a:spDef>
     <a:lnDef>
-      <a:spPr/>
+      <a:spPr bwMode="auto"/>
       <a:bodyPr/>
       <a:lstStyle/>
       <a:style>
@@ -677,38 +900,36 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y6"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="21" customWidth="1"/>
-    <col min="6" max="6" width="19" customWidth="1"/>
-    <col min="7" max="7" width="21" customWidth="1"/>
-    <col min="8" max="8" width="23" customWidth="1"/>
-    <col min="9" max="9" width="30" customWidth="1"/>
-    <col min="10" max="10" width="28" customWidth="1"/>
-    <col min="11" max="11" width="35" customWidth="1"/>
-    <col min="12" max="12" width="19" customWidth="1"/>
-    <col min="13" max="14" width="17" customWidth="1"/>
-    <col min="15" max="15" width="23" customWidth="1"/>
-    <col min="16" max="16" width="31" customWidth="1"/>
-    <col min="17" max="17" width="24" customWidth="1"/>
-    <col min="18" max="19" width="32" customWidth="1"/>
-    <col min="20" max="20" width="21" customWidth="1"/>
-    <col min="21" max="22" width="19" customWidth="1"/>
-    <col min="23" max="23" width="27" customWidth="1"/>
-    <col min="24" max="24" width="26" customWidth="1"/>
-    <col min="25" max="25" width="31" customWidth="1"/>
+    <col customWidth="1" min="1" max="3" width="10"/>
+    <col customWidth="1" min="4" max="4" width="11"/>
+    <col customWidth="1" min="5" max="5" width="21"/>
+    <col customWidth="1" min="6" max="6" width="19"/>
+    <col customWidth="1" min="7" max="7" width="21"/>
+    <col customWidth="1" min="8" max="8" width="23"/>
+    <col customWidth="1" min="9" max="9" width="30"/>
+    <col customWidth="1" min="10" max="10" width="28"/>
+    <col customWidth="1" min="11" max="11" width="35"/>
+    <col customWidth="1" min="12" max="12" width="19"/>
+    <col customWidth="1" min="13" max="14" width="17"/>
+    <col customWidth="1" min="15" max="15" width="23"/>
+    <col customWidth="1" min="16" max="16" width="31"/>
+    <col customWidth="1" min="17" max="17" width="24"/>
+    <col customWidth="1" min="18" max="19" width="32"/>
+    <col customWidth="1" min="20" max="20" width="21"/>
+    <col customWidth="1" min="21" max="22" width="19"/>
+    <col customWidth="1" min="23" max="23" width="27"/>
+    <col customWidth="1" min="24" max="24" width="26"/>
+    <col customWidth="1" min="25" max="25" width="31"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -785,7 +1006,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -802,10 +1023,10 @@
         <v>3</v>
       </c>
       <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
         <v>3</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>26</v>
@@ -841,7 +1062,7 @@
         <v>1.2</v>
       </c>
       <c r="S2">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="T2">
         <v>200</v>
@@ -862,7 +1083,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>27</v>
       </c>
@@ -918,7 +1139,7 @@
         <v>1.2</v>
       </c>
       <c r="S3">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="T3" t="s">
         <v>26</v>
@@ -939,7 +1160,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>29</v>
       </c>
@@ -995,7 +1216,7 @@
         <v>1.2</v>
       </c>
       <c r="S4">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="T4">
         <v>300</v>
@@ -1016,7 +1237,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>34</v>
       </c>
@@ -1072,7 +1293,7 @@
         <v>1.2</v>
       </c>
       <c r="S5">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="T5" t="s">
         <v>26</v>
@@ -1093,7 +1314,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>36</v>
       </c>
@@ -1149,7 +1370,7 @@
         <v>1.2</v>
       </c>
       <c r="S6">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="T6">
         <v>300</v>
@@ -1171,23 +1392,24 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="21" customWidth="1"/>
-    <col min="4" max="5" width="19" customWidth="1"/>
-    <col min="6" max="6" width="24" customWidth="1"/>
+    <col customWidth="1" min="1" max="2" width="10"/>
+    <col customWidth="1" min="3" max="3" width="21"/>
+    <col customWidth="1" min="4" max="5" width="19"/>
+    <col customWidth="1" min="6" max="6" width="24"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1207,7 +1429,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>44</v>
       </c>
@@ -1227,7 +1449,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>45</v>
       </c>
@@ -1247,7 +1469,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>46</v>
       </c>
@@ -1268,24 +1490,25 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="10"/>
+    <col customWidth="1" min="2" max="2" width="15"/>
+    <col customWidth="1" min="3" max="3" width="18"/>
+    <col customWidth="1" min="4" max="4" width="17"/>
+    <col customWidth="1" min="5" max="5" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>47</v>
       </c>
@@ -1302,7 +1525,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>52</v>
       </c>
@@ -1319,7 +1542,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>53</v>
       </c>
@@ -1336,7 +1559,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>54</v>
       </c>
@@ -1353,7 +1576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>55</v>
       </c>
@@ -1371,22 +1594,23 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col customWidth="1" min="1" max="4" width="10"/>
+    <col customWidth="1" min="5" max="5" width="11"/>
+    <col customWidth="1" min="6" max="6" width="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1406,7 +1630,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>61</v>
       </c>
@@ -1426,7 +1650,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>62</v>
       </c>
@@ -1446,7 +1670,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>63</v>
       </c>
@@ -1466,7 +1690,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>54</v>
       </c>
@@ -1486,7 +1710,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>55</v>
       </c>
@@ -1506,7 +1730,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>64</v>
       </c>
@@ -1526,7 +1750,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>65</v>
       </c>
@@ -1546,7 +1770,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>66</v>
       </c>
@@ -1567,20 +1791,21 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="10" customWidth="1"/>
+    <col customWidth="1" min="1" max="2" width="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>67</v>
       </c>
@@ -1588,7 +1813,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1596,7 +1821,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1604,7 +1829,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1612,7 +1837,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1620,7 +1845,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1628,7 +1853,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1636,7 +1861,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1644,7 +1869,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1652,7 +1877,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1660,7 +1885,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1669,23 +1894,24 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="10"/>
+    <col customWidth="1" min="2" max="2" width="13"/>
+    <col customWidth="1" min="3" max="4" width="11"/>
+    <col customWidth="1" min="5" max="5" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1702,7 +1928,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>73</v>
       </c>
@@ -1720,20 +1946,22 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="2" width="10" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="38.140625"/>
+    <col customWidth="1" min="2" max="2" width="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>74</v>
       </c>
@@ -1741,7 +1969,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>76</v>
       </c>
@@ -1749,7 +1977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>77</v>
       </c>
@@ -1757,7 +1985,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>78</v>
       </c>
@@ -1765,7 +1993,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>79</v>
       </c>
@@ -1773,7 +2001,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>80</v>
       </c>
@@ -1781,7 +2009,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>81</v>
       </c>
@@ -1789,7 +2017,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>82</v>
       </c>
@@ -1797,7 +2025,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>83</v>
       </c>
@@ -1805,7 +2033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
         <v>84</v>
       </c>
@@ -1813,31 +2041,31 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" t="s">
         <v>85</v>
       </c>
       <c r="B11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" t="s">
         <v>86</v>
       </c>
       <c r="B12">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" t="s">
         <v>87</v>
       </c>
       <c r="B13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" t="s">
         <v>88</v>
       </c>
@@ -1845,7 +2073,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="A15" t="s">
         <v>89</v>
       </c>
@@ -1853,7 +2081,7 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="A16" t="s">
         <v>90</v>
       </c>
@@ -1861,7 +2089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="A17" t="s">
         <v>91</v>
       </c>
@@ -1869,7 +2097,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18">
       <c r="A18" t="s">
         <v>93</v>
       </c>
@@ -1877,7 +2105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19">
       <c r="A19" t="s">
         <v>94</v>
       </c>
@@ -1886,7 +2114,9 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -1,28 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr/>
-  <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Districts" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Units" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Harvest" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Currencies" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="FogRings" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Research" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Settings" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet sheetId="1" name="Districts" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Units" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Harvest" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Currencies" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="FogRings" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Research" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="Settings" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="Map" state="visible" r:id="rId11"/>
   </sheets>
-  <calcPr/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="101">
   <si>
     <t>id</t>
   </si>
@@ -307,18 +303,37 @@
   </si>
   <si>
     <t>kingdom.max_builders</t>
+  </si>
+  <si>
+    <t>w</t>
+  </si>
+  <si>
+    <t>g</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>wB</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>T</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="11.000000"/>
       <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -334,25 +349,92 @@
   </fills>
   <borders count="1">
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="9">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF6FA84F"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF3D6F9E"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF9AA34F"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFC9B26A"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFDFE7EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF8B9A94"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF2E6B2E"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF7A4FA8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF8A5A34"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -365,7 +447,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -411,13 +493,13 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Angsana New"/>
+        <a:font script="Thai" typeface="Tahoma"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
@@ -440,18 +522,19 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Cordia New"/>
+        <a:font script="Thai" typeface="Tahoma"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
@@ -474,6 +557,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -508,20 +592,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -643,226 +723,9 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
-</file>
-
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle"/>
-        </a:gradFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle"/>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
   <a:objectDefaults>
     <a:spDef>
-      <a:spPr bwMode="auto"/>
+      <a:spPr/>
       <a:bodyPr/>
       <a:lstStyle/>
       <a:style>
@@ -881,7 +744,7 @@
       </a:style>
     </a:spDef>
     <a:lnDef>
-      <a:spPr bwMode="auto"/>
+      <a:spPr/>
       <a:bodyPr/>
       <a:lstStyle/>
       <a:style>
@@ -900,36 +763,38 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Y6"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col customWidth="1" min="1" max="3" width="10"/>
-    <col customWidth="1" min="4" max="4" width="11"/>
-    <col customWidth="1" min="5" max="5" width="21"/>
-    <col customWidth="1" min="6" max="6" width="19"/>
-    <col customWidth="1" min="7" max="7" width="21"/>
-    <col customWidth="1" min="8" max="8" width="23"/>
-    <col customWidth="1" min="9" max="9" width="30"/>
-    <col customWidth="1" min="10" max="10" width="28"/>
-    <col customWidth="1" min="11" max="11" width="35"/>
-    <col customWidth="1" min="12" max="12" width="19"/>
-    <col customWidth="1" min="13" max="14" width="17"/>
-    <col customWidth="1" min="15" max="15" width="23"/>
-    <col customWidth="1" min="16" max="16" width="31"/>
-    <col customWidth="1" min="17" max="17" width="24"/>
-    <col customWidth="1" min="18" max="19" width="32"/>
-    <col customWidth="1" min="20" max="20" width="21"/>
-    <col customWidth="1" min="21" max="22" width="19"/>
-    <col customWidth="1" min="23" max="23" width="27"/>
-    <col customWidth="1" min="24" max="24" width="26"/>
-    <col customWidth="1" min="25" max="25" width="31"/>
+    <col min="1" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="21" customWidth="1"/>
+    <col min="6" max="6" width="19" customWidth="1"/>
+    <col min="7" max="7" width="21" customWidth="1"/>
+    <col min="8" max="8" width="23" customWidth="1"/>
+    <col min="9" max="9" width="30" customWidth="1"/>
+    <col min="10" max="10" width="28" customWidth="1"/>
+    <col min="11" max="11" width="35" customWidth="1"/>
+    <col min="12" max="12" width="19" customWidth="1"/>
+    <col min="13" max="14" width="17" customWidth="1"/>
+    <col min="15" max="15" width="23" customWidth="1"/>
+    <col min="16" max="16" width="31" customWidth="1"/>
+    <col min="17" max="17" width="24" customWidth="1"/>
+    <col min="18" max="19" width="32" customWidth="1"/>
+    <col min="20" max="20" width="21" customWidth="1"/>
+    <col min="21" max="22" width="19" customWidth="1"/>
+    <col min="23" max="23" width="27" customWidth="1"/>
+    <col min="24" max="24" width="26" customWidth="1"/>
+    <col min="25" max="25" width="31" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1006,7 +871,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -1062,7 +927,7 @@
         <v>1.2</v>
       </c>
       <c r="S2">
-        <v>1.1499999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="T2">
         <v>200</v>
@@ -1083,7 +948,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>27</v>
       </c>
@@ -1139,7 +1004,7 @@
         <v>1.2</v>
       </c>
       <c r="S3">
-        <v>1.1499999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="T3" t="s">
         <v>26</v>
@@ -1160,7 +1025,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>29</v>
       </c>
@@ -1216,7 +1081,7 @@
         <v>1.2</v>
       </c>
       <c r="S4">
-        <v>1.1499999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="T4">
         <v>300</v>
@@ -1237,7 +1102,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>34</v>
       </c>
@@ -1293,7 +1158,7 @@
         <v>1.2</v>
       </c>
       <c r="S5">
-        <v>1.1499999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="T5" t="s">
         <v>26</v>
@@ -1314,7 +1179,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>36</v>
       </c>
@@ -1370,7 +1235,7 @@
         <v>1.2</v>
       </c>
       <c r="S6">
-        <v>1.1499999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="T6">
         <v>300</v>
@@ -1392,24 +1257,23 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col customWidth="1" min="1" max="2" width="10"/>
-    <col customWidth="1" min="3" max="3" width="21"/>
-    <col customWidth="1" min="4" max="5" width="19"/>
-    <col customWidth="1" min="6" max="6" width="24"/>
+    <col min="1" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="21" customWidth="1"/>
+    <col min="4" max="5" width="19" customWidth="1"/>
+    <col min="6" max="6" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1429,7 +1293,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>44</v>
       </c>
@@ -1449,7 +1313,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>45</v>
       </c>
@@ -1469,7 +1333,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>46</v>
       </c>
@@ -1490,25 +1354,24 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="10"/>
-    <col customWidth="1" min="2" max="2" width="15"/>
-    <col customWidth="1" min="3" max="3" width="18"/>
-    <col customWidth="1" min="4" max="4" width="17"/>
-    <col customWidth="1" min="5" max="5" width="18"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>47</v>
       </c>
@@ -1525,7 +1388,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>52</v>
       </c>
@@ -1542,7 +1405,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>53</v>
       </c>
@@ -1559,7 +1422,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>54</v>
       </c>
@@ -1576,7 +1439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>55</v>
       </c>
@@ -1594,23 +1457,22 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col customWidth="1" min="1" max="4" width="10"/>
-    <col customWidth="1" min="5" max="5" width="11"/>
-    <col customWidth="1" min="6" max="6" width="12"/>
+    <col min="1" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1630,7 +1492,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>61</v>
       </c>
@@ -1650,7 +1512,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>62</v>
       </c>
@@ -1670,7 +1532,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>63</v>
       </c>
@@ -1690,7 +1552,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>54</v>
       </c>
@@ -1710,7 +1572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>55</v>
       </c>
@@ -1730,7 +1592,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>64</v>
       </c>
@@ -1750,7 +1612,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>65</v>
       </c>
@@ -1770,7 +1632,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>66</v>
       </c>
@@ -1791,21 +1653,20 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col customWidth="1" min="1" max="2" width="10"/>
+    <col min="1" max="2" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>67</v>
       </c>
@@ -1813,7 +1674,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1821,7 +1682,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1829,7 +1690,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1837,7 +1698,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1845,7 +1706,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1853,7 +1714,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1861,7 +1722,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1869,7 +1730,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1877,7 +1738,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1885,7 +1746,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1894,24 +1755,23 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="10"/>
-    <col customWidth="1" min="2" max="2" width="13"/>
-    <col customWidth="1" min="3" max="4" width="11"/>
-    <col customWidth="1" min="5" max="5" width="18"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1928,7 +1788,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>73</v>
       </c>
@@ -1946,22 +1806,20 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B19"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="38.140625"/>
-    <col customWidth="1" min="2" max="2" width="10"/>
+    <col min="1" max="2" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>74</v>
       </c>
@@ -1969,7 +1827,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>76</v>
       </c>
@@ -1977,7 +1835,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>77</v>
       </c>
@@ -1985,7 +1843,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>78</v>
       </c>
@@ -1993,7 +1851,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>79</v>
       </c>
@@ -2001,7 +1859,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>80</v>
       </c>
@@ -2009,7 +1867,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>81</v>
       </c>
@@ -2017,7 +1875,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>82</v>
       </c>
@@ -2025,7 +1883,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>83</v>
       </c>
@@ -2033,7 +1891,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>84</v>
       </c>
@@ -2041,7 +1899,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>85</v>
       </c>
@@ -2049,7 +1907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>86</v>
       </c>
@@ -2057,7 +1915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>87</v>
       </c>
@@ -2065,7 +1923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>88</v>
       </c>
@@ -2073,7 +1931,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>89</v>
       </c>
@@ -2081,7 +1939,7 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>90</v>
       </c>
@@ -2089,7 +1947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>91</v>
       </c>
@@ -2097,7 +1955,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>93</v>
       </c>
@@ -2105,7 +1963,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>94</v>
       </c>
@@ -2114,9 +1972,627 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:N15"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="14" width="3.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="1">
+        <v>-6</v>
+      </c>
+      <c r="C1" s="1">
+        <v>-5</v>
+      </c>
+      <c r="D1" s="1">
+        <v>-4</v>
+      </c>
+      <c r="E1" s="1">
+        <v>-3</v>
+      </c>
+      <c r="F1" s="1">
+        <v>-2</v>
+      </c>
+      <c r="G1" s="1">
+        <v>-1</v>
+      </c>
+      <c r="H1" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1" s="1">
+        <v>3</v>
+      </c>
+      <c r="L1" s="1">
+        <v>4</v>
+      </c>
+      <c r="M1" s="1">
+        <v>5</v>
+      </c>
+      <c r="N1" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>-6</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>-5</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>-4</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>-3</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>-2</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>-1</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>1</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>2</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>3</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>4</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>5</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>6</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>7</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B2:N15">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"g"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"w"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"p"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+      <formula>"d"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+      <formula>"s"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+      <formula>"u"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
+      <formula>"T"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
+      <formula>"B"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="102">
   <si>
     <t>id</t>
   </si>
@@ -53,7 +53,7 @@
     <t>required_townhall_level_per_level</t>
   </si>
   <si>
-    <t>build_cost_silver</t>
+    <t>build_cost_gold</t>
   </si>
   <si>
     <t>build_cost_wood</t>
@@ -77,7 +77,7 @@
     <t>build_duration_distance_growth</t>
   </si>
   <si>
-    <t>upgrade_cost_silver</t>
+    <t>upgrade_cost_gold</t>
   </si>
   <si>
     <t>upgrade_cost_wood</t>
@@ -140,7 +140,7 @@
     <t>power</t>
   </si>
   <si>
-    <t>recruit_cost_silver</t>
+    <t>recruit_cost_gold</t>
   </si>
   <si>
     <t>recruit_cost_wood</t>
@@ -203,18 +203,18 @@
     <t>unit_value</t>
   </si>
   <si>
+    <t>gold_value</t>
+  </si>
+  <si>
+    <t>Gold</t>
+  </si>
+  <si>
     <t>Food</t>
   </si>
   <si>
-    <t>Silver</t>
-  </si>
-  <si>
     <t>Wood</t>
   </si>
   <si>
-    <t>Gold</t>
-  </si>
-  <si>
     <t>Knowledge</t>
   </si>
   <si>
@@ -227,7 +227,7 @@
     <t>cost</t>
   </si>
   <si>
-    <t>cost_silver</t>
+    <t>cost_gold</t>
   </si>
   <si>
     <t>cost_wood</t>
@@ -257,19 +257,22 @@
     <t>tap.collect_cooldown_seconds</t>
   </si>
   <si>
-    <t>townhall_cycle.cycle_seconds</t>
-  </si>
-  <si>
-    <t>townhall_cycle.tap_boost_seconds</t>
-  </si>
-  <si>
-    <t>townhall_cycle.silver_per_population</t>
+    <t>training.seconds</t>
+  </si>
+  <si>
+    <t>training.tap_boost_seconds</t>
+  </si>
+  <si>
+    <t>market.sell_interval_seconds</t>
+  </si>
+  <si>
+    <t>market.capacity</t>
   </si>
   <si>
     <t>offline_cap_hours</t>
   </si>
   <si>
-    <t>fog.silver_per_tap</t>
+    <t>fog.gold_per_tap</t>
   </si>
   <si>
     <t>fog.fallback_growth</t>
@@ -278,7 +281,7 @@
     <t>city.initial_population</t>
   </si>
   <si>
-    <t>city.initial_silver</t>
+    <t>city.initial_gold</t>
   </si>
   <si>
     <t>city.initial_food</t>
@@ -781,14 +784,12 @@
     <col min="9" max="9" width="30" customWidth="1"/>
     <col min="10" max="10" width="28" customWidth="1"/>
     <col min="11" max="11" width="35" customWidth="1"/>
-    <col min="12" max="12" width="19" customWidth="1"/>
-    <col min="13" max="14" width="17" customWidth="1"/>
+    <col min="12" max="14" width="17" customWidth="1"/>
     <col min="15" max="15" width="23" customWidth="1"/>
     <col min="16" max="16" width="31" customWidth="1"/>
     <col min="17" max="17" width="24" customWidth="1"/>
     <col min="18" max="19" width="32" customWidth="1"/>
-    <col min="20" max="20" width="21" customWidth="1"/>
-    <col min="21" max="22" width="19" customWidth="1"/>
+    <col min="20" max="22" width="19" customWidth="1"/>
     <col min="23" max="23" width="27" customWidth="1"/>
     <col min="24" max="24" width="26" customWidth="1"/>
     <col min="25" max="25" width="31" customWidth="1"/>
@@ -1268,8 +1269,7 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="21" customWidth="1"/>
-    <col min="4" max="5" width="19" customWidth="1"/>
+    <col min="3" max="5" width="19" customWidth="1"/>
     <col min="6" max="6" width="24" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1464,15 +1464,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="4" width="10" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="6" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1491,37 +1491,43 @@
       <c r="F1" s="1" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B2" t="s">
         <v>26</v>
       </c>
       <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3">
         <v>5</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3">
-        <v>50</v>
-      </c>
       <c r="D3">
         <v>1</v>
       </c>
@@ -1531,10 +1537,13 @@
       <c r="F3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
@@ -1551,8 +1560,11 @@
       <c r="F4" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>54</v>
       </c>
@@ -1566,13 +1578,16 @@
         <v>26</v>
       </c>
       <c r="E5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>55</v>
       </c>
@@ -1586,21 +1601,24 @@
         <v>26</v>
       </c>
       <c r="E6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F6">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D7" t="s">
         <v>26</v>
@@ -1611,19 +1629,22 @@
       <c r="F7" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8" t="s">
-        <v>26</v>
+        <v>10</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
       </c>
       <c r="E8" t="s">
         <v>26</v>
@@ -1631,24 +1652,7 @@
       <c r="F8" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>66</v>
-      </c>
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9">
-        <v>10</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="G8" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1766,8 +1770,7 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="4" width="11" customWidth="1"/>
+    <col min="2" max="4" width="11" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1813,7 +1816,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
@@ -1856,7 +1859,7 @@
         <v>79</v>
       </c>
       <c r="B5">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1880,7 +1883,7 @@
         <v>82</v>
       </c>
       <c r="B8">
-        <v>8</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1888,7 +1891,7 @@
         <v>83</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1896,7 +1899,7 @@
         <v>84</v>
       </c>
       <c r="B10">
-        <v>1.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -1904,7 +1907,7 @@
         <v>85</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -1928,7 +1931,7 @@
         <v>88</v>
       </c>
       <c r="B14">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -1936,7 +1939,7 @@
         <v>89</v>
       </c>
       <c r="B15">
-        <v>1.45</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -1944,23 +1947,23 @@
         <v>90</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>91</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>92</v>
+      <c r="B17">
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="B18">
-        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -1968,6 +1971,14 @@
         <v>94</v>
       </c>
       <c r="B19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>95</v>
+      </c>
+      <c r="B20">
         <v>4</v>
       </c>
     </row>
@@ -2032,28 +2043,28 @@
         <v>-6</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -2061,34 +2072,34 @@
         <v>-5</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -2096,37 +2107,37 @@
         <v>-4</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -2134,40 +2145,40 @@
         <v>-3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -2175,40 +2186,40 @@
         <v>-2</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
@@ -2216,37 +2227,37 @@
         <v>-1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -2254,37 +2265,37 @@
         <v>0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -2292,37 +2303,37 @@
         <v>1</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -2330,40 +2341,40 @@
         <v>2</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -2371,43 +2382,43 @@
         <v>3</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -2415,40 +2426,40 @@
         <v>4</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -2456,40 +2467,40 @@
         <v>5</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -2497,37 +2508,37 @@
         <v>6</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -2535,31 +2546,31 @@
         <v>7</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -9,16 +9,17 @@
     <sheet sheetId="3" name="Harvest" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="Currencies" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="FogRings" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="Research" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="Settings" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="Map" state="visible" r:id="rId11"/>
+    <sheet sheetId="6" name="Technologies" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="Upgrades" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="Settings" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="Map" state="visible" r:id="rId12"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="118">
   <si>
     <t>id</t>
   </si>
@@ -239,9 +240,45 @@
     <t>duration_seconds</t>
   </si>
   <si>
+    <t>requires</t>
+  </si>
+  <si>
     <t>Agriculture</t>
   </si>
   <si>
+    <t>Archery</t>
+  </si>
+  <si>
+    <t>CavalryTraining</t>
+  </si>
+  <si>
+    <t>cost_base</t>
+  </si>
+  <si>
+    <t>cost_growth</t>
+  </si>
+  <si>
+    <t>effect_per_level</t>
+  </si>
+  <si>
+    <t>required_tech</t>
+  </si>
+  <si>
+    <t>TapPower</t>
+  </si>
+  <si>
+    <t>QuickHands</t>
+  </si>
+  <si>
+    <t>WorkerLoad</t>
+  </si>
+  <si>
+    <t>MarketStall</t>
+  </si>
+  <si>
+    <t>TradeRoutes</t>
+  </si>
+  <si>
     <t>key</t>
   </si>
   <si>
@@ -306,6 +343,18 @@
   </si>
   <si>
     <t>kingdom.max_builders</t>
+  </si>
+  <si>
+    <t>research.tech_slots</t>
+  </si>
+  <si>
+    <t>research.max_slots</t>
+  </si>
+  <si>
+    <t>research.slot_gem_cost_base</t>
+  </si>
+  <si>
+    <t>research.slot_gem_cost_growth</t>
   </si>
   <si>
     <t>w</t>
@@ -1766,15 +1815,16 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="4" width="11" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1790,10 +1840,13 @@
       <c r="E1" s="1" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B2">
         <v>100</v>
@@ -1806,6 +1859,49 @@
       </c>
       <c r="E2">
         <v>45</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3">
+        <v>150</v>
+      </c>
+      <c r="C3">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3">
+        <v>60</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B4">
+        <v>400</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4">
+        <v>30</v>
+      </c>
+      <c r="E4">
+        <v>90</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -1816,7 +1912,146 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2">
+        <v>50</v>
+      </c>
+      <c r="C2">
+        <v>2.2</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B3">
+        <v>75</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>0.05</v>
+      </c>
+      <c r="F3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B4">
+        <v>200</v>
+      </c>
+      <c r="C4">
+        <v>2.5</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B5">
+        <v>100</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>25</v>
+      </c>
+      <c r="F5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>85</v>
+      </c>
+      <c r="B6">
+        <v>150</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>0.5</v>
+      </c>
+      <c r="F6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
@@ -1824,15 +2059,15 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -1840,7 +2075,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="B3">
         <v>8</v>
@@ -1848,7 +2083,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="B4">
         <v>0.5</v>
@@ -1856,7 +2091,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="B5">
         <v>20</v>
@@ -1864,7 +2099,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -1872,7 +2107,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="B7">
         <v>5</v>
@@ -1880,7 +2115,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="B8">
         <v>50</v>
@@ -1888,7 +2123,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="B9">
         <v>8</v>
@@ -1896,7 +2131,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -1904,7 +2139,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="B11">
         <v>1.25</v>
@@ -1912,7 +2147,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1920,7 +2155,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1928,7 +2163,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1936,7 +2171,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="B15">
         <v>5</v>
@@ -1944,7 +2179,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="B16">
         <v>1.45</v>
@@ -1952,7 +2187,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -1960,15 +2195,15 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -1976,10 +2211,42 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="B20">
         <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>108</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>109</v>
+      </c>
+      <c r="B22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>110</v>
+      </c>
+      <c r="B23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>111</v>
+      </c>
+      <c r="B24">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1988,7 +2255,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -2043,28 +2310,28 @@
         <v>-6</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -2072,34 +2339,34 @@
         <v>-5</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -2107,37 +2374,37 @@
         <v>-4</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -2145,40 +2412,40 @@
         <v>-3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -2186,40 +2453,40 @@
         <v>-2</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
@@ -2227,37 +2494,37 @@
         <v>-1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -2265,37 +2532,37 @@
         <v>0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -2303,37 +2570,37 @@
         <v>1</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -2341,40 +2608,40 @@
         <v>2</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -2382,43 +2649,43 @@
         <v>3</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -2426,40 +2693,40 @@
         <v>4</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -2467,40 +2734,40 @@
         <v>5</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -2508,37 +2775,37 @@
         <v>6</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -2546,31 +2813,31 @@
         <v>7</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="119">
   <si>
     <t>id</t>
   </si>
@@ -244,6 +244,9 @@
   </si>
   <si>
     <t>Agriculture</t>
+  </si>
+  <si>
+    <t>Irrigation</t>
   </si>
   <si>
     <t>Archery</t>
@@ -1815,7 +1818,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1869,10 +1872,10 @@
         <v>75</v>
       </c>
       <c r="B3">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="C3">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D3" t="s">
         <v>26</v>
@@ -1881,7 +1884,7 @@
         <v>60</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>26</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1889,19 +1892,39 @@
         <v>76</v>
       </c>
       <c r="B4">
+        <v>150</v>
+      </c>
+      <c r="C4">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4">
+        <v>60</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B5">
         <v>400</v>
       </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4">
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5">
         <v>30</v>
       </c>
-      <c r="E4">
+      <c r="E5">
         <v>90</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>75</v>
+      <c r="F5" s="2" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -1928,24 +1951,24 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B2">
         <v>50</v>
@@ -1965,7 +1988,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B3">
         <v>75</v>
@@ -1985,7 +2008,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B4">
         <v>200</v>
@@ -2005,7 +2028,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B5">
         <v>100</v>
@@ -2025,7 +2048,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B6">
         <v>150</v>
@@ -2059,15 +2082,15 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -2075,7 +2098,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B3">
         <v>8</v>
@@ -2083,7 +2106,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B4">
         <v>0.5</v>
@@ -2091,7 +2114,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B5">
         <v>20</v>
@@ -2099,7 +2122,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -2107,7 +2130,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B7">
         <v>5</v>
@@ -2115,7 +2138,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B8">
         <v>50</v>
@@ -2123,7 +2146,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B9">
         <v>8</v>
@@ -2131,7 +2154,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -2139,7 +2162,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B11">
         <v>1.25</v>
@@ -2147,7 +2170,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2155,7 +2178,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2163,7 +2186,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2171,7 +2194,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B15">
         <v>5</v>
@@ -2179,7 +2202,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B16">
         <v>1.45</v>
@@ -2187,7 +2210,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -2195,15 +2218,15 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -2211,7 +2234,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B20">
         <v>4</v>
@@ -2219,7 +2242,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -2227,7 +2250,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B22">
         <v>3</v>
@@ -2235,7 +2258,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B23">
         <v>10</v>
@@ -2243,7 +2266,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B24">
         <v>3</v>
@@ -2310,28 +2333,28 @@
         <v>-6</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -2339,34 +2362,34 @@
         <v>-5</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -2374,37 +2397,37 @@
         <v>-4</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -2412,40 +2435,40 @@
         <v>-3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -2453,40 +2476,40 @@
         <v>-2</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
@@ -2494,37 +2517,37 @@
         <v>-1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -2532,37 +2555,37 @@
         <v>0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -2570,37 +2593,37 @@
         <v>1</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -2608,40 +2631,40 @@
         <v>2</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -2649,43 +2672,43 @@
         <v>3</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -2693,40 +2716,40 @@
         <v>4</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -2734,40 +2757,40 @@
         <v>5</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -2775,37 +2798,37 @@
         <v>6</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -2813,31 +2836,31 @@
         <v>7</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="120">
   <si>
     <t>id</t>
   </si>
@@ -247,6 +247,9 @@
   </si>
   <si>
     <t>Irrigation</t>
+  </si>
+  <si>
+    <t>Forestry</t>
   </si>
   <si>
     <t>Archery</t>
@@ -1818,7 +1821,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1892,16 +1895,16 @@
         <v>76</v>
       </c>
       <c r="B4">
-        <v>150</v>
-      </c>
-      <c r="C4">
-        <v>20</v>
+        <v>75</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
       </c>
       <c r="D4" t="s">
         <v>26</v>
       </c>
       <c r="E4">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>26</v>
@@ -1912,19 +1915,39 @@
         <v>77</v>
       </c>
       <c r="B5">
+        <v>150</v>
+      </c>
+      <c r="C5">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5">
+        <v>60</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B6">
         <v>400</v>
       </c>
-      <c r="C5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5">
+      <c r="C6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6">
         <v>30</v>
       </c>
-      <c r="E5">
+      <c r="E6">
         <v>90</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>76</v>
+      <c r="F6" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -1951,24 +1974,24 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B2">
         <v>50</v>
@@ -1988,7 +2011,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B3">
         <v>75</v>
@@ -2008,7 +2031,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B4">
         <v>200</v>
@@ -2028,7 +2051,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B5">
         <v>100</v>
@@ -2048,7 +2071,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B6">
         <v>150</v>
@@ -2082,15 +2105,15 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -2098,7 +2121,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B3">
         <v>8</v>
@@ -2106,7 +2129,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B4">
         <v>0.5</v>
@@ -2114,7 +2137,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B5">
         <v>20</v>
@@ -2122,7 +2145,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -2130,7 +2153,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B7">
         <v>5</v>
@@ -2138,7 +2161,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B8">
         <v>50</v>
@@ -2146,7 +2169,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B9">
         <v>8</v>
@@ -2154,7 +2177,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -2162,7 +2185,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B11">
         <v>1.25</v>
@@ -2170,7 +2193,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2178,7 +2201,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2186,7 +2209,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2194,7 +2217,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B15">
         <v>5</v>
@@ -2202,7 +2225,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B16">
         <v>1.45</v>
@@ -2210,7 +2233,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -2218,15 +2241,15 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -2234,7 +2257,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B20">
         <v>4</v>
@@ -2242,7 +2265,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -2250,7 +2273,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B22">
         <v>3</v>
@@ -2258,7 +2281,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B23">
         <v>10</v>
@@ -2266,7 +2289,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B24">
         <v>3</v>
@@ -2333,28 +2356,28 @@
         <v>-6</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -2362,34 +2385,34 @@
         <v>-5</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -2397,37 +2420,37 @@
         <v>-4</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -2435,40 +2458,40 @@
         <v>-3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -2476,40 +2499,40 @@
         <v>-2</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
@@ -2517,37 +2540,37 @@
         <v>-1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -2555,37 +2578,37 @@
         <v>0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -2593,37 +2616,37 @@
         <v>1</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -2631,40 +2654,40 @@
         <v>2</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -2672,43 +2695,43 @@
         <v>3</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -2716,40 +2739,40 @@
         <v>4</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -2757,40 +2780,40 @@
         <v>5</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -2798,37 +2821,37 @@
         <v>6</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -2836,31 +2859,31 @@
         <v>7</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -246,10 +246,10 @@
     <t>Agriculture</t>
   </si>
   <si>
+    <t>Forestry</t>
+  </si>
+  <si>
     <t>Irrigation</t>
-  </si>
-  <si>
-    <t>Forestry</t>
   </si>
   <si>
     <t>Archery</t>
@@ -1867,12 +1867,12 @@
         <v>45</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>26</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B3">
         <v>250</v>
@@ -1892,7 +1892,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B4">
         <v>75</v>
@@ -1927,7 +1927,7 @@
         <v>60</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>26</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="121">
   <si>
     <t>id</t>
   </si>
@@ -175,6 +175,9 @@
   </si>
   <si>
     <t>recovery_seconds</t>
+  </si>
+  <si>
+    <t>respawn_seconds</t>
   </si>
   <si>
     <t>Forest</t>
@@ -1416,7 +1419,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1424,9 +1427,10 @@
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>47</v>
       </c>
@@ -1442,10 +1446,13 @@
       <c r="E1" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -1459,10 +1466,13 @@
       <c r="E2">
         <v>90</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -1476,10 +1486,13 @@
       <c r="E3">
         <v>60</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -1493,10 +1506,13 @@
       <c r="E4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -1509,6 +1525,9 @@
       </c>
       <c r="E5">
         <v>0</v>
+      </c>
+      <c r="F5">
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -1532,27 +1551,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B2" t="s">
         <v>26</v>
@@ -1575,7 +1594,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
@@ -1598,7 +1617,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
@@ -1621,7 +1640,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
@@ -1633,7 +1652,7 @@
         <v>26</v>
       </c>
       <c r="E5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -1644,7 +1663,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
@@ -1656,7 +1675,7 @@
         <v>26</v>
       </c>
       <c r="E6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F6">
         <v>3</v>
@@ -1667,7 +1686,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
@@ -1690,7 +1709,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
@@ -1727,10 +1746,10 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1835,24 +1854,24 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B2">
         <v>100</v>
@@ -1867,12 +1886,12 @@
         <v>45</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B3">
         <v>250</v>
@@ -1887,12 +1906,12 @@
         <v>60</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B4">
         <v>75</v>
@@ -1912,7 +1931,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B5">
         <v>150</v>
@@ -1927,12 +1946,12 @@
         <v>60</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B6">
         <v>400</v>
@@ -1947,7 +1966,7 @@
         <v>90</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -1974,24 +1993,24 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B2">
         <v>50</v>
@@ -2011,7 +2030,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B3">
         <v>75</v>
@@ -2031,7 +2050,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B4">
         <v>200</v>
@@ -2051,7 +2070,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B5">
         <v>100</v>
@@ -2071,7 +2090,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B6">
         <v>150</v>
@@ -2105,15 +2124,15 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -2121,7 +2140,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B3">
         <v>8</v>
@@ -2129,7 +2148,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B4">
         <v>0.5</v>
@@ -2137,7 +2156,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B5">
         <v>20</v>
@@ -2145,7 +2164,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -2153,7 +2172,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B7">
         <v>5</v>
@@ -2161,7 +2180,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B8">
         <v>50</v>
@@ -2169,7 +2188,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B9">
         <v>8</v>
@@ -2177,7 +2196,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -2185,7 +2204,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B11">
         <v>1.25</v>
@@ -2193,7 +2212,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2201,7 +2220,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2209,7 +2228,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2217,7 +2236,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B15">
         <v>5</v>
@@ -2225,7 +2244,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B16">
         <v>1.45</v>
@@ -2233,7 +2252,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -2241,15 +2260,15 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -2257,7 +2276,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B20">
         <v>4</v>
@@ -2265,7 +2284,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -2273,7 +2292,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B22">
         <v>3</v>
@@ -2281,7 +2300,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B23">
         <v>10</v>
@@ -2289,7 +2308,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B24">
         <v>3</v>
@@ -2356,28 +2375,28 @@
         <v>-6</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -2385,34 +2404,34 @@
         <v>-5</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -2420,37 +2439,37 @@
         <v>-4</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -2458,40 +2477,40 @@
         <v>-3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -2499,40 +2518,40 @@
         <v>-2</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
@@ -2540,37 +2559,37 @@
         <v>-1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -2578,37 +2597,37 @@
         <v>0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -2616,37 +2635,37 @@
         <v>1</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -2654,40 +2673,40 @@
         <v>2</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -2695,43 +2714,43 @@
         <v>3</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -2739,40 +2758,40 @@
         <v>4</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -2780,40 +2799,40 @@
         <v>5</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -2821,37 +2840,37 @@
         <v>6</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -2859,31 +2878,31 @@
         <v>7</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="122">
   <si>
     <t>id</t>
   </si>
@@ -253,6 +253,9 @@
   </si>
   <si>
     <t>Irrigation</t>
+  </si>
+  <si>
+    <t>Commerce</t>
   </si>
   <si>
     <t>Archery</t>
@@ -1840,7 +1843,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1936,14 +1939,14 @@
       <c r="B5">
         <v>150</v>
       </c>
-      <c r="C5">
-        <v>20</v>
+      <c r="C5" t="s">
+        <v>26</v>
       </c>
       <c r="D5" t="s">
         <v>26</v>
       </c>
       <c r="E5">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>76</v>
@@ -1954,19 +1957,39 @@
         <v>79</v>
       </c>
       <c r="B6">
+        <v>150</v>
+      </c>
+      <c r="C6">
+        <v>20</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6">
+        <v>60</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7">
         <v>400</v>
       </c>
-      <c r="C6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6">
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7">
         <v>30</v>
       </c>
-      <c r="E6">
+      <c r="E7">
         <v>90</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>78</v>
+      <c r="F7" s="2" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -1993,24 +2016,24 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B2">
         <v>50</v>
@@ -2025,12 +2048,12 @@
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>26</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B3">
         <v>75</v>
@@ -2045,12 +2068,12 @@
         <v>0.05</v>
       </c>
       <c r="F3" t="s">
-        <v>26</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B4">
         <v>200</v>
@@ -2065,12 +2088,12 @@
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>26</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B5">
         <v>100</v>
@@ -2085,12 +2108,12 @@
         <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>26</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B6">
         <v>150</v>
@@ -2105,7 +2128,7 @@
         <v>0.5</v>
       </c>
       <c r="F6" t="s">
-        <v>26</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -2124,15 +2147,15 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -2140,7 +2163,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B3">
         <v>8</v>
@@ -2148,7 +2171,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B4">
         <v>0.5</v>
@@ -2156,7 +2179,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B5">
         <v>20</v>
@@ -2164,7 +2187,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -2172,7 +2195,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B7">
         <v>5</v>
@@ -2180,7 +2203,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B8">
         <v>50</v>
@@ -2188,7 +2211,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B9">
         <v>8</v>
@@ -2196,7 +2219,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -2204,7 +2227,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B11">
         <v>1.25</v>
@@ -2212,7 +2235,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2220,7 +2243,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2228,7 +2251,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2236,7 +2259,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B15">
         <v>5</v>
@@ -2244,7 +2267,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B16">
         <v>1.45</v>
@@ -2252,7 +2275,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -2260,15 +2283,15 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -2276,7 +2299,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B20">
         <v>4</v>
@@ -2284,7 +2307,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -2292,7 +2315,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B22">
         <v>3</v>
@@ -2300,7 +2323,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B23">
         <v>10</v>
@@ -2308,7 +2331,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B24">
         <v>3</v>
@@ -2375,28 +2398,28 @@
         <v>-6</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -2404,34 +2427,34 @@
         <v>-5</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -2439,37 +2462,37 @@
         <v>-4</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -2477,40 +2500,40 @@
         <v>-3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -2518,40 +2541,40 @@
         <v>-2</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
@@ -2559,37 +2582,37 @@
         <v>-1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -2597,37 +2620,37 @@
         <v>0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -2635,37 +2658,37 @@
         <v>1</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -2673,40 +2696,40 @@
         <v>2</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -2714,43 +2737,43 @@
         <v>3</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -2758,40 +2781,40 @@
         <v>4</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -2799,40 +2822,40 @@
         <v>5</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -2840,37 +2863,37 @@
         <v>6</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -2878,31 +2901,31 @@
         <v>7</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -1,25 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <workbookPr/>
+  <bookViews>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Districts" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Units" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Harvest" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="Currencies" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="FogRings" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="Technologies" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="Upgrades" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="Settings" state="visible" r:id="rId11"/>
-    <sheet sheetId="9" name="Map" state="visible" r:id="rId12"/>
+    <sheet name="Districts" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Units" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Harvest" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Currencies" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="FogRings" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Technologies" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Upgrades" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Settings" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Map" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="127">
   <si>
     <t>id</t>
   </si>
@@ -102,12 +107,24 @@
     <t/>
   </si>
   <si>
+    <t>1.2</t>
+  </si>
+  <si>
+    <t>1.15</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
     <t>Housing</t>
   </si>
   <si>
     <t>2,4</t>
   </si>
   <si>
+    <t>1.25</t>
+  </si>
+  <si>
     <t>Farm</t>
   </si>
   <si>
@@ -136,6 +153,9 @@
   </si>
   <si>
     <t>1,2,3</t>
+  </si>
+  <si>
+    <t>1.45</t>
   </si>
   <si>
     <t>power</t>
@@ -390,14 +410,13 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2">
     <font>
+      <sz val="11.000000"/>
       <color theme="1"/>
-      <family val="2"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
@@ -413,92 +432,28 @@
   </fills>
   <borders count="1">
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF6FA84F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF3D6F9E"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF9AA34F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFC9B26A"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFDFE7EC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF8B9A94"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF2E6B2E"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF7A4FA8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF8A5A34"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -511,7 +466,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -557,13 +512,13 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Thai" typeface="Angsana New"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
@@ -586,19 +541,18 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Thai" typeface="Cordia New"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
@@ -621,7 +575,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -656,16 +609,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -787,9 +744,226 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
   <a:objectDefaults>
     <a:spDef>
-      <a:spPr/>
+      <a:spPr bwMode="auto"/>
       <a:bodyPr/>
       <a:lstStyle/>
       <a:style>
@@ -808,7 +982,7 @@
       </a:style>
     </a:spDef>
     <a:lnDef>
-      <a:spPr/>
+      <a:spPr bwMode="auto"/>
       <a:bodyPr/>
       <a:lstStyle/>
       <a:style>
@@ -827,36 +1001,34 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y6"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="21" customWidth="1"/>
-    <col min="6" max="6" width="19" customWidth="1"/>
-    <col min="7" max="7" width="21" customWidth="1"/>
-    <col min="8" max="8" width="23" customWidth="1"/>
-    <col min="9" max="9" width="30" customWidth="1"/>
-    <col min="10" max="10" width="28" customWidth="1"/>
-    <col min="11" max="11" width="35" customWidth="1"/>
-    <col min="12" max="14" width="17" customWidth="1"/>
-    <col min="15" max="15" width="23" customWidth="1"/>
-    <col min="16" max="16" width="31" customWidth="1"/>
-    <col min="17" max="17" width="24" customWidth="1"/>
-    <col min="18" max="19" width="32" customWidth="1"/>
-    <col min="20" max="22" width="19" customWidth="1"/>
-    <col min="23" max="23" width="27" customWidth="1"/>
-    <col min="24" max="24" width="26" customWidth="1"/>
-    <col min="25" max="25" width="31" customWidth="1"/>
+    <col customWidth="1" min="1" max="3" width="10"/>
+    <col customWidth="1" min="4" max="4" width="11"/>
+    <col customWidth="1" min="5" max="5" width="21"/>
+    <col customWidth="1" min="6" max="6" width="19"/>
+    <col customWidth="1" min="7" max="7" width="21"/>
+    <col customWidth="1" min="8" max="8" width="23"/>
+    <col customWidth="1" min="9" max="9" width="30"/>
+    <col customWidth="1" min="10" max="10" width="28"/>
+    <col customWidth="1" min="11" max="11" width="35"/>
+    <col customWidth="1" min="12" max="14" width="17"/>
+    <col customWidth="1" min="15" max="15" width="23"/>
+    <col customWidth="1" min="16" max="16" width="31"/>
+    <col customWidth="1" min="17" max="17" width="24"/>
+    <col customWidth="1" min="18" max="19" width="32"/>
+    <col customWidth="1" min="20" max="22" width="19"/>
+    <col customWidth="1" min="23" max="23" width="27"/>
+    <col customWidth="1" min="24" max="24" width="26"/>
+    <col customWidth="1" min="25" max="25" width="31"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -933,7 +1105,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -947,7 +1119,7 @@
         <v>2</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -979,20 +1151,17 @@
       <c r="O2">
         <v>2</v>
       </c>
-      <c r="P2">
-        <v>1.2</v>
+      <c r="P2" t="s">
+        <v>27</v>
       </c>
       <c r="Q2">
         <v>0</v>
       </c>
-      <c r="R2">
-        <v>1.2</v>
-      </c>
-      <c r="S2">
-        <v>1.15</v>
-      </c>
-      <c r="T2">
-        <v>200</v>
+      <c r="R2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S2" t="s">
+        <v>28</v>
       </c>
       <c r="U2">
         <v>25</v>
@@ -1000,19 +1169,19 @@
       <c r="V2" t="s">
         <v>26</v>
       </c>
-      <c r="W2">
-        <v>1.5</v>
+      <c r="W2" t="s">
+        <v>29</v>
       </c>
       <c r="X2">
         <v>0</v>
       </c>
-      <c r="Y2">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -1036,7 +1205,7 @@
         <v>26</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>26</v>
@@ -1044,29 +1213,26 @@
       <c r="K3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="L3">
-        <v>75</v>
-      </c>
       <c r="M3">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="N3" t="s">
         <v>26</v>
       </c>
-      <c r="O3">
-        <v>0.75</v>
-      </c>
-      <c r="P3">
-        <v>1.25</v>
+      <c r="O3" t="s">
+        <v>29</v>
+      </c>
+      <c r="P3" t="s">
+        <v>32</v>
       </c>
       <c r="Q3">
         <v>20</v>
       </c>
-      <c r="R3">
-        <v>1.2</v>
-      </c>
-      <c r="S3">
-        <v>1.15</v>
+      <c r="R3" t="s">
+        <v>27</v>
+      </c>
+      <c r="S3" t="s">
+        <v>28</v>
       </c>
       <c r="T3" t="s">
         <v>26</v>
@@ -1077,19 +1243,19 @@
       <c r="V3" t="s">
         <v>26</v>
       </c>
-      <c r="W3">
-        <v>1.5</v>
+      <c r="W3" t="s">
+        <v>29</v>
       </c>
       <c r="X3">
         <v>0</v>
       </c>
-      <c r="Y3">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -1110,19 +1276,16 @@
         <v>2</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="L4">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="M4">
         <v>10</v>
@@ -1133,20 +1296,17 @@
       <c r="O4">
         <v>2</v>
       </c>
-      <c r="P4">
-        <v>1.5</v>
+      <c r="P4" t="s">
+        <v>29</v>
       </c>
       <c r="Q4">
         <v>20</v>
       </c>
-      <c r="R4">
-        <v>1.2</v>
-      </c>
-      <c r="S4">
-        <v>1.15</v>
-      </c>
-      <c r="T4">
-        <v>300</v>
+      <c r="R4" t="s">
+        <v>27</v>
+      </c>
+      <c r="S4" t="s">
+        <v>28</v>
       </c>
       <c r="U4">
         <v>50</v>
@@ -1154,19 +1314,19 @@
       <c r="V4" t="s">
         <v>26</v>
       </c>
-      <c r="W4">
-        <v>1.5</v>
+      <c r="W4" t="s">
+        <v>29</v>
       </c>
       <c r="X4">
         <v>30</v>
       </c>
-      <c r="Y4">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -1190,15 +1350,12 @@
         <v>26</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L5" t="s">
         <v>26</v>
       </c>
       <c r="M5">
@@ -1210,17 +1367,17 @@
       <c r="O5">
         <v>2</v>
       </c>
-      <c r="P5">
-        <v>1.2</v>
+      <c r="P5" t="s">
+        <v>27</v>
       </c>
       <c r="Q5">
         <v>10</v>
       </c>
-      <c r="R5">
-        <v>1.2</v>
-      </c>
-      <c r="S5">
-        <v>1.15</v>
+      <c r="R5" t="s">
+        <v>27</v>
+      </c>
+      <c r="S5" t="s">
+        <v>28</v>
       </c>
       <c r="T5" t="s">
         <v>26</v>
@@ -1231,19 +1388,19 @@
       <c r="V5" t="s">
         <v>26</v>
       </c>
-      <c r="W5">
-        <v>1.5</v>
+      <c r="W5" t="s">
+        <v>29</v>
       </c>
       <c r="X5">
         <v>0</v>
       </c>
-      <c r="Y5">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -1264,22 +1421,19 @@
         <v>2</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="L6">
-        <v>50</v>
-      </c>
-      <c r="M6" t="s">
-        <v>26</v>
+        <v>35</v>
+      </c>
+      <c r="M6">
+        <v>20</v>
       </c>
       <c r="N6" t="s">
         <v>26</v>
@@ -1287,20 +1441,17 @@
       <c r="O6">
         <v>4</v>
       </c>
-      <c r="P6">
-        <v>1.45</v>
+      <c r="P6" t="s">
+        <v>43</v>
       </c>
       <c r="Q6">
         <v>20</v>
       </c>
-      <c r="R6">
-        <v>1.2</v>
-      </c>
-      <c r="S6">
-        <v>1.15</v>
-      </c>
-      <c r="T6">
-        <v>300</v>
+      <c r="R6" t="s">
+        <v>27</v>
+      </c>
+      <c r="S6" t="s">
+        <v>28</v>
       </c>
       <c r="U6" t="s">
         <v>26</v>
@@ -1308,55 +1459,56 @@
       <c r="V6" t="s">
         <v>26</v>
       </c>
-      <c r="W6">
-        <v>1.5</v>
+      <c r="W6" t="s">
+        <v>29</v>
       </c>
       <c r="X6">
         <v>30</v>
       </c>
-      <c r="Y6">
-        <v>1.5</v>
+      <c r="Y6" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="10" customWidth="1"/>
-    <col min="3" max="5" width="19" customWidth="1"/>
-    <col min="6" max="6" width="24" customWidth="1"/>
+    <col customWidth="1" min="1" max="2" width="10"/>
+    <col customWidth="1" min="3" max="5" width="19"/>
+    <col customWidth="1" min="6" max="6" width="24"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -1374,9 +1526,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B3">
         <v>3</v>
@@ -1394,9 +1546,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B4">
         <v>5</v>
@@ -1415,47 +1567,48 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="17" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="10"/>
+    <col customWidth="1" min="2" max="2" width="15"/>
+    <col customWidth="1" min="3" max="3" width="18"/>
+    <col customWidth="1" min="4" max="4" width="17"/>
+    <col customWidth="1" min="5" max="5" width="18"/>
+    <col customWidth="1" min="6" max="6" width="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -1473,9 +1626,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -1493,9 +1646,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -1513,9 +1666,9 @@
         <v>120</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -1534,47 +1687,48 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="6" max="7" width="12" customWidth="1"/>
+    <col customWidth="1" min="1" max="4" width="10"/>
+    <col customWidth="1" min="5" max="5" width="11"/>
+    <col customWidth="1" min="6" max="7" width="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B2" t="s">
         <v>26</v>
@@ -1595,9 +1749,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
@@ -1618,9 +1772,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
@@ -1638,12 +1792,12 @@
         <v>26</v>
       </c>
       <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
@@ -1655,7 +1809,7 @@
         <v>26</v>
       </c>
       <c r="E5" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -1664,9 +1818,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
@@ -1678,7 +1832,7 @@
         <v>26</v>
       </c>
       <c r="E6" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F6">
         <v>3</v>
@@ -1687,9 +1841,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
@@ -1710,9 +1864,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
@@ -1734,28 +1888,29 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="10" customWidth="1"/>
+    <col customWidth="1" min="1" max="2" width="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1763,7 +1918,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1771,7 +1926,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1779,7 +1934,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1787,7 +1942,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1795,7 +1950,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1803,7 +1958,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1811,7 +1966,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1819,7 +1974,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1827,7 +1982,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1836,45 +1991,46 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="10" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="10"/>
+    <col customWidth="1" min="2" max="4" width="11"/>
+    <col customWidth="1" min="5" max="5" width="18"/>
+    <col customWidth="1" min="6" max="6" width="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B2">
         <v>100</v>
@@ -1889,12 +2045,12 @@
         <v>45</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B3">
         <v>250</v>
@@ -1909,12 +2065,12 @@
         <v>60</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B4">
         <v>75</v>
@@ -1932,9 +2088,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B5">
         <v>150</v>
@@ -1949,12 +2105,12 @@
         <v>45</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B6">
         <v>150</v>
@@ -1969,12 +2125,12 @@
         <v>60</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B7">
         <v>400</v>
@@ -1989,57 +2145,58 @@
         <v>90</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="15" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="10"/>
+    <col customWidth="1" min="2" max="2" width="11"/>
+    <col customWidth="1" min="3" max="3" width="13"/>
+    <col customWidth="1" min="4" max="4" width="11"/>
+    <col customWidth="1" min="5" max="5" width="18"/>
+    <col customWidth="1" min="6" max="6" width="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B2">
         <v>50</v>
       </c>
       <c r="C2">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="D2">
         <v>5</v>
@@ -2048,12 +2205,12 @@
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B3">
         <v>75</v>
@@ -2065,15 +2222,15 @@
         <v>5</v>
       </c>
       <c r="E3">
-        <v>0.05</v>
+        <v>0.050000000000000003</v>
       </c>
       <c r="F3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B4">
         <v>200</v>
@@ -2088,12 +2245,12 @@
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B5">
         <v>100</v>
@@ -2108,12 +2265,12 @@
         <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B6">
         <v>150</v>
@@ -2128,231 +2285,233 @@
         <v>0.5</v>
       </c>
       <c r="F6" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B24"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="10" customWidth="1"/>
+    <col customWidth="1" min="1" max="2" width="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B3">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B4">
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B5">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B7">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B8">
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="B11">
         <v>1.25</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B13">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14">
       <c r="A14" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B14">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="A15" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B15">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="A16" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B16">
         <v>1.45</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="A17" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18">
       <c r="A18" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20">
       <c r="A20" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B20">
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21">
       <c r="A21" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22">
       <c r="A22" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="B22">
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23">
       <c r="A23" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B23">
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24">
       <c r="A24" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B24">
         <v>3</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N15"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="14" width="3.5" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="4"/>
+    <col customWidth="1" min="2" max="14" width="3.5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1">
       <c r="B1" s="1">
         <v>-6</v>
       </c>
@@ -2393,572 +2552,677 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" s="1">
         <v>-6</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="1">
         <v>-5</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="1">
         <v>-4</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" s="1">
         <v>-3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="1">
         <v>-2</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" s="1">
         <v>-1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" s="1">
         <v>0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" s="1">
         <v>1</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" s="1">
         <v>2</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" s="1">
         <v>3</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" s="1">
         <v>4</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" s="1">
         <v>5</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" s="1">
         <v>6</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15" s="1">
         <v>7</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:N15">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>"g"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
-      <formula>"w"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
-      <formula>"p"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
-      <formula>"d"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
-      <formula>"s"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
-      <formula>"u"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
-      <formula>"T"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
-      <formula>"B"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
+  <headerFooter/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="1" operator="equal" id="{16C8D9B6-CF2A-4A6C-8EE4-CCF9A3479663}">
+            <xm:f>"g"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FF6FA84F"/>
+                  <bgColor rgb="FF6FA84F"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>B2:N15</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="2" operator="equal" id="{8CC1138E-BCAD-4248-A383-39475CC18EB9}">
+            <xm:f>"w"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FF3D6F9E"/>
+                  <bgColor rgb="FF3D6F9E"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>B2:N15</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="3" operator="equal" id="{DAFEC3C3-85A8-49A0-AD5C-CE0E0C146893}">
+            <xm:f>"p"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FF9AA34F"/>
+                  <bgColor rgb="FF9AA34F"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>B2:N15</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="4" operator="equal" id="{5D649E4C-0BEC-445E-80C1-9BE54A75EE04}">
+            <xm:f>"d"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC9B26A"/>
+                  <bgColor rgb="FFC9B26A"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>B2:N15</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="5" operator="equal" id="{209E3CFF-3507-46CC-AB61-D9B683DA197F}">
+            <xm:f>"s"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFDFE7EC"/>
+                  <bgColor rgb="FFDFE7EC"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>B2:N15</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="6" operator="equal" id="{E7661A51-F42E-40EB-B433-5790487E673B}">
+            <xm:f>"u"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FF8B9A94"/>
+                  <bgColor rgb="FF8B9A94"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>B2:N15</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="7" operator="equal" id="{8830003C-4B33-4B49-83E6-BABC985F6492}">
+            <xm:f>"T"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FF2E6B2E"/>
+                  <bgColor rgb="FF2E6B2E"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>B2:N15</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="8" operator="equal" id="{AD295AD1-2AA6-4568-8C38-7BB71E052113}">
+            <xm:f>"B"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FF7A4FA8"/>
+                  <bgColor rgb="FF7A4FA8"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>B2:N15</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="9" operator="equal" id="{F17E4B40-8EE9-479A-94A5-AC0E2A199115}">
+            <xm:f>"A"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FF8A5A34"/>
+                  <bgColor rgb="FF8A5A34"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>B2:N15</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="Districts" sheetId="1" state="visible" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="125">
   <si>
     <t>id</t>
   </si>
@@ -107,24 +107,12 @@
     <t/>
   </si>
   <si>
-    <t>1.2</t>
-  </si>
-  <si>
-    <t>1.15</t>
-  </si>
-  <si>
-    <t>1.5</t>
-  </si>
-  <si>
     <t>Housing</t>
   </si>
   <si>
     <t>2,4</t>
   </si>
   <si>
-    <t>1.25</t>
-  </si>
-  <si>
     <t>Farm</t>
   </si>
   <si>
@@ -155,7 +143,10 @@
     <t>1,2,3</t>
   </si>
   <si>
-    <t>1.45</t>
+    <t>Market</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
   <si>
     <t>power</t>
@@ -212,6 +203,9 @@
     <t>Meat</t>
   </si>
   <si>
+    <t>Taxes</t>
+  </si>
+  <si>
     <t>cap</t>
   </si>
   <si>
@@ -278,6 +272,9 @@
     <t>Commerce</t>
   </si>
   <si>
+    <t>Militia</t>
+  </si>
+  <si>
     <t>Archery</t>
   </si>
   <si>
@@ -332,10 +329,7 @@
     <t>training.tap_boost_seconds</t>
   </si>
   <si>
-    <t>market.sell_interval_seconds</t>
-  </si>
-  <si>
-    <t>market.capacity</t>
+    <t>taxes.gold_per_population_per_minute</t>
   </si>
   <si>
     <t>offline_cap_hours</t>
@@ -442,10 +436,13 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1151,17 +1148,20 @@
       <c r="O2">
         <v>2</v>
       </c>
-      <c r="P2" t="s">
-        <v>27</v>
+      <c r="P2">
+        <v>1.2</v>
       </c>
       <c r="Q2">
         <v>0</v>
       </c>
-      <c r="R2" t="s">
-        <v>27</v>
-      </c>
-      <c r="S2" t="s">
-        <v>28</v>
+      <c r="R2">
+        <v>1.2</v>
+      </c>
+      <c r="S2">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="T2" t="s">
+        <v>26</v>
       </c>
       <c r="U2">
         <v>25</v>
@@ -1169,19 +1169,19 @@
       <c r="V2" t="s">
         <v>26</v>
       </c>
-      <c r="W2" t="s">
-        <v>29</v>
+      <c r="W2">
+        <v>1.5</v>
       </c>
       <c r="X2">
         <v>0</v>
       </c>
-      <c r="Y2" t="s">
-        <v>29</v>
+      <c r="Y2">
+        <v>1.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -1205,12 +1205,15 @@
         <v>26</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L3" t="s">
         <v>26</v>
       </c>
       <c r="M3">
@@ -1219,20 +1222,20 @@
       <c r="N3" t="s">
         <v>26</v>
       </c>
-      <c r="O3" t="s">
-        <v>29</v>
-      </c>
-      <c r="P3" t="s">
-        <v>32</v>
+      <c r="O3">
+        <v>1.5</v>
+      </c>
+      <c r="P3">
+        <v>1.25</v>
       </c>
       <c r="Q3">
         <v>20</v>
       </c>
-      <c r="R3" t="s">
-        <v>27</v>
-      </c>
-      <c r="S3" t="s">
-        <v>28</v>
+      <c r="R3">
+        <v>1.2</v>
+      </c>
+      <c r="S3">
+        <v>1.1499999999999999</v>
       </c>
       <c r="T3" t="s">
         <v>26</v>
@@ -1243,19 +1246,19 @@
       <c r="V3" t="s">
         <v>26</v>
       </c>
-      <c r="W3" t="s">
-        <v>29</v>
+      <c r="W3">
+        <v>1.5</v>
       </c>
       <c r="X3">
         <v>0</v>
       </c>
-      <c r="Y3" t="s">
-        <v>29</v>
+      <c r="Y3">
+        <v>1.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -1276,16 +1279,19 @@
         <v>2</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
+      </c>
+      <c r="L4" t="s">
+        <v>26</v>
       </c>
       <c r="M4">
         <v>10</v>
@@ -1296,17 +1302,20 @@
       <c r="O4">
         <v>2</v>
       </c>
-      <c r="P4" t="s">
-        <v>29</v>
+      <c r="P4">
+        <v>1.5</v>
       </c>
       <c r="Q4">
         <v>20</v>
       </c>
-      <c r="R4" t="s">
-        <v>27</v>
-      </c>
-      <c r="S4" t="s">
-        <v>28</v>
+      <c r="R4">
+        <v>1.2</v>
+      </c>
+      <c r="S4">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="T4" t="s">
+        <v>26</v>
       </c>
       <c r="U4">
         <v>50</v>
@@ -1314,19 +1323,19 @@
       <c r="V4" t="s">
         <v>26</v>
       </c>
-      <c r="W4" t="s">
-        <v>29</v>
+      <c r="W4">
+        <v>1.5</v>
       </c>
       <c r="X4">
         <v>30</v>
       </c>
-      <c r="Y4" t="s">
-        <v>29</v>
+      <c r="Y4">
+        <v>1.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -1350,12 +1359,15 @@
         <v>26</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L5" t="s">
         <v>26</v>
       </c>
       <c r="M5">
@@ -1367,17 +1379,17 @@
       <c r="O5">
         <v>2</v>
       </c>
-      <c r="P5" t="s">
-        <v>27</v>
+      <c r="P5">
+        <v>1.2</v>
       </c>
       <c r="Q5">
         <v>10</v>
       </c>
-      <c r="R5" t="s">
-        <v>27</v>
-      </c>
-      <c r="S5" t="s">
-        <v>28</v>
+      <c r="R5">
+        <v>1.2</v>
+      </c>
+      <c r="S5">
+        <v>1.1499999999999999</v>
       </c>
       <c r="T5" t="s">
         <v>26</v>
@@ -1388,19 +1400,19 @@
       <c r="V5" t="s">
         <v>26</v>
       </c>
-      <c r="W5" t="s">
-        <v>29</v>
+      <c r="W5">
+        <v>1.5</v>
       </c>
       <c r="X5">
         <v>0</v>
       </c>
-      <c r="Y5" t="s">
-        <v>29</v>
+      <c r="Y5">
+        <v>1.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -1421,16 +1433,19 @@
         <v>2</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="L6" t="s">
+        <v>26</v>
       </c>
       <c r="M6">
         <v>20</v>
@@ -1441,17 +1456,20 @@
       <c r="O6">
         <v>4</v>
       </c>
-      <c r="P6" t="s">
-        <v>43</v>
+      <c r="P6">
+        <v>1.45</v>
       </c>
       <c r="Q6">
         <v>20</v>
       </c>
-      <c r="R6" t="s">
-        <v>27</v>
-      </c>
-      <c r="S6" t="s">
-        <v>28</v>
+      <c r="R6">
+        <v>1.2</v>
+      </c>
+      <c r="S6">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="T6" t="s">
+        <v>26</v>
       </c>
       <c r="U6" t="s">
         <v>26</v>
@@ -1459,14 +1477,91 @@
       <c r="V6" t="s">
         <v>26</v>
       </c>
-      <c r="W6" t="s">
-        <v>29</v>
+      <c r="W6">
+        <v>1.5</v>
       </c>
       <c r="X6">
         <v>30</v>
       </c>
-      <c r="Y6" t="s">
-        <v>29</v>
+      <c r="Y6">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M7">
+        <v>40</v>
+      </c>
+      <c r="N7" t="s">
+        <v>26</v>
+      </c>
+      <c r="O7">
+        <v>2</v>
+      </c>
+      <c r="P7">
+        <v>1.2</v>
+      </c>
+      <c r="Q7">
+        <v>30</v>
+      </c>
+      <c r="R7">
+        <v>1.2</v>
+      </c>
+      <c r="S7">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="T7" t="s">
+        <v>26</v>
+      </c>
+      <c r="U7" t="s">
+        <v>26</v>
+      </c>
+      <c r="V7" t="s">
+        <v>26</v>
+      </c>
+      <c r="W7">
+        <v>1.5</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>
@@ -1491,24 +1586,24 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -1528,7 +1623,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B3">
         <v>3</v>
@@ -1548,7 +1643,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B4">
         <v>5</v>
@@ -1588,27 +1683,27 @@
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -1628,7 +1723,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -1648,7 +1743,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -1668,7 +1763,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -1684,6 +1779,26 @@
       </c>
       <c r="F5">
         <v>180</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>60</v>
+      </c>
+      <c r="F6" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1696,7 +1811,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" min="1" max="4" width="10"/>
     <col customWidth="1" min="5" max="5" width="11"/>
@@ -1708,27 +1823,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B2" t="s">
         <v>26</v>
@@ -1751,7 +1866,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
@@ -1774,7 +1889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
@@ -1797,7 +1912,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
@@ -1809,7 +1924,7 @@
         <v>26</v>
       </c>
       <c r="E5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -1820,7 +1935,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
@@ -1832,7 +1947,7 @@
         <v>26</v>
       </c>
       <c r="E6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F6">
         <v>3</v>
@@ -1843,7 +1958,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
@@ -1866,7 +1981,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
@@ -1904,10 +2019,10 @@
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2">
@@ -2013,24 +2128,24 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B2">
         <v>100</v>
@@ -2045,12 +2160,12 @@
         <v>45</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B3">
         <v>250</v>
@@ -2065,12 +2180,12 @@
         <v>60</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B4">
         <v>75</v>
@@ -2090,7 +2205,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B5">
         <v>150</v>
@@ -2105,47 +2220,67 @@
         <v>45</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B6">
-        <v>150</v>
-      </c>
-      <c r="C6">
-        <v>20</v>
+        <v>100</v>
+      </c>
+      <c r="C6" t="s">
+        <v>26</v>
       </c>
       <c r="D6" t="s">
         <v>26</v>
       </c>
       <c r="E6">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B7">
+        <v>150</v>
+      </c>
+      <c r="C7">
+        <v>20</v>
+      </c>
+      <c r="D7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7">
+        <v>60</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8">
         <v>400</v>
       </c>
-      <c r="C7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7">
+      <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8">
         <v>30</v>
       </c>
-      <c r="E7">
+      <c r="E8">
         <v>90</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>84</v>
+      <c r="F8" s="2" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -2173,24 +2308,24 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>87</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B2">
         <v>50</v>
@@ -2205,12 +2340,12 @@
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B3">
         <v>75</v>
@@ -2225,12 +2360,12 @@
         <v>0.050000000000000003</v>
       </c>
       <c r="F3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B4">
         <v>200</v>
@@ -2245,12 +2380,12 @@
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B5">
         <v>100</v>
@@ -2262,15 +2397,15 @@
         <v>4</v>
       </c>
       <c r="E5">
-        <v>25</v>
+        <v>0.050000000000000003</v>
       </c>
       <c r="F5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B6">
         <v>150</v>
@@ -2282,10 +2417,10 @@
         <v>5</v>
       </c>
       <c r="E6">
-        <v>0.5</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="F6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -2305,15 +2440,15 @@
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -2321,7 +2456,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B3">
         <v>8</v>
@@ -2329,7 +2464,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B4">
         <v>0.5</v>
@@ -2337,7 +2472,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B5">
         <v>20</v>
@@ -2345,7 +2480,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -2353,47 +2488,47 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B8">
-        <v>50</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B9">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B11">
-        <v>1.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2401,7 +2536,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2409,89 +2544,81 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B15">
-        <v>5</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B16">
-        <v>1.45</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
+        <v>111</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="B17">
-        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
         <v>113</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>114</v>
+      <c r="B18">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B20">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B22">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B23">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>120</v>
-      </c>
-      <c r="B24">
         <v>3</v>
       </c>
     </row>
@@ -2557,28 +2684,28 @@
         <v>-6</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3">
@@ -2586,34 +2713,34 @@
         <v>-5</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4">
@@ -2621,37 +2748,37 @@
         <v>-4</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>123</v>
-      </c>
       <c r="G4" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5">
@@ -2659,40 +2786,40 @@
         <v>-3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6">
@@ -2700,40 +2827,40 @@
         <v>-2</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7">
@@ -2741,37 +2868,37 @@
         <v>-1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8">
@@ -2779,37 +2906,37 @@
         <v>0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9">
@@ -2817,37 +2944,37 @@
         <v>1</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>125</v>
+        <v>120</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>120</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10">
@@ -2855,40 +2982,40 @@
         <v>2</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>123</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11">
@@ -2896,43 +3023,43 @@
         <v>3</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12">
@@ -2940,40 +3067,40 @@
         <v>4</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13">
@@ -2981,40 +3108,40 @@
         <v>5</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
@@ -3022,37 +3149,37 @@
         <v>6</v>
       </c>
       <c r="D14" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="L14" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>123</v>
-      </c>
       <c r="M14" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15">
@@ -3060,31 +3187,31 @@
         <v>7</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -3096,7 +3223,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="1" operator="equal" id="{16C8D9B6-CF2A-4A6C-8EE4-CCF9A3479663}">
+          <x14:cfRule type="cellIs" priority="1" operator="equal" id="{FDFC5291-AB1B-4159-B440-A182D3D9CA07}">
             <xm:f>"g"</xm:f>
             <x14:dxf>
               <fill>
@@ -3110,7 +3237,7 @@
           <xm:sqref>B2:N15</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" operator="equal" id="{8CC1138E-BCAD-4248-A383-39475CC18EB9}">
+          <x14:cfRule type="cellIs" priority="2" operator="equal" id="{9AEC98BE-376C-4FA8-A835-E435EA07736C}">
             <xm:f>"w"</xm:f>
             <x14:dxf>
               <fill>
@@ -3124,7 +3251,7 @@
           <xm:sqref>B2:N15</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" operator="equal" id="{DAFEC3C3-85A8-49A0-AD5C-CE0E0C146893}">
+          <x14:cfRule type="cellIs" priority="3" operator="equal" id="{89A7D72B-9308-40B5-A985-FB297F20CFF6}">
             <xm:f>"p"</xm:f>
             <x14:dxf>
               <fill>
@@ -3138,7 +3265,7 @@
           <xm:sqref>B2:N15</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" operator="equal" id="{5D649E4C-0BEC-445E-80C1-9BE54A75EE04}">
+          <x14:cfRule type="cellIs" priority="4" operator="equal" id="{5F2B5890-5517-48DE-85CE-DF66781C593C}">
             <xm:f>"d"</xm:f>
             <x14:dxf>
               <fill>
@@ -3152,7 +3279,7 @@
           <xm:sqref>B2:N15</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="5" operator="equal" id="{209E3CFF-3507-46CC-AB61-D9B683DA197F}">
+          <x14:cfRule type="cellIs" priority="5" operator="equal" id="{F30623CB-A8BC-4DFD-A032-FCD88C5B54AC}">
             <xm:f>"s"</xm:f>
             <x14:dxf>
               <fill>
@@ -3166,7 +3293,7 @@
           <xm:sqref>B2:N15</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="6" operator="equal" id="{E7661A51-F42E-40EB-B433-5790487E673B}">
+          <x14:cfRule type="cellIs" priority="6" operator="equal" id="{6F2FF608-3D72-4615-B93F-256C23AD0882}">
             <xm:f>"u"</xm:f>
             <x14:dxf>
               <fill>
@@ -3180,7 +3307,7 @@
           <xm:sqref>B2:N15</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="7" operator="equal" id="{8830003C-4B33-4B49-83E6-BABC985F6492}">
+          <x14:cfRule type="cellIs" priority="7" operator="equal" id="{A0C09C4D-E33B-4B20-B53B-7B20501EDACF}">
             <xm:f>"T"</xm:f>
             <x14:dxf>
               <fill>
@@ -3194,7 +3321,7 @@
           <xm:sqref>B2:N15</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="8" operator="equal" id="{AD295AD1-2AA6-4568-8C38-7BB71E052113}">
+          <x14:cfRule type="cellIs" priority="8" operator="equal" id="{E482E04A-9A83-41B2-91F5-92879C64478F}">
             <xm:f>"B"</xm:f>
             <x14:dxf>
               <fill>
@@ -3208,7 +3335,7 @@
           <xm:sqref>B2:N15</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="9" operator="equal" id="{F17E4B40-8EE9-479A-94A5-AC0E2A199115}">
+          <x14:cfRule type="cellIs" priority="9" operator="equal" id="{18938296-ED74-465C-94A1-044872D825E0}">
             <xm:f>"A"</xm:f>
             <x14:dxf>
               <fill>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -1,30 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr/>
-  <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="8"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Districts" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Units" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Harvest" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Currencies" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="FogRings" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Technologies" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Upgrades" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Settings" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Map" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet sheetId="1" name="Districts" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Units" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Harvest" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Currencies" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="FogRings" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Technologies" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="Upgrades" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="Adjacency" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="Settings" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="Map" state="visible" r:id="rId13"/>
   </sheets>
-  <calcPr/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="129">
   <si>
     <t>id</t>
   </si>
@@ -306,6 +302,18 @@
   </si>
   <si>
     <t>TradeRoutes</t>
+  </si>
+  <si>
+    <t>district</t>
+  </si>
+  <si>
+    <t>neighbor</t>
+  </si>
+  <si>
+    <t>gold_per_minute</t>
+  </si>
+  <si>
+    <t>gold_per_tap</t>
   </si>
   <si>
     <t>key</t>
@@ -404,13 +412,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="11.000000"/>
       <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -426,31 +435,92 @@
   </fills>
   <borders count="1">
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1" applyAlignment="1">
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="9">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF6FA84F"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF3D6F9E"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF9AA34F"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFC9B26A"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFDFE7EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF8B9A94"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF2E6B2E"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF7A4FA8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF8A5A34"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -463,7 +533,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -509,13 +579,13 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Angsana New"/>
+        <a:font script="Thai" typeface="Tahoma"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
@@ -538,18 +608,19 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Cordia New"/>
+        <a:font script="Thai" typeface="Tahoma"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
@@ -572,6 +643,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -606,20 +678,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -741,226 +809,9 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
-</file>
-
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle"/>
-        </a:gradFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle"/>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
   <a:objectDefaults>
     <a:spDef>
-      <a:spPr bwMode="auto"/>
+      <a:spPr/>
       <a:bodyPr/>
       <a:lstStyle/>
       <a:style>
@@ -979,7 +830,7 @@
       </a:style>
     </a:spDef>
     <a:lnDef>
-      <a:spPr bwMode="auto"/>
+      <a:spPr/>
       <a:bodyPr/>
       <a:lstStyle/>
       <a:style>
@@ -998,34 +849,36 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Y7"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col customWidth="1" min="1" max="3" width="10"/>
-    <col customWidth="1" min="4" max="4" width="11"/>
-    <col customWidth="1" min="5" max="5" width="21"/>
-    <col customWidth="1" min="6" max="6" width="19"/>
-    <col customWidth="1" min="7" max="7" width="21"/>
-    <col customWidth="1" min="8" max="8" width="23"/>
-    <col customWidth="1" min="9" max="9" width="30"/>
-    <col customWidth="1" min="10" max="10" width="28"/>
-    <col customWidth="1" min="11" max="11" width="35"/>
-    <col customWidth="1" min="12" max="14" width="17"/>
-    <col customWidth="1" min="15" max="15" width="23"/>
-    <col customWidth="1" min="16" max="16" width="31"/>
-    <col customWidth="1" min="17" max="17" width="24"/>
-    <col customWidth="1" min="18" max="19" width="32"/>
-    <col customWidth="1" min="20" max="22" width="19"/>
-    <col customWidth="1" min="23" max="23" width="27"/>
-    <col customWidth="1" min="24" max="24" width="26"/>
-    <col customWidth="1" min="25" max="25" width="31"/>
+    <col min="1" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="21" customWidth="1"/>
+    <col min="6" max="6" width="19" customWidth="1"/>
+    <col min="7" max="7" width="21" customWidth="1"/>
+    <col min="8" max="8" width="23" customWidth="1"/>
+    <col min="9" max="9" width="30" customWidth="1"/>
+    <col min="10" max="10" width="28" customWidth="1"/>
+    <col min="11" max="11" width="35" customWidth="1"/>
+    <col min="12" max="14" width="17" customWidth="1"/>
+    <col min="15" max="15" width="23" customWidth="1"/>
+    <col min="16" max="16" width="31" customWidth="1"/>
+    <col min="17" max="17" width="24" customWidth="1"/>
+    <col min="18" max="19" width="32" customWidth="1"/>
+    <col min="20" max="22" width="19" customWidth="1"/>
+    <col min="23" max="23" width="27" customWidth="1"/>
+    <col min="24" max="24" width="26" customWidth="1"/>
+    <col min="25" max="25" width="31" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1102,7 +955,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -1158,7 +1011,7 @@
         <v>1.2</v>
       </c>
       <c r="S2">
-        <v>1.1499999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="T2" t="s">
         <v>26</v>
@@ -1179,7 +1032,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>27</v>
       </c>
@@ -1235,7 +1088,7 @@
         <v>1.2</v>
       </c>
       <c r="S3">
-        <v>1.1499999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="T3" t="s">
         <v>26</v>
@@ -1256,7 +1109,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>29</v>
       </c>
@@ -1312,7 +1165,7 @@
         <v>1.2</v>
       </c>
       <c r="S4">
-        <v>1.1499999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="T4" t="s">
         <v>26</v>
@@ -1333,7 +1186,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>34</v>
       </c>
@@ -1389,7 +1242,7 @@
         <v>1.2</v>
       </c>
       <c r="S5">
-        <v>1.1499999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="T5" t="s">
         <v>26</v>
@@ -1410,7 +1263,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>36</v>
       </c>
@@ -1466,7 +1319,7 @@
         <v>1.2</v>
       </c>
       <c r="S6">
-        <v>1.1499999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="T6" t="s">
         <v>26</v>
@@ -1487,7 +1340,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>39</v>
       </c>
@@ -1543,7 +1396,7 @@
         <v>1.2</v>
       </c>
       <c r="S7">
-        <v>1.1499999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="T7" t="s">
         <v>26</v>
@@ -1565,23 +1418,642 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:N15"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="14" width="3.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="1">
+        <v>-6</v>
+      </c>
+      <c r="C1" s="1">
+        <v>-5</v>
+      </c>
+      <c r="D1" s="1">
+        <v>-4</v>
+      </c>
+      <c r="E1" s="1">
+        <v>-3</v>
+      </c>
+      <c r="F1" s="1">
+        <v>-2</v>
+      </c>
+      <c r="G1" s="1">
+        <v>-1</v>
+      </c>
+      <c r="H1" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1" s="1">
+        <v>3</v>
+      </c>
+      <c r="L1" s="1">
+        <v>4</v>
+      </c>
+      <c r="M1" s="1">
+        <v>5</v>
+      </c>
+      <c r="N1" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>-6</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>-5</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>-4</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>-3</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>-2</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>-1</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>1</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>2</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>3</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>4</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>5</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>6</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>7</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B2:N15">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"g"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"w"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"p"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+      <formula>"d"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+      <formula>"s"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+      <formula>"u"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
+      <formula>"T"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
+      <formula>"B"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col customWidth="1" min="1" max="2" width="10"/>
-    <col customWidth="1" min="3" max="5" width="19"/>
-    <col customWidth="1" min="6" max="6" width="24"/>
+    <col min="1" max="2" width="10" customWidth="1"/>
+    <col min="3" max="5" width="19" customWidth="1"/>
+    <col min="6" max="6" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1601,7 +2073,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>46</v>
       </c>
@@ -1621,7 +2093,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>47</v>
       </c>
@@ -1641,7 +2113,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>48</v>
       </c>
@@ -1662,26 +2134,25 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="10"/>
-    <col customWidth="1" min="2" max="2" width="15"/>
-    <col customWidth="1" min="3" max="3" width="18"/>
-    <col customWidth="1" min="4" max="4" width="17"/>
-    <col customWidth="1" min="5" max="5" width="18"/>
-    <col customWidth="1" min="6" max="6" width="17"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>49</v>
       </c>
@@ -1701,7 +2172,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>55</v>
       </c>
@@ -1721,7 +2192,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>56</v>
       </c>
@@ -1741,7 +2212,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>57</v>
       </c>
@@ -1761,7 +2232,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>58</v>
       </c>
@@ -1781,7 +2252,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>59</v>
       </c>
@@ -1802,23 +2273,22 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col customWidth="1" min="1" max="4" width="10"/>
-    <col customWidth="1" min="5" max="5" width="11"/>
-    <col customWidth="1" min="6" max="7" width="12"/>
+    <col min="1" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="6" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1841,7 +2311,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>66</v>
       </c>
@@ -1864,7 +2334,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>67</v>
       </c>
@@ -1887,7 +2357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>68</v>
       </c>
@@ -1910,7 +2380,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>57</v>
       </c>
@@ -1933,7 +2403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>58</v>
       </c>
@@ -1956,7 +2426,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>69</v>
       </c>
@@ -1979,7 +2449,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>70</v>
       </c>
@@ -2003,21 +2473,20 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col customWidth="1" min="1" max="2" width="10"/>
+    <col min="1" max="2" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>71</v>
       </c>
@@ -2025,7 +2494,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2033,7 +2502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2041,7 +2510,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2049,7 +2518,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2057,7 +2526,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2065,7 +2534,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2073,7 +2542,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2081,7 +2550,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2089,7 +2558,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2097,7 +2566,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2106,24 +2575,23 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="10"/>
-    <col customWidth="1" min="2" max="4" width="11"/>
-    <col customWidth="1" min="5" max="5" width="18"/>
-    <col customWidth="1" min="6" max="6" width="10"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2143,7 +2611,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>78</v>
       </c>
@@ -2163,7 +2631,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>80</v>
       </c>
@@ -2183,7 +2651,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>79</v>
       </c>
@@ -2203,7 +2671,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>81</v>
       </c>
@@ -2223,7 +2691,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>82</v>
       </c>
@@ -2243,7 +2711,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>83</v>
       </c>
@@ -2263,7 +2731,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>84</v>
       </c>
@@ -2284,26 +2752,25 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="10"/>
-    <col customWidth="1" min="2" max="2" width="11"/>
-    <col customWidth="1" min="3" max="3" width="13"/>
-    <col customWidth="1" min="4" max="4" width="11"/>
-    <col customWidth="1" min="5" max="5" width="18"/>
-    <col customWidth="1" min="6" max="6" width="15"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2323,7 +2790,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>89</v>
       </c>
@@ -2331,7 +2798,7 @@
         <v>50</v>
       </c>
       <c r="C2">
-        <v>2.2000000000000002</v>
+        <v>2.2</v>
       </c>
       <c r="D2">
         <v>5</v>
@@ -2343,7 +2810,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>90</v>
       </c>
@@ -2357,13 +2824,13 @@
         <v>5</v>
       </c>
       <c r="E3">
-        <v>0.050000000000000003</v>
+        <v>0.05</v>
       </c>
       <c r="F3" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>91</v>
       </c>
@@ -2383,7 +2850,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>92</v>
       </c>
@@ -2397,13 +2864,13 @@
         <v>4</v>
       </c>
       <c r="E5">
-        <v>0.050000000000000003</v>
+        <v>0.05</v>
       </c>
       <c r="F5" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>93</v>
       </c>
@@ -2417,939 +2884,256 @@
         <v>5</v>
       </c>
       <c r="E6">
-        <v>0.10000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="F6" t="s">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col customWidth="1" min="1" max="2" width="10"/>
+    <col min="1" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>94</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="2">
+      <c r="C1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B3">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B4">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>99</v>
-      </c>
-      <c r="B5">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>100</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>101</v>
-      </c>
-      <c r="B7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>102</v>
-      </c>
-      <c r="B8">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>103</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>104</v>
-      </c>
-      <c r="B10">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>105</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>106</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>107</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>108</v>
-      </c>
-      <c r="B14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>109</v>
-      </c>
-      <c r="B15">
-        <v>1.45</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>110</v>
-      </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>111</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>113</v>
-      </c>
-      <c r="B18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>114</v>
-      </c>
-      <c r="B19">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>115</v>
-      </c>
-      <c r="B20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>116</v>
-      </c>
-      <c r="B21">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>117</v>
-      </c>
-      <c r="B22">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>118</v>
-      </c>
-      <c r="B23">
-        <v>3</v>
+        <v>27</v>
+      </c>
+      <c r="B2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2">
+        <v>-1</v>
+      </c>
+      <c r="D2">
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B23"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="4"/>
-    <col customWidth="1" min="2" max="14" width="3.5"/>
+    <col min="1" max="2" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="B1" s="1">
-        <v>-6</v>
-      </c>
-      <c r="C1" s="1">
-        <v>-5</v>
-      </c>
-      <c r="D1" s="1">
-        <v>-4</v>
-      </c>
-      <c r="E1" s="1">
-        <v>-3</v>
-      </c>
-      <c r="F1" s="1">
-        <v>-2</v>
-      </c>
-      <c r="G1" s="1">
-        <v>-1</v>
-      </c>
-      <c r="H1" s="1">
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>105</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>106</v>
+      </c>
+      <c r="B8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>107</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>108</v>
+      </c>
+      <c r="B10">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B11">
         <v>0</v>
       </c>
-      <c r="I1" s="1">
-        <v>1</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2</v>
-      </c>
-      <c r="K1" s="1">
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>110</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>111</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>112</v>
+      </c>
+      <c r="B14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>113</v>
+      </c>
+      <c r="B15">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>114</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>115</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>117</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>118</v>
+      </c>
+      <c r="B19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>119</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>120</v>
+      </c>
+      <c r="B21">
         <v>3</v>
       </c>
-      <c r="L1" s="1">
-        <v>4</v>
-      </c>
-      <c r="M1" s="1">
-        <v>5</v>
-      </c>
-      <c r="N1" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1">
-        <v>-6</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1">
-        <v>-5</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1">
-        <v>-4</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="F4" s="3" t="s">
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>121</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1">
-        <v>-3</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1">
-        <v>-2</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1">
-        <v>-1</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1">
-        <v>0</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="E8" s="3" t="s">
+      <c r="B22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>122</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1">
-        <v>1</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1">
-        <v>2</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1">
+      <c r="B23">
         <v>3</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="N11" s="3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1">
-        <v>4</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1">
-        <v>5</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="N13" s="3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1">
-        <v>6</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1">
-        <v>7</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>119</v>
-      </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
-  <headerFooter/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
-      <x14:conditionalFormattings>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="1" operator="equal" id="{FDFC5291-AB1B-4159-B440-A182D3D9CA07}">
-            <xm:f>"g"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FF6FA84F"/>
-                  <bgColor rgb="FF6FA84F"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B2:N15</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" operator="equal" id="{9AEC98BE-376C-4FA8-A835-E435EA07736C}">
-            <xm:f>"w"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FF3D6F9E"/>
-                  <bgColor rgb="FF3D6F9E"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B2:N15</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" operator="equal" id="{89A7D72B-9308-40B5-A985-FB297F20CFF6}">
-            <xm:f>"p"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FF9AA34F"/>
-                  <bgColor rgb="FF9AA34F"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B2:N15</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" operator="equal" id="{5F2B5890-5517-48DE-85CE-DF66781C593C}">
-            <xm:f>"d"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC9B26A"/>
-                  <bgColor rgb="FFC9B26A"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B2:N15</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="5" operator="equal" id="{F30623CB-A8BC-4DFD-A032-FCD88C5B54AC}">
-            <xm:f>"s"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFDFE7EC"/>
-                  <bgColor rgb="FFDFE7EC"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B2:N15</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="6" operator="equal" id="{6F2FF608-3D72-4615-B93F-256C23AD0882}">
-            <xm:f>"u"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FF8B9A94"/>
-                  <bgColor rgb="FF8B9A94"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B2:N15</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="7" operator="equal" id="{A0C09C4D-E33B-4B20-B53B-7B20501EDACF}">
-            <xm:f>"T"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FF2E6B2E"/>
-                  <bgColor rgb="FF2E6B2E"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B2:N15</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="8" operator="equal" id="{E482E04A-9A83-41B2-91F5-92879C64478F}">
-            <xm:f>"B"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FF7A4FA8"/>
-                  <bgColor rgb="FF7A4FA8"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B2:N15</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="9" operator="equal" id="{18938296-ED74-465C-94A1-044872D825E0}">
-            <xm:f>"A"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FF8A5A34"/>
-                  <bgColor rgb="FF8A5A34"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B2:N15</xm:sqref>
-        </x14:conditionalFormatting>
-      </x14:conditionalFormattings>
-    </ext>
-  </extLst>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="128">
   <si>
     <t>id</t>
   </si>
@@ -199,9 +199,6 @@
     <t>Meat</t>
   </si>
   <si>
-    <t>Taxes</t>
-  </si>
-  <si>
     <t>cap</t>
   </si>
   <si>
@@ -313,9 +310,6 @@
     <t>gold_per_minute</t>
   </si>
   <si>
-    <t>gold_per_tap</t>
-  </si>
-  <si>
     <t>key</t>
   </si>
   <si>
@@ -338,6 +332,9 @@
   </si>
   <si>
     <t>taxes.gold_per_population_per_minute</t>
+  </si>
+  <si>
+    <t>taxes.tap_boost_seconds</t>
   </si>
   <si>
     <t>offline_cap_hours</t>
@@ -1478,28 +1475,28 @@
         <v>-6</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -1507,34 +1504,34 @@
         <v>-5</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -1542,37 +1539,37 @@
         <v>-4</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>125</v>
-      </c>
       <c r="G4" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -1580,40 +1577,40 @@
         <v>-3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -1621,40 +1618,40 @@
         <v>-2</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
@@ -1662,37 +1659,37 @@
         <v>-1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -1700,37 +1697,37 @@
         <v>0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -1738,37 +1735,37 @@
         <v>1</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -1776,40 +1773,40 @@
         <v>2</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H10" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="J10" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>128</v>
-      </c>
       <c r="K10" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -1817,43 +1814,43 @@
         <v>3</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -1861,40 +1858,40 @@
         <v>4</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -1902,40 +1899,40 @@
         <v>5</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -1943,37 +1940,37 @@
         <v>6</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E14" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="L14" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>125</v>
-      </c>
       <c r="M14" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -1981,31 +1978,31 @@
         <v>7</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -2141,7 +2138,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2250,26 +2247,6 @@
       </c>
       <c r="F5">
         <v>180</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>59</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6">
-        <v>60</v>
-      </c>
-      <c r="F6" t="s">
-        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -2293,27 +2270,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B2" t="s">
         <v>26</v>
@@ -2336,7 +2313,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
@@ -2359,7 +2336,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
@@ -2394,7 +2371,7 @@
         <v>26</v>
       </c>
       <c r="E5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -2417,7 +2394,7 @@
         <v>26</v>
       </c>
       <c r="E6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F6">
         <v>3</v>
@@ -2428,7 +2405,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
@@ -2451,7 +2428,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
@@ -2488,10 +2465,10 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -2596,24 +2573,24 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B2">
         <v>100</v>
@@ -2628,12 +2605,12 @@
         <v>45</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B3">
         <v>250</v>
@@ -2648,12 +2625,12 @@
         <v>60</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B4">
         <v>75</v>
@@ -2673,7 +2650,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B5">
         <v>150</v>
@@ -2688,12 +2665,12 @@
         <v>45</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B6">
         <v>100</v>
@@ -2708,12 +2685,12 @@
         <v>30</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B7">
         <v>150</v>
@@ -2728,12 +2705,12 @@
         <v>60</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B8">
         <v>400</v>
@@ -2748,7 +2725,7 @@
         <v>90</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -2775,24 +2752,24 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>86</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B2">
         <v>50</v>
@@ -2807,12 +2784,12 @@
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B3">
         <v>75</v>
@@ -2827,12 +2804,12 @@
         <v>0.05</v>
       </c>
       <c r="F3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B4">
         <v>200</v>
@@ -2847,12 +2824,12 @@
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B5">
         <v>100</v>
@@ -2867,12 +2844,12 @@
         <v>0.05</v>
       </c>
       <c r="F5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B6">
         <v>150</v>
@@ -2887,7 +2864,7 @@
         <v>0.1</v>
       </c>
       <c r="F6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -2898,29 +2875,25 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>27</v>
       </c>
@@ -2928,9 +2901,6 @@
         <v>27</v>
       </c>
       <c r="C2">
-        <v>-1</v>
-      </c>
-      <c r="D2">
         <v>-1</v>
       </c>
     </row>
@@ -2942,7 +2912,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
@@ -2950,15 +2920,15 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -2966,7 +2936,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B3">
         <v>8</v>
@@ -2974,7 +2944,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B4">
         <v>0.5</v>
@@ -2982,7 +2952,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B5">
         <v>20</v>
@@ -2990,7 +2960,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -2998,7 +2968,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B7">
         <v>2</v>
@@ -3006,39 +2976,39 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B8">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B10">
-        <v>1.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -3046,7 +3016,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -3054,81 +3024,89 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B14">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B15">
-        <v>1.45</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>115</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>117</v>
-      </c>
-      <c r="B18">
-        <v>1</v>
+        <v>114</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B19">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B21">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B22">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>121</v>
+      </c>
+      <c r="B24">
         <v>3</v>
       </c>
     </row>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -1,26 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <workbookPr/>
+  <bookViews>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Districts" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Units" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Harvest" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="Currencies" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="FogRings" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="Technologies" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="Upgrades" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="Adjacency" state="visible" r:id="rId11"/>
-    <sheet sheetId="9" name="Settings" state="visible" r:id="rId12"/>
-    <sheet sheetId="10" name="Map" state="visible" r:id="rId13"/>
+    <sheet name="Districts" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Units" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Harvest" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Currencies" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="FogRings" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Technologies" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Upgrades" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Adjacency" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Settings" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Map" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="128">
   <si>
     <t>id</t>
   </si>
@@ -409,14 +414,13 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2">
     <font>
+      <sz val="11.000000"/>
       <color theme="1"/>
-      <family val="2"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
@@ -432,92 +436,28 @@
   </fills>
   <borders count="1">
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF6FA84F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF3D6F9E"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF9AA34F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFC9B26A"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFDFE7EC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF8B9A94"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF2E6B2E"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF7A4FA8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF8A5A34"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -530,7 +470,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -576,13 +516,13 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Thai" typeface="Angsana New"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
@@ -605,19 +545,18 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Thai" typeface="Cordia New"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
@@ -640,7 +579,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -675,16 +613,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -806,9 +748,226 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
   <a:objectDefaults>
     <a:spDef>
-      <a:spPr/>
+      <a:spPr bwMode="auto"/>
       <a:bodyPr/>
       <a:lstStyle/>
       <a:style>
@@ -827,7 +986,7 @@
       </a:style>
     </a:spDef>
     <a:lnDef>
-      <a:spPr/>
+      <a:spPr bwMode="auto"/>
       <a:bodyPr/>
       <a:lstStyle/>
       <a:style>
@@ -846,36 +1005,34 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y7"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="21" customWidth="1"/>
-    <col min="6" max="6" width="19" customWidth="1"/>
-    <col min="7" max="7" width="21" customWidth="1"/>
-    <col min="8" max="8" width="23" customWidth="1"/>
-    <col min="9" max="9" width="30" customWidth="1"/>
-    <col min="10" max="10" width="28" customWidth="1"/>
-    <col min="11" max="11" width="35" customWidth="1"/>
-    <col min="12" max="14" width="17" customWidth="1"/>
-    <col min="15" max="15" width="23" customWidth="1"/>
-    <col min="16" max="16" width="31" customWidth="1"/>
-    <col min="17" max="17" width="24" customWidth="1"/>
-    <col min="18" max="19" width="32" customWidth="1"/>
-    <col min="20" max="22" width="19" customWidth="1"/>
-    <col min="23" max="23" width="27" customWidth="1"/>
-    <col min="24" max="24" width="26" customWidth="1"/>
-    <col min="25" max="25" width="31" customWidth="1"/>
+    <col customWidth="1" min="1" max="3" width="10"/>
+    <col customWidth="1" min="4" max="4" width="11"/>
+    <col customWidth="1" min="5" max="5" width="21"/>
+    <col customWidth="1" min="6" max="6" width="19"/>
+    <col customWidth="1" min="7" max="7" width="21"/>
+    <col customWidth="1" min="8" max="8" width="23"/>
+    <col customWidth="1" min="9" max="9" width="30"/>
+    <col customWidth="1" min="10" max="10" width="28"/>
+    <col customWidth="1" min="11" max="11" width="35"/>
+    <col customWidth="1" min="12" max="14" width="17"/>
+    <col customWidth="1" min="15" max="15" width="23"/>
+    <col customWidth="1" min="16" max="16" width="31"/>
+    <col customWidth="1" min="17" max="17" width="24"/>
+    <col customWidth="1" min="18" max="19" width="32"/>
+    <col customWidth="1" min="20" max="22" width="19"/>
+    <col customWidth="1" min="23" max="23" width="27"/>
+    <col customWidth="1" min="24" max="24" width="26"/>
+    <col customWidth="1" min="25" max="25" width="31"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -952,7 +1109,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -1008,7 +1165,7 @@
         <v>1.2</v>
       </c>
       <c r="S2">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="T2" t="s">
         <v>26</v>
@@ -1029,7 +1186,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>27</v>
       </c>
@@ -1043,7 +1200,7 @@
         <v>1</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -1073,10 +1230,10 @@
         <v>26</v>
       </c>
       <c r="O3">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="P3">
-        <v>1.25</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="Q3">
         <v>20</v>
@@ -1085,7 +1242,7 @@
         <v>1.2</v>
       </c>
       <c r="S3">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="T3" t="s">
         <v>26</v>
@@ -1106,7 +1263,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>29</v>
       </c>
@@ -1162,7 +1319,7 @@
         <v>1.2</v>
       </c>
       <c r="S4">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="T4" t="s">
         <v>26</v>
@@ -1183,7 +1340,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>34</v>
       </c>
@@ -1239,7 +1396,7 @@
         <v>1.2</v>
       </c>
       <c r="S5">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="T5" t="s">
         <v>26</v>
@@ -1260,7 +1417,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>36</v>
       </c>
@@ -1316,7 +1473,7 @@
         <v>1.2</v>
       </c>
       <c r="S6">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="T6" t="s">
         <v>26</v>
@@ -1337,7 +1494,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>39</v>
       </c>
@@ -1393,7 +1550,7 @@
         <v>1.2</v>
       </c>
       <c r="S7">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="T7" t="s">
         <v>26</v>
@@ -1415,21 +1572,22 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N15"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="14" width="3.5" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="4"/>
+    <col customWidth="1" min="2" max="14" width="3.5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1">
       <c r="B1" s="1">
         <v>-6</v>
       </c>
@@ -1470,7 +1628,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" s="1">
         <v>-6</v>
       </c>
@@ -1499,7 +1657,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" s="1">
         <v>-5</v>
       </c>
@@ -1534,7 +1692,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" s="1">
         <v>-4</v>
       </c>
@@ -1572,7 +1730,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" s="1">
         <v>-3</v>
       </c>
@@ -1613,7 +1771,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" s="1">
         <v>-2</v>
       </c>
@@ -1654,7 +1812,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" s="1">
         <v>-1</v>
       </c>
@@ -1692,7 +1850,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" s="1">
         <v>0</v>
       </c>
@@ -1730,7 +1888,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -1768,7 +1926,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" s="1">
         <v>2</v>
       </c>
@@ -1809,7 +1967,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" s="1">
         <v>3</v>
       </c>
@@ -1853,7 +2011,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" s="1">
         <v>4</v>
       </c>
@@ -1894,7 +2052,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" s="1">
         <v>5</v>
       </c>
@@ -1935,7 +2093,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14">
       <c r="A14" s="1">
         <v>6</v>
       </c>
@@ -1973,7 +2131,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="A15" s="1">
         <v>7</v>
       </c>
@@ -2006,51 +2164,155 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:N15">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>"g"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
-      <formula>"w"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
-      <formula>"p"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
-      <formula>"d"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
-      <formula>"s"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
-      <formula>"u"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
-      <formula>"T"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
-      <formula>"B"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
+  <headerFooter/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="1" operator="equal" id="{0ED2442A-6D6B-4937-8CA0-75D0467EF909}">
+            <xm:f>"g"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FF6FA84F"/>
+                  <bgColor rgb="FF6FA84F"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>B2:N15</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="2" operator="equal" id="{2E311035-5C74-48F4-886F-DCF0B10E3286}">
+            <xm:f>"w"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FF3D6F9E"/>
+                  <bgColor rgb="FF3D6F9E"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>B2:N15</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="3" operator="equal" id="{24F8D584-4ECE-4659-8591-07C3287816C0}">
+            <xm:f>"p"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FF9AA34F"/>
+                  <bgColor rgb="FF9AA34F"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>B2:N15</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="4" operator="equal" id="{E46A6E04-5A93-43A6-80D6-21C33B366A15}">
+            <xm:f>"d"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC9B26A"/>
+                  <bgColor rgb="FFC9B26A"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>B2:N15</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="5" operator="equal" id="{86AD3F8C-74CE-4B95-ADB2-A1D483705EC1}">
+            <xm:f>"s"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFDFE7EC"/>
+                  <bgColor rgb="FFDFE7EC"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>B2:N15</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="6" operator="equal" id="{6CE882BA-39D2-4402-B034-81144F352D58}">
+            <xm:f>"u"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FF8B9A94"/>
+                  <bgColor rgb="FF8B9A94"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>B2:N15</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="7" operator="equal" id="{0DAFB4F2-775B-40B4-B617-F43FA0C1A3DF}">
+            <xm:f>"T"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FF2E6B2E"/>
+                  <bgColor rgb="FF2E6B2E"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>B2:N15</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="8" operator="equal" id="{D5458B59-DD23-4CA5-8178-1B33BAFA7EA8}">
+            <xm:f>"B"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FF7A4FA8"/>
+                  <bgColor rgb="FF7A4FA8"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>B2:N15</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="9" operator="equal" id="{A506F298-92BB-4BE2-9744-5BB0AB5C0A71}">
+            <xm:f>"A"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FF8A5A34"/>
+                  <bgColor rgb="FF8A5A34"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>B2:N15</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="10" customWidth="1"/>
-    <col min="3" max="5" width="19" customWidth="1"/>
-    <col min="6" max="6" width="24" customWidth="1"/>
+    <col customWidth="1" min="1" max="2" width="10"/>
+    <col customWidth="1" min="3" max="5" width="19"/>
+    <col customWidth="1" min="6" max="6" width="24"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2070,7 +2332,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>46</v>
       </c>
@@ -2090,7 +2352,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>47</v>
       </c>
@@ -2110,7 +2372,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>48</v>
       </c>
@@ -2131,25 +2393,26 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="17" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="10"/>
+    <col customWidth="1" min="2" max="2" width="15"/>
+    <col customWidth="1" min="3" max="3" width="18"/>
+    <col customWidth="1" min="4" max="4" width="17"/>
+    <col customWidth="1" min="5" max="5" width="18"/>
+    <col customWidth="1" min="6" max="6" width="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>49</v>
       </c>
@@ -2169,7 +2432,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>55</v>
       </c>
@@ -2189,7 +2452,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>56</v>
       </c>
@@ -2209,7 +2472,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>57</v>
       </c>
@@ -2229,7 +2492,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>58</v>
       </c>
@@ -2250,22 +2513,23 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="6" max="7" width="12" customWidth="1"/>
+    <col customWidth="1" min="1" max="4" width="10"/>
+    <col customWidth="1" min="5" max="5" width="11"/>
+    <col customWidth="1" min="6" max="7" width="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2288,7 +2552,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>65</v>
       </c>
@@ -2311,7 +2575,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>66</v>
       </c>
@@ -2334,7 +2598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>67</v>
       </c>
@@ -2357,7 +2621,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>57</v>
       </c>
@@ -2380,7 +2644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>58</v>
       </c>
@@ -2403,7 +2667,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>68</v>
       </c>
@@ -2426,7 +2690,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>69</v>
       </c>
@@ -2450,20 +2714,21 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="10" customWidth="1"/>
+    <col customWidth="1" min="1" max="2" width="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>70</v>
       </c>
@@ -2471,7 +2736,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2479,7 +2744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2487,7 +2752,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2495,7 +2760,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2503,7 +2768,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2511,7 +2776,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2519,7 +2784,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2527,7 +2792,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2535,7 +2800,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2543,7 +2808,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2552,23 +2817,24 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="10" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="10"/>
+    <col customWidth="1" min="2" max="4" width="11"/>
+    <col customWidth="1" min="5" max="5" width="18"/>
+    <col customWidth="1" min="6" max="6" width="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2588,7 +2854,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>77</v>
       </c>
@@ -2608,7 +2874,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>79</v>
       </c>
@@ -2628,7 +2894,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>78</v>
       </c>
@@ -2648,7 +2914,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>80</v>
       </c>
@@ -2668,7 +2934,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>81</v>
       </c>
@@ -2688,7 +2954,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>82</v>
       </c>
@@ -2708,7 +2974,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>83</v>
       </c>
@@ -2729,25 +2995,26 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="15" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="10"/>
+    <col customWidth="1" min="2" max="2" width="11"/>
+    <col customWidth="1" min="3" max="3" width="13"/>
+    <col customWidth="1" min="4" max="4" width="11"/>
+    <col customWidth="1" min="5" max="5" width="18"/>
+    <col customWidth="1" min="6" max="6" width="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2767,7 +3034,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>88</v>
       </c>
@@ -2775,7 +3042,7 @@
         <v>50</v>
       </c>
       <c r="C2">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="D2">
         <v>5</v>
@@ -2787,7 +3054,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>89</v>
       </c>
@@ -2801,13 +3068,13 @@
         <v>5</v>
       </c>
       <c r="E3">
-        <v>0.05</v>
+        <v>0.050000000000000003</v>
       </c>
       <c r="F3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>90</v>
       </c>
@@ -2827,7 +3094,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>91</v>
       </c>
@@ -2841,13 +3108,13 @@
         <v>4</v>
       </c>
       <c r="E5">
-        <v>0.05</v>
+        <v>0.050000000000000003</v>
       </c>
       <c r="F5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>92</v>
       </c>
@@ -2861,28 +3128,29 @@
         <v>5</v>
       </c>
       <c r="E6">
-        <v>0.1</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="F6" t="s">
         <v>80</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="17" customWidth="1"/>
+    <col customWidth="1" min="1" max="2" width="10"/>
+    <col customWidth="1" min="3" max="3" width="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>93</v>
       </c>
@@ -2893,7 +3161,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>27</v>
       </c>
@@ -2905,20 +3173,22 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B24"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="2" width="10" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="40.28125"/>
+    <col customWidth="1" min="2" max="2" width="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>96</v>
       </c>
@@ -2926,7 +3196,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>98</v>
       </c>
@@ -2934,7 +3204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>99</v>
       </c>
@@ -2942,7 +3212,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>100</v>
       </c>
@@ -2950,7 +3220,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>101</v>
       </c>
@@ -2958,7 +3228,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>102</v>
       </c>
@@ -2966,15 +3236,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>103</v>
       </c>
       <c r="B7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" t="s">
         <v>104</v>
       </c>
@@ -2982,7 +3252,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>105</v>
       </c>
@@ -2990,7 +3260,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
         <v>106</v>
       </c>
@@ -2998,7 +3268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" t="s">
         <v>107</v>
       </c>
@@ -3006,7 +3276,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" t="s">
         <v>108</v>
       </c>
@@ -3014,7 +3284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" t="s">
         <v>109</v>
       </c>
@@ -3022,7 +3292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14">
       <c r="A14" t="s">
         <v>110</v>
       </c>
@@ -3030,7 +3300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="A15" t="s">
         <v>111</v>
       </c>
@@ -3038,7 +3308,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="A16" t="s">
         <v>112</v>
       </c>
@@ -3046,7 +3316,7 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="A17" t="s">
         <v>113</v>
       </c>
@@ -3054,7 +3324,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18">
       <c r="A18" t="s">
         <v>114</v>
       </c>
@@ -3062,7 +3332,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19">
       <c r="A19" t="s">
         <v>116</v>
       </c>
@@ -3070,7 +3340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20">
       <c r="A20" t="s">
         <v>117</v>
       </c>
@@ -3078,7 +3348,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21">
       <c r="A21" t="s">
         <v>118</v>
       </c>
@@ -3086,7 +3356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22">
       <c r="A22" t="s">
         <v>119</v>
       </c>
@@ -3094,7 +3364,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23">
       <c r="A23" t="s">
         <v>120</v>
       </c>
@@ -3102,7 +3372,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24">
       <c r="A24" t="s">
         <v>121</v>
       </c>
@@ -3111,7 +3381,9 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -1,31 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr/>
-  <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Districts" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Units" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Harvest" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Currencies" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="FogRings" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Technologies" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Upgrades" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Adjacency" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Settings" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Map" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet sheetId="1" name="Districts" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Units" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Harvest" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Currencies" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="FogRings" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Technologies" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="Upgrades" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="Adjacency" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="Settings" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="Map" state="visible" r:id="rId13"/>
   </sheets>
-  <calcPr/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="158">
   <si>
     <t>id</t>
   </si>
@@ -69,6 +64,12 @@
     <t>build_cost_food</t>
   </si>
   <si>
+    <t>build_cost_stone</t>
+  </si>
+  <si>
+    <t>build_cost_iron</t>
+  </si>
+  <si>
     <t>build_cost_multiplier</t>
   </si>
   <si>
@@ -93,6 +94,12 @@
     <t>upgrade_cost_food</t>
   </si>
   <si>
+    <t>upgrade_cost_stone</t>
+  </si>
+  <si>
+    <t>upgrade_cost_iron</t>
+  </si>
+  <si>
     <t>upgrade_cost_level_growth</t>
   </si>
   <si>
@@ -150,6 +157,15 @@
     <t>1</t>
   </si>
   <si>
+    <t>Quarry</t>
+  </si>
+  <si>
+    <t>FishingHut</t>
+  </si>
+  <si>
+    <t>Mine</t>
+  </si>
+  <si>
     <t>power</t>
   </si>
   <si>
@@ -162,6 +178,12 @@
     <t>recruit_cost_food</t>
   </si>
   <si>
+    <t>recruit_cost_stone</t>
+  </si>
+  <si>
+    <t>recruit_cost_iron</t>
+  </si>
+  <si>
     <t>train_duration_seconds</t>
   </si>
   <si>
@@ -204,6 +226,15 @@
     <t>Meat</t>
   </si>
   <si>
+    <t>Stone</t>
+  </si>
+  <si>
+    <t>Fish</t>
+  </si>
+  <si>
+    <t>Iron</t>
+  </si>
+  <si>
     <t>cap</t>
   </si>
   <si>
@@ -252,6 +283,12 @@
     <t>cost_food</t>
   </si>
   <si>
+    <t>cost_stone</t>
+  </si>
+  <si>
+    <t>cost_iron</t>
+  </si>
+  <si>
     <t>duration_seconds</t>
   </si>
   <si>
@@ -279,6 +316,15 @@
     <t>CavalryTraining</t>
   </si>
   <si>
+    <t>Masonry</t>
+  </si>
+  <si>
+    <t>Fishing</t>
+  </si>
+  <si>
+    <t>Mining</t>
+  </si>
+  <si>
     <t>cost_base</t>
   </si>
   <si>
@@ -306,6 +352,15 @@
     <t>TradeRoutes</t>
   </si>
   <si>
+    <t>Stonecutting</t>
+  </si>
+  <si>
+    <t>BigNets</t>
+  </si>
+  <si>
+    <t>IronPicks</t>
+  </si>
+  <si>
     <t>district</t>
   </si>
   <si>
@@ -393,15 +448,42 @@
     <t>research.slot_gem_cost_growth</t>
   </si>
   <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>sI</t>
+  </si>
+  <si>
     <t>w</t>
   </si>
   <si>
+    <t>u</t>
+  </si>
+  <si>
+    <t>uA</t>
+  </si>
+  <si>
     <t>g</t>
   </si>
   <si>
     <t>A</t>
   </si>
   <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>wF</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>pT</t>
+  </si>
+  <si>
+    <t>pR</t>
+  </si>
+  <si>
     <t>wB</t>
   </si>
   <si>
@@ -409,18 +491,22 @@
   </si>
   <si>
     <t>T</t>
+  </si>
+  <si>
+    <t>pA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="11.000000"/>
       <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -436,28 +522,113 @@
   </fills>
   <borders count="1">
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="12">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF6FA84F"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF3D6F9E"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF9AA34F"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFC9B26A"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFDFE7EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF8B9A94"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF2E6B2E"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF7A4FA8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF8A5A34"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF7A7F87"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF2E86AB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF4A4E57"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -470,7 +641,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -516,13 +687,13 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Angsana New"/>
+        <a:font script="Thai" typeface="Tahoma"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
@@ -545,18 +716,19 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Cordia New"/>
+        <a:font script="Thai" typeface="Tahoma"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
@@ -579,6 +751,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -613,20 +786,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -748,226 +917,9 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
-</file>
-
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle"/>
-        </a:gradFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle"/>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
   <a:objectDefaults>
     <a:spDef>
-      <a:spPr bwMode="auto"/>
+      <a:spPr/>
       <a:bodyPr/>
       <a:lstStyle/>
       <a:style>
@@ -986,7 +938,7 @@
       </a:style>
     </a:spDef>
     <a:lnDef>
-      <a:spPr bwMode="auto"/>
+      <a:spPr/>
       <a:bodyPr/>
       <a:lstStyle/>
       <a:style>
@@ -1005,34 +957,40 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AC10"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col customWidth="1" min="1" max="3" width="10"/>
-    <col customWidth="1" min="4" max="4" width="11"/>
-    <col customWidth="1" min="5" max="5" width="21"/>
-    <col customWidth="1" min="6" max="6" width="19"/>
-    <col customWidth="1" min="7" max="7" width="21"/>
-    <col customWidth="1" min="8" max="8" width="23"/>
-    <col customWidth="1" min="9" max="9" width="30"/>
-    <col customWidth="1" min="10" max="10" width="28"/>
-    <col customWidth="1" min="11" max="11" width="35"/>
-    <col customWidth="1" min="12" max="14" width="17"/>
-    <col customWidth="1" min="15" max="15" width="23"/>
-    <col customWidth="1" min="16" max="16" width="31"/>
-    <col customWidth="1" min="17" max="17" width="24"/>
-    <col customWidth="1" min="18" max="19" width="32"/>
-    <col customWidth="1" min="20" max="22" width="19"/>
-    <col customWidth="1" min="23" max="23" width="27"/>
-    <col customWidth="1" min="24" max="24" width="26"/>
-    <col customWidth="1" min="25" max="25" width="31"/>
+    <col min="1" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="21" customWidth="1"/>
+    <col min="6" max="6" width="19" customWidth="1"/>
+    <col min="7" max="7" width="21" customWidth="1"/>
+    <col min="8" max="8" width="23" customWidth="1"/>
+    <col min="9" max="9" width="30" customWidth="1"/>
+    <col min="10" max="10" width="28" customWidth="1"/>
+    <col min="11" max="11" width="35" customWidth="1"/>
+    <col min="12" max="14" width="17" customWidth="1"/>
+    <col min="15" max="15" width="18" customWidth="1"/>
+    <col min="16" max="16" width="17" customWidth="1"/>
+    <col min="17" max="17" width="23" customWidth="1"/>
+    <col min="18" max="18" width="31" customWidth="1"/>
+    <col min="19" max="19" width="24" customWidth="1"/>
+    <col min="20" max="21" width="32" customWidth="1"/>
+    <col min="22" max="24" width="19" customWidth="1"/>
+    <col min="25" max="25" width="20" customWidth="1"/>
+    <col min="26" max="26" width="19" customWidth="1"/>
+    <col min="27" max="27" width="27" customWidth="1"/>
+    <col min="28" max="28" width="26" customWidth="1"/>
+    <col min="29" max="29" width="31" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1108,10 +1066,22 @@
       <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2">
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -1132,63 +1102,75 @@
         <v>3</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="M2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="N2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O2">
+        <v>30</v>
+      </c>
+      <c r="O2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P2" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q2">
         <v>2</v>
-      </c>
-      <c r="P2">
-        <v>1.2</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
       </c>
       <c r="R2">
         <v>1.2</v>
       </c>
       <c r="S2">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="T2" t="s">
-        <v>26</v>
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>1.2</v>
       </c>
       <c r="U2">
+        <v>1.15</v>
+      </c>
+      <c r="V2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W2">
         <v>25</v>
       </c>
-      <c r="V2" t="s">
-        <v>26</v>
-      </c>
-      <c r="W2">
+      <c r="X2" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y2">
+        <v>25</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA2">
         <v>1.5</v>
       </c>
-      <c r="X2">
+      <c r="AB2">
         <v>0</v>
       </c>
-      <c r="Y2">
+      <c r="AC2">
         <v>1.5</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -1209,63 +1191,75 @@
         <v>2</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="M3">
         <v>10</v>
       </c>
       <c r="N3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O3">
+        <v>30</v>
+      </c>
+      <c r="O3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q3">
         <v>1.25</v>
       </c>
-      <c r="P3">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="Q3">
+      <c r="R3">
+        <v>1.1</v>
+      </c>
+      <c r="S3">
         <v>20</v>
       </c>
-      <c r="R3">
+      <c r="T3">
         <v>1.2</v>
       </c>
-      <c r="S3">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="T3" t="s">
-        <v>26</v>
-      </c>
-      <c r="U3" t="s">
-        <v>26</v>
+      <c r="U3">
+        <v>1.15</v>
       </c>
       <c r="V3" t="s">
-        <v>26</v>
-      </c>
-      <c r="W3">
+        <v>30</v>
+      </c>
+      <c r="W3" t="s">
+        <v>30</v>
+      </c>
+      <c r="X3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA3">
         <v>1.5</v>
       </c>
-      <c r="X3">
+      <c r="AB3">
         <v>0</v>
       </c>
-      <c r="Y3">
+      <c r="AC3">
         <v>1.5</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -1286,63 +1280,75 @@
         <v>2</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="M4">
         <v>10</v>
       </c>
       <c r="N4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O4">
+        <v>30</v>
+      </c>
+      <c r="O4" t="s">
+        <v>30</v>
+      </c>
+      <c r="P4" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q4">
         <v>2</v>
       </c>
-      <c r="P4">
+      <c r="R4">
         <v>1.5</v>
       </c>
-      <c r="Q4">
+      <c r="S4">
         <v>20</v>
       </c>
-      <c r="R4">
+      <c r="T4">
         <v>1.2</v>
       </c>
-      <c r="S4">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="T4" t="s">
-        <v>26</v>
-      </c>
       <c r="U4">
+        <v>1.15</v>
+      </c>
+      <c r="V4" t="s">
+        <v>30</v>
+      </c>
+      <c r="W4">
         <v>50</v>
       </c>
-      <c r="V4" t="s">
-        <v>26</v>
-      </c>
-      <c r="W4">
+      <c r="X4" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA4">
         <v>1.5</v>
       </c>
-      <c r="X4">
-        <v>30</v>
-      </c>
-      <c r="Y4">
+      <c r="AB4">
+        <v>30</v>
+      </c>
+      <c r="AC4">
         <v>1.5</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -1363,63 +1369,75 @@
         <v>2</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="M5">
         <v>20</v>
       </c>
       <c r="N5" t="s">
-        <v>26</v>
-      </c>
-      <c r="O5">
+        <v>30</v>
+      </c>
+      <c r="O5" t="s">
+        <v>30</v>
+      </c>
+      <c r="P5" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q5">
         <v>2</v>
-      </c>
-      <c r="P5">
-        <v>1.2</v>
-      </c>
-      <c r="Q5">
-        <v>10</v>
       </c>
       <c r="R5">
         <v>1.2</v>
       </c>
       <c r="S5">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="T5" t="s">
-        <v>26</v>
-      </c>
-      <c r="U5" t="s">
-        <v>26</v>
+        <v>10</v>
+      </c>
+      <c r="T5">
+        <v>1.2</v>
+      </c>
+      <c r="U5">
+        <v>1.15</v>
       </c>
       <c r="V5" t="s">
-        <v>26</v>
-      </c>
-      <c r="W5">
+        <v>30</v>
+      </c>
+      <c r="W5" t="s">
+        <v>30</v>
+      </c>
+      <c r="X5" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA5">
         <v>1.5</v>
       </c>
-      <c r="X5">
+      <c r="AB5">
         <v>0</v>
       </c>
-      <c r="Y5">
+      <c r="AC5">
         <v>1.5</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -1440,63 +1458,75 @@
         <v>2</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="L6" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="M6">
         <v>20</v>
       </c>
       <c r="N6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O6">
+        <v>30</v>
+      </c>
+      <c r="O6" t="s">
+        <v>30</v>
+      </c>
+      <c r="P6" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q6">
         <v>4</v>
       </c>
-      <c r="P6">
+      <c r="R6">
         <v>1.45</v>
       </c>
-      <c r="Q6">
+      <c r="S6">
         <v>20</v>
       </c>
-      <c r="R6">
+      <c r="T6">
         <v>1.2</v>
       </c>
-      <c r="S6">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="T6" t="s">
-        <v>26</v>
-      </c>
-      <c r="U6" t="s">
-        <v>26</v>
+      <c r="U6">
+        <v>1.15</v>
       </c>
       <c r="V6" t="s">
-        <v>26</v>
-      </c>
-      <c r="W6">
+        <v>30</v>
+      </c>
+      <c r="W6" t="s">
+        <v>30</v>
+      </c>
+      <c r="X6" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA6">
         <v>1.5</v>
       </c>
-      <c r="X6">
-        <v>30</v>
-      </c>
-      <c r="Y6">
+      <c r="AB6">
+        <v>30</v>
+      </c>
+      <c r="AC6">
         <v>1.5</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -1517,824 +1547,1347 @@
         <v>2</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="M7">
         <v>40</v>
       </c>
       <c r="N7" t="s">
-        <v>26</v>
-      </c>
-      <c r="O7">
+        <v>30</v>
+      </c>
+      <c r="O7" t="s">
+        <v>30</v>
+      </c>
+      <c r="P7" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q7">
         <v>2</v>
-      </c>
-      <c r="P7">
-        <v>1.2</v>
-      </c>
-      <c r="Q7">
-        <v>30</v>
       </c>
       <c r="R7">
         <v>1.2</v>
       </c>
       <c r="S7">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="T7" t="s">
-        <v>26</v>
-      </c>
-      <c r="U7" t="s">
-        <v>26</v>
+        <v>30</v>
+      </c>
+      <c r="T7">
+        <v>1.2</v>
+      </c>
+      <c r="U7">
+        <v>1.15</v>
       </c>
       <c r="V7" t="s">
-        <v>26</v>
-      </c>
-      <c r="W7">
+        <v>30</v>
+      </c>
+      <c r="W7" t="s">
+        <v>30</v>
+      </c>
+      <c r="X7" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA7">
         <v>1.5</v>
       </c>
-      <c r="X7">
+      <c r="AB7">
         <v>0</v>
       </c>
-      <c r="Y7">
+      <c r="AC7">
         <v>1.5</v>
       </c>
     </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="L8" t="s">
+        <v>30</v>
+      </c>
+      <c r="M8">
+        <v>30</v>
+      </c>
+      <c r="N8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O8" t="s">
+        <v>30</v>
+      </c>
+      <c r="P8" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q8">
+        <v>4</v>
+      </c>
+      <c r="R8">
+        <v>1.45</v>
+      </c>
+      <c r="S8">
+        <v>20</v>
+      </c>
+      <c r="T8">
+        <v>1.2</v>
+      </c>
+      <c r="U8">
+        <v>1.15</v>
+      </c>
+      <c r="V8" t="s">
+        <v>30</v>
+      </c>
+      <c r="W8">
+        <v>40</v>
+      </c>
+      <c r="X8" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA8">
+        <v>1.5</v>
+      </c>
+      <c r="AB8">
+        <v>30</v>
+      </c>
+      <c r="AC8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="L9" t="s">
+        <v>30</v>
+      </c>
+      <c r="M9">
+        <v>25</v>
+      </c>
+      <c r="N9" t="s">
+        <v>30</v>
+      </c>
+      <c r="O9" t="s">
+        <v>30</v>
+      </c>
+      <c r="P9" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q9">
+        <v>4</v>
+      </c>
+      <c r="R9">
+        <v>1.45</v>
+      </c>
+      <c r="S9">
+        <v>20</v>
+      </c>
+      <c r="T9">
+        <v>1.2</v>
+      </c>
+      <c r="U9">
+        <v>1.15</v>
+      </c>
+      <c r="V9" t="s">
+        <v>30</v>
+      </c>
+      <c r="W9">
+        <v>35</v>
+      </c>
+      <c r="X9" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA9">
+        <v>1.5</v>
+      </c>
+      <c r="AB9">
+        <v>30</v>
+      </c>
+      <c r="AC9">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="L10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M10">
+        <v>40</v>
+      </c>
+      <c r="N10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O10">
+        <v>20</v>
+      </c>
+      <c r="P10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q10">
+        <v>4</v>
+      </c>
+      <c r="R10">
+        <v>1.45</v>
+      </c>
+      <c r="S10">
+        <v>30</v>
+      </c>
+      <c r="T10">
+        <v>1.2</v>
+      </c>
+      <c r="U10">
+        <v>1.15</v>
+      </c>
+      <c r="V10" t="s">
+        <v>30</v>
+      </c>
+      <c r="W10">
+        <v>50</v>
+      </c>
+      <c r="X10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y10">
+        <v>25</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA10">
+        <v>1.5</v>
+      </c>
+      <c r="AB10">
+        <v>30</v>
+      </c>
+      <c r="AC10">
+        <v>1.5</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:T19"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="4"/>
-    <col customWidth="1" min="2" max="14" width="3.5"/>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="20" width="3.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="2:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B1" s="1">
+        <v>-8</v>
+      </c>
+      <c r="C1" s="1">
+        <v>-7</v>
+      </c>
+      <c r="D1" s="1">
         <v>-6</v>
       </c>
-      <c r="C1" s="1">
+      <c r="E1" s="1">
         <v>-5</v>
       </c>
-      <c r="D1" s="1">
+      <c r="F1" s="1">
         <v>-4</v>
       </c>
-      <c r="E1" s="1">
+      <c r="G1" s="1">
         <v>-3</v>
       </c>
-      <c r="F1" s="1">
+      <c r="H1" s="1">
         <v>-2</v>
       </c>
-      <c r="G1" s="1">
+      <c r="I1" s="1">
         <v>-1</v>
       </c>
-      <c r="H1" s="1">
+      <c r="J1" s="1">
         <v>0</v>
       </c>
-      <c r="I1" s="1">
-        <v>1</v>
-      </c>
-      <c r="J1" s="1">
+      <c r="K1" s="1">
+        <v>1</v>
+      </c>
+      <c r="L1" s="1">
         <v>2</v>
       </c>
-      <c r="K1" s="1">
+      <c r="M1" s="1">
         <v>3</v>
       </c>
-      <c r="L1" s="1">
+      <c r="N1" s="1">
         <v>4</v>
       </c>
-      <c r="M1" s="1">
+      <c r="O1" s="1">
         <v>5</v>
       </c>
-      <c r="N1" s="1">
+      <c r="P1" s="1">
         <v>6</v>
       </c>
-    </row>
-    <row r="2">
+      <c r="Q1" s="1">
+        <v>7</v>
+      </c>
+      <c r="R1" s="1">
+        <v>8</v>
+      </c>
+      <c r="S1" s="1">
+        <v>9</v>
+      </c>
+      <c r="T1" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
+        <v>-10</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>-9</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>-8</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>-7</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
         <v>-6</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1">
+      <c r="G6" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
         <v>-5</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1">
+      <c r="E7" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
         <v>-4</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1">
+      <c r="E8" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
         <v>-3</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1">
+      <c r="D9" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
         <v>-2</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1">
+      <c r="E10" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
         <v>-1</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1">
+      <c r="E11" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q11" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="R11" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="S11" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="T11" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
         <v>0</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1">
-        <v>1</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1">
+      <c r="B12" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="T12" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>1</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q13" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="R13" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="S13" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="T13" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
         <v>2</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1">
+      <c r="B14" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
         <v>3</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="N11" s="3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1">
+      <c r="B15" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="T15" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
         <v>4</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1">
+      <c r="B16" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q16" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="R16" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="S16" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="T16" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
         <v>5</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="N13" s="3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1">
+      <c r="B17" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="T17" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
         <v>6</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1">
+      <c r="B18" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
         <v>7</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>122</v>
+      <c r="B19" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
-  <headerFooter/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
-      <x14:conditionalFormattings>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="1" operator="equal" id="{0ED2442A-6D6B-4937-8CA0-75D0467EF909}">
-            <xm:f>"g"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FF6FA84F"/>
-                  <bgColor rgb="FF6FA84F"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B2:N15</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" operator="equal" id="{2E311035-5C74-48F4-886F-DCF0B10E3286}">
-            <xm:f>"w"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FF3D6F9E"/>
-                  <bgColor rgb="FF3D6F9E"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B2:N15</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" operator="equal" id="{24F8D584-4ECE-4659-8591-07C3287816C0}">
-            <xm:f>"p"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FF9AA34F"/>
-                  <bgColor rgb="FF9AA34F"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B2:N15</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" operator="equal" id="{E46A6E04-5A93-43A6-80D6-21C33B366A15}">
-            <xm:f>"d"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC9B26A"/>
-                  <bgColor rgb="FFC9B26A"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B2:N15</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="5" operator="equal" id="{86AD3F8C-74CE-4B95-ADB2-A1D483705EC1}">
-            <xm:f>"s"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFDFE7EC"/>
-                  <bgColor rgb="FFDFE7EC"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B2:N15</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="6" operator="equal" id="{6CE882BA-39D2-4402-B034-81144F352D58}">
-            <xm:f>"u"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FF8B9A94"/>
-                  <bgColor rgb="FF8B9A94"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B2:N15</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="7" operator="equal" id="{0DAFB4F2-775B-40B4-B617-F43FA0C1A3DF}">
-            <xm:f>"T"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FF2E6B2E"/>
-                  <bgColor rgb="FF2E6B2E"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B2:N15</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="8" operator="equal" id="{D5458B59-DD23-4CA5-8178-1B33BAFA7EA8}">
-            <xm:f>"B"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FF7A4FA8"/>
-                  <bgColor rgb="FF7A4FA8"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B2:N15</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="9" operator="equal" id="{A506F298-92BB-4BE2-9744-5BB0AB5C0A71}">
-            <xm:f>"A"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FF8A5A34"/>
-                  <bgColor rgb="FF8A5A34"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B2:N15</xm:sqref>
-        </x14:conditionalFormatting>
-      </x14:conditionalFormattings>
-    </ext>
-  </extLst>
+  <conditionalFormatting sqref="B2:T19">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"g"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"w"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"p"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+      <formula>"d"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+      <formula>"s"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+      <formula>"u"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
+      <formula>"T"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
+      <formula>"B"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="10" operator="equal">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="11" operator="equal">
+      <formula>"F"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="11" priority="12" operator="equal">
+      <formula>"I"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col customWidth="1" min="1" max="2" width="10"/>
-    <col customWidth="1" min="3" max="5" width="19"/>
-    <col customWidth="1" min="6" max="6" width="24"/>
+    <col min="1" max="2" width="10" customWidth="1"/>
+    <col min="3" max="5" width="19" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
+    <col min="7" max="7" width="19" customWidth="1"/>
+    <col min="8" max="8" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2">
+        <v>52</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -2346,15 +2899,21 @@
         <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2">
+        <v>30</v>
+      </c>
+      <c r="F2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2">
+        <v>5</v>
+      </c>
+      <c r="H2">
         <v>25</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B3">
         <v>3</v>
@@ -2363,18 +2922,24 @@
         <v>50</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E3">
         <v>20</v>
       </c>
-      <c r="F3">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="F3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3">
+        <v>10</v>
+      </c>
+      <c r="H3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="B4">
         <v>5</v>
@@ -2383,58 +2948,63 @@
         <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E4">
         <v>40</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4">
+        <v>20</v>
+      </c>
+      <c r="H4">
         <v>60</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="10"/>
-    <col customWidth="1" min="2" max="2" width="15"/>
-    <col customWidth="1" min="3" max="3" width="18"/>
-    <col customWidth="1" min="4" max="4" width="17"/>
-    <col customWidth="1" min="5" max="5" width="18"/>
-    <col customWidth="1" min="6" max="6" width="17"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -2449,12 +3019,12 @@
         <v>90</v>
       </c>
       <c r="F2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -2469,12 +3039,12 @@
         <v>60</v>
       </c>
       <c r="F3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -2492,9 +3062,9 @@
         <v>120</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -2512,52 +3082,111 @@
         <v>180</v>
       </c>
     </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>120</v>
+      </c>
+      <c r="F6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>5</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>5</v>
+      </c>
+      <c r="E8">
+        <v>300</v>
+      </c>
+      <c r="F8" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col customWidth="1" min="1" max="4" width="10"/>
-    <col customWidth="1" min="5" max="5" width="11"/>
-    <col customWidth="1" min="6" max="7" width="12"/>
+    <col min="1" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="6" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -2566,21 +3195,21 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C3">
         <v>5</v>
@@ -2589,21 +3218,21 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -2612,131 +3241,199 @@
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G4">
         <v>3</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
-      <c r="D5" t="s">
-        <v>26</v>
+      <c r="D5">
+        <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>66</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="F5" t="s">
+        <v>30</v>
       </c>
       <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
-      <c r="D6" t="s">
-        <v>26</v>
+      <c r="D6">
+        <v>1</v>
       </c>
       <c r="E6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>66</v>
       </c>
-      <c r="F6">
-        <v>3</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>68</v>
-      </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>78</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" t="s">
+        <v>78</v>
+      </c>
+      <c r="F8">
+        <v>3</v>
+      </c>
+      <c r="G8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>69</v>
       </c>
-      <c r="B8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8">
+      <c r="B9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" t="s">
+        <v>78</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11">
         <v>10</v>
       </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" t="s">
-        <v>26</v>
-      </c>
-      <c r="G8" t="s">
-        <v>26</v>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col customWidth="1" min="1" max="2" width="10"/>
+    <col min="1" max="2" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2744,7 +3441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2752,7 +3449,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2760,7 +3457,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2768,7 +3465,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2776,7 +3473,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2784,7 +3481,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2792,7 +3489,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2800,7 +3497,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2808,7 +3505,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2817,46 +3514,53 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="10"/>
-    <col customWidth="1" min="2" max="4" width="11"/>
-    <col customWidth="1" min="5" max="5" width="18"/>
-    <col customWidth="1" min="6" max="6" width="10"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="2">
+        <v>88</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="B2">
         <v>100</v>
@@ -2865,18 +3569,24 @@
         <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2">
+        <v>30</v>
+      </c>
+      <c r="E2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2">
         <v>45</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="H2" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="B3">
         <v>250</v>
@@ -2885,78 +3595,102 @@
         <v>50</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3">
+        <v>30</v>
+      </c>
+      <c r="E3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3">
         <v>60</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="H3" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="B4">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4">
-        <v>30</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>30</v>
+      </c>
+      <c r="E4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4">
+        <v>30</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="B5">
         <v>150</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5">
+        <v>30</v>
+      </c>
+      <c r="E5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5">
         <v>45</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="H5" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="B6">
         <v>100</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6">
-        <v>30</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>30</v>
+      </c>
+      <c r="E6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6">
+        <v>30</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="B7">
         <v>150</v>
@@ -2965,84 +3699,173 @@
         <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7">
+        <v>30</v>
+      </c>
+      <c r="E7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7">
         <v>60</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="8">
+      <c r="H7" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="B8">
         <v>400</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D8">
         <v>30</v>
       </c>
-      <c r="E8">
+      <c r="E8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8">
         <v>90</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>82</v>
+      <c r="H8" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>98</v>
+      </c>
+      <c r="B9">
+        <v>100</v>
+      </c>
+      <c r="C9">
+        <v>25</v>
+      </c>
+      <c r="D9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9">
+        <v>45</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B10">
+        <v>100</v>
+      </c>
+      <c r="C10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10">
+        <v>20</v>
+      </c>
+      <c r="E10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10">
+        <v>45</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>100</v>
+      </c>
+      <c r="B11">
+        <v>250</v>
+      </c>
+      <c r="C11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11">
+        <v>30</v>
+      </c>
+      <c r="F11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11">
+        <v>60</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="10"/>
-    <col customWidth="1" min="2" max="2" width="11"/>
-    <col customWidth="1" min="3" max="3" width="13"/>
-    <col customWidth="1" min="4" max="4" width="11"/>
-    <col customWidth="1" min="5" max="5" width="18"/>
-    <col customWidth="1" min="6" max="6" width="15"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="2">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="B2">
         <v>50</v>
       </c>
       <c r="C2">
-        <v>2.2000000000000002</v>
+        <v>2.2</v>
       </c>
       <c r="D2">
         <v>5</v>
@@ -3051,12 +3874,12 @@
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="B3">
         <v>75</v>
@@ -3068,15 +3891,15 @@
         <v>5</v>
       </c>
       <c r="E3">
-        <v>0.050000000000000003</v>
+        <v>0.05</v>
       </c>
       <c r="F3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="B4">
         <v>200</v>
@@ -3091,12 +3914,12 @@
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="B5">
         <v>100</v>
@@ -3108,15 +3931,15 @@
         <v>4</v>
       </c>
       <c r="E5">
-        <v>0.050000000000000003</v>
+        <v>0.05</v>
       </c>
       <c r="F5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="B6">
         <v>150</v>
@@ -3128,262 +3951,317 @@
         <v>5</v>
       </c>
       <c r="E6">
-        <v>0.10000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="F6" t="s">
-        <v>80</v>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B7">
+        <v>100</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>111</v>
+      </c>
+      <c r="B8">
+        <v>100</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>112</v>
+      </c>
+      <c r="B9">
+        <v>150</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <v>3</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col customWidth="1" min="1" max="2" width="10"/>
-    <col customWidth="1" min="3" max="3" width="17"/>
+    <col min="1" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="2">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C2">
         <v>-1</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B24"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="40.28125"/>
-    <col customWidth="1" min="2" max="2" width="10"/>
+    <col min="1" max="2" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="B3">
         <v>8</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="B4">
         <v>0.5</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="B5">
         <v>20</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="B7">
         <v>30</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="B8">
         <v>5</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="B9">
         <v>8</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="B11">
         <v>1.25</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="B13">
         <v>0</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="B14">
         <v>0</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="B15">
         <v>5</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="B16">
         <v>1.45</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="B20">
         <v>4</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="B22">
         <v>3</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="B23">
         <v>10</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="B24">
         <v>3</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -160,7 +160,7 @@
     <t>Quarry</t>
   </si>
   <si>
-    <t>FishingHut</t>
+    <t>Docks</t>
   </si>
   <si>
     <t>Mine</t>
@@ -3359,7 +3359,7 @@
         <v>78</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9">
         <v>2</v>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -1707,7 +1707,7 @@
         <v>46</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9">
         <v>1</v>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -2337,7 +2337,7 @@
         <v>144</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="N11" s="3" t="s">
         <v>149</v>
@@ -3119,7 +3119,7 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>150</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -3789,7 +3789,7 @@
         <v>45</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -12,15 +12,16 @@
     <sheet sheetId="6" name="Technologies" state="visible" r:id="rId9"/>
     <sheet sheetId="7" name="Upgrades" state="visible" r:id="rId10"/>
     <sheet sheetId="8" name="Adjacency" state="visible" r:id="rId11"/>
-    <sheet sheetId="9" name="Settings" state="visible" r:id="rId12"/>
-    <sheet sheetId="10" name="Map" state="visible" r:id="rId13"/>
+    <sheet sheetId="9" name="Quests" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="Settings" state="visible" r:id="rId13"/>
+    <sheet sheetId="11" name="Map" state="visible" r:id="rId14"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="227">
   <si>
     <t>id</t>
   </si>
@@ -368,6 +369,213 @@
   </si>
   <si>
     <t>gold_per_minute</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>goal_type</t>
+  </si>
+  <si>
+    <t>goal_target</t>
+  </si>
+  <si>
+    <t>goal_amount</t>
+  </si>
+  <si>
+    <t>goal_level</t>
+  </si>
+  <si>
+    <t>reward_gold</t>
+  </si>
+  <si>
+    <t>reward_wood</t>
+  </si>
+  <si>
+    <t>reward_food</t>
+  </si>
+  <si>
+    <t>reward_stone</t>
+  </si>
+  <si>
+    <t>reward_iron</t>
+  </si>
+  <si>
+    <t>FirstSteps</t>
+  </si>
+  <si>
+    <t>First steps</t>
+  </si>
+  <si>
+    <t>Tap the forest next to your Townhall to gather Wood.</t>
+  </si>
+  <si>
+    <t>CollectTaps</t>
+  </si>
+  <si>
+    <t>Timber</t>
+  </si>
+  <si>
+    <t>Timber!</t>
+  </si>
+  <si>
+    <t>Stockpile 10 Wood — enough for your first building.</t>
+  </si>
+  <si>
+    <t>HoldResource</t>
+  </si>
+  <si>
+    <t>ARoof</t>
+  </si>
+  <si>
+    <t>A roof</t>
+  </si>
+  <si>
+    <t>Build a Housing next to the Townhall.</t>
+  </si>
+  <si>
+    <t>BuildDistrict</t>
+  </si>
+  <si>
+    <t>FirstVillager</t>
+  </si>
+  <si>
+    <t>First villager</t>
+  </si>
+  <si>
+    <t>Train a villager at the Townhall — berries make fine rations.</t>
+  </si>
+  <si>
+    <t>ReachPopulation</t>
+  </si>
+  <si>
+    <t>Explorer</t>
+  </si>
+  <si>
+    <t>Spend Gold on the misty frontier — reveal 6 new map cells.</t>
+  </si>
+  <si>
+    <t>DiscoverCells</t>
+  </si>
+  <si>
+    <t>TaxDay</t>
+  </si>
+  <si>
+    <t>Tax day</t>
+  </si>
+  <si>
+    <t>Collect 30 Gold — housed villagers pay taxes every minute.</t>
+  </si>
+  <si>
+    <t>CollectResource</t>
+  </si>
+  <si>
+    <t>Woodcraft</t>
+  </si>
+  <si>
+    <t>Research Forestry — the root of the technology tree.</t>
+  </si>
+  <si>
+    <t>CompleteTech</t>
+  </si>
+  <si>
+    <t>TheSawmill</t>
+  </si>
+  <si>
+    <t>The Sawmill</t>
+  </si>
+  <si>
+    <t>Build a Sawmill near the forest.</t>
+  </si>
+  <si>
+    <t>ToWork</t>
+  </si>
+  <si>
+    <t>Put them to work</t>
+  </si>
+  <si>
+    <t>Assign a worker — they will chop wood for you.</t>
+  </si>
+  <si>
+    <t>AssignWorkers</t>
+  </si>
+  <si>
+    <t>GrowingTown</t>
+  </si>
+  <si>
+    <t>Growing town</t>
+  </si>
+  <si>
+    <t>Build a second Housing — mind the crowding penalty!</t>
+  </si>
+  <si>
+    <t>Neighbors</t>
+  </si>
+  <si>
+    <t>Reach a population of 2.</t>
+  </si>
+  <si>
+    <t>PickARoute</t>
+  </si>
+  <si>
+    <t>Pick a route</t>
+  </si>
+  <si>
+    <t>Research 3 technologies — farm the land or fish the sea, your call.</t>
+  </si>
+  <si>
+    <t>CompleteTechs</t>
+  </si>
+  <si>
+    <t>Stoneworks</t>
+  </si>
+  <si>
+    <t>Build a Quarry — Stone builds the future.</t>
+  </si>
+  <si>
+    <t>ToMarket</t>
+  </si>
+  <si>
+    <t>To market</t>
+  </si>
+  <si>
+    <t>Build the Market and open trade.</t>
+  </si>
+  <si>
+    <t>Merchant</t>
+  </si>
+  <si>
+    <t>Sell 20 goods at the Market.</t>
+  </si>
+  <si>
+    <t>SellGoods</t>
+  </si>
+  <si>
+    <t>FirstSoldier</t>
+  </si>
+  <si>
+    <t>First soldier</t>
+  </si>
+  <si>
+    <t>Train your first army unit — iron wins wars.</t>
+  </si>
+  <si>
+    <t>TrainArmy</t>
+  </si>
+  <si>
+    <t>ProperCapital</t>
+  </si>
+  <si>
+    <t>A proper capital</t>
+  </si>
+  <si>
+    <t>Upgrade the Townhall to level 2.</t>
+  </si>
+  <si>
+    <t>UpgradeDistrict</t>
   </si>
   <si>
     <t>key</t>
@@ -1888,6 +2096,212 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B24"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="2" width="10" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>189</v>
+      </c>
+      <c r="B4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>190</v>
+      </c>
+      <c r="B5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>191</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>192</v>
+      </c>
+      <c r="B7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>193</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>194</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>195</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>196</v>
+      </c>
+      <c r="B11">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>197</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>198</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>199</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>200</v>
+      </c>
+      <c r="B15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>201</v>
+      </c>
+      <c r="B16">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>202</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>203</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>205</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>206</v>
+      </c>
+      <c r="B20">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>207</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>208</v>
+      </c>
+      <c r="B22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>209</v>
+      </c>
+      <c r="B23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>210</v>
+      </c>
+      <c r="B24">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -1959,25 +2373,25 @@
         <v>-10</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>142</v>
+        <v>211</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>142</v>
+        <v>211</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>142</v>
+        <v>211</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>142</v>
+        <v>211</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>142</v>
+        <v>211</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>142</v>
+        <v>211</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>142</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -1985,31 +2399,31 @@
         <v>-9</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>142</v>
+        <v>211</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>143</v>
+        <v>212</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>142</v>
+        <v>211</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>142</v>
+        <v>211</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>142</v>
+        <v>211</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>143</v>
+        <v>212</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>142</v>
+        <v>211</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>142</v>
+        <v>211</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>142</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -2017,31 +2431,31 @@
         <v>-8</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>142</v>
+        <v>211</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>142</v>
+        <v>211</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>143</v>
+        <v>212</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>142</v>
+        <v>211</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>142</v>
+        <v>211</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>142</v>
+        <v>211</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>142</v>
+        <v>211</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>143</v>
+        <v>212</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>142</v>
+        <v>211</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -2049,43 +2463,43 @@
         <v>-7</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>145</v>
+        <v>214</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>145</v>
+        <v>214</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>145</v>
+        <v>214</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>145</v>
+        <v>214</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>146</v>
+        <v>215</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>145</v>
+        <v>214</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>145</v>
+        <v>214</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>145</v>
+        <v>214</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>145</v>
+        <v>214</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -2093,28 +2507,28 @@
         <v>-6</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -2122,34 +2536,34 @@
         <v>-5</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
@@ -2157,46 +2571,46 @@
         <v>-4</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>148</v>
+        <v>217</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>149</v>
+        <v>218</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -2204,55 +2618,55 @@
         <v>-3</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>150</v>
+        <v>219</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>151</v>
+        <v>220</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>151</v>
+        <v>220</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -2260,52 +2674,52 @@
         <v>-2</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>151</v>
+        <v>220</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>151</v>
+        <v>220</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>152</v>
+        <v>221</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -2313,52 +2727,52 @@
         <v>-1</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>150</v>
+        <v>219</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>149</v>
+        <v>218</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>151</v>
+        <v>220</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>153</v>
+        <v>222</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>151</v>
+        <v>220</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>151</v>
+        <v>220</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -2366,55 +2780,55 @@
         <v>0</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>154</v>
+        <v>223</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>151</v>
+        <v>220</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>151</v>
+        <v>220</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>151</v>
+        <v>220</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>153</v>
+        <v>222</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -2422,58 +2836,58 @@
         <v>1</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>151</v>
+        <v>220</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>151</v>
+        <v>220</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>153</v>
+        <v>222</v>
       </c>
       <c r="T13" s="3" t="s">
-        <v>151</v>
+        <v>220</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -2481,58 +2895,58 @@
         <v>2</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>150</v>
+        <v>219</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>155</v>
+        <v>224</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>156</v>
+        <v>225</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>151</v>
+        <v>220</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>151</v>
+        <v>220</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>151</v>
+        <v>220</v>
       </c>
       <c r="T14" s="3" t="s">
-        <v>151</v>
+        <v>220</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -2540,61 +2954,61 @@
         <v>3</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>156</v>
+        <v>225</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>156</v>
+        <v>225</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>156</v>
+        <v>225</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>156</v>
+        <v>225</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>156</v>
+        <v>225</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>151</v>
+        <v>220</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>153</v>
+        <v>222</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>151</v>
+        <v>220</v>
       </c>
       <c r="T15" s="3" t="s">
-        <v>151</v>
+        <v>220</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -2602,58 +3016,58 @@
         <v>4</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>150</v>
+        <v>219</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>156</v>
+        <v>225</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>156</v>
+        <v>225</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>156</v>
+        <v>225</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>156</v>
+        <v>225</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>156</v>
+        <v>225</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>157</v>
+        <v>226</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>151</v>
+        <v>220</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>151</v>
+        <v>220</v>
       </c>
       <c r="T16" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
@@ -2661,58 +3075,58 @@
         <v>5</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>156</v>
+        <v>225</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>156</v>
+        <v>225</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>151</v>
+        <v>220</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>151</v>
+        <v>220</v>
       </c>
       <c r="T17" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
@@ -2720,49 +3134,49 @@
         <v>6</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>150</v>
+        <v>219</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>148</v>
+        <v>217</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
@@ -2770,37 +3184,37 @@
         <v>7</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>150</v>
+        <v>219</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
     </row>
   </sheetData>
@@ -4062,202 +4476,701 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="6" width="13" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="10" width="13" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
+    <col min="12" max="12" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D1" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+      <c r="B2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2">
+        <v>10</v>
+      </c>
+      <c r="I2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2" t="s">
+        <v>30</v>
+      </c>
+      <c r="L2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>119</v>
-      </c>
-      <c r="B3">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+      <c r="B3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E3" t="s">
+        <v>79</v>
+      </c>
+      <c r="F3">
+        <v>10</v>
+      </c>
+      <c r="G3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3">
+        <v>15</v>
+      </c>
+      <c r="I3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>120</v>
-      </c>
-      <c r="B4">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+      <c r="B4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4">
+        <v>20</v>
+      </c>
+      <c r="I4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>121</v>
-      </c>
-      <c r="B5">
+        <v>139</v>
+      </c>
+      <c r="B5" t="s">
+        <v>140</v>
+      </c>
+      <c r="C5" t="s">
+        <v>141</v>
+      </c>
+      <c r="D5" t="s">
+        <v>142</v>
+      </c>
+      <c r="E5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5">
+        <v>25</v>
+      </c>
+      <c r="I5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5" t="s">
+        <v>30</v>
+      </c>
+      <c r="K5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C6" t="s">
+        <v>144</v>
+      </c>
+      <c r="D6" t="s">
+        <v>145</v>
+      </c>
+      <c r="E6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6">
+        <v>6</v>
+      </c>
+      <c r="G6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>122</v>
-      </c>
-      <c r="B6">
+      <c r="I6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6" t="s">
+        <v>30</v>
+      </c>
+      <c r="K6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B7" t="s">
+        <v>147</v>
+      </c>
+      <c r="C7" t="s">
+        <v>148</v>
+      </c>
+      <c r="D7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E7" t="s">
+        <v>77</v>
+      </c>
+      <c r="F7">
+        <v>30</v>
+      </c>
+      <c r="G7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7">
+        <v>20</v>
+      </c>
+      <c r="I7">
+        <v>10</v>
+      </c>
+      <c r="J7" t="s">
+        <v>30</v>
+      </c>
+      <c r="K7" t="s">
+        <v>30</v>
+      </c>
+      <c r="L7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>150</v>
+      </c>
+      <c r="B8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C8" t="s">
+        <v>151</v>
+      </c>
+      <c r="D8" t="s">
+        <v>152</v>
+      </c>
+      <c r="E8" t="s">
+        <v>92</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
+        <v>30</v>
+      </c>
+      <c r="H8">
+        <v>40</v>
+      </c>
+      <c r="I8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J8" t="s">
+        <v>30</v>
+      </c>
+      <c r="K8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>153</v>
+      </c>
+      <c r="B9" t="s">
+        <v>154</v>
+      </c>
+      <c r="C9" t="s">
+        <v>155</v>
+      </c>
+      <c r="D9" t="s">
+        <v>138</v>
+      </c>
+      <c r="E9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9">
+        <v>30</v>
+      </c>
+      <c r="I9" t="s">
+        <v>30</v>
+      </c>
+      <c r="J9" t="s">
+        <v>30</v>
+      </c>
+      <c r="K9" t="s">
+        <v>30</v>
+      </c>
+      <c r="L9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>156</v>
+      </c>
+      <c r="B10" t="s">
+        <v>157</v>
+      </c>
+      <c r="C10" t="s">
+        <v>158</v>
+      </c>
+      <c r="D10" t="s">
+        <v>159</v>
+      </c>
+      <c r="E10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H10">
+        <v>30</v>
+      </c>
+      <c r="I10" t="s">
+        <v>30</v>
+      </c>
+      <c r="J10" t="s">
+        <v>30</v>
+      </c>
+      <c r="K10" t="s">
+        <v>30</v>
+      </c>
+      <c r="L10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>160</v>
+      </c>
+      <c r="B11" t="s">
+        <v>161</v>
+      </c>
+      <c r="C11" t="s">
+        <v>162</v>
+      </c>
+      <c r="D11" t="s">
+        <v>138</v>
+      </c>
+      <c r="E11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>123</v>
-      </c>
-      <c r="B7">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>124</v>
-      </c>
-      <c r="B8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>125</v>
-      </c>
-      <c r="B9">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>126</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>127</v>
-      </c>
-      <c r="B11">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11">
+        <v>40</v>
+      </c>
+      <c r="I11" t="s">
+        <v>30</v>
+      </c>
+      <c r="J11" t="s">
+        <v>30</v>
+      </c>
+      <c r="K11" t="s">
+        <v>30</v>
+      </c>
+      <c r="L11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>128</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="B12" t="s">
+        <v>163</v>
+      </c>
+      <c r="C12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D12" t="s">
+        <v>142</v>
+      </c>
+      <c r="E12" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12">
+        <v>2</v>
+      </c>
+      <c r="G12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H12">
+        <v>50</v>
+      </c>
+      <c r="I12" t="s">
+        <v>30</v>
+      </c>
+      <c r="J12" t="s">
+        <v>30</v>
+      </c>
+      <c r="K12" t="s">
+        <v>30</v>
+      </c>
+      <c r="L12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>129</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+      <c r="B13" t="s">
+        <v>166</v>
+      </c>
+      <c r="C13" t="s">
+        <v>167</v>
+      </c>
+      <c r="D13" t="s">
+        <v>168</v>
+      </c>
+      <c r="E13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13">
+        <v>3</v>
+      </c>
+      <c r="G13" t="s">
+        <v>30</v>
+      </c>
+      <c r="H13">
+        <v>60</v>
+      </c>
+      <c r="I13" t="s">
+        <v>30</v>
+      </c>
+      <c r="J13" t="s">
+        <v>30</v>
+      </c>
+      <c r="K13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>130</v>
-      </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+      <c r="B14" t="s">
+        <v>169</v>
+      </c>
+      <c r="C14" t="s">
+        <v>170</v>
+      </c>
+      <c r="D14" t="s">
+        <v>138</v>
+      </c>
+      <c r="E14" t="s">
+        <v>45</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14" t="s">
+        <v>30</v>
+      </c>
+      <c r="H14">
+        <v>50</v>
+      </c>
+      <c r="I14" t="s">
+        <v>30</v>
+      </c>
+      <c r="J14">
+        <v>20</v>
+      </c>
+      <c r="K14" t="s">
+        <v>30</v>
+      </c>
+      <c r="L14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>131</v>
-      </c>
-      <c r="B15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+      <c r="B15" t="s">
+        <v>172</v>
+      </c>
+      <c r="C15" t="s">
+        <v>173</v>
+      </c>
+      <c r="D15" t="s">
+        <v>138</v>
+      </c>
+      <c r="E15" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15" t="s">
+        <v>30</v>
+      </c>
+      <c r="H15">
+        <v>80</v>
+      </c>
+      <c r="I15" t="s">
+        <v>30</v>
+      </c>
+      <c r="J15" t="s">
+        <v>30</v>
+      </c>
+      <c r="K15" t="s">
+        <v>30</v>
+      </c>
+      <c r="L15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>132</v>
-      </c>
-      <c r="B16">
-        <v>1.45</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+        <v>174</v>
+      </c>
+      <c r="B16" t="s">
+        <v>174</v>
+      </c>
+      <c r="C16" t="s">
+        <v>175</v>
+      </c>
+      <c r="D16" t="s">
+        <v>176</v>
+      </c>
+      <c r="E16" t="s">
+        <v>30</v>
+      </c>
+      <c r="F16">
+        <v>20</v>
+      </c>
+      <c r="G16" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16">
+        <v>100</v>
+      </c>
+      <c r="I16" t="s">
+        <v>30</v>
+      </c>
+      <c r="J16" t="s">
+        <v>30</v>
+      </c>
+      <c r="K16" t="s">
+        <v>30</v>
+      </c>
+      <c r="L16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>133</v>
-      </c>
-      <c r="B17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+      <c r="B17" t="s">
+        <v>178</v>
+      </c>
+      <c r="C17" t="s">
+        <v>179</v>
+      </c>
+      <c r="D17" t="s">
+        <v>180</v>
+      </c>
+      <c r="E17" t="s">
+        <v>30</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H17">
+        <v>100</v>
+      </c>
+      <c r="I17" t="s">
+        <v>30</v>
+      </c>
+      <c r="J17" t="s">
+        <v>30</v>
+      </c>
+      <c r="K17" t="s">
+        <v>30</v>
+      </c>
+      <c r="L17" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>134</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>136</v>
-      </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>137</v>
-      </c>
-      <c r="B20">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>138</v>
-      </c>
-      <c r="B21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>139</v>
-      </c>
-      <c r="B22">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>140</v>
-      </c>
-      <c r="B23">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>141</v>
-      </c>
-      <c r="B24">
-        <v>3</v>
+        <v>181</v>
+      </c>
+      <c r="B18" t="s">
+        <v>182</v>
+      </c>
+      <c r="C18" t="s">
+        <v>183</v>
+      </c>
+      <c r="D18" t="s">
+        <v>184</v>
+      </c>
+      <c r="E18" t="s">
+        <v>29</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>2</v>
+      </c>
+      <c r="H18">
+        <v>150</v>
+      </c>
+      <c r="I18" t="s">
+        <v>30</v>
+      </c>
+      <c r="J18" t="s">
+        <v>30</v>
+      </c>
+      <c r="K18" t="s">
+        <v>30</v>
+      </c>
+      <c r="L18" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="229">
   <si>
     <t>id</t>
   </si>
@@ -438,6 +438,12 @@
   </si>
   <si>
     <t>BuildDistrict</t>
+  </si>
+  <si>
+    <t>Rations</t>
+  </si>
+  <si>
+    <t>Gather 3 Food for your first villager — the berry bushes will do.</t>
   </si>
   <si>
     <t>FirstVillager</t>
@@ -2104,15 +2110,15 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -2120,7 +2126,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B3">
         <v>8</v>
@@ -2128,7 +2134,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B4">
         <v>0.5</v>
@@ -2136,7 +2142,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B5">
         <v>20</v>
@@ -2144,7 +2150,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -2152,7 +2158,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B7">
         <v>30</v>
@@ -2160,7 +2166,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B8">
         <v>5</v>
@@ -2168,7 +2174,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B9">
         <v>8</v>
@@ -2176,7 +2182,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -2184,7 +2190,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B11">
         <v>1.25</v>
@@ -2192,7 +2198,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2200,7 +2206,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2208,7 +2214,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2216,7 +2222,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B15">
         <v>5</v>
@@ -2224,7 +2230,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B16">
         <v>1.45</v>
@@ -2232,7 +2238,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -2240,15 +2246,15 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -2256,7 +2262,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B20">
         <v>4</v>
@@ -2264,7 +2270,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -2272,7 +2278,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B22">
         <v>3</v>
@@ -2280,7 +2286,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B23">
         <v>10</v>
@@ -2288,7 +2294,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B24">
         <v>3</v>
@@ -2373,25 +2379,25 @@
         <v>-10</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -2399,31 +2405,31 @@
         <v>-9</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -2431,31 +2437,31 @@
         <v>-8</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -2463,43 +2469,43 @@
         <v>-7</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -2507,28 +2513,28 @@
         <v>-6</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -2536,34 +2542,34 @@
         <v>-5</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
@@ -2571,46 +2577,46 @@
         <v>-4</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -2618,55 +2624,55 @@
         <v>-3</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -2674,52 +2680,52 @@
         <v>-2</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -2727,52 +2733,52 @@
         <v>-1</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="R11" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="S11" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="S11" s="3" t="s">
-        <v>220</v>
-      </c>
       <c r="T11" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -2780,55 +2786,55 @@
         <v>0</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -2836,58 +2842,58 @@
         <v>1</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="S13" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="T13" s="3" t="s">
         <v>222</v>
-      </c>
-      <c r="T13" s="3" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -2895,58 +2901,58 @@
         <v>2</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="T14" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -2954,61 +2960,61 @@
         <v>3</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="R15" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="S15" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>220</v>
-      </c>
       <c r="T15" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -3016,58 +3022,58 @@
         <v>4</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="T16" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
@@ -3075,58 +3081,58 @@
         <v>5</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="T17" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
@@ -3134,49 +3140,49 @@
         <v>6</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F18" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="N18" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>217</v>
-      </c>
       <c r="O18" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
@@ -3184,37 +3190,37 @@
         <v>7</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>
@@ -4476,7 +4482,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
@@ -4646,25 +4652,25 @@
         <v>139</v>
       </c>
       <c r="B5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C5" t="s">
         <v>140</v>
       </c>
-      <c r="C5" t="s">
-        <v>141</v>
-      </c>
       <c r="D5" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
+        <v>78</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G5" t="s">
         <v>30</v>
       </c>
       <c r="H5">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="I5" t="s">
         <v>30</v>
@@ -4681,28 +4687,28 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B6" t="s">
+        <v>142</v>
+      </c>
+      <c r="C6" t="s">
         <v>143</v>
       </c>
-      <c r="B6" t="s">
-        <v>143</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>144</v>
       </c>
-      <c r="D6" t="s">
-        <v>145</v>
-      </c>
       <c r="E6" t="s">
         <v>30</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G6" t="s">
         <v>30</v>
       </c>
       <c r="H6">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I6" t="s">
         <v>30</v>
@@ -4719,22 +4725,22 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>145</v>
+      </c>
+      <c r="B7" t="s">
+        <v>145</v>
+      </c>
+      <c r="C7" t="s">
         <v>146</v>
       </c>
-      <c r="B7" t="s">
+      <c r="D7" t="s">
         <v>147</v>
       </c>
-      <c r="C7" t="s">
-        <v>148</v>
-      </c>
-      <c r="D7" t="s">
-        <v>149</v>
-      </c>
       <c r="E7" t="s">
-        <v>77</v>
+        <v>30</v>
       </c>
       <c r="F7">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="G7" t="s">
         <v>30</v>
@@ -4742,8 +4748,8 @@
       <c r="H7">
         <v>20</v>
       </c>
-      <c r="I7">
-        <v>10</v>
+      <c r="I7" t="s">
+        <v>30</v>
       </c>
       <c r="J7" t="s">
         <v>30</v>
@@ -4757,31 +4763,31 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>148</v>
+      </c>
+      <c r="B8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C8" t="s">
         <v>150</v>
       </c>
-      <c r="B8" t="s">
-        <v>92</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>151</v>
       </c>
-      <c r="D8" t="s">
-        <v>152</v>
-      </c>
       <c r="E8" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="G8" t="s">
         <v>30</v>
       </c>
       <c r="H8">
-        <v>40</v>
-      </c>
-      <c r="I8" t="s">
-        <v>30</v>
+        <v>20</v>
+      </c>
+      <c r="I8">
+        <v>10</v>
       </c>
       <c r="J8" t="s">
         <v>30</v>
@@ -4795,28 +4801,28 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>152</v>
+      </c>
+      <c r="B9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C9" t="s">
         <v>153</v>
       </c>
-      <c r="B9" t="s">
+      <c r="D9" t="s">
         <v>154</v>
       </c>
-      <c r="C9" t="s">
-        <v>155</v>
-      </c>
-      <c r="D9" t="s">
-        <v>138</v>
-      </c>
       <c r="E9" t="s">
+        <v>92</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9">
         <v>40</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9" t="s">
-        <v>30</v>
-      </c>
-      <c r="H9">
-        <v>30</v>
       </c>
       <c r="I9" t="s">
         <v>30</v>
@@ -4833,19 +4839,19 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>155</v>
+      </c>
+      <c r="B10" t="s">
         <v>156</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>157</v>
       </c>
-      <c r="C10" t="s">
-        <v>158</v>
-      </c>
       <c r="D10" t="s">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="E10" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -4871,28 +4877,28 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>158</v>
+      </c>
+      <c r="B11" t="s">
+        <v>159</v>
+      </c>
+      <c r="C11" t="s">
         <v>160</v>
       </c>
-      <c r="B11" t="s">
+      <c r="D11" t="s">
         <v>161</v>
       </c>
-      <c r="C11" t="s">
-        <v>162</v>
-      </c>
-      <c r="D11" t="s">
-        <v>138</v>
-      </c>
       <c r="E11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" t="s">
         <v>30</v>
       </c>
       <c r="H11">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I11" t="s">
         <v>30</v>
@@ -4909,7 +4915,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B12" t="s">
         <v>163</v>
@@ -4918,10 +4924,10 @@
         <v>164</v>
       </c>
       <c r="D12" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="E12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F12">
         <v>2</v>
@@ -4930,7 +4936,7 @@
         <v>30</v>
       </c>
       <c r="H12">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I12" t="s">
         <v>30</v>
@@ -4950,25 +4956,25 @@
         <v>165</v>
       </c>
       <c r="B13" t="s">
+        <v>165</v>
+      </c>
+      <c r="C13" t="s">
         <v>166</v>
       </c>
-      <c r="C13" t="s">
-        <v>167</v>
-      </c>
       <c r="D13" t="s">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="E13" t="s">
         <v>30</v>
       </c>
       <c r="F13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G13" t="s">
         <v>30</v>
       </c>
       <c r="H13">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I13" t="s">
         <v>30</v>
@@ -4985,34 +4991,34 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>167</v>
+      </c>
+      <c r="B14" t="s">
+        <v>168</v>
+      </c>
+      <c r="C14" t="s">
         <v>169</v>
       </c>
-      <c r="B14" t="s">
-        <v>169</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>170</v>
       </c>
-      <c r="D14" t="s">
-        <v>138</v>
-      </c>
       <c r="E14" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G14" t="s">
         <v>30</v>
       </c>
       <c r="H14">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I14" t="s">
         <v>30</v>
       </c>
-      <c r="J14">
-        <v>20</v>
+      <c r="J14" t="s">
+        <v>30</v>
       </c>
       <c r="K14" t="s">
         <v>30</v>
@@ -5026,16 +5032,16 @@
         <v>171</v>
       </c>
       <c r="B15" t="s">
+        <v>171</v>
+      </c>
+      <c r="C15" t="s">
         <v>172</v>
-      </c>
-      <c r="C15" t="s">
-        <v>173</v>
       </c>
       <c r="D15" t="s">
         <v>138</v>
       </c>
       <c r="E15" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -5044,13 +5050,13 @@
         <v>30</v>
       </c>
       <c r="H15">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="I15" t="s">
         <v>30</v>
       </c>
-      <c r="J15" t="s">
-        <v>30</v>
+      <c r="J15">
+        <v>20</v>
       </c>
       <c r="K15" t="s">
         <v>30</v>
@@ -5061,7 +5067,7 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B16" t="s">
         <v>174</v>
@@ -5070,19 +5076,19 @@
         <v>175</v>
       </c>
       <c r="D16" t="s">
-        <v>176</v>
+        <v>138</v>
       </c>
       <c r="E16" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="F16">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G16" t="s">
         <v>30</v>
       </c>
       <c r="H16">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="I16" t="s">
         <v>30</v>
@@ -5099,22 +5105,22 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>176</v>
+      </c>
+      <c r="B17" t="s">
+        <v>176</v>
+      </c>
+      <c r="C17" t="s">
         <v>177</v>
       </c>
-      <c r="B17" t="s">
+      <c r="D17" t="s">
         <v>178</v>
       </c>
-      <c r="C17" t="s">
-        <v>179</v>
-      </c>
-      <c r="D17" t="s">
-        <v>180</v>
-      </c>
       <c r="E17" t="s">
         <v>30</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="G17" t="s">
         <v>30</v>
@@ -5137,39 +5143,77 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>179</v>
+      </c>
+      <c r="B18" t="s">
+        <v>180</v>
+      </c>
+      <c r="C18" t="s">
         <v>181</v>
       </c>
-      <c r="B18" t="s">
+      <c r="D18" t="s">
         <v>182</v>
       </c>
-      <c r="C18" t="s">
+      <c r="E18" t="s">
+        <v>30</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18" t="s">
+        <v>30</v>
+      </c>
+      <c r="H18">
+        <v>100</v>
+      </c>
+      <c r="I18" t="s">
+        <v>30</v>
+      </c>
+      <c r="J18" t="s">
+        <v>30</v>
+      </c>
+      <c r="K18" t="s">
+        <v>30</v>
+      </c>
+      <c r="L18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>183</v>
       </c>
-      <c r="D18" t="s">
+      <c r="B19" t="s">
         <v>184</v>
       </c>
-      <c r="E18" t="s">
+      <c r="C19" t="s">
+        <v>185</v>
+      </c>
+      <c r="D19" t="s">
+        <v>186</v>
+      </c>
+      <c r="E19" t="s">
         <v>29</v>
       </c>
-      <c r="F18">
-        <v>1</v>
-      </c>
-      <c r="G18">
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
         <v>2</v>
       </c>
-      <c r="H18">
+      <c r="H19">
         <v>150</v>
       </c>
-      <c r="I18" t="s">
-        <v>30</v>
-      </c>
-      <c r="J18" t="s">
-        <v>30</v>
-      </c>
-      <c r="K18" t="s">
-        <v>30</v>
-      </c>
-      <c r="L18" t="s">
+      <c r="I19" t="s">
+        <v>30</v>
+      </c>
+      <c r="J19" t="s">
+        <v>30</v>
+      </c>
+      <c r="K19" t="s">
+        <v>30</v>
+      </c>
+      <c r="L19" t="s">
         <v>30</v>
       </c>
     </row>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -1,27 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <workbookPr/>
+  <bookViews>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="6"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Districts" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Units" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Harvest" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="Currencies" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="FogRings" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="Technologies" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="Upgrades" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="Adjacency" state="visible" r:id="rId11"/>
-    <sheet sheetId="9" name="Quests" state="visible" r:id="rId12"/>
-    <sheet sheetId="10" name="Settings" state="visible" r:id="rId13"/>
-    <sheet sheetId="11" name="Map" state="visible" r:id="rId14"/>
+    <sheet name="Districts" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Units" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Harvest" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Currencies" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="FogRings" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Technologies" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Upgrades" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Adjacency" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Quests" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Settings" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Map" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="269">
   <si>
     <t>id</t>
   </si>
@@ -56,6 +61,9 @@
     <t>required_townhall_level_per_level</t>
   </si>
   <si>
+    <t>required_tech_per_level</t>
+  </si>
+  <si>
     <t>build_cost_gold</t>
   </si>
   <si>
@@ -116,12 +124,21 @@
     <t/>
   </si>
   <si>
+    <t>-,Architecture</t>
+  </si>
+  <si>
     <t>Housing</t>
   </si>
   <si>
     <t>2,4</t>
   </si>
   <si>
+    <t>2,4,6</t>
+  </si>
+  <si>
+    <t>UrbanPlanning</t>
+  </si>
+  <si>
     <t>Farm</t>
   </si>
   <si>
@@ -134,7 +151,10 @@
     <t>1,2</t>
   </si>
   <si>
-    <t>2,2</t>
+    <t>2</t>
+  </si>
+  <si>
+    <t>CropRotation</t>
   </si>
   <si>
     <t>FarmLands</t>
@@ -152,6 +172,12 @@
     <t>1,2,3</t>
   </si>
   <si>
+    <t>2,3,4</t>
+  </si>
+  <si>
+    <t>-,Engineering</t>
+  </si>
+  <si>
     <t>Market</t>
   </si>
   <si>
@@ -161,12 +187,24 @@
     <t>Quarry</t>
   </si>
   <si>
+    <t>Engineering</t>
+  </si>
+  <si>
     <t>Docks</t>
   </si>
   <si>
+    <t>4,6</t>
+  </si>
+  <si>
+    <t>Shipbuilding</t>
+  </si>
+  <si>
     <t>Mine</t>
   </si>
   <si>
+    <t>DeepMining</t>
+  </si>
+  <si>
     <t>power</t>
   </si>
   <si>
@@ -188,12 +226,15 @@
     <t>train_duration_seconds</t>
   </si>
   <si>
+    <t>Warrior</t>
+  </si>
+  <si>
+    <t>Lancer</t>
+  </si>
+  <si>
     <t>Archer</t>
   </si>
   <si>
-    <t>Swordsman</t>
-  </si>
-  <si>
     <t>Cavalry</t>
   </si>
   <si>
@@ -296,36 +337,42 @@
     <t>requires</t>
   </si>
   <si>
+    <t>Forestry</t>
+  </si>
+  <si>
+    <t>Communities</t>
+  </si>
+  <si>
+    <t>Architecture</t>
+  </si>
+  <si>
     <t>Agriculture</t>
   </si>
   <si>
-    <t>Forestry</t>
-  </si>
-  <si>
-    <t>Irrigation</t>
-  </si>
-  <si>
-    <t>Commerce</t>
-  </si>
-  <si>
-    <t>Militia</t>
+    <t>Farming</t>
+  </si>
+  <si>
+    <t>Masonry</t>
+  </si>
+  <si>
+    <t>Mining</t>
+  </si>
+  <si>
+    <t>Sailing</t>
+  </si>
+  <si>
+    <t>Fishing</t>
+  </si>
+  <si>
+    <t>ScalingTools</t>
+  </si>
+  <si>
+    <t>Spears</t>
   </si>
   <si>
     <t>Archery</t>
   </si>
   <si>
-    <t>CavalryTraining</t>
-  </si>
-  <si>
-    <t>Masonry</t>
-  </si>
-  <si>
-    <t>Fishing</t>
-  </si>
-  <si>
-    <t>Mining</t>
-  </si>
-  <si>
     <t>cost_base</t>
   </si>
   <si>
@@ -341,9 +388,6 @@
     <t>TapPower</t>
   </si>
   <si>
-    <t>QuickHands</t>
-  </si>
-  <si>
     <t>WorkerLoad</t>
   </si>
   <si>
@@ -404,13 +448,16 @@
     <t>reward_iron</t>
   </si>
   <si>
+    <t>reward_gems</t>
+  </si>
+  <si>
     <t>FirstSteps</t>
   </si>
   <si>
-    <t>First steps</t>
-  </si>
-  <si>
-    <t>Tap the forest next to your Townhall to gather Wood.</t>
+    <t xml:space="preserve">First steps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tap the forest next to your Townhall to gather Wood.</t>
   </si>
   <si>
     <t>CollectTaps</t>
@@ -422,7 +469,7 @@
     <t>Timber!</t>
   </si>
   <si>
-    <t>Stockpile 10 Wood — enough for your first building.</t>
+    <t xml:space="preserve">Stockpile 10 Wood — enough for your first building.</t>
   </si>
   <si>
     <t>HoldResource</t>
@@ -431,10 +478,10 @@
     <t>ARoof</t>
   </si>
   <si>
-    <t>A roof</t>
-  </si>
-  <si>
-    <t>Build a Housing next to the Townhall.</t>
+    <t xml:space="preserve">A roof</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Build a Housing next to the Townhall.</t>
   </si>
   <si>
     <t>BuildDistrict</t>
@@ -443,16 +490,16 @@
     <t>Rations</t>
   </si>
   <si>
-    <t>Gather 3 Food for your first villager — the berry bushes will do.</t>
+    <t xml:space="preserve">Gather 3 Food for your first villager — the berry bushes will do.</t>
   </si>
   <si>
     <t>FirstVillager</t>
   </si>
   <si>
-    <t>First villager</t>
-  </si>
-  <si>
-    <t>Train a villager at the Townhall — berries make fine rations.</t>
+    <t xml:space="preserve">First villager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train a villager at the Townhall — berries make fine rations.</t>
   </si>
   <si>
     <t>ReachPopulation</t>
@@ -461,7 +508,7 @@
     <t>Explorer</t>
   </si>
   <si>
-    <t>Spend Gold on the misty frontier — reveal 6 new map cells.</t>
+    <t xml:space="preserve">Spend Gold on the misty frontier — reveal 6 new map cells.</t>
   </si>
   <si>
     <t>DiscoverCells</t>
@@ -470,10 +517,10 @@
     <t>TaxDay</t>
   </si>
   <si>
-    <t>Tax day</t>
-  </si>
-  <si>
-    <t>Collect 30 Gold — housed villagers pay taxes every minute.</t>
+    <t xml:space="preserve">Tax day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collect 30 Gold — housed villagers pay taxes every minute.</t>
   </si>
   <si>
     <t>CollectResource</t>
@@ -482,7 +529,7 @@
     <t>Woodcraft</t>
   </si>
   <si>
-    <t>Research Forestry — the root of the technology tree.</t>
+    <t xml:space="preserve">Research Forestry — the root of the technology tree.</t>
   </si>
   <si>
     <t>CompleteTech</t>
@@ -491,19 +538,19 @@
     <t>TheSawmill</t>
   </si>
   <si>
-    <t>The Sawmill</t>
-  </si>
-  <si>
-    <t>Build a Sawmill near the forest.</t>
+    <t xml:space="preserve">The Sawmill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Build a Sawmill near the forest.</t>
   </si>
   <si>
     <t>ToWork</t>
   </si>
   <si>
-    <t>Put them to work</t>
-  </si>
-  <si>
-    <t>Assign a worker — they will chop wood for you.</t>
+    <t xml:space="preserve">Put them to work</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assign a worker — they will chop wood for you.</t>
   </si>
   <si>
     <t>AssignWorkers</t>
@@ -512,25 +559,25 @@
     <t>GrowingTown</t>
   </si>
   <si>
-    <t>Growing town</t>
-  </si>
-  <si>
-    <t>Build a second Housing — mind the crowding penalty!</t>
+    <t xml:space="preserve">Growing town</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Build a second Housing — mind the crowding penalty!</t>
   </si>
   <si>
     <t>Neighbors</t>
   </si>
   <si>
-    <t>Reach a population of 2.</t>
+    <t xml:space="preserve">Reach a population of 2.</t>
   </si>
   <si>
     <t>PickARoute</t>
   </si>
   <si>
-    <t>Pick a route</t>
-  </si>
-  <si>
-    <t>Research 3 technologies — farm the land or fish the sea, your call.</t>
+    <t xml:space="preserve">Pick a route</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research 3 technologies — farm the land or fish the sea, your call.</t>
   </si>
   <si>
     <t>CompleteTechs</t>
@@ -539,49 +586,127 @@
     <t>Stoneworks</t>
   </si>
   <si>
-    <t>Build a Quarry — Stone builds the future.</t>
+    <t xml:space="preserve">Build a Quarry — Stone builds the future.</t>
   </si>
   <si>
     <t>ToMarket</t>
   </si>
   <si>
-    <t>To market</t>
-  </si>
-  <si>
-    <t>Build the Market and open trade.</t>
+    <t xml:space="preserve">To market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Build the Market and open trade.</t>
   </si>
   <si>
     <t>Merchant</t>
   </si>
   <si>
-    <t>Sell 20 goods at the Market.</t>
+    <t xml:space="preserve">Sell 20 goods at the Market.</t>
   </si>
   <si>
     <t>SellGoods</t>
   </si>
   <si>
+    <t>ProperCapital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A proper capital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upgrade the Townhall to level 2.</t>
+  </si>
+  <si>
+    <t>UpgradeDistrict</t>
+  </si>
+  <si>
+    <t>MoreRoom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">More room</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research Urban Planning — homes with a second story.</t>
+  </si>
+  <si>
+    <t>SecondStory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Second story</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upgrade a Housing to level 2 — an extra resident under the same roof.</t>
+  </si>
+  <si>
+    <t>FullHouse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full house</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reach a population of 6.</t>
+  </si>
+  <si>
     <t>FirstSoldier</t>
   </si>
   <si>
-    <t>First soldier</t>
-  </si>
-  <si>
-    <t>Train your first army unit — iron wins wars.</t>
+    <t xml:space="preserve">First soldier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muster your first army unit — every capital needs a guard.</t>
   </si>
   <si>
     <t>TrainArmy</t>
   </si>
   <si>
-    <t>ProperCapital</t>
-  </si>
-  <si>
-    <t>A proper capital</t>
-  </si>
-  <si>
-    <t>Upgrade the Townhall to level 2.</t>
-  </si>
-  <si>
-    <t>UpgradeDistrict</t>
+    <t>RunningWater</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fields of plenty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research Farming — it unlocks the Farm.</t>
+  </si>
+  <si>
+    <t>Farmhand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Build a Farm — its workers harvest nearby crop plots for you.</t>
+  </si>
+  <si>
+    <t>IronRoad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The iron road</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Push the frontier to the iron veins and collect 10 Iron.</t>
+  </si>
+  <si>
+    <t>TheMine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Mine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Build a Mine near the iron veins.</t>
+  </si>
+  <si>
+    <t>Architect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The architect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research Architecture — iron-braced monuments.</t>
+  </si>
+  <si>
+    <t>GrandCapital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A grand capital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upgrade the Townhall to level 3.</t>
   </si>
   <si>
     <t>key</t>
@@ -662,13 +787,16 @@
     <t>research.slot_gem_cost_growth</t>
   </si>
   <si>
+    <t>w</t>
+  </si>
+  <si>
     <t>s</t>
   </si>
   <si>
-    <t>sI</t>
-  </si>
-  <si>
-    <t>w</t>
+    <t>mI</t>
+  </si>
+  <si>
+    <t>m</t>
   </si>
   <si>
     <t>u</t>
@@ -677,34 +805,31 @@
     <t>uA</t>
   </si>
   <si>
+    <t>wF</t>
+  </si>
+  <si>
     <t>g</t>
   </si>
   <si>
     <t>A</t>
   </si>
   <si>
+    <t>T</t>
+  </si>
+  <si>
     <t>R</t>
   </si>
   <si>
-    <t>wF</t>
-  </si>
-  <si>
     <t>p</t>
   </si>
   <si>
     <t>pT</t>
   </si>
   <si>
-    <t>pR</t>
-  </si>
-  <si>
-    <t>wB</t>
+    <t>mR</t>
   </si>
   <si>
     <t>B</t>
-  </si>
-  <si>
-    <t>T</t>
   </si>
   <si>
     <t>pA</t>
@@ -713,14 +838,13 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2">
     <font>
+      <sz val="11.000000"/>
       <color theme="1"/>
-      <family val="2"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
@@ -736,113 +860,28 @@
   </fills>
   <borders count="1">
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF6FA84F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF3D6F9E"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF9AA34F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFC9B26A"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFDFE7EC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF8B9A94"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF2E6B2E"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF7A4FA8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF8A5A34"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF7A7F87"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF2E86AB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF4A4E57"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -855,7 +894,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -901,13 +940,13 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Thai" typeface="Angsana New"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
@@ -930,19 +969,18 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Thai" typeface="Cordia New"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
@@ -965,7 +1003,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1000,16 +1037,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -1131,9 +1172,226 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
   <a:objectDefaults>
     <a:spDef>
-      <a:spPr/>
+      <a:spPr bwMode="auto"/>
       <a:bodyPr/>
       <a:lstStyle/>
       <a:style>
@@ -1152,7 +1410,7 @@
       </a:style>
     </a:spDef>
     <a:lnDef>
-      <a:spPr/>
+      <a:spPr bwMode="auto"/>
       <a:bodyPr/>
       <a:lstStyle/>
       <a:style>
@@ -1171,40 +1429,39 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AC10"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="21" customWidth="1"/>
-    <col min="6" max="6" width="19" customWidth="1"/>
-    <col min="7" max="7" width="21" customWidth="1"/>
-    <col min="8" max="8" width="23" customWidth="1"/>
-    <col min="9" max="9" width="30" customWidth="1"/>
-    <col min="10" max="10" width="28" customWidth="1"/>
-    <col min="11" max="11" width="35" customWidth="1"/>
-    <col min="12" max="14" width="17" customWidth="1"/>
-    <col min="15" max="15" width="18" customWidth="1"/>
-    <col min="16" max="16" width="17" customWidth="1"/>
-    <col min="17" max="17" width="23" customWidth="1"/>
-    <col min="18" max="18" width="31" customWidth="1"/>
-    <col min="19" max="19" width="24" customWidth="1"/>
-    <col min="20" max="21" width="32" customWidth="1"/>
-    <col min="22" max="24" width="19" customWidth="1"/>
-    <col min="25" max="25" width="20" customWidth="1"/>
-    <col min="26" max="26" width="19" customWidth="1"/>
-    <col min="27" max="27" width="27" customWidth="1"/>
-    <col min="28" max="28" width="26" customWidth="1"/>
-    <col min="29" max="29" width="31" customWidth="1"/>
+    <col customWidth="1" min="1" max="3" width="10"/>
+    <col customWidth="1" min="4" max="4" width="11"/>
+    <col customWidth="1" min="5" max="5" width="21"/>
+    <col customWidth="1" min="6" max="6" width="19"/>
+    <col customWidth="1" min="7" max="7" width="21"/>
+    <col customWidth="1" min="8" max="8" width="23"/>
+    <col customWidth="1" min="9" max="9" width="30"/>
+    <col customWidth="1" min="10" max="10" width="28"/>
+    <col customWidth="1" min="11" max="11" width="35"/>
+    <col customWidth="1" min="12" max="12" width="25"/>
+    <col customWidth="1" min="13" max="15" width="17"/>
+    <col customWidth="1" min="16" max="16" width="18"/>
+    <col customWidth="1" min="17" max="17" width="17"/>
+    <col customWidth="1" min="18" max="18" width="23"/>
+    <col customWidth="1" min="19" max="19" width="31"/>
+    <col customWidth="1" min="20" max="20" width="24"/>
+    <col customWidth="1" min="21" max="22" width="32"/>
+    <col customWidth="1" min="23" max="25" width="19"/>
+    <col customWidth="1" min="26" max="26" width="20"/>
+    <col customWidth="1" min="27" max="27" width="19"/>
+    <col customWidth="1" min="28" max="28" width="27"/>
+    <col customWidth="1" min="29" max="29" width="26"/>
+    <col customWidth="1" min="30" max="30" width="31"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1292,10 +1549,13 @@
       <c r="AC1" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -1304,10 +1564,10 @@
         <v>2</v>
       </c>
       <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -1316,87 +1576,90 @@
         <v>3</v>
       </c>
       <c r="H2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M2" t="s">
+        <v>31</v>
+      </c>
+      <c r="N2" t="s">
+        <v>31</v>
+      </c>
+      <c r="O2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>31</v>
+      </c>
+      <c r="R2">
+        <v>2</v>
+      </c>
+      <c r="S2">
+        <v>1.2</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>1.2</v>
+      </c>
+      <c r="V2">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="W2" t="s">
+        <v>31</v>
+      </c>
+      <c r="X2">
+        <v>40</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z2">
+        <v>20</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB2">
+        <v>3.8999999999999999</v>
+      </c>
+      <c r="AC2">
         <v>30</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="L2" t="s">
-        <v>30</v>
-      </c>
-      <c r="M2" t="s">
-        <v>30</v>
-      </c>
-      <c r="N2" t="s">
-        <v>30</v>
-      </c>
-      <c r="O2" t="s">
-        <v>30</v>
-      </c>
-      <c r="P2" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q2">
+      <c r="AD2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
         <v>2</v>
       </c>
-      <c r="R2">
-        <v>1.2</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <v>1.2</v>
-      </c>
-      <c r="U2">
-        <v>1.15</v>
-      </c>
-      <c r="V2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W2">
-        <v>25</v>
-      </c>
-      <c r="X2" t="s">
-        <v>30</v>
-      </c>
-      <c r="Y2">
-        <v>25</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA2">
-        <v>1.5</v>
-      </c>
-      <c r="AB2">
-        <v>0</v>
-      </c>
-      <c r="AC2">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
+      <c r="E3" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -1405,75 +1668,78 @@
         <v>2</v>
       </c>
       <c r="H3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N3">
+        <v>10</v>
+      </c>
+      <c r="O3" t="s">
+        <v>31</v>
+      </c>
+      <c r="P3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R3">
+        <v>1.25</v>
+      </c>
+      <c r="S3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="T3">
+        <v>20</v>
+      </c>
+      <c r="U3">
+        <v>1.2</v>
+      </c>
+      <c r="V3">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="W3" t="s">
+        <v>31</v>
+      </c>
+      <c r="X3">
         <v>30</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="L3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M3">
+      <c r="Y3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z3">
         <v>10</v>
       </c>
-      <c r="N3" t="s">
-        <v>30</v>
-      </c>
-      <c r="O3" t="s">
-        <v>30</v>
-      </c>
-      <c r="P3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q3">
-        <v>1.25</v>
-      </c>
-      <c r="R3">
-        <v>1.1</v>
-      </c>
-      <c r="S3">
+      <c r="AA3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB3">
+        <v>1.5</v>
+      </c>
+      <c r="AC3">
         <v>20</v>
       </c>
-      <c r="T3">
-        <v>1.2</v>
-      </c>
-      <c r="U3">
-        <v>1.15</v>
-      </c>
-      <c r="V3" t="s">
-        <v>30</v>
-      </c>
-      <c r="W3" t="s">
-        <v>30</v>
-      </c>
-      <c r="X3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA3">
+      <c r="AD3">
         <v>1.5</v>
       </c>
-      <c r="AB3">
-        <v>0</v>
-      </c>
-      <c r="AC3">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -1484,8 +1750,8 @@
       <c r="D4">
         <v>2</v>
       </c>
-      <c r="E4">
-        <v>0</v>
+      <c r="E4" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -1494,75 +1760,78 @@
         <v>2</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="L4" t="s">
+        <v>41</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M4" t="s">
+        <v>31</v>
+      </c>
+      <c r="N4">
         <v>30</v>
       </c>
-      <c r="M4">
-        <v>10</v>
-      </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
+        <v>31</v>
+      </c>
+      <c r="P4" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>31</v>
+      </c>
+      <c r="R4">
+        <v>2</v>
+      </c>
+      <c r="S4">
+        <v>1.5</v>
+      </c>
+      <c r="T4">
+        <v>20</v>
+      </c>
+      <c r="U4">
+        <v>1.2</v>
+      </c>
+      <c r="V4">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="W4" t="s">
+        <v>31</v>
+      </c>
+      <c r="X4">
+        <v>50</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>31</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB4">
+        <v>1.5</v>
+      </c>
+      <c r="AC4">
         <v>30</v>
       </c>
-      <c r="O4" t="s">
-        <v>30</v>
-      </c>
-      <c r="P4" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q4">
-        <v>2</v>
-      </c>
-      <c r="R4">
+      <c r="AD4">
         <v>1.5</v>
       </c>
-      <c r="S4">
-        <v>20</v>
-      </c>
-      <c r="T4">
-        <v>1.2</v>
-      </c>
-      <c r="U4">
-        <v>1.15</v>
-      </c>
-      <c r="V4" t="s">
-        <v>30</v>
-      </c>
-      <c r="W4">
-        <v>50</v>
-      </c>
-      <c r="X4" t="s">
-        <v>30</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA4">
-        <v>1.5</v>
-      </c>
-      <c r="AB4">
-        <v>30</v>
-      </c>
-      <c r="AC4">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -1573,8 +1842,8 @@
       <c r="D5">
         <v>1</v>
       </c>
-      <c r="E5">
-        <v>0</v>
+      <c r="E5" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -1583,75 +1852,78 @@
         <v>2</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="L5" t="s">
-        <v>30</v>
-      </c>
-      <c r="M5">
+        <v>31</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M5" t="s">
+        <v>31</v>
+      </c>
+      <c r="N5">
         <v>20</v>
       </c>
-      <c r="N5" t="s">
-        <v>30</v>
-      </c>
       <c r="O5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P5" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q5">
+        <v>31</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>31</v>
+      </c>
+      <c r="R5">
         <v>2</v>
       </c>
-      <c r="R5">
+      <c r="S5">
         <v>1.2</v>
       </c>
-      <c r="S5">
+      <c r="T5">
         <v>10</v>
       </c>
-      <c r="T5">
+      <c r="U5">
         <v>1.2</v>
       </c>
-      <c r="U5">
-        <v>1.15</v>
-      </c>
-      <c r="V5" t="s">
-        <v>30</v>
+      <c r="V5">
+        <v>1.1499999999999999</v>
       </c>
       <c r="W5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Y5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Z5" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA5">
+        <v>31</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB5">
         <v>1.5</v>
       </c>
-      <c r="AB5">
+      <c r="AC5">
         <v>0</v>
       </c>
-      <c r="AC5">
+      <c r="AD5">
         <v>1.5</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -1662,8 +1934,8 @@
       <c r="D6">
         <v>3</v>
       </c>
-      <c r="E6">
-        <v>0</v>
+      <c r="E6" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1672,75 +1944,78 @@
         <v>2</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L6" t="s">
+        <v>40</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="M6" t="s">
+        <v>31</v>
+      </c>
+      <c r="N6">
+        <v>20</v>
+      </c>
+      <c r="O6" t="s">
+        <v>31</v>
+      </c>
+      <c r="P6" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>31</v>
+      </c>
+      <c r="R6">
+        <v>2.5</v>
+      </c>
+      <c r="S6">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="T6">
+        <v>20</v>
+      </c>
+      <c r="U6">
+        <v>1.2</v>
+      </c>
+      <c r="V6">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="W6" t="s">
+        <v>31</v>
+      </c>
+      <c r="X6">
+        <v>60</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>31</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB6">
+        <v>2.5</v>
+      </c>
+      <c r="AC6">
         <v>30</v>
       </c>
-      <c r="M6">
-        <v>20</v>
-      </c>
-      <c r="N6" t="s">
-        <v>30</v>
-      </c>
-      <c r="O6" t="s">
-        <v>30</v>
-      </c>
-      <c r="P6" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q6">
-        <v>4</v>
-      </c>
-      <c r="R6">
-        <v>1.45</v>
-      </c>
-      <c r="S6">
-        <v>20</v>
-      </c>
-      <c r="T6">
-        <v>1.2</v>
-      </c>
-      <c r="U6">
-        <v>1.15</v>
-      </c>
-      <c r="V6" t="s">
-        <v>30</v>
-      </c>
-      <c r="W6" t="s">
-        <v>30</v>
-      </c>
-      <c r="X6" t="s">
-        <v>30</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA6">
+      <c r="AD6">
         <v>1.5</v>
       </c>
-      <c r="AB6">
-        <v>30</v>
-      </c>
-      <c r="AC6">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7">
       <c r="A7" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -1751,8 +2026,8 @@
       <c r="D7">
         <v>1</v>
       </c>
-      <c r="E7">
-        <v>0</v>
+      <c r="E7" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -1761,75 +2036,78 @@
         <v>2</v>
       </c>
       <c r="H7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M7" t="s">
+        <v>31</v>
+      </c>
+      <c r="N7">
+        <v>40</v>
+      </c>
+      <c r="O7" t="s">
+        <v>31</v>
+      </c>
+      <c r="P7" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>31</v>
+      </c>
+      <c r="R7">
+        <v>2</v>
+      </c>
+      <c r="S7">
+        <v>1.2</v>
+      </c>
+      <c r="T7">
         <v>30</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="L7" t="s">
-        <v>30</v>
-      </c>
-      <c r="M7">
-        <v>40</v>
-      </c>
-      <c r="N7" t="s">
-        <v>30</v>
-      </c>
-      <c r="O7" t="s">
-        <v>30</v>
-      </c>
-      <c r="P7" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q7">
-        <v>2</v>
-      </c>
-      <c r="R7">
+      <c r="U7">
         <v>1.2</v>
       </c>
-      <c r="S7">
-        <v>30</v>
-      </c>
-      <c r="T7">
-        <v>1.2</v>
-      </c>
-      <c r="U7">
-        <v>1.15</v>
-      </c>
-      <c r="V7" t="s">
-        <v>30</v>
+      <c r="V7">
+        <v>1.1499999999999999</v>
       </c>
       <c r="W7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Y7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Z7" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA7">
+        <v>31</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB7">
         <v>1.5</v>
       </c>
-      <c r="AB7">
+      <c r="AC7">
         <v>0</v>
       </c>
-      <c r="AC7">
+      <c r="AD7">
         <v>1.5</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -1840,8 +2118,8 @@
       <c r="D8">
         <v>2</v>
       </c>
-      <c r="E8">
-        <v>0</v>
+      <c r="E8" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -1850,75 +2128,78 @@
         <v>2</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="L8" t="s">
+        <v>41</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="M8" t="s">
+        <v>31</v>
+      </c>
+      <c r="N8">
         <v>30</v>
       </c>
-      <c r="M8">
+      <c r="O8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P8" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R8">
+        <v>2.5</v>
+      </c>
+      <c r="S8">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="T8">
+        <v>20</v>
+      </c>
+      <c r="U8">
+        <v>1.2</v>
+      </c>
+      <c r="V8">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="W8" t="s">
+        <v>31</v>
+      </c>
+      <c r="X8">
+        <v>40</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>31</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB8">
+        <v>1.5</v>
+      </c>
+      <c r="AC8">
         <v>30</v>
       </c>
-      <c r="N8" t="s">
-        <v>30</v>
-      </c>
-      <c r="O8" t="s">
-        <v>30</v>
-      </c>
-      <c r="P8" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q8">
-        <v>4</v>
-      </c>
-      <c r="R8">
-        <v>1.45</v>
-      </c>
-      <c r="S8">
-        <v>20</v>
-      </c>
-      <c r="T8">
-        <v>1.2</v>
-      </c>
-      <c r="U8">
-        <v>1.15</v>
-      </c>
-      <c r="V8" t="s">
-        <v>30</v>
-      </c>
-      <c r="W8">
-        <v>40</v>
-      </c>
-      <c r="X8" t="s">
-        <v>30</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA8">
+      <c r="AD8">
         <v>1.5</v>
       </c>
-      <c r="AB8">
-        <v>30</v>
-      </c>
-      <c r="AC8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9">
       <c r="A9" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -1929,8 +2210,8 @@
       <c r="D9">
         <v>2</v>
       </c>
-      <c r="E9">
-        <v>0</v>
+      <c r="E9" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -1939,75 +2220,78 @@
         <v>2</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="L9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M9" t="s">
+        <v>31</v>
+      </c>
+      <c r="N9">
+        <v>25</v>
+      </c>
+      <c r="O9" t="s">
+        <v>31</v>
+      </c>
+      <c r="P9" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>31</v>
+      </c>
+      <c r="R9">
+        <v>2.5</v>
+      </c>
+      <c r="S9">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="T9">
+        <v>20</v>
+      </c>
+      <c r="U9">
+        <v>1.2</v>
+      </c>
+      <c r="V9">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="W9" t="s">
+        <v>31</v>
+      </c>
+      <c r="X9">
+        <v>35</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>31</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB9">
+        <v>1.5</v>
+      </c>
+      <c r="AC9">
         <v>30</v>
       </c>
-      <c r="M9">
-        <v>25</v>
-      </c>
-      <c r="N9" t="s">
-        <v>30</v>
-      </c>
-      <c r="O9" t="s">
-        <v>30</v>
-      </c>
-      <c r="P9" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q9">
-        <v>4</v>
-      </c>
-      <c r="R9">
-        <v>1.45</v>
-      </c>
-      <c r="S9">
-        <v>20</v>
-      </c>
-      <c r="T9">
-        <v>1.2</v>
-      </c>
-      <c r="U9">
-        <v>1.15</v>
-      </c>
-      <c r="V9" t="s">
-        <v>30</v>
-      </c>
-      <c r="W9">
-        <v>35</v>
-      </c>
-      <c r="X9" t="s">
-        <v>30</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA9">
+      <c r="AD9">
         <v>1.5</v>
       </c>
-      <c r="AB9">
-        <v>30</v>
-      </c>
-      <c r="AC9">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -2018,8 +2302,8 @@
       <c r="D10">
         <v>2</v>
       </c>
-      <c r="E10">
-        <v>0</v>
+      <c r="E10" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -2028,294 +2312,300 @@
         <v>2</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="L10" t="s">
+        <v>41</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="M10" t="s">
+        <v>31</v>
+      </c>
+      <c r="N10">
+        <v>40</v>
+      </c>
+      <c r="O10" t="s">
+        <v>31</v>
+      </c>
+      <c r="P10">
+        <v>20</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>31</v>
+      </c>
+      <c r="R10">
+        <v>2.5</v>
+      </c>
+      <c r="S10">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="T10">
         <v>30</v>
       </c>
-      <c r="M10">
-        <v>40</v>
-      </c>
-      <c r="N10" t="s">
+      <c r="U10">
+        <v>1.2</v>
+      </c>
+      <c r="V10">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="W10" t="s">
+        <v>31</v>
+      </c>
+      <c r="X10">
+        <v>50</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z10">
+        <v>25</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB10">
+        <v>1.5</v>
+      </c>
+      <c r="AC10">
         <v>30</v>
       </c>
-      <c r="O10">
-        <v>20</v>
-      </c>
-      <c r="P10" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q10">
-        <v>4</v>
-      </c>
-      <c r="R10">
-        <v>1.45</v>
-      </c>
-      <c r="S10">
-        <v>30</v>
-      </c>
-      <c r="T10">
-        <v>1.2</v>
-      </c>
-      <c r="U10">
-        <v>1.15</v>
-      </c>
-      <c r="V10" t="s">
-        <v>30</v>
-      </c>
-      <c r="W10">
-        <v>50</v>
-      </c>
-      <c r="X10" t="s">
-        <v>30</v>
-      </c>
-      <c r="Y10">
-        <v>25</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA10">
+      <c r="AD10">
         <v>1.5</v>
       </c>
-      <c r="AB10">
-        <v>30</v>
-      </c>
-      <c r="AC10">
-        <v>1.5</v>
-      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B24"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="2" width="10" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="32.421875"/>
+    <col customWidth="1" min="2" max="2" width="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>187</v>
+        <v>227</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" t="s">
-        <v>189</v>
+        <v>229</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
-        <v>190</v>
+        <v>230</v>
       </c>
       <c r="B3">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
-        <v>191</v>
+        <v>231</v>
       </c>
       <c r="B4">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" t="s">
-        <v>192</v>
+        <v>232</v>
       </c>
       <c r="B5">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
-        <v>193</v>
+        <v>233</v>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
-        <v>194</v>
+        <v>234</v>
       </c>
       <c r="B7">
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
-        <v>195</v>
+        <v>235</v>
       </c>
       <c r="B8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" t="s">
-        <v>196</v>
+        <v>236</v>
       </c>
       <c r="B9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
-        <v>197</v>
+        <v>237</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" t="s">
-        <v>198</v>
+        <v>238</v>
       </c>
       <c r="B11">
         <v>1.25</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" t="s">
-        <v>199</v>
+        <v>239</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" t="s">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="B13">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14">
       <c r="A14" t="s">
-        <v>201</v>
+        <v>241</v>
       </c>
       <c r="B14">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="A15" t="s">
-        <v>202</v>
+        <v>242</v>
       </c>
       <c r="B15">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="A16" t="s">
-        <v>203</v>
+        <v>243</v>
       </c>
       <c r="B16">
         <v>1.45</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="A17" t="s">
-        <v>204</v>
+        <v>244</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18">
       <c r="A18" t="s">
-        <v>205</v>
+        <v>245</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19" t="s">
-        <v>207</v>
+        <v>247</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20">
       <c r="A20" t="s">
-        <v>208</v>
+        <v>248</v>
       </c>
       <c r="B20">
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21">
       <c r="A21" t="s">
-        <v>209</v>
+        <v>249</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22">
       <c r="A22" t="s">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="B22">
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23">
       <c r="A23" t="s">
-        <v>211</v>
+        <v>251</v>
       </c>
       <c r="B23">
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24">
       <c r="A24" t="s">
-        <v>212</v>
+        <v>252</v>
       </c>
       <c r="B24">
         <v>3</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T19"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="20" width="3.5" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="4"/>
+    <col customWidth="1" min="2" max="20" width="3.5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1">
       <c r="B1" s="1">
         <v>-8</v>
       </c>
@@ -2374,1057 +2664,1866 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" s="1">
         <v>-10</v>
       </c>
+      <c r="B2" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F2" t="s">
+        <v>254</v>
+      </c>
       <c r="G2" s="3" t="s">
-        <v>213</v>
+        <v>254</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>213</v>
+        <v>254</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>213</v>
+        <v>254</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>213</v>
+        <v>254</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>213</v>
+        <v>254</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>213</v>
+        <v>254</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+      <c r="N2" t="s">
+        <v>254</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="1">
         <v>-9</v>
       </c>
+      <c r="B3" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>253</v>
+      </c>
       <c r="F3" s="3" t="s">
-        <v>213</v>
+        <v>254</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>214</v>
+        <v>255</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>213</v>
+        <v>256</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>213</v>
+        <v>256</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>213</v>
+        <v>256</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>214</v>
+        <v>255</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>213</v>
+        <v>256</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>213</v>
+        <v>256</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="1">
         <v>-8</v>
       </c>
+      <c r="B4" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>253</v>
+      </c>
       <c r="F4" s="3" t="s">
-        <v>213</v>
+        <v>254</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>213</v>
+        <v>254</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>214</v>
+        <v>255</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>213</v>
+        <v>254</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>213</v>
+        <v>254</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>213</v>
+        <v>254</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>213</v>
+        <v>254</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>214</v>
+        <v>255</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" s="1">
         <v>-7</v>
       </c>
+      <c r="B5" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>253</v>
+      </c>
       <c r="D5" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>216</v>
+        <v>257</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>216</v>
+        <v>257</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>216</v>
+        <v>257</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>216</v>
+        <v>257</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>217</v>
+        <v>258</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>216</v>
+        <v>257</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>216</v>
+        <v>257</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>216</v>
+        <v>257</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>216</v>
+        <v>257</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+        <v>253</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="R5" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="S5" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="T5" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="1">
         <v>-6</v>
       </c>
+      <c r="B6" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>253</v>
+      </c>
       <c r="G6" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+        <v>253</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q6" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="R6" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="S6" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="T6" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" s="1">
         <v>-5</v>
       </c>
+      <c r="B7" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>253</v>
+      </c>
       <c r="E7" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>218</v>
+        <v>256</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>218</v>
+        <v>256</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+        <v>253</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q7" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="R7" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="S7" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="T7" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" s="1">
         <v>-4</v>
       </c>
+      <c r="B8" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>253</v>
+      </c>
       <c r="E8" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>219</v>
+        <v>261</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>218</v>
+        <v>262</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>218</v>
+        <v>262</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>218</v>
+        <v>256</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>220</v>
+        <v>263</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>218</v>
+        <v>256</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>253</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+        <v>253</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" s="1">
         <v>-3</v>
       </c>
+      <c r="B9" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>253</v>
+      </c>
       <c r="D9" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>218</v>
+        <v>256</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>218</v>
+        <v>256</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>218</v>
+        <v>256</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>221</v>
+        <v>259</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>222</v>
+        <v>264</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>222</v>
+        <v>264</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" s="1">
         <v>-2</v>
       </c>
+      <c r="B10" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>253</v>
+      </c>
       <c r="E10" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>215</v>
+        <v>261</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>215</v>
+        <v>256</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>218</v>
+        <v>256</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>222</v>
+        <v>264</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>222</v>
+        <v>264</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>223</v>
+        <v>265</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" s="1">
         <v>-1</v>
       </c>
+      <c r="B11" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>253</v>
+      </c>
       <c r="E11" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>215</v>
+        <v>259</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>215</v>
+        <v>260</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>221</v>
+        <v>256</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>220</v>
+        <v>263</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>222</v>
+        <v>264</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>224</v>
+        <v>266</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>222</v>
+        <v>264</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" s="1">
         <v>0</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>253</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>225</v>
+        <v>253</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>215</v>
+        <v>256</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>218</v>
+        <v>256</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>222</v>
+        <v>264</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>222</v>
+        <v>256</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>222</v>
+        <v>256</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" s="1">
         <v>1</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>253</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>222</v>
+        <v>264</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>222</v>
+        <v>264</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>224</v>
+        <v>266</v>
       </c>
       <c r="T13" s="3" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" s="1">
         <v>2</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>253</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>221</v>
+        <v>259</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>226</v>
+        <v>267</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>227</v>
+        <v>262</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>222</v>
+        <v>264</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>222</v>
+        <v>264</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>222</v>
+        <v>264</v>
       </c>
       <c r="T14" s="3" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15" s="1">
         <v>3</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>227</v>
+        <v>262</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>227</v>
+        <v>262</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>227</v>
+        <v>262</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>227</v>
+        <v>262</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>227</v>
+        <v>262</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>222</v>
+        <v>256</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>224</v>
+        <v>266</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>222</v>
+        <v>264</v>
       </c>
       <c r="T15" s="3" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16" s="1">
         <v>4</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>221</v>
+        <v>259</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>253</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>227</v>
+        <v>262</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>227</v>
+        <v>262</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>227</v>
+        <v>262</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>227</v>
+        <v>262</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>227</v>
+        <v>262</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>228</v>
+        <v>268</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>222</v>
+        <v>264</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>222</v>
+        <v>264</v>
       </c>
       <c r="T16" s="3" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17" s="1">
         <v>5</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>253</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>227</v>
+        <v>262</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>227</v>
+        <v>262</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>222</v>
+        <v>264</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>222</v>
+        <v>264</v>
       </c>
       <c r="T17" s="3" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18" s="1">
         <v>6</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>253</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>221</v>
+        <v>259</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>218</v>
+        <v>262</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>219</v>
+        <v>261</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>253</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+        <v>253</v>
+      </c>
+      <c r="T18" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19" s="1">
         <v>7</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>253</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>221</v>
+        <v>259</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>215</v>
+        <v>253</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="P19" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q19" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="R19" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="S19" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="T19" s="3" t="s">
+        <v>253</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:T19">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>"g"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
-      <formula>"w"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
-      <formula>"p"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
-      <formula>"d"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
-      <formula>"s"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
-      <formula>"u"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
-      <formula>"T"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
-      <formula>"B"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="10" operator="equal">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="11" operator="equal">
-      <formula>"F"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="12" operator="equal">
-      <formula>"I"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
+  <headerFooter/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="1" operator="equal" id="{394D6286-6693-4EA9-B7B9-6FF0603B9B39}">
+            <xm:f>"g"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FF6FA84F"/>
+                  <bgColor rgb="FF6FA84F"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>B2:T19</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="2" operator="equal" id="{60172045-1E50-4F1C-BF3F-F79F1D3636B4}">
+            <xm:f>"w"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FF3D6F9E"/>
+                  <bgColor rgb="FF3D6F9E"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>B2:T19</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="3" operator="equal" id="{1C595258-A8D9-4516-A3D3-8A91755EED46}">
+            <xm:f>"p"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FF9AA34F"/>
+                  <bgColor rgb="FF9AA34F"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>B2:T19</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="4" operator="equal" id="{B5650ECB-641A-433E-BAB0-4860A9292ADA}">
+            <xm:f>"d"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC9B26A"/>
+                  <bgColor rgb="FFC9B26A"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>B2:T19</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="5" operator="equal" id="{5997FEAA-425B-41E5-8A97-EEC9B6826F5F}">
+            <xm:f>"s"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFDFE7EC"/>
+                  <bgColor rgb="FFDFE7EC"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>B2:T19</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="6" operator="equal" id="{16B6DB72-6FA4-4DC5-8014-2F759D253DCE}">
+            <xm:f>"u"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FF8B9A94"/>
+                  <bgColor rgb="FF8B9A94"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>B2:T19</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="7" operator="equal" id="{48C1532A-123C-42BE-B636-F0343B2FA5C2}">
+            <xm:f>"m"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FF6B6F78"/>
+                  <bgColor rgb="FF6B6F78"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>B2:T19</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="8" operator="equal" id="{8855A863-1CFA-4C9A-8F63-242468F556AC}">
+            <xm:f>"T"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FF2E6B2E"/>
+                  <bgColor rgb="FF2E6B2E"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>B2:T19</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="9" operator="equal" id="{1D528E79-040F-48D2-B403-8292D25BEF25}">
+            <xm:f>"B"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FF7A4FA8"/>
+                  <bgColor rgb="FF7A4FA8"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>B2:T19</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="10" operator="equal" id="{03B05B35-F398-4B4D-9467-169378F3E076}">
+            <xm:f>"A"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FF8A5A34"/>
+                  <bgColor rgb="FF8A5A34"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>B2:T19</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="11" operator="equal" id="{1DE05D38-74E7-414C-9D72-F80B37A3EA9F}">
+            <xm:f>"R"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FF7A7F87"/>
+                  <bgColor rgb="FF7A7F87"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>B2:T19</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="12" operator="equal" id="{B2E53F79-3BA1-4FE8-B3CC-0F9ADFCAA39E}">
+            <xm:f>"F"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FF2E86AB"/>
+                  <bgColor rgb="FF2E86AB"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>B2:T19</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="13" operator="equal" id="{102C49CF-189D-4CD0-8DDE-70C93D3F5F16}">
+            <xm:f>"I"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FF4A4E57"/>
+                  <bgColor rgb="FF4A4E57"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>B2:T19</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="14" operator="equal" id="{75265F73-9932-428C-A84D-AC45614F70E8}">
+            <xm:f>"g"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FF6FA84F"/>
+                  <bgColor rgb="FF6FA84F"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>K9</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="15" operator="equal" id="{1E35F7C1-904C-47FE-B537-956F8D6EF408}">
+            <xm:f>"w"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FF3D6F9E"/>
+                  <bgColor rgb="FF3D6F9E"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>K9</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="16" operator="equal" id="{CCD46090-1711-4F8E-B537-2DFCBC6D070E}">
+            <xm:f>"p"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FF9AA34F"/>
+                  <bgColor rgb="FF9AA34F"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>K9</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="17" operator="equal" id="{B8F86281-BDC3-4077-BFA4-7DB6AE892008}">
+            <xm:f>"d"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC9B26A"/>
+                  <bgColor rgb="FFC9B26A"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>K9</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="18" operator="equal" id="{89F90BDE-135E-4B12-9DB7-CF14209235FE}">
+            <xm:f>"s"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFDFE7EC"/>
+                  <bgColor rgb="FFDFE7EC"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>K9</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="19" operator="equal" id="{C4D85565-E83A-464E-9336-2ACC41EF74D7}">
+            <xm:f>"u"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FF8B9A94"/>
+                  <bgColor rgb="FF8B9A94"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>K9</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="20" operator="equal" id="{D5F66C4B-93A8-4FA3-9685-D47729943AC4}">
+            <xm:f>"m"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FF6B6F78"/>
+                  <bgColor rgb="FF6B6F78"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>K9</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="21" operator="equal" id="{95D63185-FEC8-4A00-9324-092B49661A39}">
+            <xm:f>"T"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FF2E6B2E"/>
+                  <bgColor rgb="FF2E6B2E"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>K9</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="22" operator="equal" id="{BB9198CE-B140-47BD-84C1-1EC15EFF9E7F}">
+            <xm:f>"B"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FF7A4FA8"/>
+                  <bgColor rgb="FF7A4FA8"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>K9</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="23" operator="equal" id="{7D71C371-254D-4530-97F6-6F63BF25D477}">
+            <xm:f>"A"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FF8A5A34"/>
+                  <bgColor rgb="FF8A5A34"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>K9</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="24" operator="equal" id="{6B9BCDFE-68F8-4B38-9E6B-46FFCCAB2394}">
+            <xm:f>"R"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FF7A7F87"/>
+                  <bgColor rgb="FF7A7F87"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>K9</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="25" operator="equal" id="{3AE5BAAF-600E-49A4-A583-1BDCFA6918B9}">
+            <xm:f>"F"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FF2E86AB"/>
+                  <bgColor rgb="FF2E86AB"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>K9</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="26" operator="equal" id="{6207FC93-0089-4553-968A-C8B7B6D2C7B1}">
+            <xm:f>"I"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FF4A4E57"/>
+                  <bgColor rgb="FF4A4E57"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>K9</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="27" operator="equal" id="{5FFBD6FE-A491-46CD-A1D3-8052BFB821D1}">
+            <xm:f>"g"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FF6FA84F"/>
+                  <bgColor rgb="FF6FA84F"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>K8</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="28" operator="equal" id="{B505AD14-69C1-4724-AF52-F967A441EC51}">
+            <xm:f>"w"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FF3D6F9E"/>
+                  <bgColor rgb="FF3D6F9E"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>K8</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="29" operator="equal" id="{F9CF96B3-AAEC-497D-8A74-1A6113D5C382}">
+            <xm:f>"p"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FF9AA34F"/>
+                  <bgColor rgb="FF9AA34F"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>K8</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="30" operator="equal" id="{30544D32-056F-4074-85F8-60FC3DF9B705}">
+            <xm:f>"d"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC9B26A"/>
+                  <bgColor rgb="FFC9B26A"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>K8</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="31" operator="equal" id="{8C3FADC2-04C2-43F9-BFB3-6E75CA8500CB}">
+            <xm:f>"s"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFDFE7EC"/>
+                  <bgColor rgb="FFDFE7EC"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>K8</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="32" operator="equal" id="{CC827E8F-AEBD-472A-9762-FC9FF7A71429}">
+            <xm:f>"u"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FF8B9A94"/>
+                  <bgColor rgb="FF8B9A94"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>K8</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="33" operator="equal" id="{EC651E14-A51B-4553-8E62-82D998ED2790}">
+            <xm:f>"m"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FF6B6F78"/>
+                  <bgColor rgb="FF6B6F78"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>K8</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="34" operator="equal" id="{62D3164D-38E0-40CB-A791-75BAF846487E}">
+            <xm:f>"T"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FF2E6B2E"/>
+                  <bgColor rgb="FF2E6B2E"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>K8</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="35" operator="equal" id="{EDA60FA2-733C-4AFB-ADC0-D211CB8C6F90}">
+            <xm:f>"B"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FF7A4FA8"/>
+                  <bgColor rgb="FF7A4FA8"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>K8</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="36" operator="equal" id="{1B2C0567-E919-4CA2-8EE9-4946E1DE1769}">
+            <xm:f>"A"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FF8A5A34"/>
+                  <bgColor rgb="FF8A5A34"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>K8</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="37" operator="equal" id="{DD057452-AD4D-4037-82B8-2D055301CFD9}">
+            <xm:f>"R"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FF7A7F87"/>
+                  <bgColor rgb="FF7A7F87"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>K8</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="38" operator="equal" id="{03815AFC-EDEF-4C1F-966C-997C0E2BB0EE}">
+            <xm:f>"F"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FF2E86AB"/>
+                  <bgColor rgb="FF2E86AB"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>K8</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="39" operator="equal" id="{E4D9DDFF-B33A-4799-A6C3-C6BAF8626ADF}">
+            <xm:f>"I"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FF4A4E57"/>
+                  <bgColor rgb="FF4A4E57"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>K8</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="10" customWidth="1"/>
-    <col min="3" max="5" width="19" customWidth="1"/>
-    <col min="6" max="6" width="20" customWidth="1"/>
-    <col min="7" max="7" width="19" customWidth="1"/>
-    <col min="8" max="8" width="24" customWidth="1"/>
+    <col customWidth="1" min="1" max="2" width="10"/>
+    <col customWidth="1" min="3" max="5" width="19"/>
+    <col customWidth="1" min="6" max="6" width="20"/>
+    <col customWidth="1" min="7" max="7" width="19"/>
+    <col customWidth="1" min="8" max="8" width="24"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
         <v>50</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B2">
+      <c r="D2">
+        <v>10</v>
+      </c>
+      <c r="E2">
+        <v>20</v>
+      </c>
+      <c r="F2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>100</v>
+      </c>
+      <c r="D3">
+        <v>30</v>
+      </c>
+      <c r="E3">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4">
         <v>2</v>
       </c>
-      <c r="C2">
+      <c r="C4">
+        <v>60</v>
+      </c>
+      <c r="D4">
+        <v>30</v>
+      </c>
+      <c r="E4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>150</v>
+      </c>
+      <c r="D5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5">
         <v>40</v>
       </c>
-      <c r="D2">
+      <c r="F5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5">
         <v>20</v>
       </c>
-      <c r="E2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
-      <c r="H2">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="C3">
-        <v>50</v>
-      </c>
-      <c r="D3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3">
-        <v>20</v>
-      </c>
-      <c r="F3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3">
-        <v>10</v>
-      </c>
-      <c r="H3">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B4">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>100</v>
-      </c>
-      <c r="D4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4">
-        <v>40</v>
-      </c>
-      <c r="F4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4">
-        <v>20</v>
-      </c>
-      <c r="H4">
+      <c r="H5">
         <v>60</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="17" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="10"/>
+    <col customWidth="1" min="2" max="2" width="15"/>
+    <col customWidth="1" min="3" max="3" width="18"/>
+    <col customWidth="1" min="4" max="4" width="17"/>
+    <col customWidth="1" min="5" max="5" width="18"/>
+    <col customWidth="1" min="6" max="6" width="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -3439,12 +4538,12 @@
         <v>90</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -3459,12 +4558,12 @@
         <v>60</v>
       </c>
       <c r="F3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -3482,9 +4581,9 @@
         <v>120</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -3502,9 +4601,9 @@
         <v>180</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -3519,12 +4618,12 @@
         <v>120</v>
       </c>
       <c r="F6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -3542,9 +4641,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -3559,54 +4658,55 @@
         <v>300</v>
       </c>
       <c r="F8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="6" max="7" width="12" customWidth="1"/>
+    <col customWidth="1" min="1" max="4" width="10"/>
+    <col customWidth="1" min="5" max="5" width="11"/>
+    <col customWidth="1" min="6" max="7" width="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -3615,44 +4715,44 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -3661,21 +4761,21 @@
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G4">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -3684,21 +4784,21 @@
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G5">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -3707,30 +4807,30 @@
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G6">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E7" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -3739,21 +4839,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E8" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="F8">
         <v>3</v>
@@ -3762,21 +4862,21 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E9" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -3785,35 +4885,35 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G10" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -3822,38 +4922,39 @@
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="10" customWidth="1"/>
+    <col customWidth="1" min="1" max="2" width="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3861,7 +4962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3869,7 +4970,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3877,7 +4978,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3885,7 +4986,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6">
         <v>5</v>
       </c>
@@ -3893,7 +4994,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3901,7 +5002,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3909,7 +5010,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9">
         <v>8</v>
       </c>
@@ -3917,7 +5018,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3925,7 +5026,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11">
         <v>10</v>
       </c>
@@ -3934,358 +5035,620 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="33.28125"/>
+    <col customWidth="1" min="2" max="4" width="11"/>
+    <col customWidth="1" min="5" max="5" width="12"/>
+    <col customWidth="1" min="6" max="6" width="11"/>
+    <col customWidth="1" min="7" max="7" width="18"/>
+    <col customWidth="1" min="8" max="8" width="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="B2">
-        <v>100</v>
-      </c>
-      <c r="C2">
-        <v>25</v>
+        <v>75</v>
+      </c>
+      <c r="C2" t="s">
+        <v>31</v>
       </c>
       <c r="D2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2">
         <v>30</v>
       </c>
-      <c r="E2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G2">
-        <v>45</v>
-      </c>
       <c r="H2" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
-        <v>93</v>
+        <v>36</v>
       </c>
       <c r="B3">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="C3">
         <v>50</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G3">
         <v>60</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="B4">
-        <v>75</v>
-      </c>
-      <c r="C4" t="s">
-        <v>30</v>
+        <v>450</v>
+      </c>
+      <c r="C4">
+        <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G4">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="B5">
-        <v>150</v>
+        <v>600</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="F5">
+        <v>15</v>
       </c>
       <c r="G5">
-        <v>45</v>
+        <v>120</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="B6">
         <v>100</v>
       </c>
-      <c r="C6" t="s">
-        <v>30</v>
+      <c r="C6">
+        <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G6">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="B7">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="C7">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G7">
         <v>60</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" t="s">
-        <v>97</v>
+        <v>50</v>
       </c>
       <c r="B8">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="C8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8">
+        <v>45</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9">
+        <v>300</v>
+      </c>
+      <c r="C9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9">
         <v>30</v>
       </c>
-      <c r="D8">
-        <v>30</v>
-      </c>
-      <c r="E8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G8">
-        <v>90</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>98</v>
-      </c>
-      <c r="B9">
-        <v>100</v>
-      </c>
-      <c r="C9">
-        <v>25</v>
-      </c>
-      <c r="D9" t="s">
-        <v>30</v>
-      </c>
       <c r="E9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G9">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="B10">
         <v>100</v>
       </c>
-      <c r="C10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10">
-        <v>20</v>
+      <c r="C10">
+        <v>25</v>
+      </c>
+      <c r="D10" t="s">
+        <v>31</v>
       </c>
       <c r="E10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G10">
         <v>45</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="B11">
         <v>250</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E11">
         <v>30</v>
       </c>
       <c r="F11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G11">
         <v>60</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>98</v>
+        <v>108</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12">
+        <v>500</v>
+      </c>
+      <c r="C12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12">
+        <v>60</v>
+      </c>
+      <c r="F12" t="s">
+        <v>31</v>
+      </c>
+      <c r="G12">
+        <v>90</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B13">
+        <v>800</v>
+      </c>
+      <c r="C13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13">
+        <v>30</v>
+      </c>
+      <c r="F13" t="s">
+        <v>31</v>
+      </c>
+      <c r="G13">
+        <v>120</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>110</v>
+      </c>
+      <c r="B14">
+        <v>150</v>
+      </c>
+      <c r="C14">
+        <v>30</v>
+      </c>
+      <c r="D14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" t="s">
+        <v>31</v>
+      </c>
+      <c r="G14">
+        <v>45</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>111</v>
+      </c>
+      <c r="B15">
+        <v>100</v>
+      </c>
+      <c r="C15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15">
+        <v>20</v>
+      </c>
+      <c r="E15" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" t="s">
+        <v>31</v>
+      </c>
+      <c r="G15">
+        <v>45</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16">
+        <v>400</v>
+      </c>
+      <c r="C16">
+        <v>40</v>
+      </c>
+      <c r="D16" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" t="s">
+        <v>31</v>
+      </c>
+      <c r="G16">
+        <v>90</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>112</v>
+      </c>
+      <c r="B17">
+        <v>200</v>
+      </c>
+      <c r="C17">
+        <v>25</v>
+      </c>
+      <c r="D17" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" t="s">
+        <v>31</v>
+      </c>
+      <c r="F17" t="s">
+        <v>31</v>
+      </c>
+      <c r="G17">
+        <v>60</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>66</v>
+      </c>
+      <c r="B18">
+        <v>100</v>
+      </c>
+      <c r="C18" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" t="s">
+        <v>31</v>
+      </c>
+      <c r="E18" t="s">
+        <v>31</v>
+      </c>
+      <c r="F18" t="s">
+        <v>31</v>
+      </c>
+      <c r="G18">
+        <v>30</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>113</v>
+      </c>
+      <c r="B19">
+        <v>150</v>
+      </c>
+      <c r="C19">
+        <v>20</v>
+      </c>
+      <c r="D19" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G19">
+        <v>45</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>114</v>
+      </c>
+      <c r="B20">
+        <v>150</v>
+      </c>
+      <c r="C20">
+        <v>20</v>
+      </c>
+      <c r="D20" t="s">
+        <v>31</v>
+      </c>
+      <c r="E20" t="s">
+        <v>31</v>
+      </c>
+      <c r="F20" t="s">
+        <v>31</v>
+      </c>
+      <c r="G20">
+        <v>60</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>69</v>
+      </c>
+      <c r="B21">
+        <v>400</v>
+      </c>
+      <c r="C21" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21">
+        <v>30</v>
+      </c>
+      <c r="E21" t="s">
+        <v>31</v>
+      </c>
+      <c r="F21" t="s">
+        <v>31</v>
+      </c>
+      <c r="G21">
+        <v>90</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="15" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="25.140625"/>
+    <col customWidth="1" min="2" max="2" width="11"/>
+    <col customWidth="1" min="3" max="3" width="13"/>
+    <col customWidth="1" min="4" max="4" width="11"/>
+    <col customWidth="1" min="5" max="5" width="18"/>
+    <col customWidth="1" min="6" max="6" width="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="B2">
         <v>50</v>
       </c>
       <c r="C2">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="D2">
         <v>5</v>
@@ -4294,92 +5657,92 @@
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="B3">
-        <v>75</v>
+        <v>200</v>
       </c>
       <c r="C3">
+        <v>2.5</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B4">
+        <v>100</v>
+      </c>
+      <c r="C4">
         <v>2</v>
       </c>
-      <c r="D3">
-        <v>5</v>
-      </c>
-      <c r="E3">
-        <v>0.05</v>
-      </c>
-      <c r="F3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>107</v>
-      </c>
-      <c r="B4">
-        <v>200</v>
-      </c>
-      <c r="C4">
-        <v>2.5</v>
-      </c>
       <c r="D4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0.050000000000000003</v>
       </c>
       <c r="F4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="B5">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="C5">
         <v>2</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5">
-        <v>0.05</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="F5" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="B6">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="B7">
         <v>100</v>
@@ -4394,15 +5757,15 @@
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="B8">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="C8">
         <v>2</v>
@@ -4414,374 +5777,377 @@
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>112</v>
-      </c>
-      <c r="B9">
-        <v>150</v>
-      </c>
-      <c r="C9">
-        <v>2</v>
-      </c>
-      <c r="D9">
-        <v>3</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="17" customWidth="1"/>
+    <col customWidth="1" min="1" max="2" width="10"/>
+    <col customWidth="1" min="3" max="3" width="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C2">
         <v>-1</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L19"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="6" width="13" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="10" width="13" customWidth="1"/>
-    <col min="11" max="11" width="14" customWidth="1"/>
-    <col min="12" max="12" width="13" customWidth="1"/>
+    <col customWidth="1" min="1" max="2" width="10"/>
+    <col customWidth="1" min="3" max="3" width="13"/>
+    <col customWidth="1" min="4" max="4" width="11"/>
+    <col customWidth="1" min="5" max="6" width="13"/>
+    <col customWidth="1" min="7" max="7" width="12"/>
+    <col customWidth="1" min="8" max="10" width="13"/>
+    <col customWidth="1" min="11" max="11" width="14"/>
+    <col customWidth="1" min="12" max="13" width="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="B2" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="C2" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="D2" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="E2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F2">
         <v>5</v>
       </c>
       <c r="G2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H2">
         <v>10</v>
       </c>
       <c r="I2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="M2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="B3" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="C3" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="D3" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="E3" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="F3">
         <v>10</v>
       </c>
       <c r="G3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H3">
         <v>15</v>
       </c>
       <c r="I3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="M3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="B4" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="C4" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="D4" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H4">
         <v>20</v>
       </c>
       <c r="I4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="M4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="B5" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="C5" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="D5" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="E5" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="F5">
         <v>3</v>
       </c>
       <c r="G5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H5">
         <v>15</v>
       </c>
       <c r="I5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="M5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="B6" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="C6" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="D6" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H6">
         <v>25</v>
       </c>
       <c r="I6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="M6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="B7" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="C7" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="D7" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="E7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F7">
         <v>6</v>
       </c>
       <c r="G7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H7">
         <v>20</v>
       </c>
       <c r="I7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="M7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="B8" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="C8" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="D8" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="E8" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="F8">
         <v>30</v>
       </c>
       <c r="G8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H8">
         <v>20</v>
@@ -4790,369 +6156,399 @@
         <v>10</v>
       </c>
       <c r="J8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="M8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="C9" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="D9" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="E9" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
       <c r="G9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H9">
         <v>40</v>
       </c>
       <c r="I9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L9" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="M9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="B10" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="C10" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="D10" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="E10" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="G10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H10">
         <v>30</v>
       </c>
       <c r="I10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L10" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="M10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="B11" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="C11" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="D11" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="E11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H11">
         <v>30</v>
       </c>
       <c r="I11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="M11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="B12" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="C12" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="D12" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="E12" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F12">
         <v>2</v>
       </c>
       <c r="G12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H12">
         <v>40</v>
       </c>
       <c r="I12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L12" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="M12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="B13" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="C13" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="D13" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="E13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F13">
         <v>2</v>
       </c>
       <c r="G13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H13">
         <v>50</v>
       </c>
       <c r="I13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L13" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="M13" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="B14" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="C14" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="D14" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="E14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F14">
         <v>3</v>
       </c>
       <c r="G14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H14">
         <v>60</v>
       </c>
       <c r="I14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L14" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="M14" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="B15" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="C15" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="D15" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="E15" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F15">
         <v>1</v>
       </c>
       <c r="G15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H15">
         <v>50</v>
       </c>
       <c r="I15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J15">
         <v>20</v>
       </c>
       <c r="K15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L15" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="M15" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="B16" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="C16" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="D16" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="E16" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="F16">
         <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H16">
         <v>80</v>
       </c>
       <c r="I16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L16" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="M16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="B17" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="C17" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="D17" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="E17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F17">
         <v>20</v>
       </c>
       <c r="G17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H17">
         <v>100</v>
       </c>
       <c r="I17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L17" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="M17" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="B18" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="C18" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="D18" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="E18" t="s">
         <v>30</v>
@@ -5160,65 +6556,442 @@
       <c r="F18">
         <v>1</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G18">
+        <v>2</v>
+      </c>
+      <c r="H18">
+        <v>150</v>
+      </c>
+      <c r="I18" t="s">
+        <v>31</v>
+      </c>
+      <c r="J18" t="s">
+        <v>31</v>
+      </c>
+      <c r="K18" t="s">
+        <v>31</v>
+      </c>
+      <c r="L18" t="s">
+        <v>31</v>
+      </c>
+      <c r="M18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>197</v>
+      </c>
+      <c r="B19" t="s">
+        <v>198</v>
+      </c>
+      <c r="C19" t="s">
+        <v>199</v>
+      </c>
+      <c r="D19" t="s">
+        <v>168</v>
+      </c>
+      <c r="E19" t="s">
+        <v>36</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19" t="s">
+        <v>31</v>
+      </c>
+      <c r="H19">
+        <v>60</v>
+      </c>
+      <c r="I19" t="s">
+        <v>31</v>
+      </c>
+      <c r="J19" t="s">
+        <v>31</v>
+      </c>
+      <c r="K19" t="s">
+        <v>31</v>
+      </c>
+      <c r="L19" t="s">
+        <v>31</v>
+      </c>
+      <c r="M19" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>200</v>
+      </c>
+      <c r="B20" t="s">
+        <v>201</v>
+      </c>
+      <c r="C20" t="s">
+        <v>202</v>
+      </c>
+      <c r="D20" t="s">
+        <v>196</v>
+      </c>
+      <c r="E20" t="s">
+        <v>33</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20">
+        <v>2</v>
+      </c>
+      <c r="H20">
+        <v>75</v>
+      </c>
+      <c r="I20" t="s">
+        <v>31</v>
+      </c>
+      <c r="J20" t="s">
+        <v>31</v>
+      </c>
+      <c r="K20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L20" t="s">
+        <v>31</v>
+      </c>
+      <c r="M20" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>203</v>
+      </c>
+      <c r="B21" t="s">
+        <v>204</v>
+      </c>
+      <c r="C21" t="s">
+        <v>205</v>
+      </c>
+      <c r="D21" t="s">
+        <v>158</v>
+      </c>
+      <c r="E21" t="s">
+        <v>31</v>
+      </c>
+      <c r="F21">
+        <v>6</v>
+      </c>
+      <c r="G21" t="s">
+        <v>31</v>
+      </c>
+      <c r="H21">
+        <v>75</v>
+      </c>
+      <c r="I21" t="s">
+        <v>31</v>
+      </c>
+      <c r="J21">
+        <v>20</v>
+      </c>
+      <c r="K21" t="s">
+        <v>31</v>
+      </c>
+      <c r="L21" t="s">
+        <v>31</v>
+      </c>
+      <c r="M21" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>206</v>
+      </c>
+      <c r="B22" t="s">
+        <v>207</v>
+      </c>
+      <c r="C22" t="s">
+        <v>208</v>
+      </c>
+      <c r="D22" t="s">
+        <v>209</v>
+      </c>
+      <c r="E22" t="s">
+        <v>31</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22" t="s">
+        <v>31</v>
+      </c>
+      <c r="H22">
+        <v>100</v>
+      </c>
+      <c r="I22" t="s">
+        <v>31</v>
+      </c>
+      <c r="J22" t="s">
+        <v>31</v>
+      </c>
+      <c r="K22" t="s">
+        <v>31</v>
+      </c>
+      <c r="L22" t="s">
+        <v>31</v>
+      </c>
+      <c r="M22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>210</v>
+      </c>
+      <c r="B23" t="s">
+        <v>211</v>
+      </c>
+      <c r="C23" t="s">
+        <v>212</v>
+      </c>
+      <c r="D23" t="s">
+        <v>168</v>
+      </c>
+      <c r="E23" t="s">
+        <v>107</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23" t="s">
+        <v>31</v>
+      </c>
+      <c r="H23">
+        <v>60</v>
+      </c>
+      <c r="I23" t="s">
+        <v>31</v>
+      </c>
+      <c r="J23" t="s">
+        <v>31</v>
+      </c>
+      <c r="K23" t="s">
+        <v>31</v>
+      </c>
+      <c r="L23" t="s">
+        <v>31</v>
+      </c>
+      <c r="M23" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>213</v>
+      </c>
+      <c r="B24" t="s">
+        <v>213</v>
+      </c>
+      <c r="C24" t="s">
+        <v>214</v>
+      </c>
+      <c r="D24" t="s">
+        <v>152</v>
+      </c>
+      <c r="E24" t="s">
+        <v>37</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24" t="s">
+        <v>31</v>
+      </c>
+      <c r="H24">
+        <v>80</v>
+      </c>
+      <c r="I24" t="s">
+        <v>31</v>
+      </c>
+      <c r="J24" t="s">
+        <v>31</v>
+      </c>
+      <c r="K24" t="s">
+        <v>31</v>
+      </c>
+      <c r="L24" t="s">
+        <v>31</v>
+      </c>
+      <c r="M24" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>215</v>
+      </c>
+      <c r="B25" t="s">
+        <v>216</v>
+      </c>
+      <c r="C25" t="s">
+        <v>217</v>
+      </c>
+      <c r="D25" t="s">
+        <v>165</v>
+      </c>
+      <c r="E25" t="s">
+        <v>82</v>
+      </c>
+      <c r="F25">
+        <v>10</v>
+      </c>
+      <c r="G25" t="s">
+        <v>31</v>
+      </c>
+      <c r="H25">
+        <v>120</v>
+      </c>
+      <c r="I25" t="s">
+        <v>31</v>
+      </c>
+      <c r="J25" t="s">
+        <v>31</v>
+      </c>
+      <c r="K25" t="s">
+        <v>31</v>
+      </c>
+      <c r="L25" t="s">
+        <v>31</v>
+      </c>
+      <c r="M25" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>218</v>
+      </c>
+      <c r="B26" t="s">
+        <v>219</v>
+      </c>
+      <c r="C26" t="s">
+        <v>220</v>
+      </c>
+      <c r="D26" t="s">
+        <v>152</v>
+      </c>
+      <c r="E26" t="s">
+        <v>57</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26" t="s">
+        <v>31</v>
+      </c>
+      <c r="H26">
+        <v>120</v>
+      </c>
+      <c r="I26" t="s">
+        <v>31</v>
+      </c>
+      <c r="J26" t="s">
+        <v>31</v>
+      </c>
+      <c r="K26" t="s">
+        <v>31</v>
+      </c>
+      <c r="L26" t="s">
+        <v>31</v>
+      </c>
+      <c r="M26" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>221</v>
+      </c>
+      <c r="B27" t="s">
+        <v>222</v>
+      </c>
+      <c r="C27" t="s">
+        <v>223</v>
+      </c>
+      <c r="D27" t="s">
+        <v>168</v>
+      </c>
+      <c r="E27" t="s">
+        <v>105</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="G27" t="s">
+        <v>31</v>
+      </c>
+      <c r="H27">
+        <v>150</v>
+      </c>
+      <c r="I27" t="s">
+        <v>31</v>
+      </c>
+      <c r="J27" t="s">
+        <v>31</v>
+      </c>
+      <c r="K27" t="s">
+        <v>31</v>
+      </c>
+      <c r="L27" t="s">
+        <v>31</v>
+      </c>
+      <c r="M27" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>224</v>
+      </c>
+      <c r="B28" t="s">
+        <v>225</v>
+      </c>
+      <c r="C28" t="s">
+        <v>226</v>
+      </c>
+      <c r="D28" t="s">
+        <v>196</v>
+      </c>
+      <c r="E28" t="s">
         <v>30</v>
       </c>
-      <c r="H18">
-        <v>100</v>
-      </c>
-      <c r="I18" t="s">
-        <v>30</v>
-      </c>
-      <c r="J18" t="s">
-        <v>30</v>
-      </c>
-      <c r="K18" t="s">
-        <v>30</v>
-      </c>
-      <c r="L18" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>183</v>
-      </c>
-      <c r="B19" t="s">
-        <v>184</v>
-      </c>
-      <c r="C19" t="s">
-        <v>185</v>
-      </c>
-      <c r="D19" t="s">
-        <v>186</v>
-      </c>
-      <c r="E19" t="s">
-        <v>29</v>
-      </c>
-      <c r="F19">
-        <v>1</v>
-      </c>
-      <c r="G19">
-        <v>2</v>
-      </c>
-      <c r="H19">
-        <v>150</v>
-      </c>
-      <c r="I19" t="s">
-        <v>30</v>
-      </c>
-      <c r="J19" t="s">
-        <v>30</v>
-      </c>
-      <c r="K19" t="s">
-        <v>30</v>
-      </c>
-      <c r="L19" t="s">
-        <v>30</v>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28">
+        <v>3</v>
+      </c>
+      <c r="H28">
+        <v>300</v>
+      </c>
+      <c r="I28" t="s">
+        <v>31</v>
+      </c>
+      <c r="J28" t="s">
+        <v>31</v>
+      </c>
+      <c r="K28" t="s">
+        <v>31</v>
+      </c>
+      <c r="L28" t="s">
+        <v>31</v>
+      </c>
+      <c r="M28">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="270">
   <si>
     <t>id</t>
   </si>
@@ -833,6 +833,9 @@
   </si>
   <si>
     <t>pA</t>
+  </si>
+  <si>
+    <t>QuickHands</t>
   </si>
 </sst>
 </file>
@@ -2426,7 +2429,7 @@
         <v>231</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5">
@@ -5780,6 +5783,26 @@
         <v>109</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>269</v>
+      </c>
+      <c r="B9">
+        <v>75</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <v>5</v>
+      </c>
+      <c r="E9">
+        <v>0.05</v>
+      </c>
+      <c r="F9" t="s">
+        <v>103</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -1,32 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr/>
-  <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="6"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Districts" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Units" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Harvest" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Currencies" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="FogRings" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Technologies" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Upgrades" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Adjacency" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Quests" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Settings" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Map" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet sheetId="1" name="Districts" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Units" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Harvest" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Currencies" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="FogRings" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Technologies" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="Upgrades" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="Adjacency" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="Quests" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="Settings" state="visible" r:id="rId13"/>
+    <sheet sheetId="11" name="Map" state="visible" r:id="rId14"/>
   </sheets>
-  <calcPr/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="270">
   <si>
     <t>id</t>
   </si>
@@ -130,7 +125,7 @@
     <t>Housing</t>
   </si>
   <si>
-    <t>2,4</t>
+    <t>1,2</t>
   </si>
   <si>
     <t>2,4,6</t>
@@ -148,9 +143,6 @@
     <t>1,1,2</t>
   </si>
   <si>
-    <t>1,2</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
@@ -388,6 +380,9 @@
     <t>TapPower</t>
   </si>
   <si>
+    <t>QuickHands</t>
+  </si>
+  <si>
     <t>WorkerLoad</t>
   </si>
   <si>
@@ -454,10 +449,10 @@
     <t>FirstSteps</t>
   </si>
   <si>
-    <t xml:space="preserve">First steps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tap the forest next to your Townhall to gather Wood.</t>
+    <t>First steps</t>
+  </si>
+  <si>
+    <t>Tap the forest next to your Townhall to gather Wood.</t>
   </si>
   <si>
     <t>CollectTaps</t>
@@ -469,7 +464,7 @@
     <t>Timber!</t>
   </si>
   <si>
-    <t xml:space="preserve">Stockpile 10 Wood — enough for your first building.</t>
+    <t>Stockpile 10 Wood — enough for your first building.</t>
   </si>
   <si>
     <t>HoldResource</t>
@@ -478,10 +473,10 @@
     <t>ARoof</t>
   </si>
   <si>
-    <t xml:space="preserve">A roof</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Build a Housing next to the Townhall.</t>
+    <t>A roof</t>
+  </si>
+  <si>
+    <t>Build a Housing next to the Townhall.</t>
   </si>
   <si>
     <t>BuildDistrict</t>
@@ -490,16 +485,16 @@
     <t>Rations</t>
   </si>
   <si>
-    <t xml:space="preserve">Gather 3 Food for your first villager — the berry bushes will do.</t>
+    <t>Gather 3 Food for your first villager — the berry bushes will do.</t>
   </si>
   <si>
     <t>FirstVillager</t>
   </si>
   <si>
-    <t xml:space="preserve">First villager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train a villager at the Townhall — berries make fine rations.</t>
+    <t>First villager</t>
+  </si>
+  <si>
+    <t>Train a villager at the Townhall — berries make fine rations.</t>
   </si>
   <si>
     <t>ReachPopulation</t>
@@ -508,7 +503,7 @@
     <t>Explorer</t>
   </si>
   <si>
-    <t xml:space="preserve">Spend Gold on the misty frontier — reveal 6 new map cells.</t>
+    <t>Spend Gold on the misty frontier — reveal 6 new map cells.</t>
   </si>
   <si>
     <t>DiscoverCells</t>
@@ -517,10 +512,10 @@
     <t>TaxDay</t>
   </si>
   <si>
-    <t xml:space="preserve">Tax day</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Collect 30 Gold — housed villagers pay taxes every minute.</t>
+    <t>Tax day</t>
+  </si>
+  <si>
+    <t>Collect 30 Gold — housed villagers pay taxes every minute.</t>
   </si>
   <si>
     <t>CollectResource</t>
@@ -529,7 +524,7 @@
     <t>Woodcraft</t>
   </si>
   <si>
-    <t xml:space="preserve">Research Forestry — the root of the technology tree.</t>
+    <t>Research Forestry — the root of the technology tree.</t>
   </si>
   <si>
     <t>CompleteTech</t>
@@ -538,19 +533,19 @@
     <t>TheSawmill</t>
   </si>
   <si>
-    <t xml:space="preserve">The Sawmill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Build a Sawmill near the forest.</t>
+    <t>The Sawmill</t>
+  </si>
+  <si>
+    <t>Build a Sawmill near the forest.</t>
   </si>
   <si>
     <t>ToWork</t>
   </si>
   <si>
-    <t xml:space="preserve">Put them to work</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assign a worker — they will chop wood for you.</t>
+    <t>Put them to work</t>
+  </si>
+  <si>
+    <t>Assign a worker — they will chop wood for you.</t>
   </si>
   <si>
     <t>AssignWorkers</t>
@@ -559,25 +554,25 @@
     <t>GrowingTown</t>
   </si>
   <si>
-    <t xml:space="preserve">Growing town</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Build a second Housing — mind the crowding penalty!</t>
+    <t>Growing town</t>
+  </si>
+  <si>
+    <t>Build a second Housing — mind the crowding penalty!</t>
   </si>
   <si>
     <t>Neighbors</t>
   </si>
   <si>
-    <t xml:space="preserve">Reach a population of 2.</t>
+    <t>Reach a population of 2.</t>
   </si>
   <si>
     <t>PickARoute</t>
   </si>
   <si>
-    <t xml:space="preserve">Pick a route</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research 3 technologies — farm the land or fish the sea, your call.</t>
+    <t>Pick a route</t>
+  </si>
+  <si>
+    <t>Research 3 technologies — farm the land or fish the sea, your call.</t>
   </si>
   <si>
     <t>CompleteTechs</t>
@@ -586,22 +581,22 @@
     <t>Stoneworks</t>
   </si>
   <si>
-    <t xml:space="preserve">Build a Quarry — Stone builds the future.</t>
+    <t>Build a Quarry — Stone builds the future.</t>
   </si>
   <si>
     <t>ToMarket</t>
   </si>
   <si>
-    <t xml:space="preserve">To market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Build the Market and open trade.</t>
+    <t>To market</t>
+  </si>
+  <si>
+    <t>Build the Market and open trade.</t>
   </si>
   <si>
     <t>Merchant</t>
   </si>
   <si>
-    <t xml:space="preserve">Sell 20 goods at the Market.</t>
+    <t>Sell 20 goods at the Market.</t>
   </si>
   <si>
     <t>SellGoods</t>
@@ -610,10 +605,10 @@
     <t>ProperCapital</t>
   </si>
   <si>
-    <t xml:space="preserve">A proper capital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upgrade the Townhall to level 2.</t>
+    <t>A proper capital</t>
+  </si>
+  <si>
+    <t>Upgrade the Townhall to level 2.</t>
   </si>
   <si>
     <t>UpgradeDistrict</t>
@@ -622,37 +617,37 @@
     <t>MoreRoom</t>
   </si>
   <si>
-    <t xml:space="preserve">More room</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research Urban Planning — homes with a second story.</t>
+    <t>More room</t>
+  </si>
+  <si>
+    <t>Research Urban Planning — homes with a second story.</t>
   </si>
   <si>
     <t>SecondStory</t>
   </si>
   <si>
-    <t xml:space="preserve">Second story</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upgrade a Housing to level 2 — an extra resident under the same roof.</t>
+    <t>Second story</t>
+  </si>
+  <si>
+    <t>Upgrade a Housing to level 2 — an extra resident under the same roof.</t>
   </si>
   <si>
     <t>FullHouse</t>
   </si>
   <si>
-    <t xml:space="preserve">Full house</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reach a population of 6.</t>
+    <t>Full house</t>
+  </si>
+  <si>
+    <t>Reach a population of 6.</t>
   </si>
   <si>
     <t>FirstSoldier</t>
   </si>
   <si>
-    <t xml:space="preserve">First soldier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Muster your first army unit — every capital needs a guard.</t>
+    <t>First soldier</t>
+  </si>
+  <si>
+    <t>Muster your first army unit — every capital needs a guard.</t>
   </si>
   <si>
     <t>TrainArmy</t>
@@ -661,52 +656,52 @@
     <t>RunningWater</t>
   </si>
   <si>
-    <t xml:space="preserve">Fields of plenty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research Farming — it unlocks the Farm.</t>
+    <t>Fields of plenty</t>
+  </si>
+  <si>
+    <t>Research Farming — it unlocks the Farm.</t>
   </si>
   <si>
     <t>Farmhand</t>
   </si>
   <si>
-    <t xml:space="preserve">Build a Farm — its workers harvest nearby crop plots for you.</t>
+    <t>Build a Farm — its workers harvest nearby crop plots for you.</t>
   </si>
   <si>
     <t>IronRoad</t>
   </si>
   <si>
-    <t xml:space="preserve">The iron road</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Push the frontier to the iron veins and collect 10 Iron.</t>
+    <t>The iron road</t>
+  </si>
+  <si>
+    <t>Push the frontier to the iron veins and collect 10 Iron.</t>
   </si>
   <si>
     <t>TheMine</t>
   </si>
   <si>
-    <t xml:space="preserve">The Mine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Build a Mine near the iron veins.</t>
+    <t>The Mine</t>
+  </si>
+  <si>
+    <t>Build a Mine near the iron veins.</t>
   </si>
   <si>
     <t>Architect</t>
   </si>
   <si>
-    <t xml:space="preserve">The architect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research Architecture — iron-braced monuments.</t>
+    <t>The architect</t>
+  </si>
+  <si>
+    <t>Research Architecture — iron-braced monuments.</t>
   </si>
   <si>
     <t>GrandCapital</t>
   </si>
   <si>
-    <t xml:space="preserve">A grand capital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upgrade the Townhall to level 3.</t>
+    <t>A grand capital</t>
+  </si>
+  <si>
+    <t>Upgrade the Townhall to level 3.</t>
   </si>
   <si>
     <t>key</t>
@@ -736,6 +731,9 @@
     <t>taxes.tap_boost_seconds</t>
   </si>
   <si>
+    <t>taxes.cycle_seconds</t>
+  </si>
+  <si>
     <t>offline_cap_hours</t>
   </si>
   <si>
@@ -833,21 +831,19 @@
   </si>
   <si>
     <t>pA</t>
-  </si>
-  <si>
-    <t>QuickHands</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="11.000000"/>
       <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -863,28 +859,120 @@
   </fills>
   <borders count="1">
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="13">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF6FA84F"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF3D6F9E"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF9AA34F"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFC9B26A"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFDFE7EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF8B9A94"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF6B6F78"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF2E6B2E"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF7A4FA8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF8A5A34"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF7A7F87"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF2E86AB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF4A4E57"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -897,7 +985,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -943,13 +1031,13 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Angsana New"/>
+        <a:font script="Thai" typeface="Tahoma"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
@@ -972,18 +1060,19 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Cordia New"/>
+        <a:font script="Thai" typeface="Tahoma"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
@@ -1006,6 +1095,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1040,20 +1130,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -1175,226 +1261,9 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
-</file>
-
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle"/>
-        </a:gradFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle"/>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
   <a:objectDefaults>
     <a:spDef>
-      <a:spPr bwMode="auto"/>
+      <a:spPr/>
       <a:bodyPr/>
       <a:lstStyle/>
       <a:style>
@@ -1413,7 +1282,7 @@
       </a:style>
     </a:spDef>
     <a:lnDef>
-      <a:spPr bwMode="auto"/>
+      <a:spPr/>
       <a:bodyPr/>
       <a:lstStyle/>
       <a:style>
@@ -1432,39 +1301,41 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AD10"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col customWidth="1" min="1" max="3" width="10"/>
-    <col customWidth="1" min="4" max="4" width="11"/>
-    <col customWidth="1" min="5" max="5" width="21"/>
-    <col customWidth="1" min="6" max="6" width="19"/>
-    <col customWidth="1" min="7" max="7" width="21"/>
-    <col customWidth="1" min="8" max="8" width="23"/>
-    <col customWidth="1" min="9" max="9" width="30"/>
-    <col customWidth="1" min="10" max="10" width="28"/>
-    <col customWidth="1" min="11" max="11" width="35"/>
-    <col customWidth="1" min="12" max="12" width="25"/>
-    <col customWidth="1" min="13" max="15" width="17"/>
-    <col customWidth="1" min="16" max="16" width="18"/>
-    <col customWidth="1" min="17" max="17" width="17"/>
-    <col customWidth="1" min="18" max="18" width="23"/>
-    <col customWidth="1" min="19" max="19" width="31"/>
-    <col customWidth="1" min="20" max="20" width="24"/>
-    <col customWidth="1" min="21" max="22" width="32"/>
-    <col customWidth="1" min="23" max="25" width="19"/>
-    <col customWidth="1" min="26" max="26" width="20"/>
-    <col customWidth="1" min="27" max="27" width="19"/>
-    <col customWidth="1" min="28" max="28" width="27"/>
-    <col customWidth="1" min="29" max="29" width="26"/>
-    <col customWidth="1" min="30" max="30" width="31"/>
+    <col min="1" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="21" customWidth="1"/>
+    <col min="6" max="6" width="19" customWidth="1"/>
+    <col min="7" max="7" width="21" customWidth="1"/>
+    <col min="8" max="8" width="23" customWidth="1"/>
+    <col min="9" max="9" width="30" customWidth="1"/>
+    <col min="10" max="10" width="28" customWidth="1"/>
+    <col min="11" max="11" width="35" customWidth="1"/>
+    <col min="12" max="12" width="25" customWidth="1"/>
+    <col min="13" max="15" width="17" customWidth="1"/>
+    <col min="16" max="16" width="18" customWidth="1"/>
+    <col min="17" max="17" width="17" customWidth="1"/>
+    <col min="18" max="18" width="23" customWidth="1"/>
+    <col min="19" max="19" width="31" customWidth="1"/>
+    <col min="20" max="20" width="24" customWidth="1"/>
+    <col min="21" max="22" width="32" customWidth="1"/>
+    <col min="23" max="25" width="19" customWidth="1"/>
+    <col min="26" max="26" width="20" customWidth="1"/>
+    <col min="27" max="27" width="19" customWidth="1"/>
+    <col min="28" max="28" width="27" customWidth="1"/>
+    <col min="29" max="29" width="26" customWidth="1"/>
+    <col min="30" max="30" width="31" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1556,7 +1427,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>30</v>
       </c>
@@ -1621,7 +1492,7 @@
         <v>1.2</v>
       </c>
       <c r="V2">
-        <v>1.1499999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="W2" t="s">
         <v>31</v>
@@ -1639,7 +1510,7 @@
         <v>31</v>
       </c>
       <c r="AB2">
-        <v>3.8999999999999999</v>
+        <v>3.9</v>
       </c>
       <c r="AC2">
         <v>30</v>
@@ -1648,7 +1519,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>33</v>
       </c>
@@ -1704,7 +1575,7 @@
         <v>1.25</v>
       </c>
       <c r="S3">
-        <v>1.1000000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="T3">
         <v>20</v>
@@ -1713,7 +1584,7 @@
         <v>1.2</v>
       </c>
       <c r="V3">
-        <v>1.1499999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="W3" t="s">
         <v>31</v>
@@ -1740,7 +1611,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>37</v>
       </c>
@@ -1769,13 +1640,13 @@
         <v>39</v>
       </c>
       <c r="J4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="M4" t="s">
         <v>31</v>
@@ -1805,7 +1676,7 @@
         <v>1.2</v>
       </c>
       <c r="V4">
-        <v>1.1499999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="W4" t="s">
         <v>31</v>
@@ -1832,9 +1703,9 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -1858,7 +1729,7 @@
         <v>31</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>31</v>
@@ -1897,7 +1768,7 @@
         <v>1.2</v>
       </c>
       <c r="V5">
-        <v>1.1499999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="W5" t="s">
         <v>31</v>
@@ -1924,9 +1795,9 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -1947,19 +1818,19 @@
         <v>2</v>
       </c>
       <c r="H6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="J6" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="K6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="M6" t="s">
         <v>31</v>
@@ -1980,7 +1851,7 @@
         <v>2.5</v>
       </c>
       <c r="S6">
-        <v>1.1499999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="T6">
         <v>20</v>
@@ -1989,7 +1860,7 @@
         <v>1.2</v>
       </c>
       <c r="V6">
-        <v>1.1499999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="W6" t="s">
         <v>31</v>
@@ -2016,9 +1887,9 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -2042,7 +1913,7 @@
         <v>31</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>31</v>
@@ -2081,7 +1952,7 @@
         <v>1.2</v>
       </c>
       <c r="V7">
-        <v>1.1499999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="W7" t="s">
         <v>31</v>
@@ -2108,9 +1979,9 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -2134,16 +2005,16 @@
         <v>38</v>
       </c>
       <c r="I8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="J8" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="K8" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M8" t="s">
         <v>31</v>
@@ -2164,7 +2035,7 @@
         <v>2.5</v>
       </c>
       <c r="S8">
-        <v>1.1499999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="T8">
         <v>20</v>
@@ -2173,7 +2044,7 @@
         <v>1.2</v>
       </c>
       <c r="V8">
-        <v>1.1499999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="W8" t="s">
         <v>31</v>
@@ -2200,9 +2071,9 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -2226,16 +2097,16 @@
         <v>38</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L9" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="M9" t="s">
         <v>31</v>
@@ -2256,7 +2127,7 @@
         <v>2.5</v>
       </c>
       <c r="S9">
-        <v>1.1499999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="T9">
         <v>20</v>
@@ -2265,7 +2136,7 @@
         <v>1.2</v>
       </c>
       <c r="V9">
-        <v>1.1499999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="W9" t="s">
         <v>31</v>
@@ -2292,9 +2163,9 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -2318,16 +2189,16 @@
         <v>38</v>
       </c>
       <c r="I10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="J10" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="J10" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="K10" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M10" t="s">
         <v>31</v>
@@ -2348,7 +2219,7 @@
         <v>2.5</v>
       </c>
       <c r="S10">
-        <v>1.1499999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="T10">
         <v>30</v>
@@ -2357,7 +2228,7 @@
         <v>1.2</v>
       </c>
       <c r="V10">
-        <v>1.1499999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="W10" t="s">
         <v>31</v>
@@ -2385,22 +2256,20 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="32.421875"/>
-    <col customWidth="1" min="2" max="2" width="10"/>
+    <col min="1" max="2" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>227</v>
       </c>
@@ -2408,7 +2277,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>229</v>
       </c>
@@ -2416,7 +2285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>230</v>
       </c>
@@ -2424,7 +2293,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>231</v>
       </c>
@@ -2432,7 +2301,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>232</v>
       </c>
@@ -2440,7 +2309,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>233</v>
       </c>
@@ -2448,7 +2317,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>234</v>
       </c>
@@ -2456,47 +2325,47 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>235</v>
       </c>
       <c r="B8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>236</v>
       </c>
       <c r="B9">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>237</v>
       </c>
       <c r="B10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>238</v>
       </c>
       <c r="B11">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>239</v>
       </c>
       <c r="B12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>240</v>
       </c>
@@ -2504,7 +2373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>241</v>
       </c>
@@ -2512,103 +2381,110 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>242</v>
       </c>
       <c r="B15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>243</v>
       </c>
       <c r="B16">
-        <v>1.45</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>244</v>
       </c>
       <c r="B17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>245</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
+      <c r="B19" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>248</v>
       </c>
       <c r="B20">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>249</v>
       </c>
       <c r="B21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>250</v>
       </c>
       <c r="B22">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>251</v>
       </c>
       <c r="B23">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>252</v>
       </c>
       <c r="B24">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>253</v>
+      </c>
+      <c r="B25">
         <v>3</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:T19"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="4"/>
-    <col customWidth="1" min="2" max="20" width="3.5"/>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="20" width="3.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="2:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B1" s="1">
         <v>-8</v>
       </c>
@@ -2667,1722 +2543,1210 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>-10</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="F2" t="s">
-        <v>254</v>
+        <v>254</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>255</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="N2" t="s">
-        <v>254</v>
+        <v>255</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>255</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>-9</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="G3" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="N3" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>254</v>
-      </c>
       <c r="O3" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>-8</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H4" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="I4" s="3" t="s">
-        <v>254</v>
-      </c>
       <c r="J4" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M4" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="N4" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="N4" s="3" t="s">
-        <v>254</v>
-      </c>
       <c r="O4" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>-7</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J5" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="K5" s="3" t="s">
-        <v>257</v>
-      </c>
       <c r="L5" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>-6</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="T6" s="3" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>-5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="T7" s="3" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>-4</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>-3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E9" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="O9" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>259</v>
-      </c>
       <c r="P9" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>-2</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>-1</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>0</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>1</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="T13" s="3" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>2</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="T14" s="3" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>3</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="T15" s="3" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>4</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="T16" s="3" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>5</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="T17" s="3" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>6</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H18" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="N18" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>261</v>
-      </c>
       <c r="O18" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="T18" s="3" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>7</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="S19" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="T19" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
-  <headerFooter/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
-      <x14:conditionalFormattings>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="1" operator="equal" id="{394D6286-6693-4EA9-B7B9-6FF0603B9B39}">
-            <xm:f>"g"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FF6FA84F"/>
-                  <bgColor rgb="FF6FA84F"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B2:T19</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" operator="equal" id="{60172045-1E50-4F1C-BF3F-F79F1D3636B4}">
-            <xm:f>"w"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FF3D6F9E"/>
-                  <bgColor rgb="FF3D6F9E"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B2:T19</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" operator="equal" id="{1C595258-A8D9-4516-A3D3-8A91755EED46}">
-            <xm:f>"p"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FF9AA34F"/>
-                  <bgColor rgb="FF9AA34F"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B2:T19</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" operator="equal" id="{B5650ECB-641A-433E-BAB0-4860A9292ADA}">
-            <xm:f>"d"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC9B26A"/>
-                  <bgColor rgb="FFC9B26A"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B2:T19</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="5" operator="equal" id="{5997FEAA-425B-41E5-8A97-EEC9B6826F5F}">
-            <xm:f>"s"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFDFE7EC"/>
-                  <bgColor rgb="FFDFE7EC"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B2:T19</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="6" operator="equal" id="{16B6DB72-6FA4-4DC5-8014-2F759D253DCE}">
-            <xm:f>"u"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FF8B9A94"/>
-                  <bgColor rgb="FF8B9A94"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B2:T19</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="7" operator="equal" id="{48C1532A-123C-42BE-B636-F0343B2FA5C2}">
-            <xm:f>"m"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FF6B6F78"/>
-                  <bgColor rgb="FF6B6F78"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B2:T19</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="8" operator="equal" id="{8855A863-1CFA-4C9A-8F63-242468F556AC}">
-            <xm:f>"T"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FF2E6B2E"/>
-                  <bgColor rgb="FF2E6B2E"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B2:T19</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="9" operator="equal" id="{1D528E79-040F-48D2-B403-8292D25BEF25}">
-            <xm:f>"B"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FF7A4FA8"/>
-                  <bgColor rgb="FF7A4FA8"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B2:T19</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="10" operator="equal" id="{03B05B35-F398-4B4D-9467-169378F3E076}">
-            <xm:f>"A"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FF8A5A34"/>
-                  <bgColor rgb="FF8A5A34"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B2:T19</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="11" operator="equal" id="{1DE05D38-74E7-414C-9D72-F80B37A3EA9F}">
-            <xm:f>"R"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FF7A7F87"/>
-                  <bgColor rgb="FF7A7F87"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B2:T19</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="12" operator="equal" id="{B2E53F79-3BA1-4FE8-B3CC-0F9ADFCAA39E}">
-            <xm:f>"F"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FF2E86AB"/>
-                  <bgColor rgb="FF2E86AB"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B2:T19</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="13" operator="equal" id="{102C49CF-189D-4CD0-8DDE-70C93D3F5F16}">
-            <xm:f>"I"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FF4A4E57"/>
-                  <bgColor rgb="FF4A4E57"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B2:T19</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="14" operator="equal" id="{75265F73-9932-428C-A84D-AC45614F70E8}">
-            <xm:f>"g"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FF6FA84F"/>
-                  <bgColor rgb="FF6FA84F"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>K9</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="15" operator="equal" id="{1E35F7C1-904C-47FE-B537-956F8D6EF408}">
-            <xm:f>"w"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FF3D6F9E"/>
-                  <bgColor rgb="FF3D6F9E"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>K9</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="16" operator="equal" id="{CCD46090-1711-4F8E-B537-2DFCBC6D070E}">
-            <xm:f>"p"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FF9AA34F"/>
-                  <bgColor rgb="FF9AA34F"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>K9</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="17" operator="equal" id="{B8F86281-BDC3-4077-BFA4-7DB6AE892008}">
-            <xm:f>"d"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC9B26A"/>
-                  <bgColor rgb="FFC9B26A"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>K9</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="18" operator="equal" id="{89F90BDE-135E-4B12-9DB7-CF14209235FE}">
-            <xm:f>"s"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFDFE7EC"/>
-                  <bgColor rgb="FFDFE7EC"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>K9</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="19" operator="equal" id="{C4D85565-E83A-464E-9336-2ACC41EF74D7}">
-            <xm:f>"u"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FF8B9A94"/>
-                  <bgColor rgb="FF8B9A94"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>K9</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="20" operator="equal" id="{D5F66C4B-93A8-4FA3-9685-D47729943AC4}">
-            <xm:f>"m"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FF6B6F78"/>
-                  <bgColor rgb="FF6B6F78"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>K9</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="21" operator="equal" id="{95D63185-FEC8-4A00-9324-092B49661A39}">
-            <xm:f>"T"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FF2E6B2E"/>
-                  <bgColor rgb="FF2E6B2E"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>K9</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="22" operator="equal" id="{BB9198CE-B140-47BD-84C1-1EC15EFF9E7F}">
-            <xm:f>"B"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FF7A4FA8"/>
-                  <bgColor rgb="FF7A4FA8"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>K9</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="23" operator="equal" id="{7D71C371-254D-4530-97F6-6F63BF25D477}">
-            <xm:f>"A"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FF8A5A34"/>
-                  <bgColor rgb="FF8A5A34"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>K9</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="24" operator="equal" id="{6B9BCDFE-68F8-4B38-9E6B-46FFCCAB2394}">
-            <xm:f>"R"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FF7A7F87"/>
-                  <bgColor rgb="FF7A7F87"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>K9</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="25" operator="equal" id="{3AE5BAAF-600E-49A4-A583-1BDCFA6918B9}">
-            <xm:f>"F"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FF2E86AB"/>
-                  <bgColor rgb="FF2E86AB"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>K9</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="26" operator="equal" id="{6207FC93-0089-4553-968A-C8B7B6D2C7B1}">
-            <xm:f>"I"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FF4A4E57"/>
-                  <bgColor rgb="FF4A4E57"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>K9</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="27" operator="equal" id="{5FFBD6FE-A491-46CD-A1D3-8052BFB821D1}">
-            <xm:f>"g"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FF6FA84F"/>
-                  <bgColor rgb="FF6FA84F"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>K8</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="28" operator="equal" id="{B505AD14-69C1-4724-AF52-F967A441EC51}">
-            <xm:f>"w"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FF3D6F9E"/>
-                  <bgColor rgb="FF3D6F9E"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>K8</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="29" operator="equal" id="{F9CF96B3-AAEC-497D-8A74-1A6113D5C382}">
-            <xm:f>"p"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FF9AA34F"/>
-                  <bgColor rgb="FF9AA34F"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>K8</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="30" operator="equal" id="{30544D32-056F-4074-85F8-60FC3DF9B705}">
-            <xm:f>"d"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC9B26A"/>
-                  <bgColor rgb="FFC9B26A"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>K8</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="31" operator="equal" id="{8C3FADC2-04C2-43F9-BFB3-6E75CA8500CB}">
-            <xm:f>"s"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFDFE7EC"/>
-                  <bgColor rgb="FFDFE7EC"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>K8</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="32" operator="equal" id="{CC827E8F-AEBD-472A-9762-FC9FF7A71429}">
-            <xm:f>"u"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FF8B9A94"/>
-                  <bgColor rgb="FF8B9A94"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>K8</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="33" operator="equal" id="{EC651E14-A51B-4553-8E62-82D998ED2790}">
-            <xm:f>"m"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FF6B6F78"/>
-                  <bgColor rgb="FF6B6F78"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>K8</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="34" operator="equal" id="{62D3164D-38E0-40CB-A791-75BAF846487E}">
-            <xm:f>"T"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FF2E6B2E"/>
-                  <bgColor rgb="FF2E6B2E"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>K8</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="35" operator="equal" id="{EDA60FA2-733C-4AFB-ADC0-D211CB8C6F90}">
-            <xm:f>"B"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FF7A4FA8"/>
-                  <bgColor rgb="FF7A4FA8"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>K8</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="36" operator="equal" id="{1B2C0567-E919-4CA2-8EE9-4946E1DE1769}">
-            <xm:f>"A"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FF8A5A34"/>
-                  <bgColor rgb="FF8A5A34"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>K8</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="37" operator="equal" id="{DD057452-AD4D-4037-82B8-2D055301CFD9}">
-            <xm:f>"R"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FF7A7F87"/>
-                  <bgColor rgb="FF7A7F87"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>K8</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="38" operator="equal" id="{03815AFC-EDEF-4C1F-966C-997C0E2BB0EE}">
-            <xm:f>"F"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FF2E86AB"/>
-                  <bgColor rgb="FF2E86AB"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>K8</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="39" operator="equal" id="{E4D9DDFF-B33A-4799-A6C3-C6BAF8626ADF}">
-            <xm:f>"I"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FF4A4E57"/>
-                  <bgColor rgb="FF4A4E57"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>K8</xm:sqref>
-        </x14:conditionalFormatting>
-      </x14:conditionalFormattings>
-    </ext>
-  </extLst>
+  <conditionalFormatting sqref="B2:T19">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"g"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"w"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"p"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+      <formula>"d"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+      <formula>"s"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+      <formula>"u"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
+      <formula>"m"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
+      <formula>"T"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
+      <formula>"B"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="10" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="11" operator="equal">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="11" priority="12" operator="equal">
+      <formula>"F"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="13" operator="equal">
+      <formula>"I"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col customWidth="1" min="1" max="2" width="10"/>
-    <col customWidth="1" min="3" max="5" width="19"/>
-    <col customWidth="1" min="6" max="6" width="20"/>
-    <col customWidth="1" min="7" max="7" width="19"/>
-    <col customWidth="1" min="8" max="8" width="24"/>
+    <col min="1" max="2" width="10" customWidth="1"/>
+    <col min="3" max="5" width="19" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
+    <col min="7" max="7" width="19" customWidth="1"/>
+    <col min="8" max="8" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="H1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>65</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>66</v>
       </c>
       <c r="B2">
         <v>3</v>
@@ -4406,9 +3770,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B3">
         <v>4</v>
@@ -4432,9 +3796,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B4">
         <v>2</v>
@@ -4458,9 +3822,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B5">
         <v>5</v>
@@ -4485,48 +3849,47 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="10"/>
-    <col customWidth="1" min="2" max="2" width="15"/>
-    <col customWidth="1" min="3" max="3" width="18"/>
-    <col customWidth="1" min="4" max="4" width="17"/>
-    <col customWidth="1" min="5" max="5" width="18"/>
-    <col customWidth="1" min="6" max="6" width="17"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>75</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>76</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -4544,9 +3907,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -4564,9 +3927,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -4584,9 +3947,9 @@
         <v>120</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -4604,9 +3967,9 @@
         <v>180</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -4624,9 +3987,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -4644,9 +4007,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -4665,48 +4028,47 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col customWidth="1" min="1" max="4" width="10"/>
-    <col customWidth="1" min="5" max="5" width="11"/>
-    <col customWidth="1" min="6" max="7" width="12"/>
+    <col min="1" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="6" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>88</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>89</v>
       </c>
       <c r="B2" t="s">
         <v>31</v>
@@ -4727,9 +4089,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B3" t="s">
         <v>31</v>
@@ -4750,9 +4112,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B4" t="s">
         <v>31</v>
@@ -4773,9 +4135,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B5" t="s">
         <v>31</v>
@@ -4796,9 +4158,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B6" t="s">
         <v>31</v>
@@ -4819,9 +4181,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B7" t="s">
         <v>31</v>
@@ -4833,7 +4195,7 @@
         <v>31</v>
       </c>
       <c r="E7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -4842,9 +4204,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B8" t="s">
         <v>31</v>
@@ -4856,7 +4218,7 @@
         <v>31</v>
       </c>
       <c r="E8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F8">
         <v>3</v>
@@ -4865,9 +4227,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B9" t="s">
         <v>31</v>
@@ -4879,7 +4241,7 @@
         <v>31</v>
       </c>
       <c r="E9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -4888,9 +4250,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B10" t="s">
         <v>31</v>
@@ -4911,9 +4273,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
@@ -4935,29 +4297,28 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col customWidth="1" min="1" max="2" width="10"/>
+    <col min="1" max="2" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="2">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4965,7 +4326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4973,7 +4334,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4981,7 +4342,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4989,7 +4350,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4997,7 +4358,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -5005,7 +4366,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -5013,7 +4374,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -5021,7 +4382,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -5029,7 +4390,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -5038,54 +4399,53 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="33.28125"/>
-    <col customWidth="1" min="2" max="4" width="11"/>
-    <col customWidth="1" min="5" max="5" width="12"/>
-    <col customWidth="1" min="6" max="6" width="11"/>
-    <col customWidth="1" min="7" max="7" width="18"/>
-    <col customWidth="1" min="8" max="8" width="10"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="H1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>102</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>103</v>
       </c>
       <c r="B2">
         <v>75</v>
@@ -5109,7 +4469,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>36</v>
       </c>
@@ -5132,12 +4492,12 @@
         <v>60</v>
       </c>
       <c r="H3" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>103</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>104</v>
       </c>
       <c r="B4">
         <v>450</v>
@@ -5161,9 +4521,9 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B5">
         <v>600</v>
@@ -5184,12 +4544,12 @@
         <v>120</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B6">
         <v>100</v>
@@ -5210,12 +4570,12 @@
         <v>45</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B7">
         <v>250</v>
@@ -5236,12 +4596,12 @@
         <v>60</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B8">
         <v>150</v>
@@ -5262,12 +4622,12 @@
         <v>45</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B9">
         <v>300</v>
@@ -5288,12 +4648,12 @@
         <v>75</v>
       </c>
       <c r="H9" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>107</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>108</v>
       </c>
       <c r="B10">
         <v>100</v>
@@ -5314,12 +4674,12 @@
         <v>45</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B11">
         <v>250</v>
@@ -5340,12 +4700,12 @@
         <v>60</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B12">
         <v>500</v>
@@ -5366,12 +4726,12 @@
         <v>90</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B13">
         <v>800</v>
@@ -5392,12 +4752,12 @@
         <v>120</v>
       </c>
       <c r="H13" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>109</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>110</v>
       </c>
       <c r="B14">
         <v>150</v>
@@ -5418,12 +4778,12 @@
         <v>45</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B15">
         <v>100</v>
@@ -5444,12 +4804,12 @@
         <v>45</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B16">
         <v>400</v>
@@ -5470,12 +4830,12 @@
         <v>90</v>
       </c>
       <c r="H16" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>111</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>112</v>
       </c>
       <c r="B17">
         <v>200</v>
@@ -5496,12 +4856,12 @@
         <v>60</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B18">
         <v>100</v>
@@ -5522,12 +4882,12 @@
         <v>30</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B19">
         <v>150</v>
@@ -5548,12 +4908,12 @@
         <v>45</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B20">
         <v>150</v>
@@ -5574,12 +4934,12 @@
         <v>60</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B21">
         <v>400</v>
@@ -5600,58 +4960,57 @@
         <v>90</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="25.140625"/>
-    <col customWidth="1" min="2" max="2" width="11"/>
-    <col customWidth="1" min="3" max="3" width="13"/>
-    <col customWidth="1" min="4" max="4" width="11"/>
-    <col customWidth="1" min="5" max="5" width="18"/>
-    <col customWidth="1" min="6" max="6" width="15"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>116</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="F1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>118</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>119</v>
       </c>
       <c r="B2">
         <v>50</v>
       </c>
       <c r="C2">
-        <v>2.2000000000000002</v>
+        <v>2.2</v>
       </c>
       <c r="D2">
         <v>5</v>
@@ -5660,92 +5019,92 @@
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B3">
+        <v>75</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>0.05</v>
+      </c>
+      <c r="F3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>120</v>
       </c>
-      <c r="B3">
+      <c r="B4">
         <v>200</v>
       </c>
-      <c r="C3">
+      <c r="C4">
         <v>2.5</v>
       </c>
-      <c r="D3">
+      <c r="D4">
         <v>3</v>
       </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>121</v>
       </c>
-      <c r="B4">
+      <c r="B5">
         <v>100</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>4</v>
-      </c>
-      <c r="E4">
-        <v>0.050000000000000003</v>
-      </c>
-      <c r="F4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>122</v>
-      </c>
-      <c r="B5">
-        <v>150</v>
       </c>
       <c r="C5">
         <v>2</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E5">
-        <v>0.10000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="F5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B6">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="F6" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B7">
         <v>100</v>
@@ -5760,15 +5119,15 @@
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B8">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="C8">
         <v>2</v>
@@ -5780,46 +5139,45 @@
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>269</v>
+        <v>125</v>
       </c>
       <c r="B9">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="C9">
         <v>2</v>
       </c>
       <c r="D9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E9">
-        <v>0.05</v>
+        <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col customWidth="1" min="1" max="2" width="10"/>
-    <col customWidth="1" min="3" max="3" width="17"/>
+    <col min="1" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>126</v>
       </c>
@@ -5830,7 +5188,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>33</v>
       </c>
@@ -5842,28 +5200,27 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M28"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col customWidth="1" min="1" max="2" width="10"/>
-    <col customWidth="1" min="3" max="3" width="13"/>
-    <col customWidth="1" min="4" max="4" width="11"/>
-    <col customWidth="1" min="5" max="6" width="13"/>
-    <col customWidth="1" min="7" max="7" width="12"/>
-    <col customWidth="1" min="8" max="10" width="13"/>
-    <col customWidth="1" min="11" max="11" width="14"/>
-    <col customWidth="1" min="12" max="13" width="13"/>
+    <col min="1" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="6" width="13" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="10" width="13" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
+    <col min="12" max="13" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5904,7 +5261,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>141</v>
       </c>
@@ -5945,7 +5302,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>145</v>
       </c>
@@ -5959,7 +5316,7 @@
         <v>148</v>
       </c>
       <c r="E3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F3">
         <v>10</v>
@@ -5986,7 +5343,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>149</v>
       </c>
@@ -6027,7 +5384,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>153</v>
       </c>
@@ -6041,7 +5398,7 @@
         <v>148</v>
       </c>
       <c r="E5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F5">
         <v>3</v>
@@ -6068,7 +5425,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>155</v>
       </c>
@@ -6109,7 +5466,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>159</v>
       </c>
@@ -6150,7 +5507,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>162</v>
       </c>
@@ -6164,7 +5521,7 @@
         <v>165</v>
       </c>
       <c r="E8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F8">
         <v>30</v>
@@ -6191,12 +5548,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>166</v>
       </c>
       <c r="B9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C9" t="s">
         <v>167</v>
@@ -6205,7 +5562,7 @@
         <v>168</v>
       </c>
       <c r="E9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -6232,7 +5589,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>169</v>
       </c>
@@ -6246,7 +5603,7 @@
         <v>152</v>
       </c>
       <c r="E10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -6273,7 +5630,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>172</v>
       </c>
@@ -6314,7 +5671,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>176</v>
       </c>
@@ -6355,7 +5712,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>179</v>
       </c>
@@ -6396,7 +5753,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>181</v>
       </c>
@@ -6437,7 +5794,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>185</v>
       </c>
@@ -6451,7 +5808,7 @@
         <v>152</v>
       </c>
       <c r="E15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -6478,7 +5835,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>187</v>
       </c>
@@ -6492,7 +5849,7 @@
         <v>152</v>
       </c>
       <c r="E16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -6519,7 +5876,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>190</v>
       </c>
@@ -6560,7 +5917,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>193</v>
       </c>
@@ -6601,7 +5958,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>197</v>
       </c>
@@ -6642,7 +5999,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>200</v>
       </c>
@@ -6683,7 +6040,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>203</v>
       </c>
@@ -6724,7 +6081,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>206</v>
       </c>
@@ -6765,7 +6122,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>210</v>
       </c>
@@ -6779,7 +6136,7 @@
         <v>168</v>
       </c>
       <c r="E23" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -6806,7 +6163,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>213</v>
       </c>
@@ -6847,7 +6204,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>215</v>
       </c>
@@ -6861,7 +6218,7 @@
         <v>165</v>
       </c>
       <c r="E25" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F25">
         <v>10</v>
@@ -6888,7 +6245,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>218</v>
       </c>
@@ -6902,7 +6259,7 @@
         <v>152</v>
       </c>
       <c r="E26" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -6929,7 +6286,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>221</v>
       </c>
@@ -6943,7 +6300,7 @@
         <v>168</v>
       </c>
       <c r="E27" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F27">
         <v>1</v>
@@ -6970,7 +6327,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>224</v>
       </c>
@@ -7012,9 +6369,7 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -13,15 +13,17 @@
     <sheet sheetId="7" name="Upgrades" state="visible" r:id="rId10"/>
     <sheet sheetId="8" name="Adjacency" state="visible" r:id="rId11"/>
     <sheet sheetId="9" name="Quests" state="visible" r:id="rId12"/>
-    <sheet sheetId="10" name="Settings" state="visible" r:id="rId13"/>
-    <sheet sheetId="11" name="Map" state="visible" r:id="rId14"/>
+    <sheet sheetId="10" name="Landmarks" state="visible" r:id="rId13"/>
+    <sheet sheetId="11" name="Ruins" state="visible" r:id="rId14"/>
+    <sheet sheetId="12" name="Settings" state="visible" r:id="rId15"/>
+    <sheet sheetId="13" name="Map" state="visible" r:id="rId16"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1169" uniqueCount="329">
   <si>
     <t>id</t>
   </si>
@@ -197,6 +199,15 @@
     <t>DeepMining</t>
   </si>
   <si>
+    <t>Sanctum</t>
+  </si>
+  <si>
+    <t>2,3</t>
+  </si>
+  <si>
+    <t>-,-</t>
+  </si>
+  <si>
     <t>power</t>
   </si>
   <si>
@@ -296,6 +307,9 @@
     <t>Wood</t>
   </si>
   <si>
+    <t>Mana</t>
+  </si>
+  <si>
     <t>Knowledge</t>
   </si>
   <si>
@@ -365,6 +379,12 @@
     <t>Archery</t>
   </si>
   <si>
+    <t>Attunement</t>
+  </si>
+  <si>
+    <t>Warband</t>
+  </si>
+  <si>
     <t>cost_base</t>
   </si>
   <si>
@@ -704,6 +724,120 @@
     <t>Upgrade the Townhall to level 3.</t>
   </si>
   <si>
+    <t>kind</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>defended</t>
+  </si>
+  <si>
+    <t>ThornedShrine</t>
+  </si>
+  <si>
+    <t>Shrine</t>
+  </si>
+  <si>
+    <t>WhisperingStones</t>
+  </si>
+  <si>
+    <t>StandingStones</t>
+  </si>
+  <si>
+    <t>BrightLeyspring</t>
+  </si>
+  <si>
+    <t>Leyspring</t>
+  </si>
+  <si>
+    <t>OldOakShrine</t>
+  </si>
+  <si>
+    <t>CircleOfNine</t>
+  </si>
+  <si>
+    <t>SunkenLeyspring</t>
+  </si>
+  <si>
+    <t>CliffShrine</t>
+  </si>
+  <si>
+    <t>FallenStones</t>
+  </si>
+  <si>
+    <t>MirrorLeyspring</t>
+  </si>
+  <si>
+    <t>WindwardShrine</t>
+  </si>
+  <si>
+    <t>tier</t>
+  </si>
+  <si>
+    <t>difficulty</t>
+  </si>
+  <si>
+    <t>base_depth_seconds</t>
+  </si>
+  <si>
+    <t>depth_growth</t>
+  </si>
+  <si>
+    <t>max_depth</t>
+  </si>
+  <si>
+    <t>supply_food</t>
+  </si>
+  <si>
+    <t>supply_gold</t>
+  </si>
+  <si>
+    <t>supply_iron</t>
+  </si>
+  <si>
+    <t>affinity</t>
+  </si>
+  <si>
+    <t>artifact</t>
+  </si>
+  <si>
+    <t>HollowBarrow</t>
+  </si>
+  <si>
+    <t>DowsingRod</t>
+  </si>
+  <si>
+    <t>SunkenChapel</t>
+  </si>
+  <si>
+    <t>VerdantSeal</t>
+  </si>
+  <si>
+    <t>DrownedIronworks</t>
+  </si>
+  <si>
+    <t>ForemansSigil</t>
+  </si>
+  <si>
+    <t>CountingHouse</t>
+  </si>
+  <si>
+    <t>GildedLedger</t>
+  </si>
+  <si>
+    <t>StarObservatory</t>
+  </si>
+  <si>
+    <t>Any</t>
+  </si>
+  <si>
+    <t>WanderersCompass</t>
+  </si>
+  <si>
     <t>key</t>
   </si>
   <si>
@@ -783,6 +917,51 @@
   </si>
   <si>
     <t>research.slot_gem_cost_growth</t>
+  </si>
+  <si>
+    <t>mana.production_per_townhall_level</t>
+  </si>
+  <si>
+    <t>4,5,6</t>
+  </si>
+  <si>
+    <t>mana.base_cap_per_townhall_level</t>
+  </si>
+  <si>
+    <t>24,32,40</t>
+  </si>
+  <si>
+    <t>mana.sanctum_cap_per_level</t>
+  </si>
+  <si>
+    <t>12,24,36</t>
+  </si>
+  <si>
+    <t>mana.landmark_production</t>
+  </si>
+  <si>
+    <t>mana.landmark_claim_cost_base</t>
+  </si>
+  <si>
+    <t>mana.landmark_claim_cost_growth</t>
+  </si>
+  <si>
+    <t>mana.gem_refill_per_gem</t>
+  </si>
+  <si>
+    <t>attunement.base_slots</t>
+  </si>
+  <si>
+    <t>attunement.max_slots</t>
+  </si>
+  <si>
+    <t>attunement.slot_gem_cost_base</t>
+  </si>
+  <si>
+    <t>attunement.slot_gem_cost_growth</t>
+  </si>
+  <si>
+    <t>attunement.swap_lock_seconds</t>
   </si>
   <si>
     <t>w</t>
@@ -1307,7 +1486,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD10"/>
+  <dimension ref="A1:AD11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="10" customWidth="1"/>
@@ -2255,6 +2434,98 @@
         <v>1.5</v>
       </c>
     </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="M11">
+        <v>300</v>
+      </c>
+      <c r="N11" t="s">
+        <v>31</v>
+      </c>
+      <c r="O11" t="s">
+        <v>31</v>
+      </c>
+      <c r="P11">
+        <v>40</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>31</v>
+      </c>
+      <c r="R11">
+        <v>1</v>
+      </c>
+      <c r="S11">
+        <v>1</v>
+      </c>
+      <c r="T11">
+        <v>90</v>
+      </c>
+      <c r="U11">
+        <v>1</v>
+      </c>
+      <c r="V11">
+        <v>1.15</v>
+      </c>
+      <c r="W11">
+        <v>500</v>
+      </c>
+      <c r="X11" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z11">
+        <v>80</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB11">
+        <v>1.8</v>
+      </c>
+      <c r="AC11">
+        <v>120</v>
+      </c>
+      <c r="AD11">
+        <v>1.6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -2263,7 +2534,474 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="5" width="10" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B2" t="s">
+        <v>238</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>-1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B3" t="s">
+        <v>240</v>
+      </c>
+      <c r="C3">
+        <v>-1</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>241</v>
+      </c>
+      <c r="B4" t="s">
+        <v>242</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>4</v>
+      </c>
+      <c r="E4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>243</v>
+      </c>
+      <c r="B5" t="s">
+        <v>238</v>
+      </c>
+      <c r="C5">
+        <v>-2</v>
+      </c>
+      <c r="D5">
+        <v>-2</v>
+      </c>
+      <c r="E5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>244</v>
+      </c>
+      <c r="B6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>245</v>
+      </c>
+      <c r="B7" t="s">
+        <v>242</v>
+      </c>
+      <c r="C7">
+        <v>-1</v>
+      </c>
+      <c r="D7">
+        <v>5</v>
+      </c>
+      <c r="E7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>246</v>
+      </c>
+      <c r="B8" t="s">
+        <v>238</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+      <c r="D8">
+        <v>-2</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>247</v>
+      </c>
+      <c r="B9" t="s">
+        <v>240</v>
+      </c>
+      <c r="C9">
+        <v>-4</v>
+      </c>
+      <c r="D9">
+        <v>-3</v>
+      </c>
+      <c r="E9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>248</v>
+      </c>
+      <c r="B10" t="s">
+        <v>242</v>
+      </c>
+      <c r="C10">
+        <v>5</v>
+      </c>
+      <c r="D10">
+        <v>5</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>249</v>
+      </c>
+      <c r="B11" t="s">
+        <v>238</v>
+      </c>
+      <c r="C11">
+        <v>9</v>
+      </c>
+      <c r="D11">
+        <v>-1</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="9" max="11" width="13" customWidth="1"/>
+    <col min="12" max="13" width="10" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B2">
+        <v>-2</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>6</v>
+      </c>
+      <c r="F2">
+        <v>180</v>
+      </c>
+      <c r="G2">
+        <v>1.15</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>20</v>
+      </c>
+      <c r="J2">
+        <v>50</v>
+      </c>
+      <c r="K2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B3">
+        <v>5</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>14</v>
+      </c>
+      <c r="F3">
+        <v>300</v>
+      </c>
+      <c r="G3">
+        <v>1.2</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
+      </c>
+      <c r="I3">
+        <v>40</v>
+      </c>
+      <c r="J3">
+        <v>150</v>
+      </c>
+      <c r="K3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3" t="s">
+        <v>70</v>
+      </c>
+      <c r="M3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>264</v>
+      </c>
+      <c r="B4">
+        <v>-3</v>
+      </c>
+      <c r="C4">
+        <v>6</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>24</v>
+      </c>
+      <c r="F4">
+        <v>480</v>
+      </c>
+      <c r="G4">
+        <v>1.25</v>
+      </c>
+      <c r="H4">
+        <v>9</v>
+      </c>
+      <c r="I4">
+        <v>60</v>
+      </c>
+      <c r="J4">
+        <v>400</v>
+      </c>
+      <c r="K4">
+        <v>10</v>
+      </c>
+      <c r="L4" t="s">
+        <v>69</v>
+      </c>
+      <c r="M4" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>266</v>
+      </c>
+      <c r="B5">
+        <v>8</v>
+      </c>
+      <c r="C5">
+        <v>-3</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>36</v>
+      </c>
+      <c r="F5">
+        <v>720</v>
+      </c>
+      <c r="G5">
+        <v>1.3</v>
+      </c>
+      <c r="H5">
+        <v>11</v>
+      </c>
+      <c r="I5">
+        <v>100</v>
+      </c>
+      <c r="J5">
+        <v>900</v>
+      </c>
+      <c r="K5">
+        <v>20</v>
+      </c>
+      <c r="L5" t="s">
+        <v>71</v>
+      </c>
+      <c r="M5" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>268</v>
+      </c>
+      <c r="B6">
+        <v>-2</v>
+      </c>
+      <c r="C6">
+        <v>-10</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>50</v>
+      </c>
+      <c r="F6">
+        <v>1080</v>
+      </c>
+      <c r="G6">
+        <v>1.35</v>
+      </c>
+      <c r="H6">
+        <v>13</v>
+      </c>
+      <c r="I6">
+        <v>150</v>
+      </c>
+      <c r="J6">
+        <v>2000</v>
+      </c>
+      <c r="K6">
+        <v>40</v>
+      </c>
+      <c r="L6" t="s">
+        <v>269</v>
+      </c>
+      <c r="M6" t="s">
+        <v>270</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B37"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
@@ -2271,15 +3009,15 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>227</v>
+        <v>271</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>228</v>
+        <v>272</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>229</v>
+        <v>273</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -2287,7 +3025,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>230</v>
+        <v>274</v>
       </c>
       <c r="B3">
         <v>8</v>
@@ -2295,7 +3033,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>231</v>
+        <v>275</v>
       </c>
       <c r="B4">
         <v>0.5</v>
@@ -2303,7 +3041,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>232</v>
+        <v>276</v>
       </c>
       <c r="B5">
         <v>20</v>
@@ -2311,7 +3049,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>233</v>
+        <v>277</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -2319,7 +3057,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>234</v>
+        <v>278</v>
       </c>
       <c r="B7">
         <v>30</v>
@@ -2327,7 +3065,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>235</v>
+        <v>279</v>
       </c>
       <c r="B8">
         <v>20</v>
@@ -2335,7 +3073,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>236</v>
+        <v>280</v>
       </c>
       <c r="B9">
         <v>60</v>
@@ -2343,7 +3081,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>237</v>
+        <v>281</v>
       </c>
       <c r="B10">
         <v>8</v>
@@ -2351,7 +3089,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>238</v>
+        <v>282</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -2359,7 +3097,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>239</v>
+        <v>283</v>
       </c>
       <c r="B12">
         <v>1.25</v>
@@ -2367,7 +3105,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>240</v>
+        <v>284</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2375,7 +3113,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>241</v>
+        <v>285</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2383,7 +3121,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>242</v>
+        <v>286</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2391,7 +3129,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>243</v>
+        <v>287</v>
       </c>
       <c r="B16">
         <v>5</v>
@@ -2399,7 +3137,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>244</v>
+        <v>288</v>
       </c>
       <c r="B17">
         <v>1.45</v>
@@ -2407,7 +3145,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>245</v>
+        <v>289</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -2415,15 +3153,15 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>246</v>
+        <v>290</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>247</v>
+        <v>291</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>248</v>
+        <v>292</v>
       </c>
       <c r="B20">
         <v>1</v>
@@ -2431,7 +3169,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>249</v>
+        <v>293</v>
       </c>
       <c r="B21">
         <v>4</v>
@@ -2439,7 +3177,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>250</v>
+        <v>294</v>
       </c>
       <c r="B22">
         <v>1</v>
@@ -2447,7 +3185,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>251</v>
+        <v>295</v>
       </c>
       <c r="B23">
         <v>3</v>
@@ -2455,7 +3193,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>252</v>
+        <v>296</v>
       </c>
       <c r="B24">
         <v>10</v>
@@ -2463,10 +3201,106 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>253</v>
+        <v>297</v>
       </c>
       <c r="B25">
         <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>298</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>300</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>302</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>304</v>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>305</v>
+      </c>
+      <c r="B30">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>306</v>
+      </c>
+      <c r="B31">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>307</v>
+      </c>
+      <c r="B32">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>308</v>
+      </c>
+      <c r="B33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>309</v>
+      </c>
+      <c r="B34">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>310</v>
+      </c>
+      <c r="B35">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>311</v>
+      </c>
+      <c r="B36">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>312</v>
+      </c>
+      <c r="B37">
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -2475,7 +3309,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -2548,61 +3382,61 @@
         <v>-10</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>255</v>
+        <v>314</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>255</v>
+        <v>314</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>255</v>
+        <v>314</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>255</v>
+        <v>314</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>255</v>
+        <v>314</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>255</v>
+        <v>314</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>255</v>
+        <v>314</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>255</v>
+        <v>314</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>255</v>
+        <v>314</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
@@ -2610,61 +3444,61 @@
         <v>-9</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>255</v>
+        <v>314</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>256</v>
+        <v>315</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>257</v>
+        <v>316</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>257</v>
+        <v>316</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>257</v>
+        <v>316</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>256</v>
+        <v>315</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>257</v>
+        <v>316</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>257</v>
+        <v>316</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>255</v>
+        <v>314</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
@@ -2672,61 +3506,61 @@
         <v>-8</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>255</v>
+        <v>314</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>255</v>
+        <v>314</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>256</v>
+        <v>315</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>255</v>
+        <v>314</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>255</v>
+        <v>314</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>255</v>
+        <v>314</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>255</v>
+        <v>314</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>256</v>
+        <v>315</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>255</v>
+        <v>314</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -2734,61 +3568,61 @@
         <v>-7</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>258</v>
+        <v>317</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>258</v>
+        <v>317</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>258</v>
+        <v>317</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>258</v>
+        <v>317</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>259</v>
+        <v>318</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>258</v>
+        <v>317</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>258</v>
+        <v>317</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>258</v>
+        <v>317</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>258</v>
+        <v>317</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -2796,61 +3630,61 @@
         <v>-6</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>260</v>
+        <v>319</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>260</v>
+        <v>319</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="T6" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -2858,61 +3692,61 @@
         <v>-5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>257</v>
+        <v>316</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>257</v>
+        <v>316</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="T7" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -2920,61 +3754,61 @@
         <v>-4</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>262</v>
+        <v>321</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>263</v>
+        <v>322</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>263</v>
+        <v>322</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>257</v>
+        <v>316</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>264</v>
+        <v>323</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>257</v>
+        <v>316</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -2982,61 +3816,61 @@
         <v>-3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>257</v>
+        <v>316</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>257</v>
+        <v>316</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>257</v>
+        <v>316</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>260</v>
+        <v>319</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>265</v>
+        <v>324</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>265</v>
+        <v>324</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -3044,61 +3878,61 @@
         <v>-2</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>262</v>
+        <v>321</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>257</v>
+        <v>316</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>257</v>
+        <v>316</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>265</v>
+        <v>324</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>265</v>
+        <v>324</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>266</v>
+        <v>325</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -3106,61 +3940,61 @@
         <v>-1</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>260</v>
+        <v>319</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>257</v>
+        <v>316</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>264</v>
+        <v>323</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>265</v>
+        <v>324</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>267</v>
+        <v>326</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>265</v>
+        <v>324</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>265</v>
+        <v>324</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -3168,61 +4002,61 @@
         <v>0</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>260</v>
+        <v>319</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>257</v>
+        <v>316</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>257</v>
+        <v>316</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>265</v>
+        <v>324</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>257</v>
+        <v>316</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>257</v>
+        <v>316</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>267</v>
+        <v>326</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -3230,61 +4064,61 @@
         <v>1</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>265</v>
+        <v>324</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>265</v>
+        <v>324</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>267</v>
+        <v>326</v>
       </c>
       <c r="T13" s="3" t="s">
-        <v>265</v>
+        <v>324</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -3292,61 +4126,61 @@
         <v>2</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>260</v>
+        <v>319</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>268</v>
+        <v>327</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>263</v>
+        <v>322</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>265</v>
+        <v>324</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>265</v>
+        <v>324</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>265</v>
+        <v>324</v>
       </c>
       <c r="T14" s="3" t="s">
-        <v>265</v>
+        <v>324</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -3354,61 +4188,61 @@
         <v>3</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>263</v>
+        <v>322</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>263</v>
+        <v>322</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>263</v>
+        <v>322</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>263</v>
+        <v>322</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>263</v>
+        <v>322</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>257</v>
+        <v>316</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>267</v>
+        <v>326</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>265</v>
+        <v>324</v>
       </c>
       <c r="T15" s="3" t="s">
-        <v>265</v>
+        <v>324</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -3416,61 +4250,61 @@
         <v>4</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>260</v>
+        <v>319</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>263</v>
+        <v>322</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>263</v>
+        <v>322</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>263</v>
+        <v>322</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>263</v>
+        <v>322</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>263</v>
+        <v>322</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>269</v>
+        <v>328</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>265</v>
+        <v>324</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>265</v>
+        <v>324</v>
       </c>
       <c r="T16" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
@@ -3478,61 +4312,61 @@
         <v>5</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>263</v>
+        <v>322</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>263</v>
+        <v>322</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>265</v>
+        <v>324</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>265</v>
+        <v>324</v>
       </c>
       <c r="T17" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -3540,61 +4374,61 @@
         <v>6</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>260</v>
+        <v>319</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>263</v>
+        <v>322</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>262</v>
+        <v>321</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="T18" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
@@ -3602,61 +4436,61 @@
         <v>7</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>260</v>
+        <v>319</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="S19" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="T19" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
     </row>
   </sheetData>
@@ -3723,30 +4557,30 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B2">
         <v>3</v>
@@ -3772,7 +4606,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B3">
         <v>4</v>
@@ -3798,7 +4632,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B4">
         <v>2</v>
@@ -3824,7 +4658,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B5">
         <v>5</v>
@@ -3869,27 +4703,27 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -3909,7 +4743,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -3929,7 +4763,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -3949,7 +4783,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -3969,7 +4803,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -3989,7 +4823,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -4009,7 +4843,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -4035,7 +4869,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="4" width="10" customWidth="1"/>
@@ -4048,27 +4882,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B2" t="s">
         <v>31</v>
@@ -4091,7 +4925,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B3" t="s">
         <v>31</v>
@@ -4114,7 +4948,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B4" t="s">
         <v>31</v>
@@ -4137,7 +4971,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B5" t="s">
         <v>31</v>
@@ -4160,7 +4994,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B6" t="s">
         <v>31</v>
@@ -4183,7 +5017,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="B7" t="s">
         <v>31</v>
@@ -4195,18 +5029,18 @@
         <v>31</v>
       </c>
       <c r="E7" t="s">
-        <v>89</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
+        <v>31</v>
+      </c>
+      <c r="F7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B8" t="s">
         <v>31</v>
@@ -4218,18 +5052,18 @@
         <v>31</v>
       </c>
       <c r="E8" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G8">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B9" t="s">
         <v>31</v>
@@ -4241,18 +5075,18 @@
         <v>31</v>
       </c>
       <c r="E9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B10" t="s">
         <v>31</v>
@@ -4264,35 +5098,58 @@
         <v>31</v>
       </c>
       <c r="E10" t="s">
-        <v>31</v>
-      </c>
-      <c r="F10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G10" t="s">
-        <v>31</v>
+        <v>92</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
       </c>
       <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>96</v>
+      </c>
+      <c r="B12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12">
         <v>10</v>
       </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11" t="s">
-        <v>31</v>
-      </c>
-      <c r="F11" t="s">
-        <v>31</v>
-      </c>
-      <c r="G11" t="s">
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" t="s">
+        <v>31</v>
+      </c>
+      <c r="G12" t="s">
         <v>31</v>
       </c>
     </row>
@@ -4312,10 +5169,10 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -4406,7 +5263,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -4422,30 +5279,30 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B2">
         <v>75</v>
@@ -4492,12 +5349,12 @@
         <v>60</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B4">
         <v>450</v>
@@ -4523,7 +5380,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B5">
         <v>600</v>
@@ -4544,12 +5401,12 @@
         <v>120</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B6">
         <v>100</v>
@@ -4570,12 +5427,12 @@
         <v>45</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B7">
         <v>250</v>
@@ -4596,7 +5453,7 @@
         <v>60</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -4622,7 +5479,7 @@
         <v>45</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -4648,12 +5505,12 @@
         <v>75</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B10">
         <v>100</v>
@@ -4674,12 +5531,12 @@
         <v>45</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B11">
         <v>250</v>
@@ -4700,7 +5557,7 @@
         <v>60</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -4726,7 +5583,7 @@
         <v>90</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -4752,12 +5609,12 @@
         <v>120</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B14">
         <v>150</v>
@@ -4778,12 +5635,12 @@
         <v>45</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B15">
         <v>100</v>
@@ -4804,7 +5661,7 @@
         <v>45</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -4830,12 +5687,12 @@
         <v>90</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B17">
         <v>200</v>
@@ -4856,12 +5713,12 @@
         <v>60</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B18">
         <v>100</v>
@@ -4882,12 +5739,12 @@
         <v>30</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B19">
         <v>150</v>
@@ -4908,12 +5765,12 @@
         <v>45</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B20">
         <v>150</v>
@@ -4934,12 +5791,12 @@
         <v>60</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B21">
         <v>400</v>
@@ -4960,7 +5817,59 @@
         <v>90</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>118</v>
+      </c>
+      <c r="B22">
+        <v>400</v>
+      </c>
+      <c r="C22" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" t="s">
+        <v>31</v>
+      </c>
+      <c r="E22">
+        <v>40</v>
+      </c>
+      <c r="F22" t="s">
+        <v>31</v>
+      </c>
+      <c r="G22">
+        <v>120</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>119</v>
+      </c>
+      <c r="B23">
+        <v>600</v>
+      </c>
+      <c r="C23" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23" t="s">
+        <v>31</v>
+      </c>
+      <c r="F23">
+        <v>20</v>
+      </c>
+      <c r="G23">
+        <v>180</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -4987,24 +5896,24 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B2">
         <v>50</v>
@@ -5019,12 +5928,12 @@
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B3">
         <v>75</v>
@@ -5039,12 +5948,12 @@
         <v>0.05</v>
       </c>
       <c r="F3" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B4">
         <v>200</v>
@@ -5059,12 +5968,12 @@
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B5">
         <v>100</v>
@@ -5084,7 +5993,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B6">
         <v>150</v>
@@ -5104,7 +6013,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B7">
         <v>100</v>
@@ -5119,12 +6028,12 @@
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="B8">
         <v>100</v>
@@ -5139,12 +6048,12 @@
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B9">
         <v>150</v>
@@ -5159,7 +6068,7 @@
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -5179,13 +6088,13 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -5225,54 +6134,54 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="B2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="C2" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="D2" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="E2" t="s">
         <v>31</v>
@@ -5304,19 +6213,19 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B3" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C3" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="D3" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="E3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F3">
         <v>10</v>
@@ -5345,16 +6254,16 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B4" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C4" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="D4" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="E4" t="s">
         <v>33</v>
@@ -5386,19 +6295,19 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="B5" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C5" t="s">
+        <v>160</v>
+      </c>
+      <c r="D5" t="s">
         <v>154</v>
       </c>
-      <c r="D5" t="s">
-        <v>148</v>
-      </c>
       <c r="E5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F5">
         <v>3</v>
@@ -5427,16 +6336,16 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="B6" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="C6" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="D6" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="E6" t="s">
         <v>31</v>
@@ -5468,16 +6377,16 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B7" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="C7" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="D7" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="E7" t="s">
         <v>31</v>
@@ -5509,19 +6418,19 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B8" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="C8" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D8" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E8" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F8">
         <v>30</v>
@@ -5550,19 +6459,19 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="B9" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C9" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="D9" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="E9" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -5591,16 +6500,16 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B10" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="C10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="D10" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="E10" t="s">
         <v>44</v>
@@ -5632,16 +6541,16 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="B11" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="C11" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="D11" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="E11" t="s">
         <v>31</v>
@@ -5673,16 +6582,16 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B12" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C12" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="D12" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="E12" t="s">
         <v>33</v>
@@ -5714,16 +6623,16 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="B13" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C13" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="D13" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="E13" t="s">
         <v>31</v>
@@ -5755,16 +6664,16 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="B14" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="C14" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="D14" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="E14" t="s">
         <v>31</v>
@@ -5796,16 +6705,16 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="B15" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="C15" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="D15" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="E15" t="s">
         <v>51</v>
@@ -5837,16 +6746,16 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="B16" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C16" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="D16" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="E16" t="s">
         <v>49</v>
@@ -5878,16 +6787,16 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="B17" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="C17" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="D17" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="E17" t="s">
         <v>31</v>
@@ -5919,16 +6828,16 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="B18" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="C18" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="D18" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="E18" t="s">
         <v>30</v>
@@ -5960,16 +6869,16 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B19" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="C19" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="D19" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="E19" t="s">
         <v>36</v>
@@ -6001,16 +6910,16 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="B20" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="C20" t="s">
+        <v>208</v>
+      </c>
+      <c r="D20" t="s">
         <v>202</v>
-      </c>
-      <c r="D20" t="s">
-        <v>196</v>
       </c>
       <c r="E20" t="s">
         <v>33</v>
@@ -6042,16 +6951,16 @@
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="B21" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="C21" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="D21" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="E21" t="s">
         <v>31</v>
@@ -6083,16 +6992,16 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="B22" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="C22" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="D22" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E22" t="s">
         <v>31</v>
@@ -6124,19 +7033,19 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="B23" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="C23" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D23" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="E23" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -6165,16 +7074,16 @@
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="B24" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="C24" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="D24" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="E24" t="s">
         <v>37</v>
@@ -6206,19 +7115,19 @@
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B25" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="C25" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="D25" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E25" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F25">
         <v>10</v>
@@ -6247,16 +7156,16 @@
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="B26" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="C26" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="D26" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="E26" t="s">
         <v>56</v>
@@ -6288,19 +7197,19 @@
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="B27" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C27" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="D27" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="E27" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F27">
         <v>1</v>
@@ -6329,16 +7238,16 @@
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="B28" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="C28" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="D28" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="E28" t="s">
         <v>30</v>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -13,17 +13,18 @@
     <sheet sheetId="7" name="Upgrades" state="visible" r:id="rId10"/>
     <sheet sheetId="8" name="Adjacency" state="visible" r:id="rId11"/>
     <sheet sheetId="9" name="Quests" state="visible" r:id="rId12"/>
-    <sheet sheetId="10" name="Landmarks" state="visible" r:id="rId13"/>
-    <sheet sheetId="11" name="Ruins" state="visible" r:id="rId14"/>
-    <sheet sheetId="12" name="Settings" state="visible" r:id="rId15"/>
-    <sheet sheetId="13" name="Map" state="visible" r:id="rId16"/>
+    <sheet sheetId="10" name="Artifacts" state="visible" r:id="rId13"/>
+    <sheet sheetId="11" name="Landmarks" state="visible" r:id="rId14"/>
+    <sheet sheetId="12" name="Ruins" state="visible" r:id="rId15"/>
+    <sheet sheetId="13" name="Settings" state="visible" r:id="rId16"/>
+    <sheet sheetId="14" name="Map" state="visible" r:id="rId17"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1169" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1197" uniqueCount="343">
   <si>
     <t>id</t>
   </si>
@@ -724,6 +725,39 @@
     <t>Upgrade the Townhall to level 3.</t>
   </si>
   <si>
+    <t>upkeep</t>
+  </si>
+  <si>
+    <t>passive_base</t>
+  </si>
+  <si>
+    <t>passive_per_level</t>
+  </si>
+  <si>
+    <t>active_mana_cost</t>
+  </si>
+  <si>
+    <t>active_duration_seconds</t>
+  </si>
+  <si>
+    <t>active_radius</t>
+  </si>
+  <si>
+    <t>DowsingRod</t>
+  </si>
+  <si>
+    <t>VerdantSeal</t>
+  </si>
+  <si>
+    <t>ForemansSigil</t>
+  </si>
+  <si>
+    <t>GildedLedger</t>
+  </si>
+  <si>
+    <t>WanderersCompass</t>
+  </si>
+  <si>
     <t>kind</t>
   </si>
   <si>
@@ -808,36 +842,21 @@
     <t>HollowBarrow</t>
   </si>
   <si>
-    <t>DowsingRod</t>
-  </si>
-  <si>
     <t>SunkenChapel</t>
   </si>
   <si>
-    <t>VerdantSeal</t>
-  </si>
-  <si>
     <t>DrownedIronworks</t>
   </si>
   <si>
-    <t>ForemansSigil</t>
-  </si>
-  <si>
     <t>CountingHouse</t>
   </si>
   <si>
-    <t>GildedLedger</t>
-  </si>
-  <si>
     <t>StarObservatory</t>
   </si>
   <si>
     <t>Any</t>
   </si>
   <si>
-    <t>WanderersCompass</t>
-  </si>
-  <si>
     <t>key</t>
   </si>
   <si>
@@ -962,6 +981,30 @@
   </si>
   <si>
     <t>attunement.swap_lock_seconds</t>
+  </si>
+  <si>
+    <t>collection.level_cost_base</t>
+  </si>
+  <si>
+    <t>collection.level_cost_growth</t>
+  </si>
+  <si>
+    <t>collection.max_level</t>
+  </si>
+  <si>
+    <t>collection.levels_per_tier</t>
+  </si>
+  <si>
+    <t>collection.max_tier</t>
+  </si>
+  <si>
+    <t>collection.fragments_per_tier_base</t>
+  </si>
+  <si>
+    <t>collection.fragments_per_tier_growth</t>
+  </si>
+  <si>
+    <t>knowledge.drip_per_ruin_per_hour</t>
   </si>
   <si>
     <t>w</t>
@@ -2534,6 +2577,163 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="19" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="25" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>239</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>0.85</v>
+      </c>
+      <c r="D2">
+        <v>-0.015</v>
+      </c>
+      <c r="E2">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>0.75</v>
+      </c>
+      <c r="D3">
+        <v>-0.02</v>
+      </c>
+      <c r="E3">
+        <v>6</v>
+      </c>
+      <c r="F3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>241</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>0.2</v>
+      </c>
+      <c r="E4">
+        <v>10</v>
+      </c>
+      <c r="F4">
+        <v>3600</v>
+      </c>
+      <c r="G4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>242</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>1.2</v>
+      </c>
+      <c r="D5">
+        <v>0.03</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>243</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>1.5</v>
+      </c>
+      <c r="D6">
+        <v>0.1</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -2545,24 +2745,24 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="B2" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="C2">
         <v>2</v>
@@ -2576,10 +2776,10 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="B3" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="C3">
         <v>-1</v>
@@ -2593,10 +2793,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="B4" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -2610,10 +2810,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="B5" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="C5">
         <v>-2</v>
@@ -2627,10 +2827,10 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="B6" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -2644,10 +2844,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="B7" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="C7">
         <v>-1</v>
@@ -2661,10 +2861,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="B8" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="C8">
         <v>5</v>
@@ -2678,10 +2878,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="B9" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="C9">
         <v>-4</v>
@@ -2695,10 +2895,10 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="B10" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="C10">
         <v>5</v>
@@ -2712,10 +2912,10 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>260</v>
+      </c>
+      <c r="B11" t="s">
         <v>249</v>
-      </c>
-      <c r="B11" t="s">
-        <v>238</v>
       </c>
       <c r="C11">
         <v>9</v>
@@ -2733,7 +2933,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -2752,45 +2952,45 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="B2">
         <v>-2</v>
@@ -2826,12 +3026,12 @@
         <v>68</v>
       </c>
       <c r="M2" t="s">
-        <v>261</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="B3">
         <v>5</v>
@@ -2867,12 +3067,12 @@
         <v>70</v>
       </c>
       <c r="M3" t="s">
-        <v>263</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="B4">
         <v>-3</v>
@@ -2908,12 +3108,12 @@
         <v>69</v>
       </c>
       <c r="M4" t="s">
-        <v>265</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="B5">
         <v>8</v>
@@ -2949,12 +3149,12 @@
         <v>71</v>
       </c>
       <c r="M5" t="s">
-        <v>267</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="B6">
         <v>-2</v>
@@ -2987,10 +3187,10 @@
         <v>40</v>
       </c>
       <c r="L6" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="M6" t="s">
-        <v>270</v>
+        <v>243</v>
       </c>
     </row>
   </sheetData>
@@ -2999,9 +3199,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B45"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
@@ -3009,15 +3209,15 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -3025,7 +3225,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="B3">
         <v>8</v>
@@ -3033,7 +3233,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="B4">
         <v>0.5</v>
@@ -3041,7 +3241,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B5">
         <v>20</v>
@@ -3049,7 +3249,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -3057,7 +3257,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="B7">
         <v>30</v>
@@ -3065,7 +3265,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="B8">
         <v>20</v>
@@ -3073,7 +3273,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="B9">
         <v>60</v>
@@ -3081,7 +3281,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="B10">
         <v>8</v>
@@ -3089,7 +3289,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -3097,7 +3297,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="B12">
         <v>1.25</v>
@@ -3105,7 +3305,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -3113,7 +3313,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -3121,7 +3321,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -3129,7 +3329,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="B16">
         <v>5</v>
@@ -3137,7 +3337,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="B17">
         <v>1.45</v>
@@ -3145,7 +3345,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -3153,15 +3353,15 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="B20">
         <v>1</v>
@@ -3169,7 +3369,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="B21">
         <v>4</v>
@@ -3177,7 +3377,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="B22">
         <v>1</v>
@@ -3185,7 +3385,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="B23">
         <v>3</v>
@@ -3193,7 +3393,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="B24">
         <v>10</v>
@@ -3201,7 +3401,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="B25">
         <v>3</v>
@@ -3209,31 +3409,31 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="B29">
         <v>1</v>
@@ -3241,7 +3441,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="B30">
         <v>120</v>
@@ -3249,7 +3449,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B31">
         <v>1.3</v>
@@ -3257,7 +3457,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="B32">
         <v>4</v>
@@ -3265,7 +3465,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -3273,7 +3473,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="B34">
         <v>5</v>
@@ -3281,7 +3481,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="B35">
         <v>20</v>
@@ -3289,7 +3489,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="B36">
         <v>2.5</v>
@@ -3297,10 +3497,74 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="B37">
         <v>300</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>319</v>
+      </c>
+      <c r="B38">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>320</v>
+      </c>
+      <c r="B39">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>321</v>
+      </c>
+      <c r="B40">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>322</v>
+      </c>
+      <c r="B41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>323</v>
+      </c>
+      <c r="B42">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>324</v>
+      </c>
+      <c r="B43">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>325</v>
+      </c>
+      <c r="B44">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>326</v>
+      </c>
+      <c r="B45">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -3309,7 +3573,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -3382,61 +3646,61 @@
         <v>-10</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
@@ -3444,61 +3708,61 @@
         <v>-9</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
@@ -3506,61 +3770,61 @@
         <v>-8</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -3568,61 +3832,61 @@
         <v>-7</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -3630,61 +3894,61 @@
         <v>-6</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="T6" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -3692,61 +3956,61 @@
         <v>-5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="T7" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -3754,61 +4018,61 @@
         <v>-4</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>323</v>
+        <v>337</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -3816,61 +4080,61 @@
         <v>-3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -3878,61 +4142,61 @@
         <v>-2</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>325</v>
+        <v>339</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -3940,61 +4204,61 @@
         <v>-1</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>323</v>
+        <v>337</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -4002,61 +4266,61 @@
         <v>0</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -4064,61 +4328,61 @@
         <v>1</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="T13" s="3" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -4126,61 +4390,61 @@
         <v>2</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="T14" s="3" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -4188,61 +4452,61 @@
         <v>3</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="T15" s="3" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -4250,61 +4514,61 @@
         <v>4</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="T16" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
@@ -4312,61 +4576,61 @@
         <v>5</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="T17" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -4374,61 +4638,61 @@
         <v>6</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="T18" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
@@ -4436,61 +4700,61 @@
         <v>7</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="S19" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="T19" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
     </row>
   </sheetData>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -14,17 +14,18 @@
     <sheet sheetId="8" name="Adjacency" state="visible" r:id="rId11"/>
     <sheet sheetId="9" name="Quests" state="visible" r:id="rId12"/>
     <sheet sheetId="10" name="Artifacts" state="visible" r:id="rId13"/>
-    <sheet sheetId="11" name="Landmarks" state="visible" r:id="rId14"/>
-    <sheet sheetId="12" name="Ruins" state="visible" r:id="rId15"/>
-    <sheet sheetId="13" name="Settings" state="visible" r:id="rId16"/>
-    <sheet sheetId="14" name="Map" state="visible" r:id="rId17"/>
+    <sheet sheetId="11" name="Heroes" state="visible" r:id="rId14"/>
+    <sheet sheetId="12" name="Landmarks" state="visible" r:id="rId15"/>
+    <sheet sheetId="13" name="Ruins" state="visible" r:id="rId16"/>
+    <sheet sheetId="14" name="Settings" state="visible" r:id="rId17"/>
+    <sheet sheetId="15" name="Map" state="visible" r:id="rId18"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1197" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="388">
   <si>
     <t>id</t>
   </si>
@@ -62,6 +63,9 @@
     <t>required_tech_per_level</t>
   </si>
   <si>
+    <t>army_cap_per_level</t>
+  </si>
+  <si>
     <t>build_cost_gold</t>
   </si>
   <si>
@@ -209,9 +213,33 @@
     <t>-,-</t>
   </si>
   <si>
+    <t>Barracks</t>
+  </si>
+  <si>
+    <t>6,10,15</t>
+  </si>
+  <si>
+    <t>SpearHall</t>
+  </si>
+  <si>
+    <t>ShootingGrounds</t>
+  </si>
+  <si>
+    <t>Stables</t>
+  </si>
+  <si>
     <t>power</t>
   </si>
   <si>
+    <t>atk</t>
+  </si>
+  <si>
+    <t>def</t>
+  </si>
+  <si>
+    <t>hp</t>
+  </si>
+  <si>
     <t>recruit_cost_gold</t>
   </si>
   <si>
@@ -758,6 +786,54 @@
     <t>WanderersCompass</t>
   </si>
   <si>
+    <t>unit_type</t>
+  </si>
+  <si>
+    <t>trait</t>
+  </si>
+  <si>
+    <t>trait_value</t>
+  </si>
+  <si>
+    <t>atk_per_level</t>
+  </si>
+  <si>
+    <t>def_per_level</t>
+  </si>
+  <si>
+    <t>hp_per_level</t>
+  </si>
+  <si>
+    <t>Warden</t>
+  </si>
+  <si>
+    <t>PartyDefence</t>
+  </si>
+  <si>
+    <t>Quartermaster</t>
+  </si>
+  <si>
+    <t>SupplyDiscount</t>
+  </si>
+  <si>
+    <t>Scholar</t>
+  </si>
+  <si>
+    <t>KnowledgeBonus</t>
+  </si>
+  <si>
+    <t>RelicHunter</t>
+  </si>
+  <si>
+    <t>FragmentBonus</t>
+  </si>
+  <si>
+    <t>Scout</t>
+  </si>
+  <si>
+    <t>RevealNextDepth</t>
+  </si>
+  <si>
     <t>kind</t>
   </si>
   <si>
@@ -914,12 +990,6 @@
     <t>city.build_queue_capacity</t>
   </si>
   <si>
-    <t>city.max_army_power_per_townhall_level</t>
-  </si>
-  <si>
-    <t>10,20,30</t>
-  </si>
-  <si>
     <t>kingdom.start_builders</t>
   </si>
   <si>
@@ -1005,6 +1075,72 @@
   </si>
   <si>
     <t>knowledge.drip_per_ruin_per_hour</t>
+  </si>
+  <si>
+    <t>army.train_tap_boost_seconds</t>
+  </si>
+  <si>
+    <t>army.type_advantage</t>
+  </si>
+  <si>
+    <t>army.type_disadvantage</t>
+  </si>
+  <si>
+    <t>army.threat_floor_fraction</t>
+  </si>
+  <si>
+    <t>army.damage_per_strength</t>
+  </si>
+  <si>
+    <t>army.damage_absorbed_per_defence</t>
+  </si>
+  <si>
+    <t>delve.gold_per_depth_per_tier</t>
+  </si>
+  <si>
+    <t>delve.material_per_depth_per_tier</t>
+  </si>
+  <si>
+    <t>delve.knowledge_per_depth_per_tier</t>
+  </si>
+  <si>
+    <t>delve.fragments_per_depth</t>
+  </si>
+  <si>
+    <t>delve.fail_haul_loss</t>
+  </si>
+  <si>
+    <t>delve.first_clear_gems</t>
+  </si>
+  <si>
+    <t>party.base_slots</t>
+  </si>
+  <si>
+    <t>party.max_slots</t>
+  </si>
+  <si>
+    <t>party.slot_gem_cost_base</t>
+  </si>
+  <si>
+    <t>party.slot_gem_cost_growth</t>
+  </si>
+  <si>
+    <t>gacha.pull_gem_cost</t>
+  </si>
+  <si>
+    <t>gacha.hero_chance</t>
+  </si>
+  <si>
+    <t>gacha.soft_pity_at</t>
+  </si>
+  <si>
+    <t>gacha.hard_pity_at</t>
+  </si>
+  <si>
+    <t>gacha.duplicate_fragments</t>
+  </si>
+  <si>
+    <t>gacha.fragments_per_miss</t>
   </si>
   <si>
     <t>w</t>
@@ -1529,7 +1665,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AE15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="10" customWidth="1"/>
@@ -1542,22 +1678,23 @@
     <col min="10" max="10" width="28" customWidth="1"/>
     <col min="11" max="11" width="35" customWidth="1"/>
     <col min="12" max="12" width="25" customWidth="1"/>
-    <col min="13" max="15" width="17" customWidth="1"/>
-    <col min="16" max="16" width="18" customWidth="1"/>
-    <col min="17" max="17" width="17" customWidth="1"/>
-    <col min="18" max="18" width="23" customWidth="1"/>
-    <col min="19" max="19" width="31" customWidth="1"/>
-    <col min="20" max="20" width="24" customWidth="1"/>
-    <col min="21" max="22" width="32" customWidth="1"/>
-    <col min="23" max="25" width="19" customWidth="1"/>
-    <col min="26" max="26" width="20" customWidth="1"/>
-    <col min="27" max="27" width="19" customWidth="1"/>
-    <col min="28" max="28" width="27" customWidth="1"/>
-    <col min="29" max="29" width="26" customWidth="1"/>
-    <col min="30" max="30" width="31" customWidth="1"/>
+    <col min="13" max="13" width="20" customWidth="1"/>
+    <col min="14" max="16" width="17" customWidth="1"/>
+    <col min="17" max="17" width="18" customWidth="1"/>
+    <col min="18" max="18" width="17" customWidth="1"/>
+    <col min="19" max="19" width="23" customWidth="1"/>
+    <col min="20" max="20" width="31" customWidth="1"/>
+    <col min="21" max="21" width="24" customWidth="1"/>
+    <col min="22" max="23" width="32" customWidth="1"/>
+    <col min="24" max="26" width="19" customWidth="1"/>
+    <col min="27" max="27" width="20" customWidth="1"/>
+    <col min="28" max="28" width="19" customWidth="1"/>
+    <col min="29" max="29" width="27" customWidth="1"/>
+    <col min="30" max="30" width="26" customWidth="1"/>
+    <col min="31" max="31" width="31" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1648,10 +1785,13 @@
       <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -1663,7 +1803,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -1672,78 +1812,81 @@
         <v>3</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M2" t="s">
-        <v>31</v>
+        <v>33</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="N2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q2" t="s">
-        <v>31</v>
-      </c>
-      <c r="R2">
+        <v>32</v>
+      </c>
+      <c r="R2" t="s">
+        <v>32</v>
+      </c>
+      <c r="S2">
         <v>2</v>
       </c>
-      <c r="S2">
+      <c r="T2">
         <v>1.2</v>
       </c>
-      <c r="T2">
+      <c r="U2">
         <v>0</v>
       </c>
-      <c r="U2">
+      <c r="V2">
         <v>1.2</v>
       </c>
-      <c r="V2">
+      <c r="W2">
         <v>1.15</v>
       </c>
-      <c r="W2" t="s">
-        <v>31</v>
-      </c>
-      <c r="X2">
+      <c r="X2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y2">
         <v>40</v>
       </c>
-      <c r="Y2" t="s">
-        <v>31</v>
-      </c>
-      <c r="Z2">
+      <c r="Z2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA2">
         <v>20</v>
       </c>
-      <c r="AA2" t="s">
-        <v>31</v>
-      </c>
-      <c r="AB2">
+      <c r="AB2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC2">
         <v>3.9</v>
       </c>
-      <c r="AC2">
+      <c r="AD2">
         <v>30</v>
       </c>
-      <c r="AD2">
+      <c r="AE2">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -1755,7 +1898,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -1764,78 +1907,81 @@
         <v>2</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="M3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N3">
+        <v>37</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N3" t="s">
+        <v>32</v>
+      </c>
+      <c r="O3">
         <v>10</v>
       </c>
-      <c r="O3" t="s">
-        <v>31</v>
-      </c>
       <c r="P3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q3" t="s">
-        <v>31</v>
-      </c>
-      <c r="R3">
+        <v>32</v>
+      </c>
+      <c r="R3" t="s">
+        <v>32</v>
+      </c>
+      <c r="S3">
         <v>1.25</v>
       </c>
-      <c r="S3">
+      <c r="T3">
         <v>1.1</v>
       </c>
-      <c r="T3">
+      <c r="U3">
         <v>20</v>
       </c>
-      <c r="U3">
+      <c r="V3">
         <v>1.2</v>
       </c>
-      <c r="V3">
+      <c r="W3">
         <v>1.15</v>
       </c>
-      <c r="W3" t="s">
-        <v>31</v>
-      </c>
-      <c r="X3">
+      <c r="X3" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y3">
         <v>30</v>
       </c>
-      <c r="Y3" t="s">
-        <v>31</v>
-      </c>
-      <c r="Z3">
+      <c r="Z3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA3">
         <v>10</v>
       </c>
-      <c r="AA3" t="s">
-        <v>31</v>
-      </c>
-      <c r="AB3">
+      <c r="AB3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC3">
         <v>1.5</v>
       </c>
-      <c r="AC3">
+      <c r="AD3">
         <v>20</v>
       </c>
-      <c r="AD3">
+      <c r="AE3">
         <v>1.5</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -1847,7 +1993,7 @@
         <v>2</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -1856,78 +2002,81 @@
         <v>2</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M4" t="s">
-        <v>31</v>
-      </c>
-      <c r="N4">
+        <v>42</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N4" t="s">
+        <v>32</v>
+      </c>
+      <c r="O4">
         <v>30</v>
       </c>
-      <c r="O4" t="s">
-        <v>31</v>
-      </c>
       <c r="P4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q4" t="s">
-        <v>31</v>
-      </c>
-      <c r="R4">
+        <v>32</v>
+      </c>
+      <c r="R4" t="s">
+        <v>32</v>
+      </c>
+      <c r="S4">
         <v>2</v>
       </c>
-      <c r="S4">
+      <c r="T4">
         <v>1.5</v>
       </c>
-      <c r="T4">
+      <c r="U4">
         <v>20</v>
       </c>
-      <c r="U4">
+      <c r="V4">
         <v>1.2</v>
       </c>
-      <c r="V4">
+      <c r="W4">
         <v>1.15</v>
       </c>
-      <c r="W4" t="s">
-        <v>31</v>
-      </c>
-      <c r="X4">
+      <c r="X4" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y4">
         <v>50</v>
       </c>
-      <c r="Y4" t="s">
-        <v>31</v>
-      </c>
       <c r="Z4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AA4" t="s">
-        <v>31</v>
-      </c>
-      <c r="AB4">
+        <v>32</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC4">
         <v>1.5</v>
       </c>
-      <c r="AC4">
+      <c r="AD4">
         <v>30</v>
       </c>
-      <c r="AD4">
+      <c r="AE4">
         <v>1.5</v>
       </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -1939,7 +2088,7 @@
         <v>1</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -1948,78 +2097,81 @@
         <v>2</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="M5" t="s">
-        <v>31</v>
-      </c>
-      <c r="N5">
+        <v>32</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N5" t="s">
+        <v>32</v>
+      </c>
+      <c r="O5">
         <v>20</v>
       </c>
-      <c r="O5" t="s">
-        <v>31</v>
-      </c>
       <c r="P5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q5" t="s">
-        <v>31</v>
-      </c>
-      <c r="R5">
+        <v>32</v>
+      </c>
+      <c r="R5" t="s">
+        <v>32</v>
+      </c>
+      <c r="S5">
         <v>2</v>
       </c>
-      <c r="S5">
+      <c r="T5">
         <v>1.2</v>
       </c>
-      <c r="T5">
+      <c r="U5">
         <v>10</v>
       </c>
-      <c r="U5">
+      <c r="V5">
         <v>1.2</v>
       </c>
-      <c r="V5">
+      <c r="W5">
         <v>1.15</v>
       </c>
-      <c r="W5" t="s">
-        <v>31</v>
-      </c>
       <c r="X5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Y5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Z5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AA5" t="s">
-        <v>31</v>
-      </c>
-      <c r="AB5">
+        <v>32</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC5">
         <v>1.5</v>
       </c>
-      <c r="AC5">
+      <c r="AD5">
         <v>0</v>
       </c>
-      <c r="AD5">
+      <c r="AE5">
         <v>1.5</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -2031,7 +2183,7 @@
         <v>3</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -2040,78 +2192,81 @@
         <v>2</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="M6" t="s">
-        <v>31</v>
-      </c>
-      <c r="N6">
+        <v>49</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N6" t="s">
+        <v>32</v>
+      </c>
+      <c r="O6">
         <v>20</v>
       </c>
-      <c r="O6" t="s">
-        <v>31</v>
-      </c>
       <c r="P6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q6" t="s">
-        <v>31</v>
-      </c>
-      <c r="R6">
+        <v>32</v>
+      </c>
+      <c r="R6" t="s">
+        <v>32</v>
+      </c>
+      <c r="S6">
         <v>2.5</v>
       </c>
-      <c r="S6">
+      <c r="T6">
         <v>1.15</v>
       </c>
-      <c r="T6">
+      <c r="U6">
         <v>20</v>
       </c>
-      <c r="U6">
+      <c r="V6">
         <v>1.2</v>
       </c>
-      <c r="V6">
+      <c r="W6">
         <v>1.15</v>
       </c>
-      <c r="W6" t="s">
-        <v>31</v>
-      </c>
-      <c r="X6">
+      <c r="X6" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y6">
         <v>60</v>
       </c>
-      <c r="Y6" t="s">
-        <v>31</v>
-      </c>
       <c r="Z6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AA6" t="s">
-        <v>31</v>
-      </c>
-      <c r="AB6">
+        <v>32</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC6">
         <v>2.5</v>
       </c>
-      <c r="AC6">
+      <c r="AD6">
         <v>30</v>
       </c>
-      <c r="AD6">
+      <c r="AE6">
         <v>1.5</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -2123,7 +2278,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -2132,78 +2287,81 @@
         <v>2</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="M7" t="s">
-        <v>31</v>
-      </c>
-      <c r="N7">
+        <v>32</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N7" t="s">
+        <v>32</v>
+      </c>
+      <c r="O7">
         <v>40</v>
       </c>
-      <c r="O7" t="s">
-        <v>31</v>
-      </c>
       <c r="P7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R7">
+        <v>32</v>
+      </c>
+      <c r="R7" t="s">
+        <v>32</v>
+      </c>
+      <c r="S7">
         <v>2</v>
       </c>
-      <c r="S7">
+      <c r="T7">
         <v>1.2</v>
       </c>
-      <c r="T7">
+      <c r="U7">
         <v>30</v>
       </c>
-      <c r="U7">
+      <c r="V7">
         <v>1.2</v>
       </c>
-      <c r="V7">
+      <c r="W7">
         <v>1.15</v>
       </c>
-      <c r="W7" t="s">
-        <v>31</v>
-      </c>
       <c r="X7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Y7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Z7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AA7" t="s">
-        <v>31</v>
-      </c>
-      <c r="AB7">
+        <v>32</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC7">
         <v>1.5</v>
       </c>
-      <c r="AC7">
+      <c r="AD7">
         <v>0</v>
       </c>
-      <c r="AD7">
+      <c r="AE7">
         <v>1.5</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -2215,7 +2373,7 @@
         <v>2</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -2224,78 +2382,81 @@
         <v>2</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O8">
+        <v>30</v>
+      </c>
+      <c r="P8" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>32</v>
+      </c>
+      <c r="R8" t="s">
+        <v>32</v>
+      </c>
+      <c r="S8">
+        <v>2.5</v>
+      </c>
+      <c r="T8">
+        <v>1.15</v>
+      </c>
+      <c r="U8">
+        <v>20</v>
+      </c>
+      <c r="V8">
+        <v>1.2</v>
+      </c>
+      <c r="W8">
+        <v>1.15</v>
+      </c>
+      <c r="X8" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y8">
         <v>40</v>
       </c>
-      <c r="L8" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="M8" t="s">
-        <v>31</v>
-      </c>
-      <c r="N8">
+      <c r="Z8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC8">
+        <v>1.5</v>
+      </c>
+      <c r="AD8">
         <v>30</v>
       </c>
-      <c r="O8" t="s">
-        <v>31</v>
-      </c>
-      <c r="P8" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>31</v>
-      </c>
-      <c r="R8">
-        <v>2.5</v>
-      </c>
-      <c r="S8">
-        <v>1.15</v>
-      </c>
-      <c r="T8">
-        <v>20</v>
-      </c>
-      <c r="U8">
-        <v>1.2</v>
-      </c>
-      <c r="V8">
-        <v>1.15</v>
-      </c>
-      <c r="W8" t="s">
-        <v>31</v>
-      </c>
-      <c r="X8">
-        <v>40</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>31</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>31</v>
-      </c>
-      <c r="AA8" t="s">
-        <v>31</v>
-      </c>
-      <c r="AB8">
+      <c r="AE8">
         <v>1.5</v>
       </c>
-      <c r="AC8">
-        <v>30</v>
-      </c>
-      <c r="AD8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -2307,7 +2468,7 @@
         <v>2</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -2316,78 +2477,81 @@
         <v>2</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="M9" t="s">
-        <v>31</v>
-      </c>
-      <c r="N9">
+        <v>56</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N9" t="s">
+        <v>32</v>
+      </c>
+      <c r="O9">
         <v>25</v>
       </c>
-      <c r="O9" t="s">
-        <v>31</v>
-      </c>
       <c r="P9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q9" t="s">
-        <v>31</v>
-      </c>
-      <c r="R9">
+        <v>32</v>
+      </c>
+      <c r="R9" t="s">
+        <v>32</v>
+      </c>
+      <c r="S9">
         <v>2.5</v>
       </c>
-      <c r="S9">
+      <c r="T9">
         <v>1.15</v>
       </c>
-      <c r="T9">
+      <c r="U9">
         <v>20</v>
       </c>
-      <c r="U9">
+      <c r="V9">
         <v>1.2</v>
       </c>
-      <c r="V9">
+      <c r="W9">
         <v>1.15</v>
       </c>
-      <c r="W9" t="s">
-        <v>31</v>
-      </c>
-      <c r="X9">
+      <c r="X9" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y9">
         <v>35</v>
       </c>
-      <c r="Y9" t="s">
-        <v>31</v>
-      </c>
       <c r="Z9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AA9" t="s">
-        <v>31</v>
-      </c>
-      <c r="AB9">
+        <v>32</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC9">
         <v>1.5</v>
       </c>
-      <c r="AC9">
+      <c r="AD9">
         <v>30</v>
       </c>
-      <c r="AD9">
+      <c r="AE9">
         <v>1.5</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -2399,7 +2563,7 @@
         <v>2</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -2408,78 +2572,81 @@
         <v>2</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N10" t="s">
+        <v>32</v>
+      </c>
+      <c r="O10">
         <v>40</v>
       </c>
-      <c r="L10" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="M10" t="s">
-        <v>31</v>
-      </c>
-      <c r="N10">
-        <v>40</v>
-      </c>
-      <c r="O10" t="s">
-        <v>31</v>
-      </c>
-      <c r="P10">
+      <c r="P10" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q10">
         <v>20</v>
       </c>
-      <c r="Q10" t="s">
-        <v>31</v>
-      </c>
-      <c r="R10">
+      <c r="R10" t="s">
+        <v>32</v>
+      </c>
+      <c r="S10">
         <v>2.5</v>
       </c>
-      <c r="S10">
+      <c r="T10">
         <v>1.15</v>
       </c>
-      <c r="T10">
+      <c r="U10">
         <v>30</v>
       </c>
-      <c r="U10">
+      <c r="V10">
         <v>1.2</v>
       </c>
-      <c r="V10">
+      <c r="W10">
         <v>1.15</v>
       </c>
-      <c r="W10" t="s">
-        <v>31</v>
-      </c>
-      <c r="X10">
+      <c r="X10" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y10">
         <v>50</v>
       </c>
-      <c r="Y10" t="s">
-        <v>31</v>
-      </c>
-      <c r="Z10">
+      <c r="Z10" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA10">
         <v>25</v>
       </c>
-      <c r="AA10" t="s">
-        <v>31</v>
-      </c>
-      <c r="AB10">
+      <c r="AB10" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC10">
         <v>1.5</v>
       </c>
-      <c r="AC10">
+      <c r="AD10">
         <v>30</v>
       </c>
-      <c r="AD10">
+      <c r="AE10">
         <v>1.5</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -2491,7 +2658,7 @@
         <v>3</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -2500,72 +2667,455 @@
         <v>2</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L11" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N11">
+        <v>300</v>
+      </c>
+      <c r="O11" t="s">
+        <v>32</v>
+      </c>
+      <c r="P11" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q11">
+        <v>40</v>
+      </c>
+      <c r="R11" t="s">
+        <v>32</v>
+      </c>
+      <c r="S11">
+        <v>1</v>
+      </c>
+      <c r="T11">
+        <v>1</v>
+      </c>
+      <c r="U11">
+        <v>90</v>
+      </c>
+      <c r="V11">
+        <v>1</v>
+      </c>
+      <c r="W11">
+        <v>1.15</v>
+      </c>
+      <c r="X11">
+        <v>500</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA11">
+        <v>80</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC11">
+        <v>1.8</v>
+      </c>
+      <c r="AD11">
+        <v>120</v>
+      </c>
+      <c r="AE11">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>3</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="N12" t="s">
+        <v>32</v>
+      </c>
+      <c r="O12">
         <v>60</v>
       </c>
-      <c r="M11">
-        <v>300</v>
-      </c>
-      <c r="N11" t="s">
-        <v>31</v>
-      </c>
-      <c r="O11" t="s">
-        <v>31</v>
-      </c>
-      <c r="P11">
+      <c r="P12" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q12">
+        <v>20</v>
+      </c>
+      <c r="R12" t="s">
+        <v>32</v>
+      </c>
+      <c r="S12">
+        <v>1</v>
+      </c>
+      <c r="T12">
+        <v>1</v>
+      </c>
+      <c r="U12">
+        <v>45</v>
+      </c>
+      <c r="V12">
+        <v>1</v>
+      </c>
+      <c r="W12">
+        <v>1.15</v>
+      </c>
+      <c r="X12" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y12">
+        <v>180</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA12">
+        <v>60</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC12">
+        <v>1.8</v>
+      </c>
+      <c r="AD12">
+        <v>90</v>
+      </c>
+      <c r="AE12">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>3</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="N13" t="s">
+        <v>32</v>
+      </c>
+      <c r="O13">
+        <v>80</v>
+      </c>
+      <c r="P13" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q13">
+        <v>30</v>
+      </c>
+      <c r="R13" t="s">
+        <v>32</v>
+      </c>
+      <c r="S13">
+        <v>1</v>
+      </c>
+      <c r="T13">
+        <v>1</v>
+      </c>
+      <c r="U13">
+        <v>60</v>
+      </c>
+      <c r="V13">
+        <v>1</v>
+      </c>
+      <c r="W13">
+        <v>1.15</v>
+      </c>
+      <c r="X13" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y13">
+        <v>240</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA13">
+        <v>90</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC13">
+        <v>1.8</v>
+      </c>
+      <c r="AD13">
+        <v>120</v>
+      </c>
+      <c r="AE13">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>3</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="N14" t="s">
+        <v>32</v>
+      </c>
+      <c r="O14">
+        <v>80</v>
+      </c>
+      <c r="P14" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q14">
+        <v>30</v>
+      </c>
+      <c r="R14" t="s">
+        <v>32</v>
+      </c>
+      <c r="S14">
+        <v>1</v>
+      </c>
+      <c r="T14">
+        <v>1</v>
+      </c>
+      <c r="U14">
+        <v>60</v>
+      </c>
+      <c r="V14">
+        <v>1</v>
+      </c>
+      <c r="W14">
+        <v>1.15</v>
+      </c>
+      <c r="X14" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y14">
+        <v>240</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA14">
+        <v>90</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC14">
+        <v>1.8</v>
+      </c>
+      <c r="AD14">
+        <v>120</v>
+      </c>
+      <c r="AE14">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>66</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>3</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="N15" t="s">
+        <v>32</v>
+      </c>
+      <c r="O15">
+        <v>120</v>
+      </c>
+      <c r="P15" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q15">
         <v>40</v>
       </c>
-      <c r="Q11" t="s">
-        <v>31</v>
-      </c>
-      <c r="R11">
-        <v>1</v>
-      </c>
-      <c r="S11">
-        <v>1</v>
-      </c>
-      <c r="T11">
+      <c r="R15">
+        <v>10</v>
+      </c>
+      <c r="S15">
+        <v>1</v>
+      </c>
+      <c r="T15">
+        <v>1</v>
+      </c>
+      <c r="U15">
         <v>90</v>
       </c>
-      <c r="U11">
-        <v>1</v>
-      </c>
-      <c r="V11">
+      <c r="V15">
+        <v>1</v>
+      </c>
+      <c r="W15">
         <v>1.15</v>
       </c>
-      <c r="W11">
-        <v>500</v>
-      </c>
-      <c r="X11" t="s">
-        <v>31</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>31</v>
-      </c>
-      <c r="Z11">
-        <v>80</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>31</v>
-      </c>
-      <c r="AB11">
+      <c r="X15" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y15">
+        <v>360</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA15">
+        <v>120</v>
+      </c>
+      <c r="AB15">
+        <v>30</v>
+      </c>
+      <c r="AC15">
         <v>1.8</v>
       </c>
-      <c r="AC11">
-        <v>120</v>
-      </c>
-      <c r="AD11">
+      <c r="AD15">
+        <v>180</v>
+      </c>
+      <c r="AE15">
         <v>1.6</v>
       </c>
     </row>
@@ -2593,27 +3143,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -2628,15 +3178,15 @@
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -2651,7 +3201,7 @@
         <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -2659,7 +3209,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="B4">
         <v>2</v>
@@ -2677,12 +3227,12 @@
         <v>3600</v>
       </c>
       <c r="G4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="B5">
         <v>3</v>
@@ -2697,15 +3247,15 @@
         <v>0</v>
       </c>
       <c r="F5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -2720,10 +3270,10 @@
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -2733,6 +3283,218 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="7" width="10" customWidth="1"/>
+    <col min="8" max="9" width="15" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2" t="s">
+        <v>260</v>
+      </c>
+      <c r="D2">
+        <v>0.2</v>
+      </c>
+      <c r="E2">
+        <v>4</v>
+      </c>
+      <c r="F2">
+        <v>6</v>
+      </c>
+      <c r="G2">
+        <v>24</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>261</v>
+      </c>
+      <c r="B3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" t="s">
+        <v>262</v>
+      </c>
+      <c r="D3">
+        <v>0.25</v>
+      </c>
+      <c r="E3">
+        <v>6</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>16</v>
+      </c>
+      <c r="H3">
+        <v>1.5</v>
+      </c>
+      <c r="I3">
+        <v>0.5</v>
+      </c>
+      <c r="J3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>263</v>
+      </c>
+      <c r="B4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" t="s">
+        <v>264</v>
+      </c>
+      <c r="D4">
+        <v>0.5</v>
+      </c>
+      <c r="E4">
+        <v>7</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <v>12</v>
+      </c>
+      <c r="H4">
+        <v>1.5</v>
+      </c>
+      <c r="I4">
+        <v>0.4</v>
+      </c>
+      <c r="J4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>265</v>
+      </c>
+      <c r="B5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C5" t="s">
+        <v>266</v>
+      </c>
+      <c r="D5">
+        <v>0.5</v>
+      </c>
+      <c r="E5">
+        <v>8</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>18</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>0.5</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>267</v>
+      </c>
+      <c r="B6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" t="s">
+        <v>268</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>14</v>
+      </c>
+      <c r="H6">
+        <v>1.5</v>
+      </c>
+      <c r="I6">
+        <v>0.5</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -2745,24 +3507,24 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>244</v>
+        <v>269</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>247</v>
+        <v>272</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>248</v>
+        <v>273</v>
       </c>
       <c r="B2" t="s">
-        <v>249</v>
+        <v>274</v>
       </c>
       <c r="C2">
         <v>2</v>
@@ -2771,15 +3533,15 @@
         <v>-1</v>
       </c>
       <c r="E2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="B3" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="C3">
         <v>-1</v>
@@ -2788,15 +3550,15 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="B4" t="s">
-        <v>253</v>
+        <v>278</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -2805,15 +3567,15 @@
         <v>4</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>254</v>
+        <v>279</v>
       </c>
       <c r="B5" t="s">
-        <v>249</v>
+        <v>274</v>
       </c>
       <c r="C5">
         <v>-2</v>
@@ -2822,15 +3584,15 @@
         <v>-2</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>255</v>
+        <v>280</v>
       </c>
       <c r="B6" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -2844,10 +3606,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>256</v>
+        <v>281</v>
       </c>
       <c r="B7" t="s">
-        <v>253</v>
+        <v>278</v>
       </c>
       <c r="C7">
         <v>-1</v>
@@ -2856,15 +3618,15 @@
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>257</v>
+        <v>282</v>
       </c>
       <c r="B8" t="s">
-        <v>249</v>
+        <v>274</v>
       </c>
       <c r="C8">
         <v>5</v>
@@ -2878,10 +3640,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>258</v>
+        <v>283</v>
       </c>
       <c r="B9" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="C9">
         <v>-4</v>
@@ -2890,15 +3652,15 @@
         <v>-3</v>
       </c>
       <c r="E9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>259</v>
+        <v>284</v>
       </c>
       <c r="B10" t="s">
-        <v>253</v>
+        <v>278</v>
       </c>
       <c r="C10">
         <v>5</v>
@@ -2912,10 +3674,10 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>260</v>
+        <v>285</v>
       </c>
       <c r="B11" t="s">
-        <v>249</v>
+        <v>274</v>
       </c>
       <c r="C11">
         <v>9</v>
@@ -2933,7 +3695,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -2952,45 +3714,45 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>261</v>
+        <v>286</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>262</v>
+        <v>287</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>263</v>
+        <v>288</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>264</v>
+        <v>289</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>265</v>
+        <v>290</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>266</v>
+        <v>291</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>267</v>
+        <v>292</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>268</v>
+        <v>293</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>269</v>
+        <v>294</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>270</v>
+        <v>295</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>271</v>
+        <v>296</v>
       </c>
       <c r="B2">
         <v>-2</v>
@@ -3020,18 +3782,18 @@
         <v>50</v>
       </c>
       <c r="K2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L2" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="M2" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>272</v>
+        <v>297</v>
       </c>
       <c r="B3">
         <v>5</v>
@@ -3061,18 +3823,18 @@
         <v>150</v>
       </c>
       <c r="K3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L3" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="M3" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>273</v>
+        <v>298</v>
       </c>
       <c r="B4">
         <v>-3</v>
@@ -3105,15 +3867,15 @@
         <v>10</v>
       </c>
       <c r="L4" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="M4" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>274</v>
+        <v>299</v>
       </c>
       <c r="B5">
         <v>8</v>
@@ -3146,15 +3908,15 @@
         <v>20</v>
       </c>
       <c r="L5" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="M5" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="B6">
         <v>-2</v>
@@ -3187,10 +3949,10 @@
         <v>40</v>
       </c>
       <c r="L6" t="s">
-        <v>276</v>
+        <v>301</v>
       </c>
       <c r="M6" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
     </row>
   </sheetData>
@@ -3199,9 +3961,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:B66"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
@@ -3209,15 +3971,15 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>277</v>
+        <v>302</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>278</v>
+        <v>303</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>279</v>
+        <v>304</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -3225,7 +3987,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="B3">
         <v>8</v>
@@ -3233,7 +3995,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>281</v>
+        <v>306</v>
       </c>
       <c r="B4">
         <v>0.5</v>
@@ -3241,7 +4003,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>282</v>
+        <v>307</v>
       </c>
       <c r="B5">
         <v>20</v>
@@ -3249,7 +4011,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>283</v>
+        <v>308</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -3257,7 +4019,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="B7">
         <v>30</v>
@@ -3265,7 +4027,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="B8">
         <v>20</v>
@@ -3273,7 +4035,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="B9">
         <v>60</v>
@@ -3281,7 +4043,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>287</v>
+        <v>312</v>
       </c>
       <c r="B10">
         <v>8</v>
@@ -3289,7 +4051,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>288</v>
+        <v>313</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -3297,7 +4059,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>289</v>
+        <v>314</v>
       </c>
       <c r="B12">
         <v>1.25</v>
@@ -3305,7 +4067,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -3313,7 +4075,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>291</v>
+        <v>316</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -3321,7 +4083,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>292</v>
+        <v>317</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -3329,7 +4091,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
       <c r="B16">
         <v>5</v>
@@ -3337,7 +4099,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>294</v>
+        <v>319</v>
       </c>
       <c r="B17">
         <v>1.45</v>
@@ -3345,7 +4107,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>295</v>
+        <v>320</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -3353,207 +4115,207 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>296</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>297</v>
+        <v>321</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>298</v>
+        <v>322</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>299</v>
+        <v>323</v>
       </c>
       <c r="B21">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>300</v>
+        <v>324</v>
       </c>
       <c r="B22">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>301</v>
+        <v>325</v>
       </c>
       <c r="B23">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>302</v>
+        <v>326</v>
       </c>
       <c r="B24">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>303</v>
-      </c>
-      <c r="B25">
-        <v>3</v>
+        <v>327</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>304</v>
+        <v>329</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>305</v>
+        <v>330</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>306</v>
+        <v>331</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>307</v>
+        <v>332</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>308</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>309</v>
+        <v>333</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>310</v>
+        <v>334</v>
       </c>
       <c r="B29">
-        <v>1</v>
+        <v>120</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>311</v>
+        <v>335</v>
       </c>
       <c r="B30">
-        <v>120</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>312</v>
+        <v>336</v>
       </c>
       <c r="B31">
-        <v>1.3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>313</v>
+        <v>337</v>
       </c>
       <c r="B32">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="B33">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>315</v>
+        <v>339</v>
       </c>
       <c r="B34">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>316</v>
+        <v>340</v>
       </c>
       <c r="B35">
-        <v>20</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>317</v>
+        <v>341</v>
       </c>
       <c r="B36">
-        <v>2.5</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>318</v>
+        <v>342</v>
       </c>
       <c r="B37">
-        <v>300</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>319</v>
+        <v>343</v>
       </c>
       <c r="B38">
-        <v>20</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>320</v>
+        <v>344</v>
       </c>
       <c r="B39">
-        <v>1.6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>321</v>
+        <v>345</v>
       </c>
       <c r="B40">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>322</v>
+        <v>346</v>
       </c>
       <c r="B41">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>323</v>
+        <v>347</v>
       </c>
       <c r="B42">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>324</v>
+        <v>348</v>
       </c>
       <c r="B43">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>325</v>
+        <v>349</v>
       </c>
       <c r="B44">
         <v>2</v>
@@ -3561,10 +4323,178 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>326</v>
+        <v>350</v>
       </c>
       <c r="B45">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>351</v>
+      </c>
+      <c r="B46">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>352</v>
+      </c>
+      <c r="B47">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>353</v>
+      </c>
+      <c r="B48">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>354</v>
+      </c>
+      <c r="B49">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>355</v>
+      </c>
+      <c r="B50">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>356</v>
+      </c>
+      <c r="B51">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>357</v>
+      </c>
+      <c r="B52">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>358</v>
+      </c>
+      <c r="B53">
         <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>359</v>
+      </c>
+      <c r="B54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>360</v>
+      </c>
+      <c r="B55">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>361</v>
+      </c>
+      <c r="B56">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>362</v>
+      </c>
+      <c r="B57">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>363</v>
+      </c>
+      <c r="B58">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>364</v>
+      </c>
+      <c r="B59">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>365</v>
+      </c>
+      <c r="B60">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>366</v>
+      </c>
+      <c r="B61">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>367</v>
+      </c>
+      <c r="B62">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>368</v>
+      </c>
+      <c r="B63">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>369</v>
+      </c>
+      <c r="B64">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>370</v>
+      </c>
+      <c r="B65">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>371</v>
+      </c>
+      <c r="B66">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -3573,7 +4503,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -3646,61 +4576,61 @@
         <v>-10</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>328</v>
+        <v>373</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>328</v>
+        <v>373</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>328</v>
+        <v>373</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>328</v>
+        <v>373</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>328</v>
+        <v>373</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>328</v>
+        <v>373</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>328</v>
+        <v>373</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>328</v>
+        <v>373</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>328</v>
+        <v>373</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
@@ -3708,61 +4638,61 @@
         <v>-9</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>328</v>
+        <v>373</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>329</v>
+        <v>374</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>330</v>
+        <v>375</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>330</v>
+        <v>375</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>330</v>
+        <v>375</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>329</v>
+        <v>374</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>330</v>
+        <v>375</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>330</v>
+        <v>375</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>328</v>
+        <v>373</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
@@ -3770,61 +4700,61 @@
         <v>-8</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>328</v>
+        <v>373</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>328</v>
+        <v>373</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>329</v>
+        <v>374</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>328</v>
+        <v>373</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>328</v>
+        <v>373</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>328</v>
+        <v>373</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>328</v>
+        <v>373</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>329</v>
+        <v>374</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>328</v>
+        <v>373</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -3832,61 +4762,61 @@
         <v>-7</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>331</v>
+        <v>376</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>331</v>
+        <v>376</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>331</v>
+        <v>376</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>331</v>
+        <v>376</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>332</v>
+        <v>377</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>331</v>
+        <v>376</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>331</v>
+        <v>376</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>331</v>
+        <v>376</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>331</v>
+        <v>376</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -3894,61 +4824,61 @@
         <v>-6</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>333</v>
+        <v>378</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>333</v>
+        <v>378</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="T6" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -3956,61 +4886,61 @@
         <v>-5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>330</v>
+        <v>375</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>330</v>
+        <v>375</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="T7" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -4018,61 +4948,61 @@
         <v>-4</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>335</v>
+        <v>380</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>336</v>
+        <v>381</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>336</v>
+        <v>381</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>330</v>
+        <v>375</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>337</v>
+        <v>382</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>330</v>
+        <v>375</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -4080,61 +5010,61 @@
         <v>-3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>330</v>
+        <v>375</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>330</v>
+        <v>375</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>330</v>
+        <v>375</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>333</v>
+        <v>378</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>338</v>
+        <v>383</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>338</v>
+        <v>383</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -4142,61 +5072,61 @@
         <v>-2</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>335</v>
+        <v>380</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>330</v>
+        <v>375</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>330</v>
+        <v>375</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>338</v>
+        <v>383</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>338</v>
+        <v>383</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>339</v>
+        <v>384</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -4204,61 +5134,61 @@
         <v>-1</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>333</v>
+        <v>378</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>330</v>
+        <v>375</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>337</v>
+        <v>382</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>338</v>
+        <v>383</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>340</v>
+        <v>385</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>338</v>
+        <v>383</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>338</v>
+        <v>383</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -4266,61 +5196,61 @@
         <v>0</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>333</v>
+        <v>378</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>330</v>
+        <v>375</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>330</v>
+        <v>375</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>338</v>
+        <v>383</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>330</v>
+        <v>375</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>330</v>
+        <v>375</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>340</v>
+        <v>385</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -4328,61 +5258,61 @@
         <v>1</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>338</v>
+        <v>383</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>338</v>
+        <v>383</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>340</v>
+        <v>385</v>
       </c>
       <c r="T13" s="3" t="s">
-        <v>338</v>
+        <v>383</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -4390,61 +5320,61 @@
         <v>2</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>333</v>
+        <v>378</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>341</v>
+        <v>386</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>336</v>
+        <v>381</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>338</v>
+        <v>383</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>338</v>
+        <v>383</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>338</v>
+        <v>383</v>
       </c>
       <c r="T14" s="3" t="s">
-        <v>338</v>
+        <v>383</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -4452,61 +5382,61 @@
         <v>3</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>336</v>
+        <v>381</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>336</v>
+        <v>381</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>336</v>
+        <v>381</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>336</v>
+        <v>381</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>336</v>
+        <v>381</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>330</v>
+        <v>375</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>340</v>
+        <v>385</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>338</v>
+        <v>383</v>
       </c>
       <c r="T15" s="3" t="s">
-        <v>338</v>
+        <v>383</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -4514,61 +5444,61 @@
         <v>4</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>333</v>
+        <v>378</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>336</v>
+        <v>381</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>336</v>
+        <v>381</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>336</v>
+        <v>381</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>336</v>
+        <v>381</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>336</v>
+        <v>381</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>342</v>
+        <v>387</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>338</v>
+        <v>383</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>338</v>
+        <v>383</v>
       </c>
       <c r="T16" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
@@ -4576,61 +5506,61 @@
         <v>5</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>336</v>
+        <v>381</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>336</v>
+        <v>381</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>338</v>
+        <v>383</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>338</v>
+        <v>383</v>
       </c>
       <c r="T17" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -4638,61 +5568,61 @@
         <v>6</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>333</v>
+        <v>378</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>336</v>
+        <v>381</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>335</v>
+        <v>380</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="T18" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
@@ -4700,61 +5630,61 @@
         <v>7</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>333</v>
+        <v>378</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="S19" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="T19" s="3" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
     </row>
   </sheetData>
@@ -4806,143 +5736,188 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="2" width="10" customWidth="1"/>
-    <col min="3" max="5" width="19" customWidth="1"/>
-    <col min="6" max="6" width="20" customWidth="1"/>
-    <col min="7" max="7" width="19" customWidth="1"/>
-    <col min="8" max="8" width="24" customWidth="1"/>
+    <col min="1" max="5" width="10" customWidth="1"/>
+    <col min="6" max="8" width="19" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="10" max="10" width="19" customWidth="1"/>
+    <col min="11" max="11" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="B2">
         <v>3</v>
       </c>
       <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>12</v>
+      </c>
+      <c r="F2">
         <v>50</v>
       </c>
-      <c r="D2">
+      <c r="G2">
         <v>10</v>
       </c>
-      <c r="E2">
+      <c r="H2">
         <v>20</v>
       </c>
-      <c r="F2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H2">
+      <c r="I2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K2">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>8</v>
+      </c>
+      <c r="F3">
         <v>100</v>
       </c>
-      <c r="D3">
+      <c r="G3">
         <v>30</v>
       </c>
-      <c r="E3">
+      <c r="H3">
         <v>10</v>
       </c>
-      <c r="F3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H3">
+      <c r="I3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3">
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="B4">
+        <v>6</v>
+      </c>
+      <c r="C4">
+        <v>6</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>6</v>
+      </c>
+      <c r="F4">
+        <v>60</v>
+      </c>
+      <c r="G4">
+        <v>30</v>
+      </c>
+      <c r="H4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B5">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+      <c r="D5">
         <v>2</v>
       </c>
-      <c r="C4">
-        <v>60</v>
-      </c>
-      <c r="D4">
-        <v>30</v>
-      </c>
-      <c r="E4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H4">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
+      <c r="E5">
+        <v>10</v>
+      </c>
+      <c r="F5">
         <v>150</v>
       </c>
-      <c r="D5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5">
+      <c r="G5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5">
         <v>40</v>
       </c>
-      <c r="F5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5">
+      <c r="I5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5">
         <v>20</v>
       </c>
-      <c r="H5">
+      <c r="K5">
         <v>60</v>
       </c>
     </row>
@@ -4967,27 +5942,27 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -5002,12 +5977,12 @@
         <v>90</v>
       </c>
       <c r="F2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -5022,12 +5997,12 @@
         <v>60</v>
       </c>
       <c r="F3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -5047,7 +6022,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -5067,7 +6042,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -5082,12 +6057,12 @@
         <v>120</v>
       </c>
       <c r="F6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -5107,7 +6082,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -5122,7 +6097,7 @@
         <v>300</v>
       </c>
       <c r="F8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -5146,30 +6121,30 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -5178,21 +6153,21 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -5201,10 +6176,10 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -5212,10 +6187,10 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -5224,10 +6199,10 @@
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4">
         <v>3</v>
@@ -5235,10 +6210,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -5247,10 +6222,10 @@
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -5258,10 +6233,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -5270,10 +6245,10 @@
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G6">
         <v>6</v>
@@ -5281,42 +6256,42 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E8" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -5327,19 +6302,19 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E9" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="F9">
         <v>3</v>
@@ -5350,19 +6325,19 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -5373,33 +6348,33 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C12">
         <v>10</v>
@@ -5408,13 +6383,13 @@
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -5433,10 +6408,10 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -5543,56 +6518,56 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="B2">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G2">
         <v>30</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B3">
         <v>200</v>
@@ -5601,24 +6576,24 @@
         <v>50</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G3">
         <v>60</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="B4">
         <v>450</v>
@@ -5627,36 +6602,36 @@
         <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4">
         <v>90</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B5">
         <v>600</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5">
         <v>15</v>
@@ -5665,12 +6640,12 @@
         <v>120</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="B6">
         <v>100</v>
@@ -5679,24 +6654,24 @@
         <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G6">
         <v>45</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="B7">
         <v>250</v>
@@ -5705,76 +6680,76 @@
         <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G7">
         <v>60</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B8">
         <v>150</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G8">
         <v>45</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B9">
         <v>300</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D9">
         <v>30</v>
       </c>
       <c r="E9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G9">
         <v>75</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="B10">
         <v>100</v>
@@ -5783,102 +6758,102 @@
         <v>25</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G10">
         <v>45</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B11">
         <v>250</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E11">
         <v>30</v>
       </c>
       <c r="F11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G11">
         <v>60</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B12">
         <v>500</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E12">
         <v>60</v>
       </c>
       <c r="F12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G12">
         <v>90</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B13">
         <v>800</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E13">
         <v>30</v>
       </c>
       <c r="F13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G13">
         <v>120</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="B14">
         <v>150</v>
@@ -5887,50 +6862,50 @@
         <v>30</v>
       </c>
       <c r="D14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G14">
         <v>45</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="B15">
         <v>100</v>
       </c>
       <c r="C15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D15">
         <v>20</v>
       </c>
       <c r="E15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G15">
         <v>45</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B16">
         <v>400</v>
@@ -5939,24 +6914,24 @@
         <v>40</v>
       </c>
       <c r="D16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G16">
         <v>90</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B17">
         <v>200</v>
@@ -5965,50 +6940,50 @@
         <v>25</v>
       </c>
       <c r="D17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G17">
         <v>60</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="B18">
         <v>100</v>
       </c>
       <c r="C18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G18">
         <v>30</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B19">
         <v>150</v>
@@ -6017,24 +6992,24 @@
         <v>20</v>
       </c>
       <c r="D19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G19">
         <v>45</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="B20">
         <v>150</v>
@@ -6043,88 +7018,88 @@
         <v>20</v>
       </c>
       <c r="D20" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E20" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F20" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G20">
         <v>60</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="B21">
         <v>400</v>
       </c>
       <c r="C21" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D21">
         <v>30</v>
       </c>
       <c r="E21" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F21" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G21">
         <v>90</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="B22">
         <v>400</v>
       </c>
       <c r="C22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E22">
         <v>40</v>
       </c>
       <c r="F22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G22">
         <v>120</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B23">
         <v>600</v>
       </c>
       <c r="C23" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D23" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E23" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F23">
         <v>20</v>
@@ -6133,7 +7108,7 @@
         <v>180</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -6160,24 +7135,24 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="B2">
         <v>50</v>
@@ -6192,12 +7167,12 @@
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="B3">
         <v>75</v>
@@ -6212,12 +7187,12 @@
         <v>0.05</v>
       </c>
       <c r="F3" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B4">
         <v>200</v>
@@ -6232,12 +7207,12 @@
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="B5">
         <v>100</v>
@@ -6252,12 +7227,12 @@
         <v>0.05</v>
       </c>
       <c r="F5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="B6">
         <v>150</v>
@@ -6272,12 +7247,12 @@
         <v>0.1</v>
       </c>
       <c r="F6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="B7">
         <v>100</v>
@@ -6292,12 +7267,12 @@
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B8">
         <v>100</v>
@@ -6312,12 +7287,12 @@
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="B9">
         <v>150</v>
@@ -6332,7 +7307,7 @@
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -6352,21 +7327,21 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C2">
         <v>-1</v>
@@ -6398,309 +7373,309 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="B2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="C2" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="D2" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="E2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F2">
         <v>5</v>
       </c>
       <c r="G2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H2">
         <v>10</v>
       </c>
       <c r="I2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="B3" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="C3" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="D3" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="E3" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="F3">
         <v>10</v>
       </c>
       <c r="G3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H3">
         <v>15</v>
       </c>
       <c r="I3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="B4" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="C4" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="D4" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H4">
         <v>20</v>
       </c>
       <c r="I4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="B5" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="C5" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="D5" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="E5" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="F5">
         <v>3</v>
       </c>
       <c r="G5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H5">
         <v>15</v>
       </c>
       <c r="I5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="B6" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="C6" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="D6" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H6">
         <v>25</v>
       </c>
       <c r="I6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="B7" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="C7" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="D7" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F7">
         <v>6</v>
       </c>
       <c r="G7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H7">
         <v>20</v>
       </c>
       <c r="I7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="B8" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="C8" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="D8" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="E8" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="F8">
         <v>30</v>
       </c>
       <c r="G8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H8">
         <v>20</v>
@@ -6709,402 +7684,402 @@
         <v>10</v>
       </c>
       <c r="J8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="B9" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="C9" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="D9" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="E9" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
       <c r="G9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H9">
         <v>40</v>
       </c>
       <c r="I9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="B10" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="C10" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="D10" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="E10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="G10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H10">
         <v>30</v>
       </c>
       <c r="I10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="B11" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="C11" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="D11" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="E11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H11">
         <v>30</v>
       </c>
       <c r="I11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="B12" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="C12" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="D12" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="E12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F12">
         <v>2</v>
       </c>
       <c r="G12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H12">
         <v>40</v>
       </c>
       <c r="I12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="B13" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="C13" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="D13" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="E13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F13">
         <v>2</v>
       </c>
       <c r="G13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H13">
         <v>50</v>
       </c>
       <c r="I13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="B14" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="C14" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="D14" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="E14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F14">
         <v>3</v>
       </c>
       <c r="G14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H14">
         <v>60</v>
       </c>
       <c r="I14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="B15" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="C15" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D15" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="E15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F15">
         <v>1</v>
       </c>
       <c r="G15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H15">
         <v>50</v>
       </c>
       <c r="I15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J15">
         <v>20</v>
       </c>
       <c r="K15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="B16" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="C16" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="D16" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="E16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F16">
         <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H16">
         <v>80</v>
       </c>
       <c r="I16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="B17" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="C17" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="D17" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="E17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F17">
         <v>20</v>
       </c>
       <c r="G17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H17">
         <v>100</v>
       </c>
       <c r="I17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B18" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="C18" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="D18" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -7116,16 +8091,16 @@
         <v>150</v>
       </c>
       <c r="I18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M18">
         <v>5</v>
@@ -7133,60 +8108,60 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="B19" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="C19" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="D19" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="E19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
       <c r="G19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H19">
         <v>60</v>
       </c>
       <c r="I19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="B20" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="C20" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="D20" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -7198,323 +8173,323 @@
         <v>75</v>
       </c>
       <c r="I20" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J20" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K20" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L20" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M20" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="B21" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="C21" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="D21" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="E21" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F21">
         <v>6</v>
       </c>
       <c r="G21" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H21">
         <v>75</v>
       </c>
       <c r="I21" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J21">
         <v>20</v>
       </c>
       <c r="K21" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L21" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M21" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="B22" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="C22" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="D22" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="E22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F22">
         <v>1</v>
       </c>
       <c r="G22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H22">
         <v>100</v>
       </c>
       <c r="I22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="B23" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="C23" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="D23" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="E23" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F23">
         <v>1</v>
       </c>
       <c r="G23" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H23">
         <v>60</v>
       </c>
       <c r="I23" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J23" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K23" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L23" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M23" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="B24" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="C24" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="D24" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="E24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F24">
         <v>1</v>
       </c>
       <c r="G24" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H24">
         <v>80</v>
       </c>
       <c r="I24" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J24" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K24" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L24" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M24" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="B25" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="C25" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="D25" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="E25" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="F25">
         <v>10</v>
       </c>
       <c r="G25" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H25">
         <v>120</v>
       </c>
       <c r="I25" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J25" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K25" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L25" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M25" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="B26" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="C26" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="D26" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="E26" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F26">
         <v>1</v>
       </c>
       <c r="G26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H26">
         <v>120</v>
       </c>
       <c r="I26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="B27" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="C27" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="D27" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="E27" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="F27">
         <v>1</v>
       </c>
       <c r="G27" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H27">
         <v>150</v>
       </c>
       <c r="I27" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J27" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K27" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L27" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M27" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="B28" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="C28" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="D28" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E28" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F28">
         <v>1</v>
@@ -7526,16 +8501,16 @@
         <v>300</v>
       </c>
       <c r="I28" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J28" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K28" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L28" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M28">
         <v>10</v>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1419" uniqueCount="422">
   <si>
     <t>id</t>
   </si>
@@ -751,6 +751,108 @@
   </si>
   <si>
     <t>Upgrade the Townhall to level 3.</t>
+  </si>
+  <si>
+    <t>TheFirstShrine</t>
+  </si>
+  <si>
+    <t>Old Stones</t>
+  </si>
+  <si>
+    <t>Claim a landmark — it feeds your kingdom Mana every hour, for good.</t>
+  </si>
+  <si>
+    <t>ClaimLandmarks</t>
+  </si>
+  <si>
+    <t>Attuned</t>
+  </si>
+  <si>
+    <t>Research Attunement — a second relic can then be worn at once.</t>
+  </si>
+  <si>
+    <t>TheSanctum</t>
+  </si>
+  <si>
+    <t>A Place for Magic</t>
+  </si>
+  <si>
+    <t>Build the Sanctum — a bigger pool holds a longer absence.</t>
+  </si>
+  <si>
+    <t>Mustered</t>
+  </si>
+  <si>
+    <t>Build a Barracks — an army is a city decision now, not a Townhall one.</t>
+  </si>
+  <si>
+    <t>AWarband</t>
+  </si>
+  <si>
+    <t>A Warband</t>
+  </si>
+  <si>
+    <t>Train four units — enough to send someone into the dark.</t>
+  </si>
+  <si>
+    <t>IntoTheDark</t>
+  </si>
+  <si>
+    <t>Into the Dark</t>
+  </si>
+  <si>
+    <t>Send a party into a ruin and clear its first depth.</t>
+  </si>
+  <si>
+    <t>ReachDepth</t>
+  </si>
+  <si>
+    <t>TheBarrowsPrize</t>
+  </si>
+  <si>
+    <t>The Barrow’s Prize</t>
+  </si>
+  <si>
+    <t>Clear a ruin to its bottom — the relic waiting there is yours.</t>
+  </si>
+  <si>
+    <t>ClearRuins</t>
+  </si>
+  <si>
+    <t>WornWell</t>
+  </si>
+  <si>
+    <t>Worn Well</t>
+  </si>
+  <si>
+    <t>Attune a relic. It works while you wear it, and only while you wear it.</t>
+  </si>
+  <si>
+    <t>OwnArtifacts</t>
+  </si>
+  <si>
+    <t>Leylines</t>
+  </si>
+  <si>
+    <t>Claim four landmarks — every one makes the next stretch of fog cheaper.</t>
+  </si>
+  <si>
+    <t>DeeperStill</t>
+  </si>
+  <si>
+    <t>Deeper Still</t>
+  </si>
+  <si>
+    <t>Reach depth five. Past your safe floor is a gamble you choose.</t>
+  </si>
+  <si>
+    <t>TheReliquary</t>
+  </si>
+  <si>
+    <t>The Reliquary</t>
+  </si>
+  <si>
+    <t>Recover three relics. Each ruin holds exactly one.</t>
   </si>
   <si>
     <t>upkeep</t>
@@ -3143,27 +3245,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>242</v>
+        <v>276</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>243</v>
+        <v>277</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>244</v>
+        <v>278</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>245</v>
+        <v>279</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>246</v>
+        <v>280</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>247</v>
+        <v>281</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>248</v>
+        <v>282</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -3186,7 +3288,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>249</v>
+        <v>283</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -3209,7 +3311,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>250</v>
+        <v>284</v>
       </c>
       <c r="B4">
         <v>2</v>
@@ -3232,7 +3334,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>251</v>
+        <v>285</v>
       </c>
       <c r="B5">
         <v>3</v>
@@ -3255,7 +3357,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>252</v>
+        <v>286</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -3301,13 +3403,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>253</v>
+        <v>287</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>254</v>
+        <v>288</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>255</v>
+        <v>289</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>68</v>
@@ -3319,24 +3421,24 @@
         <v>70</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>256</v>
+        <v>290</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>257</v>
+        <v>291</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>258</v>
+        <v>292</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>259</v>
+        <v>293</v>
       </c>
       <c r="B2" t="s">
         <v>77</v>
       </c>
       <c r="C2" t="s">
-        <v>260</v>
+        <v>294</v>
       </c>
       <c r="D2">
         <v>0.2</v>
@@ -3362,13 +3464,13 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>261</v>
+        <v>295</v>
       </c>
       <c r="B3" t="s">
         <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>262</v>
+        <v>296</v>
       </c>
       <c r="D3">
         <v>0.25</v>
@@ -3394,13 +3496,13 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>263</v>
+        <v>297</v>
       </c>
       <c r="B4" t="s">
         <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>264</v>
+        <v>298</v>
       </c>
       <c r="D4">
         <v>0.5</v>
@@ -3426,13 +3528,13 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>265</v>
+        <v>299</v>
       </c>
       <c r="B5" t="s">
         <v>80</v>
       </c>
       <c r="C5" t="s">
-        <v>266</v>
+        <v>300</v>
       </c>
       <c r="D5">
         <v>0.5</v>
@@ -3458,13 +3560,13 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>267</v>
+        <v>301</v>
       </c>
       <c r="B6" t="s">
         <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>268</v>
+        <v>302</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -3507,24 +3609,24 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>269</v>
+        <v>303</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>270</v>
+        <v>304</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>271</v>
+        <v>305</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>272</v>
+        <v>306</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>273</v>
+        <v>307</v>
       </c>
       <c r="B2" t="s">
-        <v>274</v>
+        <v>308</v>
       </c>
       <c r="C2">
         <v>2</v>
@@ -3538,10 +3640,10 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>275</v>
+        <v>309</v>
       </c>
       <c r="B3" t="s">
-        <v>276</v>
+        <v>310</v>
       </c>
       <c r="C3">
         <v>-1</v>
@@ -3555,10 +3657,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>277</v>
+        <v>311</v>
       </c>
       <c r="B4" t="s">
-        <v>278</v>
+        <v>312</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -3572,10 +3674,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>279</v>
+        <v>313</v>
       </c>
       <c r="B5" t="s">
-        <v>274</v>
+        <v>308</v>
       </c>
       <c r="C5">
         <v>-2</v>
@@ -3589,10 +3691,10 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>280</v>
+        <v>314</v>
       </c>
       <c r="B6" t="s">
-        <v>276</v>
+        <v>310</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -3606,10 +3708,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>281</v>
+        <v>315</v>
       </c>
       <c r="B7" t="s">
-        <v>278</v>
+        <v>312</v>
       </c>
       <c r="C7">
         <v>-1</v>
@@ -3623,10 +3725,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>282</v>
+        <v>316</v>
       </c>
       <c r="B8" t="s">
-        <v>274</v>
+        <v>308</v>
       </c>
       <c r="C8">
         <v>5</v>
@@ -3640,10 +3742,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>283</v>
+        <v>317</v>
       </c>
       <c r="B9" t="s">
-        <v>276</v>
+        <v>310</v>
       </c>
       <c r="C9">
         <v>-4</v>
@@ -3657,10 +3759,10 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>284</v>
+        <v>318</v>
       </c>
       <c r="B10" t="s">
-        <v>278</v>
+        <v>312</v>
       </c>
       <c r="C10">
         <v>5</v>
@@ -3674,10 +3776,10 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>285</v>
+        <v>319</v>
       </c>
       <c r="B11" t="s">
-        <v>274</v>
+        <v>308</v>
       </c>
       <c r="C11">
         <v>9</v>
@@ -3714,45 +3816,45 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>270</v>
+        <v>304</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>271</v>
+        <v>305</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>286</v>
+        <v>320</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>287</v>
+        <v>321</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>288</v>
+        <v>322</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>289</v>
+        <v>323</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>290</v>
+        <v>324</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>291</v>
+        <v>325</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>292</v>
+        <v>326</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>293</v>
+        <v>327</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>294</v>
+        <v>328</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>295</v>
+        <v>329</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>296</v>
+        <v>330</v>
       </c>
       <c r="B2">
         <v>-2</v>
@@ -3788,12 +3890,12 @@
         <v>77</v>
       </c>
       <c r="M2" t="s">
-        <v>248</v>
+        <v>282</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>297</v>
+        <v>331</v>
       </c>
       <c r="B3">
         <v>5</v>
@@ -3829,12 +3931,12 @@
         <v>79</v>
       </c>
       <c r="M3" t="s">
-        <v>249</v>
+        <v>283</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>298</v>
+        <v>332</v>
       </c>
       <c r="B4">
         <v>-3</v>
@@ -3870,12 +3972,12 @@
         <v>78</v>
       </c>
       <c r="M4" t="s">
-        <v>250</v>
+        <v>284</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>299</v>
+        <v>333</v>
       </c>
       <c r="B5">
         <v>8</v>
@@ -3911,12 +4013,12 @@
         <v>80</v>
       </c>
       <c r="M5" t="s">
-        <v>251</v>
+        <v>285</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>300</v>
+        <v>334</v>
       </c>
       <c r="B6">
         <v>-2</v>
@@ -3949,10 +4051,10 @@
         <v>40</v>
       </c>
       <c r="L6" t="s">
-        <v>301</v>
+        <v>335</v>
       </c>
       <c r="M6" t="s">
-        <v>252</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>
@@ -3971,15 +4073,15 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>302</v>
+        <v>336</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>303</v>
+        <v>337</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>304</v>
+        <v>338</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -3987,7 +4089,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>305</v>
+        <v>339</v>
       </c>
       <c r="B3">
         <v>8</v>
@@ -3995,7 +4097,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>306</v>
+        <v>340</v>
       </c>
       <c r="B4">
         <v>0.5</v>
@@ -4003,7 +4105,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>307</v>
+        <v>341</v>
       </c>
       <c r="B5">
         <v>20</v>
@@ -4011,7 +4113,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>308</v>
+        <v>342</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -4019,7 +4121,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>309</v>
+        <v>343</v>
       </c>
       <c r="B7">
         <v>30</v>
@@ -4027,7 +4129,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>310</v>
+        <v>344</v>
       </c>
       <c r="B8">
         <v>20</v>
@@ -4035,7 +4137,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>311</v>
+        <v>345</v>
       </c>
       <c r="B9">
         <v>60</v>
@@ -4043,7 +4145,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>312</v>
+        <v>346</v>
       </c>
       <c r="B10">
         <v>8</v>
@@ -4051,7 +4153,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>313</v>
+        <v>347</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -4059,7 +4161,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>314</v>
+        <v>348</v>
       </c>
       <c r="B12">
         <v>1.25</v>
@@ -4067,7 +4169,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>315</v>
+        <v>349</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -4075,7 +4177,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>316</v>
+        <v>350</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -4083,7 +4185,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>317</v>
+        <v>351</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -4091,7 +4193,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>318</v>
+        <v>352</v>
       </c>
       <c r="B16">
         <v>5</v>
@@ -4099,7 +4201,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>319</v>
+        <v>353</v>
       </c>
       <c r="B17">
         <v>1.45</v>
@@ -4107,7 +4209,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>320</v>
+        <v>354</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -4115,7 +4217,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>321</v>
+        <v>355</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -4123,7 +4225,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>322</v>
+        <v>356</v>
       </c>
       <c r="B20">
         <v>4</v>
@@ -4131,7 +4233,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>323</v>
+        <v>357</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -4139,7 +4241,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>324</v>
+        <v>358</v>
       </c>
       <c r="B22">
         <v>3</v>
@@ -4147,7 +4249,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>325</v>
+        <v>359</v>
       </c>
       <c r="B23">
         <v>10</v>
@@ -4155,7 +4257,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>326</v>
+        <v>360</v>
       </c>
       <c r="B24">
         <v>3</v>
@@ -4163,31 +4265,31 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>327</v>
+        <v>361</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>328</v>
+        <v>362</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>329</v>
+        <v>363</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>330</v>
+        <v>364</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>331</v>
+        <v>365</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>332</v>
+        <v>366</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>333</v>
+        <v>367</v>
       </c>
       <c r="B28">
         <v>1</v>
@@ -4195,7 +4297,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>334</v>
+        <v>368</v>
       </c>
       <c r="B29">
         <v>120</v>
@@ -4203,7 +4305,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>335</v>
+        <v>369</v>
       </c>
       <c r="B30">
         <v>1.3</v>
@@ -4211,7 +4313,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>336</v>
+        <v>370</v>
       </c>
       <c r="B31">
         <v>4</v>
@@ -4219,7 +4321,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>337</v>
+        <v>371</v>
       </c>
       <c r="B32">
         <v>1</v>
@@ -4227,7 +4329,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>338</v>
+        <v>372</v>
       </c>
       <c r="B33">
         <v>5</v>
@@ -4235,7 +4337,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>339</v>
+        <v>373</v>
       </c>
       <c r="B34">
         <v>20</v>
@@ -4243,7 +4345,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>340</v>
+        <v>374</v>
       </c>
       <c r="B35">
         <v>2.5</v>
@@ -4251,7 +4353,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>341</v>
+        <v>375</v>
       </c>
       <c r="B36">
         <v>300</v>
@@ -4259,7 +4361,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>342</v>
+        <v>376</v>
       </c>
       <c r="B37">
         <v>20</v>
@@ -4267,7 +4369,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>343</v>
+        <v>377</v>
       </c>
       <c r="B38">
         <v>1.6</v>
@@ -4275,7 +4377,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>344</v>
+        <v>378</v>
       </c>
       <c r="B39">
         <v>10</v>
@@ -4283,7 +4385,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>345</v>
+        <v>379</v>
       </c>
       <c r="B40">
         <v>2</v>
@@ -4291,7 +4393,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>346</v>
+        <v>380</v>
       </c>
       <c r="B41">
         <v>5</v>
@@ -4299,7 +4401,7 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>347</v>
+        <v>381</v>
       </c>
       <c r="B42">
         <v>10</v>
@@ -4307,7 +4409,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>348</v>
+        <v>382</v>
       </c>
       <c r="B43">
         <v>2</v>
@@ -4315,7 +4417,7 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>349</v>
+        <v>383</v>
       </c>
       <c r="B44">
         <v>2</v>
@@ -4323,7 +4425,7 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>350</v>
+        <v>384</v>
       </c>
       <c r="B45">
         <v>3</v>
@@ -4331,7 +4433,7 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>351</v>
+        <v>385</v>
       </c>
       <c r="B46">
         <v>1.5</v>
@@ -4339,7 +4441,7 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>352</v>
+        <v>386</v>
       </c>
       <c r="B47">
         <v>0.75</v>
@@ -4347,7 +4449,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>353</v>
+        <v>387</v>
       </c>
       <c r="B48">
         <v>0.4</v>
@@ -4355,7 +4457,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>354</v>
+        <v>388</v>
       </c>
       <c r="B49">
         <v>0.9</v>
@@ -4363,7 +4465,7 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>355</v>
+        <v>389</v>
       </c>
       <c r="B50">
         <v>0.5</v>
@@ -4371,7 +4473,7 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>356</v>
+        <v>390</v>
       </c>
       <c r="B51">
         <v>25</v>
@@ -4379,7 +4481,7 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>357</v>
+        <v>391</v>
       </c>
       <c r="B52">
         <v>4</v>
@@ -4387,7 +4489,7 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>358</v>
+        <v>392</v>
       </c>
       <c r="B53">
         <v>2</v>
@@ -4395,7 +4497,7 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>359</v>
+        <v>393</v>
       </c>
       <c r="B54">
         <v>1</v>
@@ -4403,7 +4505,7 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>360</v>
+        <v>394</v>
       </c>
       <c r="B55">
         <v>0.5</v>
@@ -4411,7 +4513,7 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>361</v>
+        <v>395</v>
       </c>
       <c r="B56">
         <v>10</v>
@@ -4419,7 +4521,7 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>362</v>
+        <v>396</v>
       </c>
       <c r="B57">
         <v>2</v>
@@ -4427,7 +4529,7 @@
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>363</v>
+        <v>397</v>
       </c>
       <c r="B58">
         <v>5</v>
@@ -4435,7 +4537,7 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>364</v>
+        <v>398</v>
       </c>
       <c r="B59">
         <v>25</v>
@@ -4443,7 +4545,7 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>365</v>
+        <v>399</v>
       </c>
       <c r="B60">
         <v>2.2</v>
@@ -4451,7 +4553,7 @@
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>366</v>
+        <v>400</v>
       </c>
       <c r="B61">
         <v>30</v>
@@ -4459,7 +4561,7 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>367</v>
+        <v>401</v>
       </c>
       <c r="B62">
         <v>0.06</v>
@@ -4467,7 +4569,7 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>368</v>
+        <v>402</v>
       </c>
       <c r="B63">
         <v>40</v>
@@ -4475,7 +4577,7 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>369</v>
+        <v>403</v>
       </c>
       <c r="B64">
         <v>60</v>
@@ -4483,7 +4585,7 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>370</v>
+        <v>404</v>
       </c>
       <c r="B65">
         <v>20</v>
@@ -4491,7 +4593,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>371</v>
+        <v>405</v>
       </c>
       <c r="B66">
         <v>3</v>
@@ -4576,61 +4678,61 @@
         <v>-10</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>373</v>
+        <v>407</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>373</v>
+        <v>407</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>373</v>
+        <v>407</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>373</v>
+        <v>407</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>373</v>
+        <v>407</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>373</v>
+        <v>407</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>373</v>
+        <v>407</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>373</v>
+        <v>407</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>373</v>
+        <v>407</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
@@ -4638,61 +4740,61 @@
         <v>-9</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>373</v>
+        <v>407</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>374</v>
+        <v>408</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>375</v>
+        <v>409</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>375</v>
+        <v>409</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>375</v>
+        <v>409</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>374</v>
+        <v>408</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>375</v>
+        <v>409</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>375</v>
+        <v>409</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>373</v>
+        <v>407</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
@@ -4700,61 +4802,61 @@
         <v>-8</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>373</v>
+        <v>407</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>373</v>
+        <v>407</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>374</v>
+        <v>408</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>373</v>
+        <v>407</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>373</v>
+        <v>407</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>373</v>
+        <v>407</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>373</v>
+        <v>407</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>374</v>
+        <v>408</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>373</v>
+        <v>407</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -4762,61 +4864,61 @@
         <v>-7</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>376</v>
+        <v>410</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>376</v>
+        <v>410</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>376</v>
+        <v>410</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>376</v>
+        <v>410</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>377</v>
+        <v>411</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>376</v>
+        <v>410</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>376</v>
+        <v>410</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>376</v>
+        <v>410</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>376</v>
+        <v>410</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -4824,61 +4926,61 @@
         <v>-6</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>378</v>
+        <v>412</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>378</v>
+        <v>412</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="T6" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -4886,61 +4988,61 @@
         <v>-5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>375</v>
+        <v>409</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>375</v>
+        <v>409</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="T7" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -4948,61 +5050,61 @@
         <v>-4</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>380</v>
+        <v>414</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>381</v>
+        <v>415</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>381</v>
+        <v>415</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>375</v>
+        <v>409</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>382</v>
+        <v>416</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>375</v>
+        <v>409</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -5010,61 +5112,61 @@
         <v>-3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>375</v>
+        <v>409</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>375</v>
+        <v>409</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>375</v>
+        <v>409</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>378</v>
+        <v>412</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>383</v>
+        <v>417</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>383</v>
+        <v>417</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -5072,61 +5174,61 @@
         <v>-2</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>380</v>
+        <v>414</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>375</v>
+        <v>409</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>375</v>
+        <v>409</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>383</v>
+        <v>417</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>383</v>
+        <v>417</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>384</v>
+        <v>418</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -5134,61 +5236,61 @@
         <v>-1</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>378</v>
+        <v>412</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>375</v>
+        <v>409</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>382</v>
+        <v>416</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>383</v>
+        <v>417</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>385</v>
+        <v>419</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>383</v>
+        <v>417</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>383</v>
+        <v>417</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -5196,61 +5298,61 @@
         <v>0</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>378</v>
+        <v>412</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>375</v>
+        <v>409</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>375</v>
+        <v>409</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>383</v>
+        <v>417</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>375</v>
+        <v>409</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>375</v>
+        <v>409</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>385</v>
+        <v>419</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -5258,61 +5360,61 @@
         <v>1</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>383</v>
+        <v>417</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>383</v>
+        <v>417</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>385</v>
+        <v>419</v>
       </c>
       <c r="T13" s="3" t="s">
-        <v>383</v>
+        <v>417</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -5320,61 +5422,61 @@
         <v>2</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>378</v>
+        <v>412</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>386</v>
+        <v>420</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>381</v>
+        <v>415</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>383</v>
+        <v>417</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>383</v>
+        <v>417</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>383</v>
+        <v>417</v>
       </c>
       <c r="T14" s="3" t="s">
-        <v>383</v>
+        <v>417</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -5382,61 +5484,61 @@
         <v>3</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>381</v>
+        <v>415</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>381</v>
+        <v>415</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>381</v>
+        <v>415</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>381</v>
+        <v>415</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>381</v>
+        <v>415</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>375</v>
+        <v>409</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>385</v>
+        <v>419</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>383</v>
+        <v>417</v>
       </c>
       <c r="T15" s="3" t="s">
-        <v>383</v>
+        <v>417</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -5444,61 +5546,61 @@
         <v>4</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>378</v>
+        <v>412</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>381</v>
+        <v>415</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>381</v>
+        <v>415</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>381</v>
+        <v>415</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>381</v>
+        <v>415</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>381</v>
+        <v>415</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>387</v>
+        <v>421</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>383</v>
+        <v>417</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>383</v>
+        <v>417</v>
       </c>
       <c r="T16" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
@@ -5506,61 +5608,61 @@
         <v>5</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>381</v>
+        <v>415</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>381</v>
+        <v>415</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>383</v>
+        <v>417</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>383</v>
+        <v>417</v>
       </c>
       <c r="T17" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -5568,61 +5670,61 @@
         <v>6</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>378</v>
+        <v>412</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>381</v>
+        <v>415</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>380</v>
+        <v>414</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="T18" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
@@ -5630,61 +5732,61 @@
         <v>7</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>378</v>
+        <v>412</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="S19" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="T19" s="3" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
     </row>
   </sheetData>
@@ -7355,7 +7457,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
@@ -8516,6 +8618,457 @@
         <v>10</v>
       </c>
     </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>242</v>
+      </c>
+      <c r="B29" t="s">
+        <v>243</v>
+      </c>
+      <c r="C29" t="s">
+        <v>244</v>
+      </c>
+      <c r="D29" t="s">
+        <v>245</v>
+      </c>
+      <c r="E29" t="s">
+        <v>32</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29" t="s">
+        <v>32</v>
+      </c>
+      <c r="H29">
+        <v>150</v>
+      </c>
+      <c r="I29" t="s">
+        <v>32</v>
+      </c>
+      <c r="J29" t="s">
+        <v>32</v>
+      </c>
+      <c r="K29" t="s">
+        <v>32</v>
+      </c>
+      <c r="L29" t="s">
+        <v>32</v>
+      </c>
+      <c r="M29" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>246</v>
+      </c>
+      <c r="B30" t="s">
+        <v>127</v>
+      </c>
+      <c r="C30" t="s">
+        <v>247</v>
+      </c>
+      <c r="D30" t="s">
+        <v>183</v>
+      </c>
+      <c r="E30" t="s">
+        <v>127</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30" t="s">
+        <v>32</v>
+      </c>
+      <c r="H30">
+        <v>200</v>
+      </c>
+      <c r="I30" t="s">
+        <v>32</v>
+      </c>
+      <c r="J30" t="s">
+        <v>32</v>
+      </c>
+      <c r="K30" t="s">
+        <v>32</v>
+      </c>
+      <c r="L30" t="s">
+        <v>32</v>
+      </c>
+      <c r="M30" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>248</v>
+      </c>
+      <c r="B31" t="s">
+        <v>249</v>
+      </c>
+      <c r="C31" t="s">
+        <v>250</v>
+      </c>
+      <c r="D31" t="s">
+        <v>167</v>
+      </c>
+      <c r="E31" t="s">
+        <v>59</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="G31" t="s">
+        <v>32</v>
+      </c>
+      <c r="H31">
+        <v>250</v>
+      </c>
+      <c r="I31" t="s">
+        <v>32</v>
+      </c>
+      <c r="J31" t="s">
+        <v>32</v>
+      </c>
+      <c r="K31">
+        <v>40</v>
+      </c>
+      <c r="L31" t="s">
+        <v>32</v>
+      </c>
+      <c r="M31">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>251</v>
+      </c>
+      <c r="B32" t="s">
+        <v>251</v>
+      </c>
+      <c r="C32" t="s">
+        <v>252</v>
+      </c>
+      <c r="D32" t="s">
+        <v>167</v>
+      </c>
+      <c r="E32" t="s">
+        <v>62</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="G32" t="s">
+        <v>32</v>
+      </c>
+      <c r="H32">
+        <v>200</v>
+      </c>
+      <c r="I32">
+        <v>60</v>
+      </c>
+      <c r="J32" t="s">
+        <v>32</v>
+      </c>
+      <c r="K32" t="s">
+        <v>32</v>
+      </c>
+      <c r="L32" t="s">
+        <v>32</v>
+      </c>
+      <c r="M32" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>253</v>
+      </c>
+      <c r="B33" t="s">
+        <v>254</v>
+      </c>
+      <c r="C33" t="s">
+        <v>255</v>
+      </c>
+      <c r="D33" t="s">
+        <v>224</v>
+      </c>
+      <c r="E33" t="s">
+        <v>32</v>
+      </c>
+      <c r="F33">
+        <v>4</v>
+      </c>
+      <c r="G33" t="s">
+        <v>32</v>
+      </c>
+      <c r="H33">
+        <v>250</v>
+      </c>
+      <c r="I33" t="s">
+        <v>32</v>
+      </c>
+      <c r="J33">
+        <v>60</v>
+      </c>
+      <c r="K33" t="s">
+        <v>32</v>
+      </c>
+      <c r="L33" t="s">
+        <v>32</v>
+      </c>
+      <c r="M33" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>256</v>
+      </c>
+      <c r="B34" t="s">
+        <v>257</v>
+      </c>
+      <c r="C34" t="s">
+        <v>258</v>
+      </c>
+      <c r="D34" t="s">
+        <v>259</v>
+      </c>
+      <c r="E34" t="s">
+        <v>32</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+      <c r="G34" t="s">
+        <v>32</v>
+      </c>
+      <c r="H34">
+        <v>300</v>
+      </c>
+      <c r="I34" t="s">
+        <v>32</v>
+      </c>
+      <c r="J34">
+        <v>80</v>
+      </c>
+      <c r="K34" t="s">
+        <v>32</v>
+      </c>
+      <c r="L34" t="s">
+        <v>32</v>
+      </c>
+      <c r="M34">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>260</v>
+      </c>
+      <c r="B35" t="s">
+        <v>261</v>
+      </c>
+      <c r="C35" t="s">
+        <v>262</v>
+      </c>
+      <c r="D35" t="s">
+        <v>263</v>
+      </c>
+      <c r="E35" t="s">
+        <v>32</v>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+      <c r="G35" t="s">
+        <v>32</v>
+      </c>
+      <c r="H35">
+        <v>400</v>
+      </c>
+      <c r="I35" t="s">
+        <v>32</v>
+      </c>
+      <c r="J35" t="s">
+        <v>32</v>
+      </c>
+      <c r="K35" t="s">
+        <v>32</v>
+      </c>
+      <c r="L35" t="s">
+        <v>32</v>
+      </c>
+      <c r="M35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>264</v>
+      </c>
+      <c r="B36" t="s">
+        <v>265</v>
+      </c>
+      <c r="C36" t="s">
+        <v>266</v>
+      </c>
+      <c r="D36" t="s">
+        <v>267</v>
+      </c>
+      <c r="E36" t="s">
+        <v>32</v>
+      </c>
+      <c r="F36">
+        <v>1</v>
+      </c>
+      <c r="G36" t="s">
+        <v>32</v>
+      </c>
+      <c r="H36">
+        <v>300</v>
+      </c>
+      <c r="I36" t="s">
+        <v>32</v>
+      </c>
+      <c r="J36" t="s">
+        <v>32</v>
+      </c>
+      <c r="K36" t="s">
+        <v>32</v>
+      </c>
+      <c r="L36" t="s">
+        <v>32</v>
+      </c>
+      <c r="M36" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>268</v>
+      </c>
+      <c r="B37" t="s">
+        <v>268</v>
+      </c>
+      <c r="C37" t="s">
+        <v>269</v>
+      </c>
+      <c r="D37" t="s">
+        <v>245</v>
+      </c>
+      <c r="E37" t="s">
+        <v>32</v>
+      </c>
+      <c r="F37">
+        <v>4</v>
+      </c>
+      <c r="G37" t="s">
+        <v>32</v>
+      </c>
+      <c r="H37">
+        <v>500</v>
+      </c>
+      <c r="I37" t="s">
+        <v>32</v>
+      </c>
+      <c r="J37" t="s">
+        <v>32</v>
+      </c>
+      <c r="K37">
+        <v>60</v>
+      </c>
+      <c r="L37" t="s">
+        <v>32</v>
+      </c>
+      <c r="M37">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>270</v>
+      </c>
+      <c r="B38" t="s">
+        <v>271</v>
+      </c>
+      <c r="C38" t="s">
+        <v>272</v>
+      </c>
+      <c r="D38" t="s">
+        <v>259</v>
+      </c>
+      <c r="E38" t="s">
+        <v>32</v>
+      </c>
+      <c r="F38">
+        <v>5</v>
+      </c>
+      <c r="G38" t="s">
+        <v>32</v>
+      </c>
+      <c r="H38">
+        <v>600</v>
+      </c>
+      <c r="I38" t="s">
+        <v>32</v>
+      </c>
+      <c r="J38" t="s">
+        <v>32</v>
+      </c>
+      <c r="K38" t="s">
+        <v>32</v>
+      </c>
+      <c r="L38">
+        <v>30</v>
+      </c>
+      <c r="M38">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>273</v>
+      </c>
+      <c r="B39" t="s">
+        <v>274</v>
+      </c>
+      <c r="C39" t="s">
+        <v>275</v>
+      </c>
+      <c r="D39" t="s">
+        <v>267</v>
+      </c>
+      <c r="E39" t="s">
+        <v>32</v>
+      </c>
+      <c r="F39">
+        <v>3</v>
+      </c>
+      <c r="G39" t="s">
+        <v>32</v>
+      </c>
+      <c r="H39">
+        <v>900</v>
+      </c>
+      <c r="I39" t="s">
+        <v>32</v>
+      </c>
+      <c r="J39" t="s">
+        <v>32</v>
+      </c>
+      <c r="K39" t="s">
+        <v>32</v>
+      </c>
+      <c r="L39" t="s">
+        <v>32</v>
+      </c>
+      <c r="M39">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1419" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1431" uniqueCount="428">
   <si>
     <t>id</t>
   </si>
@@ -871,6 +871,24 @@
   </si>
   <si>
     <t>active_radius</t>
+  </si>
+  <si>
+    <t>carried_atk</t>
+  </si>
+  <si>
+    <t>carried_def</t>
+  </si>
+  <si>
+    <t>carried_hp</t>
+  </si>
+  <si>
+    <t>carried_atk_per_level</t>
+  </si>
+  <si>
+    <t>carried_def_per_level</t>
+  </si>
+  <si>
+    <t>carried_hp_per_level</t>
   </si>
   <si>
     <t>DowsingRod</t>
@@ -3229,7 +3247,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
@@ -3238,9 +3256,13 @@
     <col min="5" max="5" width="18" customWidth="1"/>
     <col min="6" max="6" width="25" customWidth="1"/>
     <col min="7" max="7" width="15" customWidth="1"/>
+    <col min="8" max="9" width="13" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="12" width="23" customWidth="1"/>
+    <col min="13" max="13" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3262,10 +3284,28 @@
       <c r="G1" s="1" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H1" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -3285,10 +3325,28 @@
       <c r="G2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H2">
+        <v>4</v>
+      </c>
+      <c r="I2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J2">
+        <v>10</v>
+      </c>
+      <c r="K2">
+        <v>0.4</v>
+      </c>
+      <c r="L2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -3308,10 +3366,28 @@
       <c r="G3">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3">
+        <v>6</v>
+      </c>
+      <c r="J3">
+        <v>25</v>
+      </c>
+      <c r="K3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3">
+        <v>0.6</v>
+      </c>
+      <c r="M3">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="B4">
         <v>2</v>
@@ -3331,10 +3407,28 @@
       <c r="G4" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H4">
+        <v>8</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="J4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4">
+        <v>0.8</v>
+      </c>
+      <c r="L4">
+        <v>0.2</v>
+      </c>
+      <c r="M4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="B5">
         <v>3</v>
@@ -3354,10 +3448,28 @@
       <c r="G5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>15</v>
+      </c>
+      <c r="K5">
+        <v>0.2</v>
+      </c>
+      <c r="L5">
+        <v>0.4</v>
+      </c>
+      <c r="M5">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -3376,6 +3488,24 @@
       </c>
       <c r="G6" t="s">
         <v>32</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>0.5</v>
+      </c>
+      <c r="L6">
+        <v>0.3</v>
+      </c>
+      <c r="M6">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -3403,13 +3533,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>68</v>
@@ -3421,24 +3551,24 @@
         <v>70</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="B2" t="s">
         <v>77</v>
       </c>
       <c r="C2" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="D2">
         <v>0.2</v>
@@ -3464,13 +3594,13 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="B3" t="s">
         <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="D3">
         <v>0.25</v>
@@ -3496,13 +3626,13 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="B4" t="s">
         <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="D4">
         <v>0.5</v>
@@ -3528,13 +3658,13 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="B5" t="s">
         <v>80</v>
       </c>
       <c r="C5" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="D5">
         <v>0.5</v>
@@ -3560,13 +3690,13 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="B6" t="s">
         <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -3609,24 +3739,24 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="B2" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="C2">
         <v>2</v>
@@ -3640,10 +3770,10 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="B3" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="C3">
         <v>-1</v>
@@ -3657,10 +3787,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="B4" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -3674,10 +3804,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="B5" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="C5">
         <v>-2</v>
@@ -3691,10 +3821,10 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="B6" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -3708,10 +3838,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="B7" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C7">
         <v>-1</v>
@@ -3725,10 +3855,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="B8" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="C8">
         <v>5</v>
@@ -3742,10 +3872,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="B9" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="C9">
         <v>-4</v>
@@ -3759,10 +3889,10 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>324</v>
+      </c>
+      <c r="B10" t="s">
         <v>318</v>
-      </c>
-      <c r="B10" t="s">
-        <v>312</v>
       </c>
       <c r="C10">
         <v>5</v>
@@ -3776,10 +3906,10 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="B11" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="C11">
         <v>9</v>
@@ -3816,45 +3946,45 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="B2">
         <v>-2</v>
@@ -3890,12 +4020,12 @@
         <v>77</v>
       </c>
       <c r="M2" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="B3">
         <v>5</v>
@@ -3931,12 +4061,12 @@
         <v>79</v>
       </c>
       <c r="M3" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="B4">
         <v>-3</v>
@@ -3972,12 +4102,12 @@
         <v>78</v>
       </c>
       <c r="M4" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="B5">
         <v>8</v>
@@ -4013,12 +4143,12 @@
         <v>80</v>
       </c>
       <c r="M5" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="B6">
         <v>-2</v>
@@ -4051,10 +4181,10 @@
         <v>40</v>
       </c>
       <c r="L6" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="M6" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
     </row>
   </sheetData>
@@ -4073,15 +4203,15 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -4089,7 +4219,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="B3">
         <v>8</v>
@@ -4097,7 +4227,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="B4">
         <v>0.5</v>
@@ -4105,7 +4235,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="B5">
         <v>20</v>
@@ -4113,7 +4243,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -4121,7 +4251,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="B7">
         <v>30</v>
@@ -4129,7 +4259,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="B8">
         <v>20</v>
@@ -4137,7 +4267,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="B9">
         <v>60</v>
@@ -4145,7 +4275,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="B10">
         <v>8</v>
@@ -4153,7 +4283,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -4161,7 +4291,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B12">
         <v>1.25</v>
@@ -4169,7 +4299,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -4177,7 +4307,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -4185,7 +4315,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -4193,7 +4323,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="B16">
         <v>5</v>
@@ -4201,7 +4331,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="B17">
         <v>1.45</v>
@@ -4209,7 +4339,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -4217,7 +4347,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -4225,7 +4355,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="B20">
         <v>4</v>
@@ -4233,7 +4363,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -4241,7 +4371,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="B22">
         <v>3</v>
@@ -4249,7 +4379,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="B23">
         <v>10</v>
@@ -4257,7 +4387,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="B24">
         <v>3</v>
@@ -4265,31 +4395,31 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="B28">
         <v>1</v>
@@ -4297,7 +4427,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="B29">
         <v>120</v>
@@ -4305,7 +4435,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="B30">
         <v>1.3</v>
@@ -4313,7 +4443,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="B31">
         <v>4</v>
@@ -4321,7 +4451,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="B32">
         <v>1</v>
@@ -4329,7 +4459,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="B33">
         <v>5</v>
@@ -4337,7 +4467,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B34">
         <v>20</v>
@@ -4345,7 +4475,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="B35">
         <v>2.5</v>
@@ -4353,7 +4483,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B36">
         <v>300</v>
@@ -4361,7 +4491,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="B37">
         <v>20</v>
@@ -4369,7 +4499,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="B38">
         <v>1.6</v>
@@ -4377,7 +4507,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B39">
         <v>10</v>
@@ -4385,7 +4515,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="B40">
         <v>2</v>
@@ -4393,7 +4523,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="B41">
         <v>5</v>
@@ -4401,7 +4531,7 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="B42">
         <v>10</v>
@@ -4409,7 +4539,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="B43">
         <v>2</v>
@@ -4417,7 +4547,7 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="B44">
         <v>2</v>
@@ -4425,7 +4555,7 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B45">
         <v>3</v>
@@ -4433,7 +4563,7 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="B46">
         <v>1.5</v>
@@ -4441,7 +4571,7 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="B47">
         <v>0.75</v>
@@ -4449,7 +4579,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="B48">
         <v>0.4</v>
@@ -4457,7 +4587,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="B49">
         <v>0.9</v>
@@ -4465,7 +4595,7 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="B50">
         <v>0.5</v>
@@ -4473,7 +4603,7 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="B51">
         <v>25</v>
@@ -4481,7 +4611,7 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="B52">
         <v>4</v>
@@ -4489,7 +4619,7 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="B53">
         <v>2</v>
@@ -4497,7 +4627,7 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="B54">
         <v>1</v>
@@ -4505,7 +4635,7 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="B55">
         <v>0.5</v>
@@ -4513,7 +4643,7 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="B56">
         <v>10</v>
@@ -4521,7 +4651,7 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="B57">
         <v>2</v>
@@ -4529,7 +4659,7 @@
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="B58">
         <v>5</v>
@@ -4537,7 +4667,7 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="B59">
         <v>25</v>
@@ -4545,7 +4675,7 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B60">
         <v>2.2</v>
@@ -4553,7 +4683,7 @@
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="B61">
         <v>30</v>
@@ -4561,7 +4691,7 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="B62">
         <v>0.06</v>
@@ -4569,7 +4699,7 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="B63">
         <v>40</v>
@@ -4577,7 +4707,7 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="B64">
         <v>60</v>
@@ -4585,7 +4715,7 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="B65">
         <v>20</v>
@@ -4593,7 +4723,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="B66">
         <v>3</v>
@@ -4678,61 +4808,61 @@
         <v>-10</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
@@ -4740,61 +4870,61 @@
         <v>-9</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
@@ -4802,61 +4932,61 @@
         <v>-8</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -4864,61 +4994,61 @@
         <v>-7</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -4926,61 +5056,61 @@
         <v>-6</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="T6" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -4988,61 +5118,61 @@
         <v>-5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="T7" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -5050,61 +5180,61 @@
         <v>-4</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="I8" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="K8" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="L8" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="M8" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>409</v>
-      </c>
       <c r="N8" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -5112,61 +5242,61 @@
         <v>-3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -5174,61 +5304,61 @@
         <v>-2</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -5236,61 +5366,61 @@
         <v>-1</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -5298,61 +5428,61 @@
         <v>0</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -5360,61 +5490,61 @@
         <v>1</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="T13" s="3" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -5422,61 +5552,61 @@
         <v>2</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="T14" s="3" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -5484,61 +5614,61 @@
         <v>3</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="G15" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="Q15" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="P15" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="Q15" s="3" t="s">
-        <v>409</v>
-      </c>
       <c r="R15" s="3" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="T15" s="3" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -5546,61 +5676,61 @@
         <v>4</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="T16" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
@@ -5608,61 +5738,61 @@
         <v>5</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="T17" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -5670,61 +5800,61 @@
         <v>6</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="T18" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
@@ -5732,61 +5862,61 @@
         <v>7</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="S19" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="T19" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
     </row>
   </sheetData>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1433" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1367" uniqueCount="428">
   <si>
     <t>id</t>
   </si>
@@ -351,19 +351,7 @@
     <t>cost</t>
   </si>
   <si>
-    <t>cost_gold</t>
-  </si>
-  <si>
-    <t>cost_wood</t>
-  </si>
-  <si>
-    <t>cost_food</t>
-  </si>
-  <si>
-    <t>cost_stone</t>
-  </si>
-  <si>
-    <t>cost_iron</t>
+    <t>cost_knowledge</t>
   </si>
   <si>
     <t>duration_seconds</t>
@@ -495,6 +483,9 @@
     <t>reward_gems</t>
   </si>
   <si>
+    <t>reward_knowledge</t>
+  </si>
+  <si>
     <t>FirstSteps</t>
   </si>
   <si>
@@ -1189,6 +1180,9 @@
   </si>
   <si>
     <t>knowledge.drip_per_ruin_per_hour</t>
+  </si>
+  <si>
+    <t>knowledge.per_reveal_ring</t>
   </si>
   <si>
     <t>army.train_tap_boost_seconds</t>
@@ -3273,42 +3267,42 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>283</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B2">
         <v>0.85</v>
@@ -3346,7 +3340,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B3">
         <v>0.75</v>
@@ -3384,7 +3378,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -3422,7 +3416,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B5">
         <v>1.2</v>
@@ -3460,7 +3454,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B6">
         <v>1.5</v>
@@ -3521,13 +3515,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>68</v>
@@ -3539,24 +3533,24 @@
         <v>70</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B2" t="s">
         <v>77</v>
       </c>
       <c r="C2" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="D2">
         <v>0.2</v>
@@ -3582,13 +3576,13 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B3" t="s">
         <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="D3">
         <v>0.25</v>
@@ -3614,13 +3608,13 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B4" t="s">
         <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D4">
         <v>0.5</v>
@@ -3646,13 +3640,13 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B5" t="s">
         <v>80</v>
       </c>
       <c r="C5" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D5">
         <v>0.5</v>
@@ -3678,13 +3672,13 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B6" t="s">
         <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -3728,27 +3722,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>309</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B2" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C2">
         <v>2</v>
@@ -3765,10 +3759,10 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B3" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C3">
         <v>-4</v>
@@ -3785,10 +3779,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B4" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -3805,10 +3799,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B5" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C5">
         <v>-2</v>
@@ -3825,10 +3819,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B6" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C6">
         <v>8</v>
@@ -3845,10 +3839,10 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="B7" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C7">
         <v>5</v>
@@ -3865,10 +3859,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B8" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C8">
         <v>3</v>
@@ -3885,10 +3879,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B9" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C9">
         <v>-5</v>
@@ -3905,10 +3899,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B10" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C10">
         <v>-3</v>
@@ -3925,10 +3919,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B11" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -3968,45 +3962,45 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>332</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B2">
         <v>-2</v>
@@ -4042,12 +4036,12 @@
         <v>77</v>
       </c>
       <c r="M2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B3">
         <v>5</v>
@@ -4083,12 +4077,12 @@
         <v>79</v>
       </c>
       <c r="M3" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B4">
         <v>-3</v>
@@ -4124,12 +4118,12 @@
         <v>78</v>
       </c>
       <c r="M4" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B5">
         <v>8</v>
@@ -4165,12 +4159,12 @@
         <v>80</v>
       </c>
       <c r="M5" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B6">
         <v>-2</v>
@@ -4203,10 +4197,10 @@
         <v>40</v>
       </c>
       <c r="L6" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="M6" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
   </sheetData>
@@ -4217,7 +4211,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B68"/>
+  <dimension ref="A1:B69"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
@@ -4225,15 +4219,15 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -4241,7 +4235,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B3">
         <v>8</v>
@@ -4249,7 +4243,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B4">
         <v>0.5</v>
@@ -4257,7 +4251,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B5">
         <v>20</v>
@@ -4265,7 +4259,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -4273,7 +4267,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B7">
         <v>30</v>
@@ -4281,7 +4275,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -4289,7 +4283,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="B9">
         <v>45</v>
@@ -4297,7 +4291,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="B10">
         <v>8</v>
@@ -4305,7 +4299,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -4313,7 +4307,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B12">
         <v>1.25</v>
@@ -4321,7 +4315,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -4329,7 +4323,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -4337,7 +4331,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -4345,7 +4339,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B16">
         <v>5</v>
@@ -4353,7 +4347,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B17">
         <v>1.45</v>
@@ -4361,7 +4355,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -4369,7 +4363,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -4377,7 +4371,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B20">
         <v>4</v>
@@ -4385,7 +4379,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -4393,7 +4387,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B22">
         <v>3</v>
@@ -4401,7 +4395,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B23">
         <v>10</v>
@@ -4409,7 +4403,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B24">
         <v>3</v>
@@ -4417,31 +4411,31 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B28">
         <v>10</v>
@@ -4449,7 +4443,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B29">
         <v>4</v>
@@ -4457,7 +4451,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="B30">
         <v>1</v>
@@ -4465,7 +4459,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B31">
         <v>5</v>
@@ -4473,7 +4467,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B32">
         <v>20</v>
@@ -4481,7 +4475,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B33">
         <v>2.5</v>
@@ -4489,7 +4483,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="B34">
         <v>300</v>
@@ -4497,7 +4491,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B35">
         <v>20</v>
@@ -4505,7 +4499,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B36">
         <v>1.6</v>
@@ -4513,7 +4507,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B37">
         <v>10</v>
@@ -4521,7 +4515,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="B38">
         <v>2</v>
@@ -4529,7 +4523,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B39">
         <v>5</v>
@@ -4537,7 +4531,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B40">
         <v>10</v>
@@ -4545,7 +4539,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B41">
         <v>2</v>
@@ -4553,7 +4547,7 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B42">
         <v>2</v>
@@ -4561,209 +4555,217 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B43">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="B44">
-        <v>1.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B45">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="B46">
-        <v>0.4</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="B47">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B48">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="B49">
-        <v>25</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B50">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B51">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B52">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="B53">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B54">
-        <v>10</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="B55">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="B56">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B57">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="B58">
-        <v>2.2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="B59">
-        <v>30</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="B60">
-        <v>0.06</v>
+        <v>30</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B61">
-        <v>40</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="B62">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="B63">
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="B64">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B65">
-        <v>30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B66">
-        <v>90</v>
+        <v>30</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="B67">
-        <v>0.5</v>
+        <v>90</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="B68">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>411</v>
+      </c>
+      <c r="B69">
         <v>5</v>
       </c>
     </row>
@@ -4846,61 +4848,61 @@
         <v>-10</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
@@ -4908,61 +4910,61 @@
         <v>-9</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="H3" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="F3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>417</v>
-      </c>
       <c r="M3" s="3" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
@@ -4970,61 +4972,61 @@
         <v>-8</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="I4" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="M4" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>416</v>
-      </c>
       <c r="N4" s="3" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -5032,61 +5034,61 @@
         <v>-7</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -5094,61 +5096,61 @@
         <v>-6</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="T6" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -5156,61 +5158,61 @@
         <v>-5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="T7" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -5218,61 +5220,61 @@
         <v>-4</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="G8" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="J8" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="L8" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>424</v>
-      </c>
       <c r="M8" s="3" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -5280,61 +5282,61 @@
         <v>-3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -5342,61 +5344,61 @@
         <v>-2</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -5404,61 +5406,61 @@
         <v>-1</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="Q11" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="R11" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="R11" s="3" t="s">
-        <v>427</v>
-      </c>
       <c r="S11" s="3" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -5466,61 +5468,61 @@
         <v>0</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="Q12" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="T12" s="3" t="s">
         <v>425</v>
-      </c>
-      <c r="R12" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="S12" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="T12" s="3" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -5528,61 +5530,61 @@
         <v>1</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="Q13" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="R13" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="S13" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="R13" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="S13" s="3" t="s">
-        <v>427</v>
-      </c>
       <c r="T13" s="3" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -5590,61 +5592,61 @@
         <v>2</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="F14" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="L14" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>428</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="L14" s="3" t="s">
+      <c r="M14" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="Q14" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>425</v>
-      </c>
       <c r="R14" s="3" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="T14" s="3" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -5652,61 +5654,61 @@
         <v>3</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="E15" s="3" t="s">
+      <c r="H15" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="I15" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="K15" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="L15" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="S15" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="H15" s="3" t="s">
+      <c r="T15" s="3" t="s">
         <v>423</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="P15" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="Q15" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="R15" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="S15" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="T15" s="3" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -5714,61 +5716,61 @@
         <v>4</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C16" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="F16" s="3" t="s">
+      <c r="H16" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="I16" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="Q16" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="R16" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="H16" s="3" t="s">
+      <c r="S16" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="I16" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="N16" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="O16" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="P16" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="Q16" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="R16" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="S16" s="3" t="s">
-        <v>425</v>
-      </c>
       <c r="T16" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
@@ -5776,61 +5778,61 @@
         <v>5</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="F17" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="L17" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="M17" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="L17" s="3" t="s">
+      <c r="N17" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="R17" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="M17" s="3" t="s">
+      <c r="S17" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="O17" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="P17" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="Q17" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="R17" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="S17" s="3" t="s">
-        <v>425</v>
-      </c>
       <c r="T17" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -5838,61 +5840,61 @@
         <v>6</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="F18" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="N18" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>422</v>
-      </c>
       <c r="O18" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="T18" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
@@ -5900,61 +5902,61 @@
         <v>7</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="S19" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="T19" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
   </sheetData>
@@ -6772,18 +6774,16 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6796,589 +6796,313 @@
       <c r="D1" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="E1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>111</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>115</v>
-      </c>
       <c r="B2">
-        <v>75</v>
-      </c>
-      <c r="C2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G2">
+        <v>8</v>
+      </c>
+      <c r="C2">
         <v>30</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D2" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>37</v>
       </c>
       <c r="B3">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="C3">
-        <v>50</v>
-      </c>
-      <c r="D3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3">
         <v>60</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="D3" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B4">
+        <v>45</v>
+      </c>
+      <c r="C4">
+        <v>90</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B5">
+        <v>60</v>
+      </c>
+      <c r="C5">
+        <v>120</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B6">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>45</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B4">
-        <v>450</v>
-      </c>
-      <c r="C4">
+      <c r="B7">
+        <v>25</v>
+      </c>
+      <c r="C7">
         <v>60</v>
       </c>
-      <c r="D4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G4">
-        <v>90</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>117</v>
-      </c>
-      <c r="B5">
-        <v>600</v>
-      </c>
-      <c r="C5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5">
-        <v>15</v>
-      </c>
-      <c r="G5">
-        <v>120</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>118</v>
-      </c>
-      <c r="B6">
-        <v>100</v>
-      </c>
-      <c r="C6">
-        <v>25</v>
-      </c>
-      <c r="D6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F6" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6">
-        <v>45</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>119</v>
-      </c>
-      <c r="B7">
-        <v>250</v>
-      </c>
-      <c r="C7">
-        <v>50</v>
-      </c>
-      <c r="D7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G7">
-        <v>60</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D7" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>50</v>
       </c>
       <c r="B8">
-        <v>150</v>
-      </c>
-      <c r="C8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" t="s">
-        <v>32</v>
-      </c>
-      <c r="F8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G8">
+        <v>15</v>
+      </c>
+      <c r="C8">
         <v>45</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D8" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
       <c r="B9">
-        <v>300</v>
-      </c>
-      <c r="C9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9">
         <v>30</v>
       </c>
-      <c r="E9" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9" t="s">
-        <v>32</v>
-      </c>
-      <c r="G9">
+      <c r="C9">
         <v>75</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D9" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B10">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="C10">
+        <v>45</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>117</v>
+      </c>
+      <c r="B11">
         <v>25</v>
       </c>
-      <c r="D10" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" t="s">
-        <v>32</v>
-      </c>
-      <c r="F10" t="s">
-        <v>32</v>
-      </c>
-      <c r="G10">
-        <v>45</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>121</v>
-      </c>
-      <c r="B11">
-        <v>250</v>
-      </c>
-      <c r="C11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" t="s">
-        <v>32</v>
-      </c>
-      <c r="E11">
-        <v>30</v>
-      </c>
-      <c r="F11" t="s">
-        <v>32</v>
-      </c>
-      <c r="G11">
+      <c r="C11">
         <v>60</v>
       </c>
-      <c r="H11" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D11" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>53</v>
       </c>
       <c r="B12">
-        <v>500</v>
-      </c>
-      <c r="C12" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12">
-        <v>60</v>
-      </c>
-      <c r="F12" t="s">
-        <v>32</v>
-      </c>
-      <c r="G12">
+        <v>50</v>
+      </c>
+      <c r="C12">
         <v>90</v>
       </c>
-      <c r="H12" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D12" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>58</v>
       </c>
       <c r="B13">
-        <v>800</v>
-      </c>
-      <c r="C13" t="s">
-        <v>32</v>
-      </c>
-      <c r="D13" t="s">
-        <v>32</v>
-      </c>
-      <c r="E13">
-        <v>30</v>
-      </c>
-      <c r="F13" t="s">
-        <v>32</v>
-      </c>
-      <c r="G13">
+        <v>80</v>
+      </c>
+      <c r="C13">
         <v>120</v>
       </c>
-      <c r="H13" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D13" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B14">
-        <v>150</v>
+        <v>15</v>
       </c>
       <c r="C14">
-        <v>30</v>
-      </c>
-      <c r="D14" t="s">
-        <v>32</v>
-      </c>
-      <c r="E14" t="s">
-        <v>32</v>
-      </c>
-      <c r="F14" t="s">
-        <v>32</v>
-      </c>
-      <c r="G14">
         <v>45</v>
       </c>
-      <c r="H14" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D14" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B15">
-        <v>100</v>
-      </c>
-      <c r="C15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15">
-        <v>20</v>
-      </c>
-      <c r="E15" t="s">
-        <v>32</v>
-      </c>
-      <c r="F15" t="s">
-        <v>32</v>
-      </c>
-      <c r="G15">
+        <v>10</v>
+      </c>
+      <c r="C15">
         <v>45</v>
       </c>
-      <c r="H15" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D15" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>56</v>
       </c>
       <c r="B16">
-        <v>400</v>
+        <v>40</v>
       </c>
       <c r="C16">
-        <v>40</v>
-      </c>
-      <c r="D16" t="s">
-        <v>32</v>
-      </c>
-      <c r="E16" t="s">
-        <v>32</v>
-      </c>
-      <c r="F16" t="s">
-        <v>32</v>
-      </c>
-      <c r="G16">
         <v>90</v>
       </c>
-      <c r="H16" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D16" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B17">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="C17">
-        <v>25</v>
-      </c>
-      <c r="D17" t="s">
-        <v>32</v>
-      </c>
-      <c r="E17" t="s">
-        <v>32</v>
-      </c>
-      <c r="F17" t="s">
-        <v>32</v>
-      </c>
-      <c r="G17">
         <v>60</v>
       </c>
-      <c r="H17" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D17" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>77</v>
       </c>
       <c r="B18">
-        <v>100</v>
-      </c>
-      <c r="C18" t="s">
-        <v>32</v>
-      </c>
-      <c r="D18" t="s">
-        <v>32</v>
-      </c>
-      <c r="E18" t="s">
-        <v>32</v>
-      </c>
-      <c r="F18" t="s">
-        <v>32</v>
-      </c>
-      <c r="G18">
+        <v>10</v>
+      </c>
+      <c r="C18">
         <v>30</v>
       </c>
-      <c r="H18" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D18" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B19">
-        <v>150</v>
+        <v>15</v>
       </c>
       <c r="C19">
-        <v>20</v>
-      </c>
-      <c r="D19" t="s">
-        <v>32</v>
-      </c>
-      <c r="E19" t="s">
-        <v>32</v>
-      </c>
-      <c r="F19" t="s">
-        <v>32</v>
-      </c>
-      <c r="G19">
         <v>45</v>
       </c>
-      <c r="H19" s="2" t="s">
+      <c r="D19" s="2" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B20">
-        <v>150</v>
+        <v>15</v>
       </c>
       <c r="C20">
-        <v>20</v>
-      </c>
-      <c r="D20" t="s">
-        <v>32</v>
-      </c>
-      <c r="E20" t="s">
-        <v>32</v>
-      </c>
-      <c r="F20" t="s">
-        <v>32</v>
-      </c>
-      <c r="G20">
         <v>60</v>
       </c>
-      <c r="H20" s="2" t="s">
+      <c r="D20" s="2" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>80</v>
       </c>
       <c r="B21">
-        <v>400</v>
-      </c>
-      <c r="C21" t="s">
-        <v>32</v>
-      </c>
-      <c r="D21">
-        <v>30</v>
-      </c>
-      <c r="E21" t="s">
-        <v>32</v>
-      </c>
-      <c r="F21" t="s">
-        <v>32</v>
-      </c>
-      <c r="G21">
+        <v>40</v>
+      </c>
+      <c r="C21">
         <v>90</v>
       </c>
-      <c r="H21" s="2" t="s">
+      <c r="D21" s="2" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B22">
-        <v>400</v>
-      </c>
-      <c r="C22" t="s">
-        <v>32</v>
-      </c>
-      <c r="D22" t="s">
-        <v>32</v>
-      </c>
-      <c r="E22">
         <v>40</v>
       </c>
-      <c r="F22" t="s">
-        <v>32</v>
-      </c>
-      <c r="G22">
+      <c r="C22">
         <v>120</v>
       </c>
-      <c r="H22" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D22" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B23">
-        <v>600</v>
-      </c>
-      <c r="C23" t="s">
-        <v>32</v>
-      </c>
-      <c r="D23" t="s">
-        <v>32</v>
-      </c>
-      <c r="E23" t="s">
-        <v>32</v>
-      </c>
-      <c r="F23">
-        <v>20</v>
-      </c>
-      <c r="G23">
+        <v>60</v>
+      </c>
+      <c r="C23">
         <v>180</v>
       </c>
-      <c r="H23" s="2" t="s">
-        <v>126</v>
+      <c r="D23" s="2" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -7405,24 +7129,24 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B2">
         <v>50</v>
@@ -7437,12 +7161,12 @@
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B3">
         <v>75</v>
@@ -7457,12 +7181,12 @@
         <v>0.05</v>
       </c>
       <c r="F3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B4">
         <v>200</v>
@@ -7477,12 +7201,12 @@
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B5">
         <v>100</v>
@@ -7502,7 +7226,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B6">
         <v>150</v>
@@ -7522,7 +7246,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B7">
         <v>100</v>
@@ -7537,12 +7261,12 @@
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B8">
         <v>100</v>
@@ -7557,12 +7281,12 @@
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B9">
         <v>150</v>
@@ -7577,7 +7301,7 @@
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -7597,13 +7321,13 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -7625,7 +7349,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:N39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
@@ -7636,61 +7360,65 @@
     <col min="8" max="10" width="13" customWidth="1"/>
     <col min="11" max="11" width="14" customWidth="1"/>
     <col min="12" max="13" width="13" customWidth="1"/>
+    <col min="14" max="14" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="K1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>153</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="B2" t="s">
         <v>154</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="C2" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="D2" t="s">
         <v>156</v>
-      </c>
-      <c r="B2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C2" t="s">
-        <v>158</v>
-      </c>
-      <c r="D2" t="s">
-        <v>159</v>
       </c>
       <c r="E2" t="s">
         <v>32</v>
@@ -7719,19 +7447,22 @@
       <c r="M2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D3" t="s">
         <v>160</v>
-      </c>
-      <c r="B3" t="s">
-        <v>161</v>
-      </c>
-      <c r="C3" t="s">
-        <v>162</v>
-      </c>
-      <c r="D3" t="s">
-        <v>163</v>
       </c>
       <c r="E3" t="s">
         <v>102</v>
@@ -7760,19 +7491,22 @@
       <c r="M3" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B4" t="s">
+        <v>162</v>
+      </c>
+      <c r="C4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D4" t="s">
         <v>164</v>
-      </c>
-      <c r="B4" t="s">
-        <v>165</v>
-      </c>
-      <c r="C4" t="s">
-        <v>166</v>
-      </c>
-      <c r="D4" t="s">
-        <v>167</v>
       </c>
       <c r="E4" t="s">
         <v>34</v>
@@ -7801,19 +7535,22 @@
       <c r="M4" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B5" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C5" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D5" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E5" t="s">
         <v>101</v>
@@ -7842,19 +7579,22 @@
       <c r="M5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>167</v>
+      </c>
+      <c r="B6" t="s">
+        <v>168</v>
+      </c>
+      <c r="C6" t="s">
+        <v>169</v>
+      </c>
+      <c r="D6" t="s">
         <v>170</v>
-      </c>
-      <c r="B6" t="s">
-        <v>171</v>
-      </c>
-      <c r="C6" t="s">
-        <v>172</v>
-      </c>
-      <c r="D6" t="s">
-        <v>173</v>
       </c>
       <c r="E6" t="s">
         <v>32</v>
@@ -7883,19 +7623,22 @@
       <c r="M6" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B7" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C7" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D7" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E7" t="s">
         <v>32</v>
@@ -7924,19 +7667,22 @@
       <c r="M7" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>174</v>
+      </c>
+      <c r="B8" t="s">
+        <v>175</v>
+      </c>
+      <c r="C8" t="s">
+        <v>176</v>
+      </c>
+      <c r="D8" t="s">
         <v>177</v>
-      </c>
-      <c r="B8" t="s">
-        <v>178</v>
-      </c>
-      <c r="C8" t="s">
-        <v>179</v>
-      </c>
-      <c r="D8" t="s">
-        <v>180</v>
       </c>
       <c r="E8" t="s">
         <v>100</v>
@@ -7965,22 +7711,25 @@
       <c r="M8" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B9" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C9" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E9" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -8006,19 +7755,22 @@
       <c r="M9" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B10" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C10" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D10" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E10" t="s">
         <v>45</v>
@@ -8047,19 +7799,22 @@
       <c r="M10" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>184</v>
+      </c>
+      <c r="B11" t="s">
+        <v>185</v>
+      </c>
+      <c r="C11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D11" t="s">
         <v>187</v>
-      </c>
-      <c r="B11" t="s">
-        <v>188</v>
-      </c>
-      <c r="C11" t="s">
-        <v>189</v>
-      </c>
-      <c r="D11" t="s">
-        <v>190</v>
       </c>
       <c r="E11" t="s">
         <v>32</v>
@@ -8088,19 +7843,22 @@
       <c r="M11" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B12" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C12" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D12" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E12" t="s">
         <v>34</v>
@@ -8129,19 +7887,22 @@
       <c r="M12" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B13" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C13" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D13" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E13" t="s">
         <v>32</v>
@@ -8170,19 +7931,22 @@
       <c r="M13" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>193</v>
+      </c>
+      <c r="B14" t="s">
+        <v>194</v>
+      </c>
+      <c r="C14" t="s">
+        <v>195</v>
+      </c>
+      <c r="D14" t="s">
         <v>196</v>
-      </c>
-      <c r="B14" t="s">
-        <v>197</v>
-      </c>
-      <c r="C14" t="s">
-        <v>198</v>
-      </c>
-      <c r="D14" t="s">
-        <v>199</v>
       </c>
       <c r="E14" t="s">
         <v>32</v>
@@ -8211,19 +7975,22 @@
       <c r="M14" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B15" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C15" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D15" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E15" t="s">
         <v>52</v>
@@ -8252,19 +8019,22 @@
       <c r="M15" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B16" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C16" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D16" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E16" t="s">
         <v>50</v>
@@ -8293,19 +8063,22 @@
       <c r="M16" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N16">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B17" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C17" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D17" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E17" t="s">
         <v>32</v>
@@ -8334,19 +8107,22 @@
       <c r="M17" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>205</v>
+      </c>
+      <c r="B18" t="s">
+        <v>206</v>
+      </c>
+      <c r="C18" t="s">
+        <v>207</v>
+      </c>
+      <c r="D18" t="s">
         <v>208</v>
-      </c>
-      <c r="B18" t="s">
-        <v>209</v>
-      </c>
-      <c r="C18" t="s">
-        <v>210</v>
-      </c>
-      <c r="D18" t="s">
-        <v>211</v>
       </c>
       <c r="E18" t="s">
         <v>31</v>
@@ -8375,19 +8151,22 @@
       <c r="M18">
         <v>5</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N18">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B19" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C19" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D19" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E19" t="s">
         <v>37</v>
@@ -8416,19 +8195,22 @@
       <c r="M19" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N19">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B20" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C20" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D20" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E20" t="s">
         <v>34</v>
@@ -8457,19 +8239,22 @@
       <c r="M20" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N20">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B21" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C21" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D21" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E21" t="s">
         <v>32</v>
@@ -8498,19 +8283,22 @@
       <c r="M21" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N21">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>218</v>
+      </c>
+      <c r="B22" t="s">
+        <v>219</v>
+      </c>
+      <c r="C22" t="s">
+        <v>220</v>
+      </c>
+      <c r="D22" t="s">
         <v>221</v>
-      </c>
-      <c r="B22" t="s">
-        <v>222</v>
-      </c>
-      <c r="C22" t="s">
-        <v>223</v>
-      </c>
-      <c r="D22" t="s">
-        <v>224</v>
       </c>
       <c r="E22" t="s">
         <v>32</v>
@@ -8539,22 +8327,25 @@
       <c r="M22" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B23" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C23" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D23" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E23" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -8580,19 +8371,22 @@
       <c r="M23" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B24" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C24" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D24" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E24" t="s">
         <v>38</v>
@@ -8621,19 +8415,22 @@
       <c r="M24" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N24">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B25" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C25" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="D25" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E25" t="s">
         <v>93</v>
@@ -8662,19 +8459,22 @@
       <c r="M25" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B26" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C26" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D26" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E26" t="s">
         <v>57</v>
@@ -8703,22 +8503,25 @@
       <c r="M26" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N26">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B27" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C27" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D27" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E27" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F27">
         <v>1</v>
@@ -8744,19 +8547,22 @@
       <c r="M27" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N27">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B28" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C28" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D28" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E28" t="s">
         <v>31</v>
@@ -8785,19 +8591,22 @@
       <c r="M28">
         <v>10</v>
       </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N28">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>239</v>
+      </c>
+      <c r="B29" t="s">
+        <v>240</v>
+      </c>
+      <c r="C29" t="s">
+        <v>241</v>
+      </c>
+      <c r="D29" t="s">
         <v>242</v>
-      </c>
-      <c r="B29" t="s">
-        <v>243</v>
-      </c>
-      <c r="C29" t="s">
-        <v>244</v>
-      </c>
-      <c r="D29" t="s">
-        <v>245</v>
       </c>
       <c r="E29" t="s">
         <v>32</v>
@@ -8826,22 +8635,25 @@
       <c r="M29" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N29">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B30" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C30" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="D30" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E30" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="F30">
         <v>1</v>
@@ -8867,19 +8679,22 @@
       <c r="M30" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N30">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B31" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C31" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="D31" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E31" t="s">
         <v>59</v>
@@ -8908,19 +8723,22 @@
       <c r="M31">
         <v>5</v>
       </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N31">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B32" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C32" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="D32" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E32" t="s">
         <v>62</v>
@@ -8949,19 +8767,22 @@
       <c r="M32" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N32">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B33" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C33" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D33" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E33" t="s">
         <v>32</v>
@@ -8990,19 +8811,22 @@
       <c r="M33" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N33">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>253</v>
+      </c>
+      <c r="B34" t="s">
+        <v>254</v>
+      </c>
+      <c r="C34" t="s">
+        <v>255</v>
+      </c>
+      <c r="D34" t="s">
         <v>256</v>
-      </c>
-      <c r="B34" t="s">
-        <v>257</v>
-      </c>
-      <c r="C34" t="s">
-        <v>258</v>
-      </c>
-      <c r="D34" t="s">
-        <v>259</v>
       </c>
       <c r="E34" t="s">
         <v>32</v>
@@ -9031,19 +8855,22 @@
       <c r="M34">
         <v>5</v>
       </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N34">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>257</v>
+      </c>
+      <c r="B35" t="s">
+        <v>258</v>
+      </c>
+      <c r="C35" t="s">
+        <v>259</v>
+      </c>
+      <c r="D35" t="s">
         <v>260</v>
-      </c>
-      <c r="B35" t="s">
-        <v>261</v>
-      </c>
-      <c r="C35" t="s">
-        <v>262</v>
-      </c>
-      <c r="D35" t="s">
-        <v>263</v>
       </c>
       <c r="E35" t="s">
         <v>32</v>
@@ -9072,19 +8899,22 @@
       <c r="M35">
         <v>5</v>
       </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N35">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>261</v>
+      </c>
+      <c r="B36" t="s">
+        <v>262</v>
+      </c>
+      <c r="C36" t="s">
+        <v>263</v>
+      </c>
+      <c r="D36" t="s">
         <v>264</v>
-      </c>
-      <c r="B36" t="s">
-        <v>265</v>
-      </c>
-      <c r="C36" t="s">
-        <v>266</v>
-      </c>
-      <c r="D36" t="s">
-        <v>267</v>
       </c>
       <c r="E36" t="s">
         <v>32</v>
@@ -9113,19 +8943,22 @@
       <c r="M36" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N36">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B37" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C37" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="D37" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="E37" t="s">
         <v>32</v>
@@ -9154,19 +8987,22 @@
       <c r="M37">
         <v>5</v>
       </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N37">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B38" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C38" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D38" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="E38" t="s">
         <v>32</v>
@@ -9195,19 +9031,22 @@
       <c r="M38">
         <v>5</v>
       </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N38">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B39" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C39" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="D39" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E39" t="s">
         <v>32</v>
@@ -9235,6 +9074,9 @@
       </c>
       <c r="M39">
         <v>10</v>
+      </c>
+      <c r="N39">
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -564,7 +564,7 @@
     <t>Tax day</t>
   </si>
   <si>
-    <t>Your villager pays rent. Collect 30 Gold — exploring is not free.</t>
+    <t>Your villager pays rent. Tap the House to hurry it along — 30 Gold.</t>
   </si>
   <si>
     <t>Explorer</t>
@@ -585,7 +585,7 @@
     <t>First plot</t>
   </si>
   <si>
-    <t>Build a crop plot on open grass.</t>
+    <t>Build two crop plots on open grass.</t>
   </si>
   <si>
     <t>ByHand</t>
@@ -594,7 +594,7 @@
     <t>By hand</t>
   </si>
   <si>
-    <t>Tap the plot for Food. Doing this forever is not the plan.</t>
+    <t>Tap the plots for Food. Doing this forever is not the plan.</t>
   </si>
   <si>
     <t>Lumber</t>
@@ -624,19 +624,19 @@
     <t>AssignWorkers</t>
   </si>
   <si>
+    <t>GrowingTown</t>
+  </si>
+  <si>
+    <t>Growing town</t>
+  </si>
+  <si>
+    <t>Build a second House. The Wood is starting to add up.</t>
+  </si>
+  <si>
     <t>Neighbors</t>
   </si>
   <si>
-    <t>One House holds two. Train another villager.</t>
-  </si>
-  <si>
-    <t>GrowingTown</t>
-  </si>
-  <si>
-    <t>Growing town</t>
-  </si>
-  <si>
-    <t>Build a second House. Notice what the Wood costs now.</t>
+    <t>Train another villager — the new House has the room.</t>
   </si>
   <si>
     <t>ProperCapital</t>
@@ -7980,7 +7980,7 @@
         <v>44</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" t="s">
         <v>32</v>
@@ -8188,16 +8188,16 @@
         <v>199</v>
       </c>
       <c r="B16" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C16" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D16" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="E16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F16">
         <v>2</v>
@@ -8206,7 +8206,7 @@
         <v>32</v>
       </c>
       <c r="H16">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="I16" t="s">
         <v>32</v>
@@ -8224,12 +8224,12 @@
         <v>32</v>
       </c>
       <c r="N16">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B17" t="s">
         <v>202</v>
@@ -8238,19 +8238,19 @@
         <v>203</v>
       </c>
       <c r="D17" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="E17" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G17" t="s">
         <v>32</v>
       </c>
       <c r="H17">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I17" t="s">
         <v>32</v>
@@ -8268,7 +8268,7 @@
         <v>32</v>
       </c>
       <c r="N17">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1506" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1507" uniqueCount="460">
   <si>
     <t>id</t>
   </si>
@@ -1188,7 +1188,10 @@
     <t>city.initial_food</t>
   </si>
   <si>
-    <t>city.population_cost_base</t>
+    <t>city.population_cost_first</t>
+  </si>
+  <si>
+    <t>5,20,100,300,500,1000</t>
   </si>
   <si>
     <t>city.population_cost_growth</t>
@@ -4442,13 +4445,13 @@
       <c r="A17" t="s">
         <v>387</v>
       </c>
-      <c r="B17">
-        <v>5</v>
+      <c r="B17" s="2" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B18">
         <v>1.45</v>
@@ -4456,7 +4459,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -4464,7 +4467,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B20">
         <v>1</v>
@@ -4472,7 +4475,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B21">
         <v>4</v>
@@ -4480,7 +4483,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B22">
         <v>1</v>
@@ -4488,7 +4491,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B23">
         <v>3</v>
@@ -4496,7 +4499,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B24">
         <v>10</v>
@@ -4504,7 +4507,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B25">
         <v>3</v>
@@ -4512,31 +4515,31 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B29">
         <v>10</v>
@@ -4544,7 +4547,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B30">
         <v>4</v>
@@ -4552,7 +4555,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B31">
         <v>1</v>
@@ -4560,7 +4563,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B32">
         <v>5</v>
@@ -4568,7 +4571,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B33">
         <v>20</v>
@@ -4576,7 +4579,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B34">
         <v>2.5</v>
@@ -4584,7 +4587,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B35">
         <v>300</v>
@@ -4592,7 +4595,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B36">
         <v>20</v>
@@ -4600,7 +4603,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B37">
         <v>1.6</v>
@@ -4608,7 +4611,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B38">
         <v>10</v>
@@ -4616,7 +4619,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B39">
         <v>2</v>
@@ -4624,7 +4627,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B40">
         <v>5</v>
@@ -4632,7 +4635,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B41">
         <v>10</v>
@@ -4640,7 +4643,7 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B42">
         <v>2</v>
@@ -4648,7 +4651,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B43">
         <v>2</v>
@@ -4656,7 +4659,7 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B44">
         <v>1</v>
@@ -4664,7 +4667,7 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B45">
         <v>3</v>
@@ -4672,7 +4675,7 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B46">
         <v>1.5</v>
@@ -4680,7 +4683,7 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B47">
         <v>0.75</v>
@@ -4688,7 +4691,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B48">
         <v>0.4</v>
@@ -4696,7 +4699,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B49">
         <v>0.9</v>
@@ -4704,7 +4707,7 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B50">
         <v>0.5</v>
@@ -4712,7 +4715,7 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B51">
         <v>25</v>
@@ -4720,7 +4723,7 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B52">
         <v>4</v>
@@ -4728,7 +4731,7 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B53">
         <v>2</v>
@@ -4736,7 +4739,7 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B54">
         <v>1</v>
@@ -4744,7 +4747,7 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B55">
         <v>0.5</v>
@@ -4752,7 +4755,7 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B56">
         <v>10</v>
@@ -4760,7 +4763,7 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B57">
         <v>2</v>
@@ -4768,7 +4771,7 @@
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B58">
         <v>5</v>
@@ -4776,7 +4779,7 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B59">
         <v>25</v>
@@ -4784,7 +4787,7 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B60">
         <v>2.2</v>
@@ -4792,7 +4795,7 @@
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B61">
         <v>30</v>
@@ -4800,7 +4803,7 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B62">
         <v>0.06</v>
@@ -4808,7 +4811,7 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B63">
         <v>40</v>
@@ -4816,7 +4819,7 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B64">
         <v>60</v>
@@ -4824,7 +4827,7 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B65">
         <v>20</v>
@@ -4832,7 +4835,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B66">
         <v>3</v>
@@ -4840,7 +4843,7 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B67">
         <v>30</v>
@@ -4848,7 +4851,7 @@
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B68">
         <v>90</v>
@@ -4856,7 +4859,7 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B69">
         <v>0.5</v>
@@ -4864,7 +4867,7 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B70">
         <v>5</v>
@@ -4949,61 +4952,61 @@
         <v>-10</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
@@ -5011,61 +5014,61 @@
         <v>-9</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="G3" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="N3" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>446</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>445</v>
-      </c>
       <c r="O3" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
@@ -5073,61 +5076,61 @@
         <v>-8</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H4" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="I4" s="3" t="s">
-        <v>445</v>
-      </c>
       <c r="J4" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M4" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="N4" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="N4" s="3" t="s">
-        <v>445</v>
-      </c>
       <c r="O4" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -5135,61 +5138,61 @@
         <v>-7</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="J5" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="K5" s="3" t="s">
-        <v>448</v>
-      </c>
       <c r="L5" s="3" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -5197,61 +5200,61 @@
         <v>-6</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="T6" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -5259,61 +5262,61 @@
         <v>-5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="T7" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -5321,61 +5324,61 @@
         <v>-4</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H8" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="N8" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>453</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>453</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>454</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>451</v>
-      </c>
       <c r="O8" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -5383,61 +5386,61 @@
         <v>-3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E9" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="O9" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>450</v>
-      </c>
       <c r="P9" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -5445,61 +5448,61 @@
         <v>-2</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="I10" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="J10" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>451</v>
-      </c>
       <c r="K10" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -5507,61 +5510,61 @@
         <v>-1</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Q11" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="R11" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="R11" s="3" t="s">
-        <v>454</v>
-      </c>
       <c r="S11" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -5569,61 +5572,61 @@
         <v>0</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Q12" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="T12" s="3" t="s">
         <v>455</v>
-      </c>
-      <c r="R12" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="S12" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="T12" s="3" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -5631,61 +5634,61 @@
         <v>1</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Q13" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="R13" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="S13" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="R13" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="S13" s="3" t="s">
-        <v>454</v>
-      </c>
       <c r="T13" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -5693,61 +5696,61 @@
         <v>2</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="T14" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -5755,61 +5758,61 @@
         <v>3</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="T15" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -5817,61 +5820,61 @@
         <v>4</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="T16" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
@@ -5879,61 +5882,61 @@
         <v>5</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="T17" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -5941,61 +5944,61 @@
         <v>6</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H18" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="N18" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>452</v>
-      </c>
       <c r="O18" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="T18" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
@@ -6003,61 +6006,61 @@
         <v>7</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="S19" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="T19" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
   </sheetData>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -1080,7 +1080,7 @@
     <t>taxes.tap_boost_seconds</t>
   </si>
   <si>
-    <t>taxes.cycle_seconds</t>
+    <t>tap.mana_cost</t>
   </si>
   <si>
     <t>offline_cap_hours</t>
@@ -1137,7 +1137,7 @@
     <t>mana.base_cap_per_townhall_level</t>
   </si>
   <si>
-    <t>24,32,40</t>
+    <t>50,66,82</t>
   </si>
   <si>
     <t>mana.sanctum_cap_per_level</t>
@@ -4270,7 +4270,7 @@
         <v>351</v>
       </c>
       <c r="B9">
-        <v>60</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1505" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1506" uniqueCount="459">
   <si>
     <t>id</t>
   </si>
@@ -123,69 +123,69 @@
     <t>Townhall</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
+    <t>-,Architecture</t>
+  </si>
+  <si>
+    <t>Housing</t>
+  </si>
+  <si>
+    <t>2,4</t>
+  </si>
+  <si>
+    <t>2,4,6</t>
+  </si>
+  <si>
+    <t>UrbanPlanning</t>
+  </si>
+  <si>
+    <t>Farm</t>
+  </si>
+  <si>
+    <t>3,5</t>
+  </si>
+  <si>
+    <t>1,1,2</t>
+  </si>
+  <si>
+    <t>1,2</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Farming</t>
+  </si>
+  <si>
+    <t>FarmLands</t>
+  </si>
+  <si>
+    <t>6,6,12</t>
+  </si>
+  <si>
+    <t>Sawmill</t>
+  </si>
+  <si>
+    <t>3,5,7</t>
+  </si>
+  <si>
+    <t>1,2,3</t>
+  </si>
+  <si>
+    <t>2,3,4</t>
+  </si>
+  <si>
+    <t>-,Engineering</t>
+  </si>
+  <si>
+    <t>Market</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>-,Architecture</t>
-  </si>
-  <si>
-    <t>Housing</t>
-  </si>
-  <si>
-    <t>2,4</t>
-  </si>
-  <si>
-    <t>2,4,6</t>
-  </si>
-  <si>
-    <t>UrbanPlanning</t>
-  </si>
-  <si>
-    <t>Farm</t>
-  </si>
-  <si>
-    <t>3,5</t>
-  </si>
-  <si>
-    <t>1,1,2</t>
-  </si>
-  <si>
-    <t>1,2</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Farming</t>
-  </si>
-  <si>
-    <t>FarmLands</t>
-  </si>
-  <si>
-    <t>6,6,12</t>
-  </si>
-  <si>
-    <t>Sawmill</t>
-  </si>
-  <si>
-    <t>3,5,7</t>
-  </si>
-  <si>
-    <t>1,2,3</t>
-  </si>
-  <si>
-    <t>2,3,4</t>
-  </si>
-  <si>
-    <t>-,Engineering</t>
-  </si>
-  <si>
-    <t>Market</t>
-  </si>
-  <si>
     <t>Quarry</t>
   </si>
   <si>
@@ -516,13 +516,34 @@
     <t>CompleteTech</t>
   </si>
   <si>
+    <t>Timber</t>
+  </si>
+  <si>
+    <t>Timber!</t>
+  </si>
+  <si>
+    <t>Now tap the trees beside your Townhall. Twenty-five Wood buys a roof and a field.</t>
+  </si>
+  <si>
+    <t>CollectResource</t>
+  </si>
+  <si>
+    <t>ARoof</t>
+  </si>
+  <si>
+    <t>A roof</t>
+  </si>
+  <si>
+    <t>Build a House. Somebody has to live here.</t>
+  </si>
+  <si>
+    <t>BuildDistrict</t>
+  </si>
+  <si>
     <t>Rations</t>
   </si>
   <si>
-    <t>Now tap the berry bush west of your Townhall for Food.</t>
-  </si>
-  <si>
-    <t>CollectResource</t>
+    <t>Tap the berry bush west of your Townhall for Food. Villagers eat.</t>
   </si>
   <si>
     <t>FirstVillager</t>
@@ -531,33 +552,12 @@
     <t>First villager</t>
   </si>
   <si>
-    <t>Train your first villager. There is a bed in the Townhall already.</t>
+    <t>Train your first villager — your new House has room for two.</t>
   </si>
   <si>
     <t>ReachPopulation</t>
   </si>
   <si>
-    <t>Timber</t>
-  </si>
-  <si>
-    <t>Timber!</t>
-  </si>
-  <si>
-    <t>Now tap the trees beside your Townhall. Twenty-five Wood buys a roof and a field.</t>
-  </si>
-  <si>
-    <t>ARoof</t>
-  </si>
-  <si>
-    <t>A roof</t>
-  </si>
-  <si>
-    <t>Build a House. Somebody has to live here.</t>
-  </si>
-  <si>
-    <t>BuildDistrict</t>
-  </si>
-  <si>
     <t>TaxDay</t>
   </si>
   <si>
@@ -1174,6 +1174,9 @@
   </si>
   <si>
     <t>fog.fallback_growth</t>
+  </si>
+  <si>
+    <t>fog.claim_discover_radius</t>
   </si>
   <si>
     <t>city.initial_population</t>
@@ -2022,37 +2025,37 @@
         <v>2</v>
       </c>
       <c r="H2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="M2" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S2">
         <v>2</v>
@@ -2070,19 +2073,19 @@
         <v>1.15</v>
       </c>
       <c r="X2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y2">
         <v>60</v>
       </c>
       <c r="Z2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AA2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AB2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC2">
         <v>3.9</v>
@@ -2096,7 +2099,7 @@
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -2108,7 +2111,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -2117,37 +2120,37 @@
         <v>2</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="J3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="M3" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O3">
         <v>10</v>
       </c>
       <c r="P3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S3">
         <v>1.25</v>
@@ -2165,19 +2168,19 @@
         <v>1.15</v>
       </c>
       <c r="X3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y3">
         <v>30</v>
       </c>
       <c r="Z3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AA3">
         <v>10</v>
       </c>
       <c r="AB3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC3">
         <v>1.5</v>
@@ -2191,7 +2194,7 @@
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -2203,7 +2206,7 @@
         <v>2</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -2212,37 +2215,37 @@
         <v>2</v>
       </c>
       <c r="H4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="L4" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="M4" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O4">
         <v>30</v>
       </c>
       <c r="P4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S4">
         <v>2</v>
@@ -2260,19 +2263,19 @@
         <v>1.15</v>
       </c>
       <c r="X4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y4">
         <v>50</v>
       </c>
       <c r="Z4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AA4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AB4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC4">
         <v>1.5</v>
@@ -2286,7 +2289,7 @@
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -2298,7 +2301,7 @@
         <v>1</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -2307,37 +2310,37 @@
         <v>2</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O5">
         <v>10</v>
       </c>
       <c r="P5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S5">
         <v>2</v>
@@ -2355,19 +2358,19 @@
         <v>1.15</v>
       </c>
       <c r="X5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Z5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AA5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AB5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC5">
         <v>1.5</v>
@@ -2381,7 +2384,7 @@
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -2393,7 +2396,7 @@
         <v>3</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -2402,37 +2405,37 @@
         <v>2</v>
       </c>
       <c r="H6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="J6" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="K6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L6" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="M6" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O6">
         <v>20</v>
       </c>
       <c r="P6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S6">
         <v>2.5</v>
@@ -2450,19 +2453,19 @@
         <v>1.15</v>
       </c>
       <c r="X6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y6">
         <v>60</v>
       </c>
       <c r="Z6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AA6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AB6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC6">
         <v>2.5</v>
@@ -2476,7 +2479,7 @@
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -2488,7 +2491,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -2497,37 +2500,37 @@
         <v>2</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O7">
         <v>40</v>
       </c>
       <c r="P7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S7">
         <v>2</v>
@@ -2545,19 +2548,19 @@
         <v>1.15</v>
       </c>
       <c r="X7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Z7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AA7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AB7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC7">
         <v>1.5</v>
@@ -2583,7 +2586,7 @@
         <v>2</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -2592,37 +2595,37 @@
         <v>2</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="J8" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="K8" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>54</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O8">
         <v>30</v>
       </c>
       <c r="P8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S8">
         <v>2.5</v>
@@ -2640,19 +2643,19 @@
         <v>1.15</v>
       </c>
       <c r="X8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y8">
         <v>40</v>
       </c>
       <c r="Z8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AA8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AB8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC8">
         <v>1.5</v>
@@ -2678,7 +2681,7 @@
         <v>2</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -2687,37 +2690,37 @@
         <v>2</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>56</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>57</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O9">
         <v>25</v>
       </c>
       <c r="P9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S9">
         <v>2.5</v>
@@ -2735,19 +2738,19 @@
         <v>1.15</v>
       </c>
       <c r="X9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y9">
         <v>35</v>
       </c>
       <c r="Z9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AA9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AB9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC9">
         <v>1.5</v>
@@ -2773,7 +2776,7 @@
         <v>2</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -2782,37 +2785,37 @@
         <v>2</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="J10" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="J10" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="K10" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>59</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O10">
         <v>40</v>
       </c>
       <c r="P10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q10">
         <v>20</v>
       </c>
       <c r="R10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S10">
         <v>2.5</v>
@@ -2830,19 +2833,19 @@
         <v>1.15</v>
       </c>
       <c r="X10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y10">
         <v>50</v>
       </c>
       <c r="Z10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AA10">
         <v>25</v>
       </c>
       <c r="AB10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC10">
         <v>1.5</v>
@@ -2868,7 +2871,7 @@
         <v>3</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -2877,13 +2880,13 @@
         <v>2</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>61</v>
@@ -2892,22 +2895,22 @@
         <v>62</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N11">
         <v>300</v>
       </c>
       <c r="O11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q11">
         <v>40</v>
       </c>
       <c r="R11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S11">
         <v>1</v>
@@ -2928,16 +2931,16 @@
         <v>500</v>
       </c>
       <c r="Y11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Z11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AA11">
         <v>80</v>
       </c>
       <c r="AB11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC11">
         <v>1.8</v>
@@ -2963,7 +2966,7 @@
         <v>3</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -2972,16 +2975,16 @@
         <v>1</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>62</v>
@@ -2990,19 +2993,19 @@
         <v>64</v>
       </c>
       <c r="N12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O12">
         <v>60</v>
       </c>
       <c r="P12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q12">
         <v>20</v>
       </c>
       <c r="R12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S12">
         <v>1</v>
@@ -3020,19 +3023,19 @@
         <v>1.15</v>
       </c>
       <c r="X12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y12">
         <v>180</v>
       </c>
       <c r="Z12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AA12">
         <v>60</v>
       </c>
       <c r="AB12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC12">
         <v>1.8</v>
@@ -3058,7 +3061,7 @@
         <v>3</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -3067,16 +3070,16 @@
         <v>1</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>62</v>
@@ -3085,19 +3088,19 @@
         <v>64</v>
       </c>
       <c r="N13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O13">
         <v>80</v>
       </c>
       <c r="P13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q13">
         <v>30</v>
       </c>
       <c r="R13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S13">
         <v>1</v>
@@ -3115,19 +3118,19 @@
         <v>1.15</v>
       </c>
       <c r="X13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y13">
         <v>240</v>
       </c>
       <c r="Z13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AA13">
         <v>90</v>
       </c>
       <c r="AB13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC13">
         <v>1.8</v>
@@ -3153,7 +3156,7 @@
         <v>3</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -3162,16 +3165,16 @@
         <v>1</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>62</v>
@@ -3180,19 +3183,19 @@
         <v>64</v>
       </c>
       <c r="N14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O14">
         <v>80</v>
       </c>
       <c r="P14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q14">
         <v>30</v>
       </c>
       <c r="R14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S14">
         <v>1</v>
@@ -3210,19 +3213,19 @@
         <v>1.15</v>
       </c>
       <c r="X14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y14">
         <v>240</v>
       </c>
       <c r="Z14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AA14">
         <v>90</v>
       </c>
       <c r="AB14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC14">
         <v>1.8</v>
@@ -3248,7 +3251,7 @@
         <v>3</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -3257,16 +3260,16 @@
         <v>1</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>62</v>
@@ -3275,13 +3278,13 @@
         <v>64</v>
       </c>
       <c r="N15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O15">
         <v>120</v>
       </c>
       <c r="P15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q15">
         <v>40</v>
@@ -3305,13 +3308,13 @@
         <v>1.15</v>
       </c>
       <c r="X15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y15">
         <v>360</v>
       </c>
       <c r="Z15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AA15">
         <v>120</v>
@@ -3404,16 +3407,16 @@
         <v>8</v>
       </c>
       <c r="E2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G2">
         <v>4</v>
       </c>
       <c r="H2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I2">
         <v>10</v>
@@ -3422,7 +3425,7 @@
         <v>0.4</v>
       </c>
       <c r="K2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -3442,13 +3445,13 @@
         <v>6</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F3">
         <v>2</v>
       </c>
       <c r="G3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H3">
         <v>6</v>
@@ -3457,7 +3460,7 @@
         <v>25</v>
       </c>
       <c r="J3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K3">
         <v>0.6</v>
@@ -3483,7 +3486,7 @@
         <v>3600</v>
       </c>
       <c r="F4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G4">
         <v>8</v>
@@ -3492,7 +3495,7 @@
         <v>2</v>
       </c>
       <c r="I4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J4">
         <v>0.8</v>
@@ -3501,7 +3504,7 @@
         <v>0.2</v>
       </c>
       <c r="L4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -3518,10 +3521,10 @@
         <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -3556,10 +3559,10 @@
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -3835,16 +3838,16 @@
         <v>342</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F2">
-        <v>400</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -3861,7 +3864,7 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F3">
         <v>25000</v>
@@ -3881,7 +3884,7 @@
         <v>6</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F4">
         <v>25000</v>
@@ -3901,7 +3904,7 @@
         <v>-5</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F5">
         <v>25000</v>
@@ -3941,7 +3944,7 @@
         <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     